--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -228,9 +228,6 @@
     <t xml:space="preserve">Antony Gilbert</t>
   </si>
   <si>
-    <t xml:space="preserve">Ashton Patteron</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ashton Patterson</t>
   </si>
   <si>
@@ -703,9 +700,6 @@
   </si>
   <si>
     <t xml:space="preserve">Elvin Liriano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gleyvin Peneda</t>
   </si>
   <si>
     <t xml:space="preserve">Gleyvin Pineda</t>
@@ -964,8 +958,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K160" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K159" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K159"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -984,8 +978,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K133" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K133"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K132" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K132"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -3278,19 +3272,33 @@
       <c r="B58" t="s">
         <v>69</v>
       </c>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
+      <c r="C58" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="F58" t="n">
+        <v>8.5</v>
+      </c>
       <c r="G58" t="n">
-        <v>33.3</v>
+        <v>25.8</v>
       </c>
       <c r="H58" t="n">
-        <v>50</v>
-      </c>
-      <c r="I58"/>
-      <c r="J58"/>
-      <c r="K58"/>
+        <v>13.2</v>
+      </c>
+      <c r="I58" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="J58" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
@@ -3300,31 +3308,31 @@
         <v>69</v>
       </c>
       <c r="C59" t="n">
-        <v>58.1</v>
+        <v>100</v>
       </c>
       <c r="D59" t="n">
-        <v>8.5</v>
+        <v>20</v>
       </c>
       <c r="E59" t="n">
-        <v>49.6</v>
+        <v>80</v>
       </c>
       <c r="F59" t="n">
-        <v>8.5</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
-        <v>25.6</v>
+        <v>43.8</v>
       </c>
       <c r="H59" t="n">
-        <v>12.1</v>
+        <v>22.2</v>
       </c>
       <c r="I59" t="n">
-        <v>57.9</v>
+        <v>40</v>
       </c>
       <c r="J59" t="n">
-        <v>13.2</v>
+        <v>60</v>
       </c>
       <c r="K59" t="n">
-        <v>32.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -3335,31 +3343,31 @@
         <v>69</v>
       </c>
       <c r="C60" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D60" t="n">
-        <v>20</v>
+        <v>45.7</v>
       </c>
       <c r="E60" t="n">
-        <v>80</v>
+        <v>12.1</v>
       </c>
       <c r="F60" t="n">
-        <v>20</v>
+        <v>45.7</v>
       </c>
       <c r="G60" t="n">
-        <v>43.8</v>
+        <v>31</v>
       </c>
       <c r="H60" t="n">
-        <v>22.2</v>
+        <v>3.3</v>
       </c>
       <c r="I60" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="J60" t="n">
-        <v>60</v>
+        <v>21.1</v>
       </c>
       <c r="K60" t="n">
-        <v>20</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="61">
@@ -3370,31 +3378,31 @@
         <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
       <c r="D61" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="n">
-        <v>12.1</v>
+        <v>44.6</v>
       </c>
       <c r="F61" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="G61" t="n">
-        <v>31</v>
+        <v>14.3</v>
       </c>
       <c r="H61" t="n">
-        <v>3.3</v>
+        <v>16.7</v>
       </c>
       <c r="I61" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="J61" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -3405,31 +3413,31 @@
         <v>69</v>
       </c>
       <c r="C62" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E62" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F62" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G62" t="n">
-        <v>14.3</v>
+        <v>38</v>
       </c>
       <c r="H62" t="n">
-        <v>16.7</v>
+        <v>9.8</v>
       </c>
       <c r="I62" t="n">
-        <v>100</v>
+        <v>42.6</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="K62" t="n">
-        <v>60</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="63">
@@ -3440,31 +3448,31 @@
         <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D63" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E63" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F63" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
-        <v>38</v>
+        <v>41.2</v>
       </c>
       <c r="H63" t="n">
-        <v>9.8</v>
+        <v>14.3</v>
       </c>
       <c r="I63" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>24.6</v>
+        <v>30</v>
       </c>
       <c r="K63" t="n">
-        <v>47.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3475,31 +3483,31 @@
         <v>69</v>
       </c>
       <c r="C64" t="n">
-        <v>72.4</v>
+        <v>74.7</v>
       </c>
       <c r="D64" t="n">
-        <v>10</v>
+        <v>21.4</v>
       </c>
       <c r="E64" t="n">
-        <v>62.4</v>
+        <v>53.3</v>
       </c>
       <c r="F64" t="n">
-        <v>10</v>
+        <v>21.4</v>
       </c>
       <c r="G64" t="n">
-        <v>41.2</v>
+        <v>22.3</v>
       </c>
       <c r="H64" t="n">
-        <v>14.3</v>
+        <v>16.3</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>47.7</v>
       </c>
       <c r="J64" t="n">
-        <v>30</v>
+        <v>21.5</v>
       </c>
       <c r="K64" t="n">
-        <v>30</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="65">
@@ -3510,31 +3518,31 @@
         <v>69</v>
       </c>
       <c r="C65" t="n">
-        <v>74.7</v>
+        <v>81</v>
       </c>
       <c r="D65" t="n">
-        <v>21.4</v>
+        <v>16.1</v>
       </c>
       <c r="E65" t="n">
-        <v>53.3</v>
+        <v>64.9</v>
       </c>
       <c r="F65" t="n">
-        <v>21.4</v>
+        <v>16.1</v>
       </c>
       <c r="G65" t="n">
-        <v>22.3</v>
+        <v>24.7</v>
       </c>
       <c r="H65" t="n">
-        <v>16.3</v>
+        <v>11.4</v>
       </c>
       <c r="I65" t="n">
-        <v>47.7</v>
+        <v>50</v>
       </c>
       <c r="J65" t="n">
-        <v>21.5</v>
+        <v>15.4</v>
       </c>
       <c r="K65" t="n">
-        <v>38.1</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="66">
@@ -3545,31 +3553,31 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D66" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="E66" t="n">
-        <v>64.9</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="G66" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="H66" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J66" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -3580,16 +3588,16 @@
         <v>69</v>
       </c>
       <c r="C67" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D67" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G67" t="n">
         <v>25</v>
@@ -3598,13 +3606,13 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -3615,31 +3623,31 @@
         <v>69</v>
       </c>
       <c r="C68" t="n">
-        <v>33.3</v>
+        <v>74.1</v>
       </c>
       <c r="D68" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>74.1</v>
       </c>
       <c r="F68" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>25</v>
+        <v>31.4</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I68" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K68" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="69">
@@ -3650,31 +3658,31 @@
         <v>69</v>
       </c>
       <c r="C69" t="n">
-        <v>74.1</v>
+        <v>69.6</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E69" t="n">
-        <v>74.1</v>
+        <v>36.3</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G69" t="n">
-        <v>31.4</v>
+        <v>20</v>
       </c>
       <c r="H69" t="n">
-        <v>18.8</v>
+        <v>11.8</v>
       </c>
       <c r="I69" t="n">
-        <v>62.5</v>
+        <v>46.2</v>
       </c>
       <c r="J69" t="n">
-        <v>12.5</v>
+        <v>30.8</v>
       </c>
       <c r="K69" t="n">
-        <v>12.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="70">
@@ -3685,31 +3693,31 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>69.6</v>
+        <v>87.5</v>
       </c>
       <c r="D70" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E70" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G70" t="n">
+        <v>60</v>
+      </c>
+      <c r="H70" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I70" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J70" t="n">
         <v>33.3</v>
       </c>
-      <c r="E70" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="F70" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G70" t="n">
-        <v>20</v>
-      </c>
-      <c r="H70" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I70" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J70" t="n">
-        <v>30.8</v>
-      </c>
       <c r="K70" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -3720,31 +3728,31 @@
         <v>69</v>
       </c>
       <c r="C71" t="n">
-        <v>87.5</v>
+        <v>68.6</v>
       </c>
       <c r="D71" t="n">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
       <c r="E71" t="n">
-        <v>69.3</v>
+        <v>36.8</v>
       </c>
       <c r="F71" t="n">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
       <c r="G71" t="n">
-        <v>60</v>
+        <v>11.1</v>
       </c>
       <c r="H71" t="n">
-        <v>16.7</v>
+        <v>3.4</v>
       </c>
       <c r="I71" t="n">
-        <v>66.7</v>
+        <v>47.6</v>
       </c>
       <c r="J71" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K71" t="n">
-        <v>100</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="72">
@@ -3755,31 +3763,31 @@
         <v>69</v>
       </c>
       <c r="C72" t="n">
-        <v>68.6</v>
+        <v>67.3</v>
       </c>
       <c r="D72" t="n">
-        <v>31.8</v>
+        <v>18.2</v>
       </c>
       <c r="E72" t="n">
-        <v>36.8</v>
+        <v>49.1</v>
       </c>
       <c r="F72" t="n">
-        <v>31.8</v>
+        <v>18.2</v>
       </c>
       <c r="G72" t="n">
-        <v>11.1</v>
+        <v>26.9</v>
       </c>
       <c r="H72" t="n">
-        <v>3.4</v>
+        <v>9.9</v>
       </c>
       <c r="I72" t="n">
-        <v>47.6</v>
+        <v>42.2</v>
       </c>
       <c r="J72" t="n">
-        <v>28.6</v>
+        <v>29.7</v>
       </c>
       <c r="K72" t="n">
-        <v>38.1</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="73">
@@ -3790,31 +3798,31 @@
         <v>69</v>
       </c>
       <c r="C73" t="n">
-        <v>67.3</v>
+        <v>79.2</v>
       </c>
       <c r="D73" t="n">
-        <v>18.2</v>
+        <v>37</v>
       </c>
       <c r="E73" t="n">
-        <v>49.1</v>
+        <v>42.2</v>
       </c>
       <c r="F73" t="n">
-        <v>18.2</v>
+        <v>37</v>
       </c>
       <c r="G73" t="n">
-        <v>26.9</v>
+        <v>23.1</v>
       </c>
       <c r="H73" t="n">
-        <v>9.9</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
-        <v>42.2</v>
+        <v>40.5</v>
       </c>
       <c r="J73" t="n">
-        <v>29.7</v>
+        <v>36.5</v>
       </c>
       <c r="K73" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -3825,31 +3833,31 @@
         <v>69</v>
       </c>
       <c r="C74" t="n">
-        <v>79.2</v>
+        <v>56.7</v>
       </c>
       <c r="D74" t="n">
-        <v>37</v>
+        <v>8.7</v>
       </c>
       <c r="E74" t="n">
-        <v>42.2</v>
+        <v>48</v>
       </c>
       <c r="F74" t="n">
-        <v>37</v>
+        <v>8.7</v>
       </c>
       <c r="G74" t="n">
-        <v>23.1</v>
+        <v>33.3</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>15.2</v>
       </c>
       <c r="I74" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="J74" t="n">
-        <v>36.5</v>
+        <v>27.3</v>
       </c>
       <c r="K74" t="n">
-        <v>50</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="75">
@@ -3860,31 +3868,31 @@
         <v>69</v>
       </c>
       <c r="C75" t="n">
-        <v>56.7</v>
+        <v>66.7</v>
       </c>
       <c r="D75" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>48</v>
+        <v>66.7</v>
       </c>
       <c r="F75" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
+        <v>24</v>
+      </c>
+      <c r="H75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I75" t="n">
         <v>33.3</v>
       </c>
-      <c r="H75" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="I75" t="n">
-        <v>50</v>
-      </c>
       <c r="J75" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="K75" t="n">
-        <v>24.4</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="76">
@@ -3895,31 +3903,31 @@
         <v>69</v>
       </c>
       <c r="C76" t="n">
-        <v>66.7</v>
+        <v>75.8</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E76" t="n">
-        <v>66.7</v>
+        <v>56.8</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G76" t="n">
-        <v>24</v>
+        <v>34.3</v>
       </c>
       <c r="H76" t="n">
-        <v>13.3</v>
+        <v>9.3</v>
       </c>
       <c r="I76" t="n">
-        <v>33.3</v>
+        <v>47.8</v>
       </c>
       <c r="J76" t="n">
-        <v>33.3</v>
+        <v>28.3</v>
       </c>
       <c r="K76" t="n">
-        <v>55.6</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="77">
@@ -3927,69 +3935,69 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C77" t="n">
-        <v>75.8</v>
+        <v>82.7</v>
       </c>
       <c r="D77" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="E77" t="n">
-        <v>56.8</v>
+        <v>68.2</v>
       </c>
       <c r="F77" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="G77" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="H77" t="n">
-        <v>9.3</v>
+        <v>11.9</v>
       </c>
       <c r="I77" t="n">
-        <v>47.8</v>
+        <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>28.3</v>
+        <v>51.9</v>
       </c>
       <c r="K77" t="n">
-        <v>53.2</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
+        <v>92</v>
+      </c>
+      <c r="B78" t="s">
         <v>91</v>
       </c>
-      <c r="B78" t="s">
-        <v>92</v>
-      </c>
       <c r="C78" t="n">
-        <v>82.7</v>
+        <v>72.7</v>
       </c>
       <c r="D78" t="n">
-        <v>14.5</v>
+        <v>31.8</v>
       </c>
       <c r="E78" t="n">
-        <v>68.2</v>
+        <v>40.9</v>
       </c>
       <c r="F78" t="n">
-        <v>14.5</v>
+        <v>31.8</v>
       </c>
       <c r="G78" t="n">
-        <v>38.8</v>
+        <v>21.4</v>
       </c>
       <c r="H78" t="n">
-        <v>11.9</v>
+        <v>4.6</v>
       </c>
       <c r="I78" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="J78" t="n">
-        <v>51.9</v>
+        <v>22.2</v>
       </c>
       <c r="K78" t="n">
-        <v>58.6</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="79">
@@ -3997,34 +4005,34 @@
         <v>93</v>
       </c>
       <c r="B79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C79" t="n">
-        <v>72.7</v>
+        <v>74.7</v>
       </c>
       <c r="D79" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="E79" t="n">
-        <v>40.9</v>
+        <v>46.1</v>
       </c>
       <c r="F79" t="n">
-        <v>31.8</v>
+        <v>28.6</v>
       </c>
       <c r="G79" t="n">
-        <v>21.4</v>
+        <v>33.9</v>
       </c>
       <c r="H79" t="n">
-        <v>4.6</v>
+        <v>10.8</v>
       </c>
       <c r="I79" t="n">
-        <v>60</v>
+        <v>43.1</v>
       </c>
       <c r="J79" t="n">
-        <v>22.2</v>
+        <v>25.5</v>
       </c>
       <c r="K79" t="n">
-        <v>44.2</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="80">
@@ -4032,34 +4040,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C80" t="n">
-        <v>74.7</v>
+        <v>73.6</v>
       </c>
       <c r="D80" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="E80" t="n">
-        <v>46.1</v>
+        <v>44.9</v>
       </c>
       <c r="F80" t="n">
-        <v>28.6</v>
+        <v>28.7</v>
       </c>
       <c r="G80" t="n">
-        <v>33.9</v>
+        <v>27</v>
       </c>
       <c r="H80" t="n">
-        <v>10.8</v>
+        <v>7.1</v>
       </c>
       <c r="I80" t="n">
-        <v>43.1</v>
+        <v>53.6</v>
       </c>
       <c r="J80" t="n">
-        <v>25.5</v>
+        <v>21.4</v>
       </c>
       <c r="K80" t="n">
-        <v>64.2</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="81">
@@ -4067,34 +4075,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" t="n">
-        <v>73.6</v>
+        <v>78.6</v>
       </c>
       <c r="D81" t="n">
-        <v>28.7</v>
+        <v>30.1</v>
       </c>
       <c r="E81" t="n">
-        <v>44.9</v>
+        <v>48.5</v>
       </c>
       <c r="F81" t="n">
-        <v>28.7</v>
+        <v>30.1</v>
       </c>
       <c r="G81" t="n">
-        <v>27</v>
+        <v>24.4</v>
       </c>
       <c r="H81" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>53.6</v>
+        <v>38.9</v>
       </c>
       <c r="J81" t="n">
-        <v>21.4</v>
+        <v>27.8</v>
       </c>
       <c r="K81" t="n">
-        <v>42.6</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="82">
@@ -4102,34 +4110,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C82" t="n">
-        <v>78.6</v>
+        <v>74</v>
       </c>
       <c r="D82" t="n">
-        <v>30.1</v>
+        <v>19.1</v>
       </c>
       <c r="E82" t="n">
-        <v>48.5</v>
+        <v>54.9</v>
       </c>
       <c r="F82" t="n">
-        <v>30.1</v>
+        <v>19.1</v>
       </c>
       <c r="G82" t="n">
-        <v>24.4</v>
+        <v>24.1</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I82" t="n">
-        <v>38.9</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>27.8</v>
+        <v>37.9</v>
       </c>
       <c r="K82" t="n">
-        <v>66.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -4137,34 +4145,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C83" t="n">
-        <v>74</v>
+        <v>72.4</v>
       </c>
       <c r="D83" t="n">
-        <v>19.1</v>
+        <v>22.6</v>
       </c>
       <c r="E83" t="n">
-        <v>54.9</v>
+        <v>49.8</v>
       </c>
       <c r="F83" t="n">
-        <v>19.1</v>
+        <v>22.6</v>
       </c>
       <c r="G83" t="n">
-        <v>24.1</v>
+        <v>30.5</v>
       </c>
       <c r="H83" t="n">
-        <v>11.4</v>
+        <v>7.3</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>48.5</v>
       </c>
       <c r="J83" t="n">
-        <v>37.9</v>
+        <v>24.2</v>
       </c>
       <c r="K83" t="n">
-        <v>25</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="84">
@@ -4172,34 +4180,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C84" t="n">
-        <v>72.4</v>
+        <v>40</v>
       </c>
       <c r="D84" t="n">
-        <v>22.6</v>
+        <v>25</v>
       </c>
       <c r="E84" t="n">
-        <v>49.8</v>
+        <v>15</v>
       </c>
       <c r="F84" t="n">
-        <v>22.6</v>
+        <v>25</v>
       </c>
       <c r="G84" t="n">
-        <v>30.5</v>
+        <v>43.8</v>
       </c>
       <c r="H84" t="n">
-        <v>7.3</v>
+        <v>26.7</v>
       </c>
       <c r="I84" t="n">
-        <v>48.5</v>
+        <v>60</v>
       </c>
       <c r="J84" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>32.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="85">
@@ -4207,34 +4215,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C85" t="n">
-        <v>40</v>
+        <v>70.7</v>
       </c>
       <c r="D85" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="E85" t="n">
-        <v>15</v>
+        <v>43.8</v>
       </c>
       <c r="F85" t="n">
-        <v>25</v>
+        <v>26.9</v>
       </c>
       <c r="G85" t="n">
-        <v>43.8</v>
+        <v>19.2</v>
       </c>
       <c r="H85" t="n">
-        <v>26.7</v>
+        <v>6.7</v>
       </c>
       <c r="I85" t="n">
-        <v>60</v>
+        <v>57.6</v>
       </c>
       <c r="J85" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="K85" t="n">
-        <v>60</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="86">
@@ -4242,34 +4250,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C86" t="n">
-        <v>70.7</v>
+        <v>75.7</v>
       </c>
       <c r="D86" t="n">
-        <v>26.9</v>
+        <v>32.3</v>
       </c>
       <c r="E86" t="n">
-        <v>43.8</v>
+        <v>43.4</v>
       </c>
       <c r="F86" t="n">
-        <v>26.9</v>
+        <v>32.3</v>
       </c>
       <c r="G86" t="n">
-        <v>19.2</v>
+        <v>23.7</v>
       </c>
       <c r="H86" t="n">
-        <v>6.7</v>
+        <v>10.8</v>
       </c>
       <c r="I86" t="n">
-        <v>57.6</v>
+        <v>48</v>
       </c>
       <c r="J86" t="n">
-        <v>18.6</v>
+        <v>32</v>
       </c>
       <c r="K86" t="n">
-        <v>40.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87">
@@ -4277,34 +4285,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C87" t="n">
-        <v>75.7</v>
+        <v>80</v>
       </c>
       <c r="D87" t="n">
-        <v>32.3</v>
+        <v>30</v>
       </c>
       <c r="E87" t="n">
-        <v>43.4</v>
+        <v>50</v>
       </c>
       <c r="F87" t="n">
-        <v>32.3</v>
+        <v>30</v>
       </c>
       <c r="G87" t="n">
-        <v>23.7</v>
+        <v>30.8</v>
       </c>
       <c r="H87" t="n">
-        <v>10.8</v>
+        <v>18.2</v>
       </c>
       <c r="I87" t="n">
-        <v>48</v>
+        <v>57.1</v>
       </c>
       <c r="J87" t="n">
-        <v>32</v>
+        <v>14.3</v>
       </c>
       <c r="K87" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="88">
@@ -4312,34 +4320,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C88" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D88" t="n">
-        <v>30</v>
+        <v>15.9</v>
       </c>
       <c r="E88" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F88" t="n">
-        <v>30</v>
+        <v>15.9</v>
       </c>
       <c r="G88" t="n">
-        <v>30.8</v>
+        <v>18.8</v>
       </c>
       <c r="H88" t="n">
-        <v>18.2</v>
+        <v>12.5</v>
       </c>
       <c r="I88" t="n">
-        <v>57.1</v>
+        <v>63</v>
       </c>
       <c r="J88" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="K88" t="n">
-        <v>42.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="89">
@@ -4347,34 +4355,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C89" t="n">
-        <v>64</v>
+        <v>53.6</v>
       </c>
       <c r="D89" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="E89" t="n">
-        <v>48.1</v>
+        <v>38</v>
       </c>
       <c r="F89" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="G89" t="n">
-        <v>18.8</v>
+        <v>30.8</v>
       </c>
       <c r="H89" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="I89" t="n">
-        <v>63</v>
+        <v>66.7</v>
       </c>
       <c r="J89" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="K89" t="n">
-        <v>40.7</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="90">
@@ -4382,57 +4390,51 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C90" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="D90" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="E90" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="G90" t="n">
-        <v>30.8</v>
+        <v>100</v>
       </c>
       <c r="H90" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I90" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J90" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="K90" t="n">
-        <v>27.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I90"/>
+      <c r="J90"/>
+      <c r="K90"/>
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91" t="s">
         <v>105</v>
       </c>
-      <c r="B91" t="s">
-        <v>106</v>
-      </c>
       <c r="C91" t="n">
+        <v>100</v>
+      </c>
+      <c r="D91" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F91" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G91" t="n">
         <v>50</v>
-      </c>
-      <c r="D91" t="n">
-        <v>50</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="n">
-        <v>50</v>
-      </c>
-      <c r="G91" t="n">
-        <v>100</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4443,66 +4445,72 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C92" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D92" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="E92" t="n">
-        <v>66.7</v>
+        <v>47</v>
       </c>
       <c r="F92" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="G92" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H92" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J92" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="K92" t="n">
         <v>50</v>
       </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92"/>
-      <c r="J92"/>
-      <c r="K92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="B93" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C93" t="n">
-        <v>57.8</v>
+        <v>71.4</v>
       </c>
       <c r="D93" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="E93" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
       <c r="F93" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="G93" t="n">
-        <v>26.2</v>
+        <v>16.7</v>
       </c>
       <c r="H93" t="n">
-        <v>13.2</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -4510,34 +4518,34 @@
         <v>108</v>
       </c>
       <c r="B94" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C94" t="n">
-        <v>71.4</v>
+        <v>62.2</v>
       </c>
       <c r="D94" t="n">
-        <v>20</v>
+        <v>43.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.4</v>
+        <v>18.7</v>
       </c>
       <c r="F94" t="n">
-        <v>20</v>
+        <v>43.5</v>
       </c>
       <c r="G94" t="n">
-        <v>16.7</v>
+        <v>34</v>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>3.3</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>41.2</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="95">
@@ -4545,34 +4553,34 @@
         <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C95" t="n">
-        <v>62.2</v>
+        <v>77.3</v>
       </c>
       <c r="D95" t="n">
-        <v>43.5</v>
+        <v>40</v>
       </c>
       <c r="E95" t="n">
-        <v>18.7</v>
+        <v>37.3</v>
       </c>
       <c r="F95" t="n">
-        <v>43.5</v>
+        <v>40</v>
       </c>
       <c r="G95" t="n">
-        <v>34</v>
+        <v>43.6</v>
       </c>
       <c r="H95" t="n">
-        <v>3.3</v>
+        <v>11.3</v>
       </c>
       <c r="I95" t="n">
-        <v>41.2</v>
+        <v>53.6</v>
       </c>
       <c r="J95" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="K95" t="n">
-        <v>12.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96">
@@ -4580,34 +4588,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C96" t="n">
-        <v>77.3</v>
+        <v>76.5</v>
       </c>
       <c r="D96" t="n">
-        <v>40</v>
+        <v>21.3</v>
       </c>
       <c r="E96" t="n">
-        <v>37.3</v>
+        <v>55.2</v>
       </c>
       <c r="F96" t="n">
-        <v>40</v>
+        <v>21.3</v>
       </c>
       <c r="G96" t="n">
-        <v>43.6</v>
+        <v>15.6</v>
       </c>
       <c r="H96" t="n">
-        <v>11.3</v>
+        <v>6.9</v>
       </c>
       <c r="I96" t="n">
-        <v>53.6</v>
+        <v>48.4</v>
       </c>
       <c r="J96" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="K96" t="n">
-        <v>37</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="97">
@@ -4615,34 +4623,34 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C97" t="n">
-        <v>76.5</v>
+        <v>65.5</v>
       </c>
       <c r="D97" t="n">
-        <v>21.3</v>
+        <v>9.7</v>
       </c>
       <c r="E97" t="n">
-        <v>55.2</v>
+        <v>55.8</v>
       </c>
       <c r="F97" t="n">
-        <v>21.3</v>
+        <v>9.7</v>
       </c>
       <c r="G97" t="n">
-        <v>15.6</v>
+        <v>32.3</v>
       </c>
       <c r="H97" t="n">
-        <v>6.9</v>
+        <v>23.1</v>
       </c>
       <c r="I97" t="n">
-        <v>48.4</v>
+        <v>28.3</v>
       </c>
       <c r="J97" t="n">
-        <v>18.8</v>
+        <v>34</v>
       </c>
       <c r="K97" t="n">
-        <v>29.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="98">
@@ -4650,34 +4658,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C98" t="n">
-        <v>65.5</v>
+        <v>75</v>
       </c>
       <c r="D98" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="n">
-        <v>55.8</v>
+        <v>62.5</v>
       </c>
       <c r="F98" t="n">
-        <v>9.7</v>
+        <v>12.5</v>
       </c>
       <c r="G98" t="n">
-        <v>32.3</v>
+        <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>23.1</v>
+        <v>50</v>
       </c>
       <c r="I98" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>43.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4685,25 +4693,25 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C99" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="F99" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
@@ -4720,34 +4728,34 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C100" t="n">
-        <v>100</v>
+        <v>70.5</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E100" t="n">
-        <v>100</v>
+        <v>43.5</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>22.8</v>
       </c>
       <c r="H100" t="n">
-        <v>0</v>
+        <v>9.3</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="101">
@@ -4755,34 +4763,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C101" t="n">
-        <v>70.5</v>
+        <v>81</v>
       </c>
       <c r="D101" t="n">
-        <v>27</v>
+        <v>25.9</v>
       </c>
       <c r="E101" t="n">
-        <v>43.5</v>
+        <v>55.1</v>
       </c>
       <c r="F101" t="n">
-        <v>27</v>
+        <v>25.9</v>
       </c>
       <c r="G101" t="n">
-        <v>22.8</v>
+        <v>34.6</v>
       </c>
       <c r="H101" t="n">
-        <v>9.3</v>
+        <v>6.7</v>
       </c>
       <c r="I101" t="n">
-        <v>42.9</v>
+        <v>38</v>
       </c>
       <c r="J101" t="n">
-        <v>28.6</v>
+        <v>32</v>
       </c>
       <c r="K101" t="n">
-        <v>47.1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="102">
@@ -4790,34 +4798,34 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C102" t="n">
-        <v>81</v>
+        <v>71.4</v>
       </c>
       <c r="D102" t="n">
-        <v>25.9</v>
+        <v>35.7</v>
       </c>
       <c r="E102" t="n">
-        <v>55.1</v>
+        <v>35.7</v>
       </c>
       <c r="F102" t="n">
-        <v>25.9</v>
+        <v>35.7</v>
       </c>
       <c r="G102" t="n">
-        <v>34.6</v>
+        <v>6.1</v>
       </c>
       <c r="H102" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="I102" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="J102" t="n">
-        <v>32</v>
+        <v>15.4</v>
       </c>
       <c r="K102" t="n">
-        <v>54</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="103">
@@ -4825,34 +4833,34 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C103" t="n">
-        <v>71.4</v>
+        <v>62.5</v>
       </c>
       <c r="D103" t="n">
-        <v>35.7</v>
+        <v>14</v>
       </c>
       <c r="E103" t="n">
-        <v>35.7</v>
+        <v>48.5</v>
       </c>
       <c r="F103" t="n">
-        <v>35.7</v>
+        <v>14</v>
       </c>
       <c r="G103" t="n">
-        <v>6.1</v>
+        <v>32.7</v>
       </c>
       <c r="H103" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>38.5</v>
+        <v>42.1</v>
       </c>
       <c r="J103" t="n">
-        <v>15.4</v>
+        <v>36.8</v>
       </c>
       <c r="K103" t="n">
-        <v>30.8</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="104">
@@ -4860,34 +4868,34 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C104" t="n">
-        <v>62.5</v>
+        <v>78.7</v>
       </c>
       <c r="D104" t="n">
-        <v>14</v>
+        <v>26.9</v>
       </c>
       <c r="E104" t="n">
-        <v>48.5</v>
+        <v>51.8</v>
       </c>
       <c r="F104" t="n">
-        <v>14</v>
+        <v>26.9</v>
       </c>
       <c r="G104" t="n">
-        <v>32.7</v>
+        <v>36.3</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I104" t="n">
-        <v>42.1</v>
+        <v>38.8</v>
       </c>
       <c r="J104" t="n">
-        <v>36.8</v>
+        <v>28.6</v>
       </c>
       <c r="K104" t="n">
-        <v>47.4</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="105">
@@ -4895,34 +4903,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C105" t="n">
-        <v>78.7</v>
+        <v>66.7</v>
       </c>
       <c r="D105" t="n">
-        <v>26.9</v>
+        <v>17.3</v>
       </c>
       <c r="E105" t="n">
-        <v>51.8</v>
+        <v>49.4</v>
       </c>
       <c r="F105" t="n">
-        <v>26.9</v>
+        <v>17.3</v>
       </c>
       <c r="G105" t="n">
-        <v>36.3</v>
+        <v>16.7</v>
       </c>
       <c r="H105" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="I105" t="n">
-        <v>38.8</v>
+        <v>39.2</v>
       </c>
       <c r="J105" t="n">
-        <v>28.6</v>
+        <v>20.3</v>
       </c>
       <c r="K105" t="n">
-        <v>40.8</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106">
@@ -4930,34 +4938,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C106" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D106" t="n">
-        <v>17.3</v>
+        <v>22.2</v>
       </c>
       <c r="E106" t="n">
-        <v>49.4</v>
+        <v>33.4</v>
       </c>
       <c r="F106" t="n">
-        <v>17.3</v>
+        <v>22.2</v>
       </c>
       <c r="G106" t="n">
-        <v>16.7</v>
+        <v>18.5</v>
       </c>
       <c r="H106" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="I106" t="n">
-        <v>39.2</v>
+        <v>44.8</v>
       </c>
       <c r="J106" t="n">
-        <v>20.3</v>
+        <v>23.9</v>
       </c>
       <c r="K106" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="107">
@@ -4965,34 +4973,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C107" t="n">
-        <v>55.6</v>
+        <v>65.3</v>
       </c>
       <c r="D107" t="n">
-        <v>22.2</v>
+        <v>17</v>
       </c>
       <c r="E107" t="n">
-        <v>33.4</v>
+        <v>48.3</v>
       </c>
       <c r="F107" t="n">
-        <v>22.2</v>
+        <v>17</v>
       </c>
       <c r="G107" t="n">
-        <v>18.5</v>
+        <v>22.4</v>
       </c>
       <c r="H107" t="n">
-        <v>11</v>
+        <v>9.8</v>
       </c>
       <c r="I107" t="n">
-        <v>44.8</v>
+        <v>54.5</v>
       </c>
       <c r="J107" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="K107" t="n">
-        <v>43.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="108">
@@ -5000,69 +5008,69 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C108" t="n">
-        <v>65.3</v>
+        <v>66.2</v>
       </c>
       <c r="D108" t="n">
-        <v>17</v>
+        <v>36.1</v>
       </c>
       <c r="E108" t="n">
-        <v>48.3</v>
+        <v>30.1</v>
       </c>
       <c r="F108" t="n">
-        <v>17</v>
+        <v>36.1</v>
       </c>
       <c r="G108" t="n">
-        <v>22.4</v>
+        <v>27.9</v>
       </c>
       <c r="H108" t="n">
-        <v>9.8</v>
+        <v>7.3</v>
       </c>
       <c r="I108" t="n">
-        <v>54.5</v>
+        <v>40.7</v>
       </c>
       <c r="J108" t="n">
-        <v>27.3</v>
+        <v>33.3</v>
       </c>
       <c r="K108" t="n">
-        <v>51.8</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>124</v>
+      </c>
+      <c r="B109" t="s">
         <v>123</v>
       </c>
-      <c r="B109" t="s">
-        <v>124</v>
-      </c>
       <c r="C109" t="n">
-        <v>66.2</v>
+        <v>80</v>
       </c>
       <c r="D109" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="E109" t="n">
-        <v>30.1</v>
+        <v>80</v>
       </c>
       <c r="F109" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="H109" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I109" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K109" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -5070,34 +5078,34 @@
         <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C110" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="E110" t="n">
-        <v>80</v>
+        <v>44.3</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="G110" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>10.9</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>38.8</v>
       </c>
       <c r="J110" t="n">
-        <v>100</v>
+        <v>32.7</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="111">
@@ -5105,34 +5113,34 @@
         <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C111" t="n">
-        <v>69</v>
+        <v>65.4</v>
       </c>
       <c r="D111" t="n">
-        <v>24.7</v>
+        <v>28.2</v>
       </c>
       <c r="E111" t="n">
-        <v>44.3</v>
+        <v>37.2</v>
       </c>
       <c r="F111" t="n">
-        <v>24.7</v>
+        <v>28.2</v>
       </c>
       <c r="G111" t="n">
-        <v>11.1</v>
+        <v>31.9</v>
       </c>
       <c r="H111" t="n">
-        <v>10.9</v>
+        <v>5.5</v>
       </c>
       <c r="I111" t="n">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="J111" t="n">
-        <v>32.7</v>
+        <v>26.2</v>
       </c>
       <c r="K111" t="n">
-        <v>48.9</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="112">
@@ -5140,34 +5148,34 @@
         <v>127</v>
       </c>
       <c r="B112" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C112" t="n">
-        <v>65.4</v>
+        <v>80.1</v>
       </c>
       <c r="D112" t="n">
-        <v>28.2</v>
+        <v>32.5</v>
       </c>
       <c r="E112" t="n">
-        <v>37.2</v>
+        <v>47.6</v>
       </c>
       <c r="F112" t="n">
-        <v>28.2</v>
+        <v>32.5</v>
       </c>
       <c r="G112" t="n">
-        <v>31.9</v>
+        <v>25</v>
       </c>
       <c r="H112" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I112" t="n">
-        <v>40.5</v>
+        <v>41.3</v>
       </c>
       <c r="J112" t="n">
-        <v>26.2</v>
+        <v>28</v>
       </c>
       <c r="K112" t="n">
-        <v>42.9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -5175,34 +5183,34 @@
         <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C113" t="n">
-        <v>80.1</v>
+        <v>53.4</v>
       </c>
       <c r="D113" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="E113" t="n">
-        <v>47.6</v>
+        <v>25.3</v>
       </c>
       <c r="F113" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="G113" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H113" t="n">
-        <v>5.7</v>
+        <v>7.9</v>
       </c>
       <c r="I113" t="n">
-        <v>41.3</v>
+        <v>61.9</v>
       </c>
       <c r="J113" t="n">
-        <v>28</v>
+        <v>11.9</v>
       </c>
       <c r="K113" t="n">
-        <v>27</v>
+        <v>52.4</v>
       </c>
     </row>
     <row r="114">
@@ -5210,34 +5218,34 @@
         <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C114" t="n">
-        <v>53.4</v>
+        <v>54.7</v>
       </c>
       <c r="D114" t="n">
-        <v>28.1</v>
+        <v>22.6</v>
       </c>
       <c r="E114" t="n">
-        <v>25.3</v>
+        <v>32.1</v>
       </c>
       <c r="F114" t="n">
-        <v>28.1</v>
+        <v>22.6</v>
       </c>
       <c r="G114" t="n">
-        <v>19</v>
+        <v>9.1</v>
       </c>
       <c r="H114" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
       <c r="I114" t="n">
-        <v>61.9</v>
+        <v>60.3</v>
       </c>
       <c r="J114" t="n">
-        <v>11.9</v>
+        <v>12.8</v>
       </c>
       <c r="K114" t="n">
-        <v>52.4</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="115">
@@ -5245,34 +5253,34 @@
         <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C115" t="n">
-        <v>54.7</v>
+        <v>80</v>
       </c>
       <c r="D115" t="n">
-        <v>22.6</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="n">
-        <v>32.1</v>
+        <v>68.9</v>
       </c>
       <c r="F115" t="n">
-        <v>22.6</v>
+        <v>11.1</v>
       </c>
       <c r="G115" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>10</v>
+      </c>
+      <c r="I115" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="J115" t="n">
         <v>9.1</v>
       </c>
-      <c r="H115" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I115" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J115" t="n">
-        <v>12.8</v>
-      </c>
       <c r="K115" t="n">
-        <v>20.8</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="116">
@@ -5280,34 +5288,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C116" t="n">
-        <v>80</v>
+        <v>71.5</v>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>28.3</v>
       </c>
       <c r="E116" t="n">
-        <v>68.9</v>
+        <v>43.2</v>
       </c>
       <c r="F116" t="n">
-        <v>11.1</v>
+        <v>28.3</v>
       </c>
       <c r="G116" t="n">
-        <v>39.5</v>
+        <v>21.2</v>
       </c>
       <c r="H116" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I116" t="n">
-        <v>63.6</v>
+        <v>40.4</v>
       </c>
       <c r="J116" t="n">
-        <v>9.1</v>
+        <v>31.9</v>
       </c>
       <c r="K116" t="n">
-        <v>45.5</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="117">
@@ -5315,34 +5323,34 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C117" t="n">
-        <v>71.5</v>
+        <v>70</v>
       </c>
       <c r="D117" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
       <c r="E117" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="F117" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
       <c r="G117" t="n">
-        <v>21.2</v>
+        <v>14.8</v>
       </c>
       <c r="H117" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="I117" t="n">
-        <v>40.4</v>
+        <v>60</v>
       </c>
       <c r="J117" t="n">
-        <v>31.9</v>
+        <v>30</v>
       </c>
       <c r="K117" t="n">
-        <v>42.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118">
@@ -5350,34 +5358,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C118" t="n">
-        <v>70</v>
+        <v>56.8</v>
       </c>
       <c r="D118" t="n">
-        <v>26.7</v>
+        <v>19.6</v>
       </c>
       <c r="E118" t="n">
-        <v>43.3</v>
+        <v>37.2</v>
       </c>
       <c r="F118" t="n">
-        <v>26.7</v>
+        <v>19.6</v>
       </c>
       <c r="G118" t="n">
-        <v>14.8</v>
+        <v>19.6</v>
       </c>
       <c r="H118" t="n">
-        <v>12.5</v>
+        <v>11.4</v>
       </c>
       <c r="I118" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J118" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K118" t="n">
-        <v>10</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="119">
@@ -5385,34 +5393,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C119" t="n">
-        <v>56.8</v>
+        <v>73.5</v>
       </c>
       <c r="D119" t="n">
-        <v>19.6</v>
+        <v>24.1</v>
       </c>
       <c r="E119" t="n">
-        <v>37.2</v>
+        <v>49.4</v>
       </c>
       <c r="F119" t="n">
-        <v>19.6</v>
+        <v>24.1</v>
       </c>
       <c r="G119" t="n">
-        <v>19.6</v>
+        <v>31.7</v>
       </c>
       <c r="H119" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="I119" t="n">
         <v>50</v>
       </c>
       <c r="J119" t="n">
-        <v>25</v>
+        <v>20.3</v>
       </c>
       <c r="K119" t="n">
-        <v>52.6</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="120">
@@ -5420,34 +5428,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>73.5</v>
+        <v>75.9</v>
       </c>
       <c r="D120" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="E120" t="n">
-        <v>49.4</v>
+        <v>51.5</v>
       </c>
       <c r="F120" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="G120" t="n">
-        <v>31.7</v>
+        <v>30</v>
       </c>
       <c r="H120" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I120" t="n">
-        <v>50</v>
+        <v>38.6</v>
       </c>
       <c r="J120" t="n">
-        <v>20.3</v>
+        <v>27.1</v>
       </c>
       <c r="K120" t="n">
-        <v>41.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121">
@@ -5455,34 +5463,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C121" t="n">
-        <v>75.9</v>
+        <v>73.6</v>
       </c>
       <c r="D121" t="n">
-        <v>24.4</v>
+        <v>22.3</v>
       </c>
       <c r="E121" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F121" t="n">
-        <v>24.4</v>
+        <v>22.3</v>
       </c>
       <c r="G121" t="n">
-        <v>30</v>
+        <v>26.1</v>
       </c>
       <c r="H121" t="n">
-        <v>9.6</v>
+        <v>8.8</v>
       </c>
       <c r="I121" t="n">
-        <v>38.6</v>
+        <v>40.8</v>
       </c>
       <c r="J121" t="n">
-        <v>27.1</v>
+        <v>34.2</v>
       </c>
       <c r="K121" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="122">
@@ -5490,34 +5498,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C122" t="n">
-        <v>73.6</v>
+        <v>71.2</v>
       </c>
       <c r="D122" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="E122" t="n">
-        <v>51.3</v>
+        <v>52.6</v>
       </c>
       <c r="F122" t="n">
-        <v>22.3</v>
+        <v>18.6</v>
       </c>
       <c r="G122" t="n">
-        <v>26.1</v>
+        <v>14.5</v>
       </c>
       <c r="H122" t="n">
-        <v>8.8</v>
+        <v>11.4</v>
       </c>
       <c r="I122" t="n">
-        <v>40.8</v>
+        <v>46.2</v>
       </c>
       <c r="J122" t="n">
-        <v>34.2</v>
+        <v>19.2</v>
       </c>
       <c r="K122" t="n">
-        <v>50</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="123">
@@ -5525,63 +5533,63 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C123" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="D123" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="E123" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="F123" t="n">
-        <v>18.6</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
       <c r="G123" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>19.2</v>
+        <v>100</v>
       </c>
       <c r="K123" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>140</v>
+      </c>
+      <c r="B124" t="s">
         <v>139</v>
       </c>
-      <c r="B124" t="s">
-        <v>140</v>
-      </c>
       <c r="C124" t="n">
-        <v>100</v>
-      </c>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
+        <v>77.8</v>
+      </c>
+      <c r="D124" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>27.3</v>
+      </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="J124" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="125">
@@ -5589,34 +5597,34 @@
         <v>141</v>
       </c>
       <c r="B125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C125" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="D125" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="E125" t="n">
-        <v>50.5</v>
+        <v>6.7</v>
       </c>
       <c r="F125" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="G125" t="n">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I125" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K125" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -5624,34 +5632,34 @@
         <v>142</v>
       </c>
       <c r="B126" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C126" t="n">
-        <v>66.7</v>
+        <v>64.6</v>
       </c>
       <c r="D126" t="n">
-        <v>60</v>
+        <v>21.7</v>
       </c>
       <c r="E126" t="n">
-        <v>6.7</v>
+        <v>42.9</v>
       </c>
       <c r="F126" t="n">
-        <v>60</v>
+        <v>21.7</v>
       </c>
       <c r="G126" t="n">
-        <v>33.3</v>
+        <v>15.7</v>
       </c>
       <c r="H126" t="n">
-        <v>11.1</v>
+        <v>7.7</v>
       </c>
       <c r="I126" t="n">
-        <v>25</v>
+        <v>48.6</v>
       </c>
       <c r="J126" t="n">
-        <v>25</v>
+        <v>21.6</v>
       </c>
       <c r="K126" t="n">
-        <v>0</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="127">
@@ -5659,34 +5667,34 @@
         <v>143</v>
       </c>
       <c r="B127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C127" t="n">
-        <v>64.6</v>
+        <v>35</v>
       </c>
       <c r="D127" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E127" t="n">
         <v>21.7</v>
       </c>
-      <c r="E127" t="n">
-        <v>42.9</v>
-      </c>
       <c r="F127" t="n">
-        <v>21.7</v>
+        <v>13.3</v>
       </c>
       <c r="G127" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="H127" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="J127" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -5694,34 +5702,34 @@
         <v>144</v>
       </c>
       <c r="B128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C128" t="n">
-        <v>35</v>
+        <v>73.1</v>
       </c>
       <c r="D128" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
       <c r="E128" t="n">
-        <v>21.7</v>
+        <v>39.2</v>
       </c>
       <c r="F128" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
       <c r="G128" t="n">
-        <v>33.3</v>
+        <v>35.7</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="I128" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="129">
@@ -5729,34 +5737,34 @@
         <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C129" t="n">
-        <v>73.1</v>
+        <v>71.7</v>
       </c>
       <c r="D129" t="n">
-        <v>33.9</v>
+        <v>27.7</v>
       </c>
       <c r="E129" t="n">
-        <v>39.2</v>
+        <v>44</v>
       </c>
       <c r="F129" t="n">
-        <v>33.9</v>
+        <v>27.7</v>
       </c>
       <c r="G129" t="n">
-        <v>35.7</v>
+        <v>32.8</v>
       </c>
       <c r="H129" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
       <c r="I129" t="n">
-        <v>53.8</v>
+        <v>35.9</v>
       </c>
       <c r="J129" t="n">
-        <v>23.1</v>
+        <v>35.9</v>
       </c>
       <c r="K129" t="n">
-        <v>38.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="130">
@@ -5764,34 +5772,34 @@
         <v>146</v>
       </c>
       <c r="B130" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C130" t="n">
-        <v>71.7</v>
+        <v>60</v>
       </c>
       <c r="D130" t="n">
-        <v>27.7</v>
+        <v>36.4</v>
       </c>
       <c r="E130" t="n">
-        <v>44</v>
+        <v>23.6</v>
       </c>
       <c r="F130" t="n">
-        <v>27.7</v>
+        <v>36.4</v>
       </c>
       <c r="G130" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>10.8</v>
+        <v>16.7</v>
       </c>
       <c r="I130" t="n">
-        <v>35.9</v>
+        <v>40</v>
       </c>
       <c r="J130" t="n">
-        <v>35.9</v>
+        <v>40</v>
       </c>
       <c r="K130" t="n">
-        <v>42.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -5799,34 +5807,34 @@
         <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C131" t="n">
-        <v>60</v>
+        <v>62.6</v>
       </c>
       <c r="D131" t="n">
-        <v>36.4</v>
+        <v>23.9</v>
       </c>
       <c r="E131" t="n">
-        <v>23.6</v>
+        <v>38.7</v>
       </c>
       <c r="F131" t="n">
-        <v>36.4</v>
+        <v>23.9</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="H131" t="n">
-        <v>16.7</v>
+        <v>6.6</v>
       </c>
       <c r="I131" t="n">
-        <v>40</v>
+        <v>58.8</v>
       </c>
       <c r="J131" t="n">
-        <v>40</v>
+        <v>15.7</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="132">
@@ -5834,34 +5842,34 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C132" t="n">
-        <v>62.6</v>
+        <v>66.7</v>
       </c>
       <c r="D132" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>38.7</v>
+        <v>66.7</v>
       </c>
       <c r="F132" t="n">
-        <v>23.9</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="H132" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>58.8</v>
+        <v>75</v>
       </c>
       <c r="J132" t="n">
-        <v>15.7</v>
+        <v>25</v>
       </c>
       <c r="K132" t="n">
-        <v>35.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5869,34 +5877,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C133" t="n">
-        <v>66.7</v>
+        <v>65.6</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="E133" t="n">
-        <v>66.7</v>
+        <v>43.9</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="G133" t="n">
-        <v>18.2</v>
+        <v>35</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I133" t="n">
-        <v>75</v>
+        <v>81.2</v>
       </c>
       <c r="J133" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="134">
@@ -5904,34 +5912,34 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C134" t="n">
-        <v>65.6</v>
+        <v>51.9</v>
       </c>
       <c r="D134" t="n">
-        <v>21.7</v>
+        <v>15</v>
       </c>
       <c r="E134" t="n">
-        <v>43.9</v>
+        <v>36.9</v>
       </c>
       <c r="F134" t="n">
-        <v>21.7</v>
+        <v>15</v>
       </c>
       <c r="G134" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H134" t="n">
-        <v>8</v>
+        <v>13.3</v>
       </c>
       <c r="I134" t="n">
-        <v>81.2</v>
+        <v>71.4</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K134" t="n">
-        <v>43.8</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="135">
@@ -5939,34 +5947,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C135" t="n">
-        <v>51.9</v>
+        <v>67.2</v>
       </c>
       <c r="D135" t="n">
-        <v>15</v>
+        <v>29.6</v>
       </c>
       <c r="E135" t="n">
-        <v>36.9</v>
+        <v>37.6</v>
       </c>
       <c r="F135" t="n">
-        <v>15</v>
+        <v>29.6</v>
       </c>
       <c r="G135" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="H135" t="n">
-        <v>13.3</v>
+        <v>7.2</v>
       </c>
       <c r="I135" t="n">
-        <v>71.4</v>
+        <v>36</v>
       </c>
       <c r="J135" t="n">
-        <v>28.6</v>
+        <v>28</v>
       </c>
       <c r="K135" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="136">
@@ -5974,34 +5982,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C136" t="n">
-        <v>67.2</v>
+        <v>81.8</v>
       </c>
       <c r="D136" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="E136" t="n">
-        <v>37.6</v>
+        <v>81.8</v>
       </c>
       <c r="F136" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>31.5</v>
+        <v>11.1</v>
       </c>
       <c r="H136" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I136" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="J136" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K136" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137">
@@ -6009,104 +6017,104 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C137" t="n">
-        <v>81.8</v>
+        <v>64.7</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E137" t="n">
-        <v>81.8</v>
+        <v>39.7</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G137" t="n">
-        <v>11.1</v>
+        <v>21.2</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I137" t="n">
-        <v>20</v>
+        <v>61.1</v>
       </c>
       <c r="J137" t="n">
-        <v>40</v>
+        <v>22.2</v>
       </c>
       <c r="K137" t="n">
-        <v>20</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="B138" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C138" t="n">
-        <v>64.7</v>
+        <v>56.1</v>
       </c>
       <c r="D138" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="E138" t="n">
-        <v>39.7</v>
+        <v>36.9</v>
       </c>
       <c r="F138" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="G138" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="H138" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I138" t="n">
-        <v>61.1</v>
+        <v>40.5</v>
       </c>
       <c r="J138" t="n">
-        <v>22.2</v>
+        <v>27</v>
       </c>
       <c r="K138" t="n">
-        <v>30.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="B139" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C139" t="n">
-        <v>56.1</v>
+        <v>78.6</v>
       </c>
       <c r="D139" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="E139" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="F139" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="G139" t="n">
-        <v>22.5</v>
+        <v>28.9</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>40.5</v>
+        <v>57.1</v>
       </c>
       <c r="J139" t="n">
-        <v>27</v>
+        <v>14.3</v>
       </c>
       <c r="K139" t="n">
-        <v>40.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="140">
@@ -6114,34 +6122,34 @@
         <v>155</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C140" t="n">
-        <v>78.6</v>
+        <v>61.5</v>
       </c>
       <c r="D140" t="n">
-        <v>39.1</v>
+        <v>11.2</v>
       </c>
       <c r="E140" t="n">
-        <v>39.5</v>
+        <v>50.3</v>
       </c>
       <c r="F140" t="n">
-        <v>39.1</v>
+        <v>11.2</v>
       </c>
       <c r="G140" t="n">
-        <v>28.9</v>
+        <v>9.3</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I140" t="n">
-        <v>57.1</v>
+        <v>49.1</v>
       </c>
       <c r="J140" t="n">
-        <v>14.3</v>
+        <v>10.9</v>
       </c>
       <c r="K140" t="n">
-        <v>14.3</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="141">
@@ -6149,34 +6157,34 @@
         <v>156</v>
       </c>
       <c r="B141" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C141" t="n">
-        <v>61.5</v>
+        <v>63.2</v>
       </c>
       <c r="D141" t="n">
-        <v>11.2</v>
+        <v>45</v>
       </c>
       <c r="E141" t="n">
-        <v>50.3</v>
+        <v>18.2</v>
       </c>
       <c r="F141" t="n">
-        <v>11.2</v>
+        <v>45</v>
       </c>
       <c r="G141" t="n">
-        <v>9.3</v>
+        <v>26.9</v>
       </c>
       <c r="H141" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="I141" t="n">
-        <v>49.1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>10.9</v>
+        <v>25</v>
       </c>
       <c r="K141" t="n">
-        <v>35.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142">
@@ -6184,34 +6192,34 @@
         <v>157</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C142" t="n">
-        <v>63.2</v>
+        <v>75</v>
       </c>
       <c r="D142" t="n">
-        <v>45</v>
+        <v>12.7</v>
       </c>
       <c r="E142" t="n">
-        <v>18.2</v>
+        <v>62.3</v>
       </c>
       <c r="F142" t="n">
-        <v>45</v>
+        <v>12.7</v>
       </c>
       <c r="G142" t="n">
-        <v>26.9</v>
+        <v>23.8</v>
       </c>
       <c r="H142" t="n">
-        <v>7.7</v>
+        <v>15.7</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="143">
@@ -6219,34 +6227,34 @@
         <v>158</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C143" t="n">
-        <v>75</v>
+        <v>74.6</v>
       </c>
       <c r="D143" t="n">
-        <v>12.7</v>
+        <v>25.3</v>
       </c>
       <c r="E143" t="n">
-        <v>62.3</v>
+        <v>49.3</v>
       </c>
       <c r="F143" t="n">
-        <v>12.7</v>
+        <v>25.3</v>
       </c>
       <c r="G143" t="n">
-        <v>23.8</v>
+        <v>8.6</v>
       </c>
       <c r="H143" t="n">
-        <v>15.7</v>
+        <v>2.4</v>
       </c>
       <c r="I143" t="n">
-        <v>29.6</v>
+        <v>46.4</v>
       </c>
       <c r="J143" t="n">
-        <v>37</v>
+        <v>23.2</v>
       </c>
       <c r="K143" t="n">
-        <v>37</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="144">
@@ -6254,69 +6262,69 @@
         <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C144" t="n">
-        <v>74.6</v>
+        <v>70.5</v>
       </c>
       <c r="D144" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="E144" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F144" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="G144" t="n">
-        <v>8.6</v>
+        <v>37.9</v>
       </c>
       <c r="H144" t="n">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="I144" t="n">
-        <v>46.4</v>
+        <v>52.1</v>
       </c>
       <c r="J144" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="K144" t="n">
-        <v>33.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
+        <v>161</v>
+      </c>
+      <c r="B145" t="s">
         <v>160</v>
       </c>
-      <c r="B145" t="s">
-        <v>161</v>
-      </c>
       <c r="C145" t="n">
-        <v>70.5</v>
+        <v>66.9</v>
       </c>
       <c r="D145" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="E145" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="F145" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="G145" t="n">
-        <v>37.9</v>
+        <v>15.8</v>
       </c>
       <c r="H145" t="n">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="I145" t="n">
-        <v>52.1</v>
+        <v>56.7</v>
       </c>
       <c r="J145" t="n">
-        <v>22.9</v>
+        <v>19.4</v>
       </c>
       <c r="K145" t="n">
-        <v>40.5</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="146">
@@ -6324,34 +6332,34 @@
         <v>162</v>
       </c>
       <c r="B146" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C146" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="D146" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="E146" t="n">
-        <v>45.6</v>
+        <v>47.9</v>
       </c>
       <c r="F146" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="G146" t="n">
-        <v>15.8</v>
+        <v>37.7</v>
       </c>
       <c r="H146" t="n">
-        <v>7.1</v>
+        <v>12.5</v>
       </c>
       <c r="I146" t="n">
-        <v>56.7</v>
+        <v>29.6</v>
       </c>
       <c r="J146" t="n">
-        <v>19.4</v>
+        <v>48.1</v>
       </c>
       <c r="K146" t="n">
-        <v>41.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="147">
@@ -6359,34 +6367,34 @@
         <v>163</v>
       </c>
       <c r="B147" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C147" t="n">
-        <v>64.6</v>
+        <v>59</v>
       </c>
       <c r="D147" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E147" t="n">
-        <v>47.9</v>
+        <v>37.9</v>
       </c>
       <c r="F147" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G147" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="H147" t="n">
         <v>12.5</v>
       </c>
       <c r="I147" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="J147" t="n">
-        <v>48.1</v>
+        <v>36.8</v>
       </c>
       <c r="K147" t="n">
-        <v>38.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="148">
@@ -6394,34 +6402,34 @@
         <v>164</v>
       </c>
       <c r="B148" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C148" t="n">
-        <v>59</v>
+        <v>65.9</v>
       </c>
       <c r="D148" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="E148" t="n">
-        <v>37.9</v>
+        <v>50.4</v>
       </c>
       <c r="F148" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="G148" t="n">
-        <v>34.5</v>
+        <v>9.8</v>
       </c>
       <c r="H148" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="I148" t="n">
-        <v>31.6</v>
+        <v>63.9</v>
       </c>
       <c r="J148" t="n">
-        <v>36.8</v>
+        <v>18.1</v>
       </c>
       <c r="K148" t="n">
-        <v>29.4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149">
@@ -6429,34 +6437,34 @@
         <v>165</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C149" t="n">
-        <v>65.9</v>
+        <v>80</v>
       </c>
       <c r="D149" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E149" t="n">
-        <v>50.4</v>
+        <v>64</v>
       </c>
       <c r="F149" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G149" t="n">
-        <v>9.8</v>
+        <v>23.3</v>
       </c>
       <c r="H149" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="I149" t="n">
-        <v>63.9</v>
+        <v>38</v>
       </c>
       <c r="J149" t="n">
-        <v>18.1</v>
+        <v>32.9</v>
       </c>
       <c r="K149" t="n">
-        <v>38</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="150">
@@ -6464,34 +6472,34 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C150" t="n">
-        <v>80</v>
+        <v>55.2</v>
       </c>
       <c r="D150" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="E150" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="F150" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="G150" t="n">
-        <v>23.3</v>
+        <v>28.6</v>
       </c>
       <c r="H150" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="I150" t="n">
-        <v>38</v>
+        <v>52.3</v>
       </c>
       <c r="J150" t="n">
-        <v>32.9</v>
+        <v>25</v>
       </c>
       <c r="K150" t="n">
-        <v>47.3</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="151">
@@ -6499,34 +6507,34 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C151" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="D151" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>36.9</v>
+        <v>75</v>
       </c>
       <c r="F151" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>28.6</v>
+        <v>66.7</v>
       </c>
       <c r="H151" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>52.3</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6534,34 +6542,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C152" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E152" t="n">
-        <v>75</v>
+        <v>37.7</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="G152" t="n">
-        <v>66.7</v>
+        <v>13.6</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>17.4</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>36.1</v>
       </c>
       <c r="J152" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="153">
@@ -6569,34 +6577,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C153" t="n">
-        <v>56.2</v>
+        <v>61.3</v>
       </c>
       <c r="D153" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="E153" t="n">
-        <v>37.7</v>
+        <v>40.6</v>
       </c>
       <c r="F153" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="G153" t="n">
-        <v>13.6</v>
+        <v>9.9</v>
       </c>
       <c r="H153" t="n">
-        <v>17.4</v>
+        <v>7.9</v>
       </c>
       <c r="I153" t="n">
-        <v>36.1</v>
+        <v>60.2</v>
       </c>
       <c r="J153" t="n">
-        <v>31.1</v>
+        <v>17.3</v>
       </c>
       <c r="K153" t="n">
-        <v>46.4</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="154">
@@ -6604,34 +6612,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C154" t="n">
-        <v>61.3</v>
+        <v>71.2</v>
       </c>
       <c r="D154" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="E154" t="n">
-        <v>40.6</v>
+        <v>54.6</v>
       </c>
       <c r="F154" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="G154" t="n">
-        <v>9.9</v>
+        <v>24.2</v>
       </c>
       <c r="H154" t="n">
-        <v>7.9</v>
+        <v>12.5</v>
       </c>
       <c r="I154" t="n">
-        <v>60.2</v>
+        <v>37.2</v>
       </c>
       <c r="J154" t="n">
-        <v>17.3</v>
+        <v>32.1</v>
       </c>
       <c r="K154" t="n">
-        <v>29.8</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="155">
@@ -6639,34 +6647,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C155" t="n">
-        <v>71.2</v>
+        <v>78</v>
       </c>
       <c r="D155" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="E155" t="n">
-        <v>54.6</v>
+        <v>47.3</v>
       </c>
       <c r="F155" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="G155" t="n">
-        <v>24.2</v>
+        <v>39.4</v>
       </c>
       <c r="H155" t="n">
-        <v>12.5</v>
+        <v>8</v>
       </c>
       <c r="I155" t="n">
-        <v>37.2</v>
+        <v>36.4</v>
       </c>
       <c r="J155" t="n">
-        <v>32.1</v>
+        <v>22.7</v>
       </c>
       <c r="K155" t="n">
-        <v>57.1</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="156">
@@ -6674,34 +6682,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C156" t="n">
-        <v>78</v>
+        <v>73.6</v>
       </c>
       <c r="D156" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="E156" t="n">
-        <v>47.3</v>
+        <v>53.6</v>
       </c>
       <c r="F156" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="G156" t="n">
-        <v>39.4</v>
+        <v>18</v>
       </c>
       <c r="H156" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="I156" t="n">
-        <v>36.4</v>
+        <v>30.3</v>
       </c>
       <c r="J156" t="n">
-        <v>22.7</v>
+        <v>30.3</v>
       </c>
       <c r="K156" t="n">
-        <v>68.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="157">
@@ -6709,57 +6717,51 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>73.6</v>
+        <v>37.5</v>
       </c>
       <c r="D157" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E157" t="n">
-        <v>53.6</v>
+        <v>4.2</v>
       </c>
       <c r="F157" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G157" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="I157" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="J157" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="K157" t="n">
-        <v>47.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I157"/>
+      <c r="J157"/>
+      <c r="K157"/>
     </row>
     <row r="158">
       <c r="A158" t="s">
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C158" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
         <v>33.3</v>
       </c>
       <c r="E158" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F158" t="n">
         <v>33.3</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -6769,64 +6771,35 @@
       <c r="K158"/>
     </row>
     <row r="159">
-      <c r="A159" t="s">
+      <c r="A159"/>
+      <c r="B159" t="s">
         <v>175</v>
       </c>
-      <c r="B159" t="s">
-        <v>161</v>
-      </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="D159" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="E159" t="n">
-        <v>-33.3</v>
+        <v>46.7</v>
       </c>
       <c r="F159" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="G159" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="H159" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159"/>
-      <c r="J159"/>
-      <c r="K159"/>
-    </row>
-    <row r="160">
-      <c r="A160"/>
-      <c r="B160" t="s">
-        <v>176</v>
-      </c>
-      <c r="C160" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="D160" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E160" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="I159" t="n">
         <v>46.7</v>
       </c>
-      <c r="F160" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G160" t="n">
-        <v>26</v>
-      </c>
-      <c r="H160" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I160" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="J160" t="n">
+      <c r="J159" t="n">
         <v>25.3</v>
       </c>
-      <c r="K160" t="n">
+      <c r="K159" t="n">
         <v>38.5</v>
       </c>
     </row>
@@ -6859,22 +6832,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -6883,18 +6856,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -6929,7 +6902,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -6999,7 +6972,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7034,7 +7007,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7069,7 +7042,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7104,7 +7077,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7139,7 +7112,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7209,7 +7182,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7244,7 +7217,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7279,7 +7252,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7314,7 +7287,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7382,7 +7355,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7417,7 +7390,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7452,7 +7425,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7522,7 +7495,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s">
         <v>34</v>
@@ -7557,7 +7530,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
@@ -7592,7 +7565,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s">
         <v>34</v>
@@ -7627,7 +7600,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B23" t="s">
         <v>34</v>
@@ -7662,7 +7635,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s">
         <v>34</v>
@@ -7697,7 +7670,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B25" t="s">
         <v>34</v>
@@ -7732,7 +7705,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B26" t="s">
         <v>34</v>
@@ -7767,7 +7740,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s">
         <v>34</v>
@@ -7802,7 +7775,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B28" t="s">
         <v>34</v>
@@ -7837,7 +7810,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B29" t="s">
         <v>34</v>
@@ -7872,7 +7845,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s">
         <v>34</v>
@@ -7907,7 +7880,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
         <v>34</v>
@@ -7942,7 +7915,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B32" t="s">
         <v>51</v>
@@ -7977,7 +7950,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
         <v>51</v>
@@ -8012,7 +7985,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B34" t="s">
         <v>51</v>
@@ -8045,7 +8018,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B35" t="s">
         <v>51</v>
@@ -8115,7 +8088,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
         <v>51</v>
@@ -8150,7 +8123,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B38" t="s">
         <v>51</v>
@@ -8185,7 +8158,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B39" t="s">
         <v>51</v>
@@ -8220,7 +8193,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s">
         <v>51</v>
@@ -8253,7 +8226,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B41" t="s">
         <v>51</v>
@@ -8288,7 +8261,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B42" t="s">
         <v>51</v>
@@ -8323,7 +8296,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
         <v>51</v>
@@ -8358,7 +8331,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B44" t="s">
         <v>51</v>
@@ -8393,7 +8366,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B45" t="s">
         <v>51</v>
@@ -8428,7 +8401,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B46" t="s">
         <v>51</v>
@@ -8463,7 +8436,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B47" t="s">
         <v>51</v>
@@ -8498,7 +8471,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
         <v>51</v>
@@ -8531,7 +8504,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B49" t="s">
         <v>51</v>
@@ -8566,7 +8539,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B50" t="s">
         <v>69</v>
@@ -8601,7 +8574,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
         <v>69</v>
@@ -8636,7 +8609,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
         <v>69</v>
@@ -8671,7 +8644,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s">
         <v>69</v>
@@ -8704,7 +8677,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
         <v>69</v>
@@ -8739,7 +8712,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
         <v>69</v>
@@ -8774,2722 +8747,2689 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B56" t="s">
         <v>69</v>
       </c>
       <c r="C56" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="D56" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="E56"/>
+        <v>59.4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>12</v>
+      </c>
       <c r="F56" t="n">
-        <v>50</v>
+        <v>64.3</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>20</v>
+        <v>46.9</v>
       </c>
       <c r="K56" t="n">
-        <v>33.3</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
         <v>69</v>
       </c>
       <c r="C57" t="n">
-        <v>65.2</v>
+        <v>61.7</v>
       </c>
       <c r="D57" t="n">
-        <v>58.7</v>
+        <v>63.1</v>
       </c>
       <c r="E57" t="n">
-        <v>12</v>
+        <v>23.4</v>
       </c>
       <c r="F57" t="n">
-        <v>66.7</v>
+        <v>34</v>
       </c>
       <c r="G57" t="n">
-        <v>19</v>
+        <v>8.1</v>
       </c>
       <c r="H57" t="n">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J57" t="n">
-        <v>50</v>
+        <v>15.7</v>
       </c>
       <c r="K57" t="n">
-        <v>19.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B58" t="s">
         <v>69</v>
       </c>
       <c r="C58" t="n">
-        <v>61.7</v>
+        <v>60.3</v>
       </c>
       <c r="D58" t="n">
-        <v>63.1</v>
+        <v>63.8</v>
       </c>
       <c r="E58" t="n">
-        <v>23.4</v>
+        <v>18.5</v>
       </c>
       <c r="F58" t="n">
-        <v>34</v>
+        <v>43.2</v>
       </c>
       <c r="G58" t="n">
-        <v>8.1</v>
+        <v>6.8</v>
       </c>
       <c r="H58" t="n">
-        <v>34.6</v>
+        <v>62.5</v>
       </c>
       <c r="I58" t="n">
         <v>4.1</v>
       </c>
       <c r="J58" t="n">
-        <v>15.7</v>
+        <v>33.6</v>
       </c>
       <c r="K58" t="n">
-        <v>4.1</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B59" t="s">
         <v>69</v>
       </c>
       <c r="C59" t="n">
-        <v>60.3</v>
+        <v>56.5</v>
       </c>
       <c r="D59" t="n">
-        <v>63.8</v>
+        <v>61.6</v>
       </c>
       <c r="E59" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="F59" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="G59" t="n">
-        <v>6.8</v>
+        <v>8.7</v>
       </c>
       <c r="H59" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
       <c r="I59" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J59" t="n">
-        <v>33.6</v>
+        <v>23.8</v>
       </c>
       <c r="K59" t="n">
-        <v>14.8</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B60" t="s">
         <v>69</v>
       </c>
       <c r="C60" t="n">
-        <v>56.5</v>
+        <v>65.7</v>
       </c>
       <c r="D60" t="n">
-        <v>61.6</v>
+        <v>66.9</v>
       </c>
       <c r="E60" t="n">
-        <v>6.5</v>
+        <v>29.4</v>
       </c>
       <c r="F60" t="n">
-        <v>42.9</v>
+        <v>33.9</v>
       </c>
       <c r="G60" t="n">
-        <v>8.7</v>
+        <v>5</v>
       </c>
       <c r="H60" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="I60" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J60" t="n">
-        <v>23.8</v>
+        <v>19.6</v>
       </c>
       <c r="K60" t="n">
-        <v>10.9</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B61" t="s">
         <v>69</v>
       </c>
       <c r="C61" t="n">
-        <v>65.7</v>
+        <v>63.8</v>
       </c>
       <c r="D61" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="E61" t="n">
-        <v>29.4</v>
+        <v>33.3</v>
       </c>
       <c r="F61" t="n">
-        <v>33.9</v>
+        <v>38.1</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H61" t="n">
-        <v>55.8</v>
+        <v>19.4</v>
       </c>
       <c r="I61" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>19.6</v>
+        <v>20.5</v>
       </c>
       <c r="K61" t="n">
-        <v>9.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>236</v>
+        <v>85</v>
       </c>
       <c r="B62" t="s">
         <v>69</v>
       </c>
       <c r="C62" t="n">
-        <v>63.8</v>
+        <v>30</v>
       </c>
       <c r="D62" t="n">
-        <v>64.6</v>
+        <v>60.6</v>
       </c>
       <c r="E62" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="F62" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>19.4</v>
+        <v>25</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J62" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>235</v>
       </c>
       <c r="B63" t="s">
         <v>69</v>
       </c>
       <c r="C63" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D63" t="n">
-        <v>60.6</v>
+        <v>51.9</v>
       </c>
       <c r="E63" t="n">
+        <v>25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G63" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H63" t="n">
         <v>46.7</v>
       </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>25</v>
-      </c>
       <c r="I63" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>237</v>
+        <v>87</v>
       </c>
       <c r="B64" t="s">
         <v>69</v>
       </c>
       <c r="C64" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D64" t="n">
-        <v>51.9</v>
+        <v>57.1</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F64" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>46.7</v>
+        <v>20</v>
       </c>
       <c r="I64" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="J64" t="n">
-        <v>32.5</v>
+        <v>14.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>236</v>
       </c>
       <c r="B65" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>69.5</v>
       </c>
       <c r="D65" t="n">
-        <v>57.1</v>
+        <v>68.7</v>
       </c>
       <c r="E65" t="n">
-        <v>37.5</v>
+        <v>18</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>48.3</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H65" t="n">
-        <v>20</v>
+        <v>54.3</v>
       </c>
       <c r="I65" t="n">
-        <v>40</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
-        <v>14.3</v>
+        <v>24.4</v>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C66" t="n">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="D66" t="n">
-        <v>68.7</v>
+        <v>67.1</v>
       </c>
       <c r="E66" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="F66" t="n">
-        <v>48.3</v>
+        <v>33.3</v>
       </c>
       <c r="G66" t="n">
         <v>3.4</v>
       </c>
       <c r="H66" t="n">
-        <v>54.3</v>
+        <v>36.4</v>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="J66" t="n">
-        <v>24.4</v>
+        <v>7.5</v>
       </c>
       <c r="K66" t="n">
-        <v>20.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C67" t="n">
-        <v>69</v>
+        <v>46.2</v>
       </c>
       <c r="D67" t="n">
-        <v>67.1</v>
+        <v>65.2</v>
       </c>
       <c r="E67" t="n">
-        <v>17.9</v>
+        <v>31.8</v>
       </c>
       <c r="F67" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="G67" t="n">
-        <v>3.4</v>
+        <v>15.4</v>
       </c>
       <c r="H67" t="n">
-        <v>36.4</v>
+        <v>44.4</v>
       </c>
       <c r="I67" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="K67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C68" t="n">
-        <v>46.2</v>
+        <v>56.4</v>
       </c>
       <c r="D68" t="n">
-        <v>65.2</v>
+        <v>61.5</v>
       </c>
       <c r="E68" t="n">
-        <v>31.8</v>
+        <v>20.5</v>
       </c>
       <c r="F68" t="n">
-        <v>28.6</v>
+        <v>40</v>
       </c>
       <c r="G68" t="n">
-        <v>15.4</v>
+        <v>12.8</v>
       </c>
       <c r="H68" t="n">
-        <v>44.4</v>
+        <v>48</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>19.3</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69" t="n">
-        <v>56.4</v>
+        <v>64.7</v>
       </c>
       <c r="D69" t="n">
-        <v>61.5</v>
+        <v>65.1</v>
       </c>
       <c r="E69" t="n">
-        <v>20.5</v>
+        <v>37.5</v>
       </c>
       <c r="F69" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="G69" t="n">
-        <v>12.8</v>
+        <v>14.7</v>
       </c>
       <c r="H69" t="n">
-        <v>48</v>
+        <v>52.9</v>
       </c>
       <c r="I69" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>19.3</v>
+        <v>28.9</v>
       </c>
       <c r="K69" t="n">
-        <v>2.6</v>
+        <v>8.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C70" t="n">
-        <v>64.7</v>
+        <v>61.1</v>
       </c>
       <c r="D70" t="n">
-        <v>65.1</v>
+        <v>63</v>
       </c>
       <c r="E70" t="n">
-        <v>37.5</v>
+        <v>17.6</v>
       </c>
       <c r="F70" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="G70" t="n">
-        <v>14.7</v>
+        <v>7.1</v>
       </c>
       <c r="H70" t="n">
-        <v>52.9</v>
+        <v>56.5</v>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J70" t="n">
-        <v>28.9</v>
+        <v>36.2</v>
       </c>
       <c r="K70" t="n">
-        <v>8.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C71" t="n">
-        <v>61.1</v>
+        <v>67</v>
       </c>
       <c r="D71" t="n">
-        <v>63</v>
+        <v>60.6</v>
       </c>
       <c r="E71" t="n">
-        <v>17.6</v>
+        <v>29</v>
       </c>
       <c r="F71" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G71" t="n">
-        <v>7.1</v>
+        <v>9</v>
       </c>
       <c r="H71" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>36.2</v>
+        <v>41.7</v>
       </c>
       <c r="K71" t="n">
-        <v>22.1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C72" t="n">
-        <v>67</v>
+        <v>57.1</v>
       </c>
       <c r="D72" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="E72" t="n">
-        <v>29</v>
+        <v>34.5</v>
       </c>
       <c r="F72" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G72" t="n">
-        <v>9</v>
+        <v>7.1</v>
       </c>
       <c r="H72" t="n">
-        <v>58.1</v>
+        <v>47.8</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
-        <v>41.7</v>
+        <v>22.7</v>
       </c>
       <c r="K72" t="n">
-        <v>27</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C73" t="n">
-        <v>57.1</v>
+        <v>72.7</v>
       </c>
       <c r="D73" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="E73" t="n">
-        <v>34.5</v>
+        <v>21.7</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>38.5</v>
       </c>
       <c r="G73" t="n">
-        <v>7.1</v>
+        <v>13.6</v>
       </c>
       <c r="H73" t="n">
-        <v>47.8</v>
+        <v>46.2</v>
       </c>
       <c r="I73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>22.7</v>
+        <v>30.6</v>
       </c>
       <c r="K73" t="n">
-        <v>3.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C74" t="n">
-        <v>72.7</v>
+        <v>68.3</v>
       </c>
       <c r="D74" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E74" t="n">
-        <v>21.7</v>
+        <v>26.9</v>
       </c>
       <c r="F74" t="n">
         <v>38.5</v>
       </c>
       <c r="G74" t="n">
-        <v>13.6</v>
+        <v>7.3</v>
       </c>
       <c r="H74" t="n">
-        <v>46.2</v>
+        <v>56.7</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J74" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="K74" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C75" t="n">
-        <v>68.3</v>
+        <v>60.1</v>
       </c>
       <c r="D75" t="n">
-        <v>69</v>
+        <v>62.7</v>
       </c>
       <c r="E75" t="n">
-        <v>26.9</v>
+        <v>25.7</v>
       </c>
       <c r="F75" t="n">
-        <v>38.5</v>
+        <v>55.2</v>
       </c>
       <c r="G75" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="H75" t="n">
-        <v>56.7</v>
+        <v>37.6</v>
       </c>
       <c r="I75" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="J75" t="n">
-        <v>25</v>
+        <v>30.1</v>
       </c>
       <c r="K75" t="n">
-        <v>11</v>
+        <v>18.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C76" t="n">
-        <v>60.1</v>
+        <v>64.5</v>
       </c>
       <c r="D76" t="n">
-        <v>62.7</v>
+        <v>64.8</v>
       </c>
       <c r="E76" t="n">
-        <v>25.7</v>
+        <v>25</v>
       </c>
       <c r="F76" t="n">
-        <v>55.2</v>
+        <v>30.8</v>
       </c>
       <c r="G76" t="n">
-        <v>7.9</v>
+        <v>9.4</v>
       </c>
       <c r="H76" t="n">
-        <v>37.6</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="J76" t="n">
-        <v>30.1</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>18.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="C77" t="n">
-        <v>64.5</v>
+        <v>42</v>
       </c>
       <c r="D77" t="n">
-        <v>64.8</v>
+        <v>44.7</v>
       </c>
       <c r="E77" t="n">
-        <v>25</v>
+        <v>6.3</v>
       </c>
       <c r="F77" t="n">
-        <v>30.8</v>
+        <v>46.4</v>
       </c>
       <c r="G77" t="n">
-        <v>9.4</v>
+        <v>31.9</v>
       </c>
       <c r="H77" t="n">
-        <v>40</v>
+        <v>41.4</v>
       </c>
       <c r="I77" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J77" t="n">
-        <v>20</v>
+        <v>30.4</v>
       </c>
       <c r="K77" t="n">
-        <v>3.1</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C78" t="n">
-        <v>42</v>
+        <v>67.9</v>
       </c>
       <c r="D78" t="n">
-        <v>44.7</v>
+        <v>63.4</v>
       </c>
       <c r="E78" t="n">
-        <v>6.3</v>
+        <v>26</v>
       </c>
       <c r="F78" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="G78" t="n">
-        <v>31.9</v>
+        <v>10.5</v>
       </c>
       <c r="H78" t="n">
-        <v>41.4</v>
+        <v>53.7</v>
       </c>
       <c r="I78" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J78" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="K78" t="n">
-        <v>-13.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C79" t="n">
-        <v>67.9</v>
+        <v>50</v>
       </c>
       <c r="D79" t="n">
-        <v>63.4</v>
+        <v>53.5</v>
       </c>
       <c r="E79" t="n">
-        <v>26</v>
+        <v>10.1</v>
       </c>
       <c r="F79" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="G79" t="n">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
       <c r="H79" t="n">
-        <v>53.7</v>
+        <v>38.5</v>
       </c>
       <c r="I79" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J79" t="n">
-        <v>29.9</v>
+        <v>22.1</v>
       </c>
       <c r="K79" t="n">
-        <v>12.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>186</v>
+        <v>250</v>
       </c>
       <c r="B80" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C80" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="D80" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="E80" t="n">
-        <v>10.1</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E80"/>
       <c r="F80" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>13.6</v>
+        <v>42.9</v>
       </c>
       <c r="H80" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="I80" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>22.1</v>
+        <v>14.3</v>
       </c>
       <c r="K80" t="n">
-        <v>6.1</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B81" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C81" t="n">
-        <v>28.6</v>
+        <v>68.8</v>
       </c>
       <c r="D81" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E81"/>
+        <v>64.9</v>
+      </c>
+      <c r="E81" t="n">
+        <v>22.2</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G81" t="n">
-        <v>42.9</v>
+        <v>18.8</v>
       </c>
       <c r="H81" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K81" t="n">
-        <v>-42.9</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C82" t="n">
-        <v>68.8</v>
+        <v>48.6</v>
       </c>
       <c r="D82" t="n">
-        <v>64.9</v>
+        <v>56.4</v>
       </c>
       <c r="E82" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="F82" t="n">
-        <v>25</v>
+        <v>41.5</v>
       </c>
       <c r="G82" t="n">
-        <v>18.8</v>
+        <v>14.9</v>
       </c>
       <c r="H82" t="n">
-        <v>50</v>
+        <v>32.6</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J82" t="n">
-        <v>21.4</v>
+        <v>33.6</v>
       </c>
       <c r="K82" t="n">
-        <v>-6.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>107</v>
       </c>
       <c r="B83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C83" t="n">
-        <v>48.6</v>
+        <v>57.9</v>
       </c>
       <c r="D83" t="n">
-        <v>56.4</v>
+        <v>58.5</v>
       </c>
       <c r="E83" t="n">
-        <v>22.6</v>
+        <v>19.1</v>
       </c>
       <c r="F83" t="n">
-        <v>41.5</v>
+        <v>23.3</v>
       </c>
       <c r="G83" t="n">
-        <v>14.9</v>
+        <v>6.9</v>
       </c>
       <c r="H83" t="n">
-        <v>32.6</v>
+        <v>39.5</v>
       </c>
       <c r="I83" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="J83" t="n">
-        <v>33.6</v>
+        <v>22</v>
       </c>
       <c r="K83" t="n">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>108</v>
+        <v>253</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C84" t="n">
-        <v>57.9</v>
+        <v>71.4</v>
       </c>
       <c r="D84" t="n">
-        <v>58.5</v>
+        <v>70.6</v>
       </c>
       <c r="E84" t="n">
-        <v>19.1</v>
+        <v>22.2</v>
       </c>
       <c r="F84" t="n">
-        <v>23.3</v>
+        <v>28.6</v>
       </c>
       <c r="G84" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H84" t="n">
-        <v>39.5</v>
+        <v>45.5</v>
       </c>
       <c r="I84" t="n">
-        <v>5.2</v>
+        <v>7.1</v>
       </c>
       <c r="J84" t="n">
-        <v>22</v>
+        <v>10.7</v>
       </c>
       <c r="K84" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>255</v>
+        <v>213</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C85" t="n">
-        <v>71.4</v>
+        <v>62.9</v>
       </c>
       <c r="D85" t="n">
-        <v>70.6</v>
+        <v>66.7</v>
       </c>
       <c r="E85" t="n">
-        <v>22.2</v>
+        <v>27.9</v>
       </c>
       <c r="F85" t="n">
-        <v>28.6</v>
+        <v>39</v>
       </c>
       <c r="G85" t="n">
-        <v>7.1</v>
+        <v>5.1</v>
       </c>
       <c r="H85" t="n">
-        <v>45.5</v>
+        <v>41.8</v>
       </c>
       <c r="I85" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="J85" t="n">
-        <v>10.7</v>
+        <v>22.3</v>
       </c>
       <c r="K85" t="n">
-        <v>7.2</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="B86" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C86" t="n">
-        <v>62.9</v>
+        <v>54.5</v>
       </c>
       <c r="D86" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="E86" t="n">
-        <v>27.9</v>
+        <v>10.4</v>
       </c>
       <c r="F86" t="n">
-        <v>39</v>
+        <v>29.4</v>
       </c>
       <c r="G86" t="n">
-        <v>5.1</v>
+        <v>15.2</v>
       </c>
       <c r="H86" t="n">
-        <v>41.8</v>
+        <v>45</v>
       </c>
       <c r="I86" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J86" t="n">
-        <v>22.3</v>
+        <v>26.6</v>
       </c>
       <c r="K86" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C87" t="n">
-        <v>54.5</v>
+        <v>67.3</v>
       </c>
       <c r="D87" t="n">
-        <v>55.6</v>
+        <v>65.4</v>
       </c>
       <c r="E87" t="n">
-        <v>10.4</v>
+        <v>27.7</v>
       </c>
       <c r="F87" t="n">
-        <v>29.4</v>
+        <v>39.3</v>
       </c>
       <c r="G87" t="n">
-        <v>15.2</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
-        <v>45</v>
+        <v>46.7</v>
       </c>
       <c r="I87" t="n">
-        <v>6.1</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
-        <v>26.6</v>
+        <v>29</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C88" t="n">
-        <v>67.3</v>
+        <v>69.2</v>
       </c>
       <c r="D88" t="n">
-        <v>65.4</v>
+        <v>61.2</v>
       </c>
       <c r="E88" t="n">
-        <v>27.7</v>
+        <v>14</v>
       </c>
       <c r="F88" t="n">
-        <v>39.3</v>
+        <v>42.9</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="H88" t="n">
-        <v>46.7</v>
+        <v>61.5</v>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>29</v>
+        <v>26.3</v>
       </c>
       <c r="K88" t="n">
-        <v>10.8</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B89" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C89" t="n">
-        <v>69.2</v>
+        <v>52.6</v>
       </c>
       <c r="D89" t="n">
-        <v>61.2</v>
+        <v>55.8</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>25.6</v>
       </c>
       <c r="F89" t="n">
-        <v>42.9</v>
+        <v>37.9</v>
       </c>
       <c r="G89" t="n">
-        <v>11.5</v>
+        <v>12.4</v>
       </c>
       <c r="H89" t="n">
-        <v>61.5</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J89" t="n">
-        <v>26.3</v>
+        <v>24.9</v>
       </c>
       <c r="K89" t="n">
-        <v>11.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B90" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C90" t="n">
-        <v>52.6</v>
+        <v>75</v>
       </c>
       <c r="D90" t="n">
-        <v>55.8</v>
+        <v>65</v>
       </c>
       <c r="E90" t="n">
-        <v>25.6</v>
+        <v>12.1</v>
       </c>
       <c r="F90" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="G90" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>30</v>
+        <v>53.8</v>
       </c>
       <c r="I90" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J90" t="n">
-        <v>24.9</v>
+        <v>26.9</v>
       </c>
       <c r="K90" t="n">
-        <v>3.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C91" t="n">
-        <v>75</v>
+        <v>55.2</v>
       </c>
       <c r="D91" t="n">
-        <v>65</v>
+        <v>61.1</v>
       </c>
       <c r="E91" t="n">
-        <v>12.1</v>
+        <v>23.4</v>
       </c>
       <c r="F91" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H91" t="n">
-        <v>53.8</v>
+        <v>50.7</v>
       </c>
       <c r="I91" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J91" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="K91" t="n">
-        <v>18.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C92" t="n">
-        <v>55.2</v>
+        <v>74.2</v>
       </c>
       <c r="D92" t="n">
-        <v>61.1</v>
+        <v>69.7</v>
       </c>
       <c r="E92" t="n">
-        <v>23.4</v>
+        <v>39.1</v>
       </c>
       <c r="F92" t="n">
-        <v>38.3</v>
+        <v>33.3</v>
       </c>
       <c r="G92" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="H92" t="n">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="I92" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="K92" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C93" t="n">
-        <v>74.2</v>
+        <v>61.9</v>
       </c>
       <c r="D93" t="n">
-        <v>69.7</v>
+        <v>57.3</v>
       </c>
       <c r="E93" t="n">
-        <v>39.1</v>
+        <v>15.4</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="G93" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="H93" t="n">
-        <v>52.2</v>
+        <v>39.3</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J93" t="n">
-        <v>22.9</v>
+        <v>32.4</v>
       </c>
       <c r="K93" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C94" t="n">
-        <v>61.9</v>
+        <v>57.5</v>
       </c>
       <c r="D94" t="n">
-        <v>57.3</v>
+        <v>64.6</v>
       </c>
       <c r="E94" t="n">
-        <v>15.4</v>
+        <v>30</v>
       </c>
       <c r="F94" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="G94" t="n">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="H94" t="n">
-        <v>39.3</v>
+        <v>50</v>
       </c>
       <c r="I94" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J94" t="n">
-        <v>32.4</v>
+        <v>21.8</v>
       </c>
       <c r="K94" t="n">
-        <v>4.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C95" t="n">
-        <v>57.5</v>
+        <v>59.7</v>
       </c>
       <c r="D95" t="n">
-        <v>64.6</v>
+        <v>64.4</v>
       </c>
       <c r="E95" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
       <c r="F95" t="n">
-        <v>40.8</v>
+        <v>48.6</v>
       </c>
       <c r="G95" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
-        <v>21.8</v>
+        <v>31.2</v>
       </c>
       <c r="K95" t="n">
-        <v>8.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C96" t="n">
-        <v>59.7</v>
+        <v>65.3</v>
       </c>
       <c r="D96" t="n">
-        <v>64.4</v>
+        <v>67.2</v>
       </c>
       <c r="E96" t="n">
-        <v>32.3</v>
+        <v>33.8</v>
       </c>
       <c r="F96" t="n">
-        <v>48.6</v>
+        <v>64</v>
       </c>
       <c r="G96" t="n">
-        <v>11.9</v>
+        <v>6.1</v>
       </c>
       <c r="H96" t="n">
-        <v>59</v>
+        <v>55.2</v>
       </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="K96" t="n">
-        <v>15</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C97" t="n">
-        <v>65.3</v>
+        <v>60.6</v>
       </c>
       <c r="D97" t="n">
-        <v>67.2</v>
+        <v>64.6</v>
       </c>
       <c r="E97" t="n">
-        <v>33.8</v>
+        <v>21.7</v>
       </c>
       <c r="F97" t="n">
-        <v>64</v>
+        <v>25.7</v>
       </c>
       <c r="G97" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H97" t="n">
-        <v>55.2</v>
+        <v>67.9</v>
       </c>
       <c r="I97" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
-        <v>31.8</v>
+        <v>19.3</v>
       </c>
       <c r="K97" t="n">
-        <v>26.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C98" t="n">
-        <v>60.6</v>
+        <v>72.2</v>
       </c>
       <c r="D98" t="n">
-        <v>64.6</v>
+        <v>67.9</v>
       </c>
       <c r="E98" t="n">
-        <v>21.7</v>
+        <v>34.3</v>
       </c>
       <c r="F98" t="n">
-        <v>25.7</v>
+        <v>50</v>
       </c>
       <c r="G98" t="n">
-        <v>5.9</v>
+        <v>11.1</v>
       </c>
       <c r="H98" t="n">
-        <v>67.9</v>
+        <v>50</v>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J98" t="n">
-        <v>19.3</v>
+        <v>38.7</v>
       </c>
       <c r="K98" t="n">
-        <v>7.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" t="n">
-        <v>72.2</v>
+        <v>66.3</v>
       </c>
       <c r="D99" t="n">
-        <v>67.9</v>
+        <v>65.8</v>
       </c>
       <c r="E99" t="n">
-        <v>34.3</v>
+        <v>23.1</v>
       </c>
       <c r="F99" t="n">
-        <v>50</v>
+        <v>37.2</v>
       </c>
       <c r="G99" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="I99" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
-        <v>38.7</v>
+        <v>21.5</v>
       </c>
       <c r="K99" t="n">
-        <v>16.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C100" t="n">
-        <v>66.3</v>
+        <v>67.6</v>
       </c>
       <c r="D100" t="n">
-        <v>65.8</v>
+        <v>70.2</v>
       </c>
       <c r="E100" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="F100" t="n">
-        <v>37.2</v>
+        <v>48</v>
       </c>
       <c r="G100" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="H100" t="n">
-        <v>41.3</v>
+        <v>44</v>
       </c>
       <c r="I100" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="K100" t="n">
-        <v>6.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C101" t="n">
-        <v>67.6</v>
+        <v>64.4</v>
       </c>
       <c r="D101" t="n">
-        <v>70.2</v>
+        <v>61.4</v>
       </c>
       <c r="E101" t="n">
-        <v>22.7</v>
+        <v>13.4</v>
       </c>
       <c r="F101" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G101" t="n">
-        <v>0.5</v>
+        <v>16.4</v>
       </c>
       <c r="H101" t="n">
-        <v>44</v>
+        <v>32.3</v>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J101" t="n">
-        <v>21.6</v>
+        <v>36.4</v>
       </c>
       <c r="K101" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B102" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="C102" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D102" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E102" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F102" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H102" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J102" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B103" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C103" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="D103" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="E103" t="n">
-        <v>36.4</v>
+        <v>13.5</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G103" t="n">
-        <v>33.3</v>
+        <v>15.6</v>
       </c>
       <c r="H103" t="n">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="I103" t="n">
-        <v>33.3</v>
+        <v>3.1</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>16.3</v>
       </c>
       <c r="K103" t="n">
-        <v>-33.3</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>273</v>
+        <v>140</v>
       </c>
       <c r="B104" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C104" t="n">
-        <v>50</v>
+        <v>51.6</v>
       </c>
       <c r="D104" t="n">
-        <v>54.4</v>
+        <v>58.9</v>
       </c>
       <c r="E104" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="F104" t="n">
-        <v>20</v>
+        <v>40.9</v>
       </c>
       <c r="G104" t="n">
-        <v>15.6</v>
+        <v>12.9</v>
       </c>
       <c r="H104" t="n">
-        <v>40.9</v>
+        <v>44.4</v>
       </c>
       <c r="I104" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
       <c r="J104" t="n">
-        <v>16.3</v>
+        <v>24.4</v>
       </c>
       <c r="K104" t="n">
-        <v>-9.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>141</v>
+        <v>272</v>
       </c>
       <c r="B105" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C105" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D105" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E105" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F105" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G105" t="n">
-        <v>12.9</v>
+        <v>8.3</v>
       </c>
       <c r="H105" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I105" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J105" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K105" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B106" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C106" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D106" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E106" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F106" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F106"/>
       <c r="G106" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="H106" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B107" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C107" t="n">
-        <v>50</v>
+        <v>69.7</v>
       </c>
       <c r="D107" t="n">
-        <v>45.5</v>
+        <v>62.4</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107"/>
+        <v>25</v>
+      </c>
+      <c r="F107" t="n">
+        <v>20</v>
+      </c>
       <c r="G107" t="n">
-        <v>25</v>
+        <v>14.6</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>53.7</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="K107" t="n">
-        <v>-25</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B108" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C108" t="n">
-        <v>69.7</v>
+        <v>54.1</v>
       </c>
       <c r="D108" t="n">
-        <v>62.4</v>
+        <v>61.9</v>
       </c>
       <c r="E108" t="n">
-        <v>25</v>
+        <v>17.2</v>
       </c>
       <c r="F108" t="n">
         <v>20</v>
       </c>
       <c r="G108" t="n">
-        <v>14.6</v>
+        <v>5.4</v>
       </c>
       <c r="H108" t="n">
-        <v>53.7</v>
+        <v>44.8</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>8.1</v>
       </c>
       <c r="J108" t="n">
-        <v>21.9</v>
+        <v>15.6</v>
       </c>
       <c r="K108" t="n">
-        <v>-5.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>277</v>
+        <v>150</v>
       </c>
       <c r="B109" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C109" t="n">
-        <v>54.1</v>
+        <v>51.6</v>
       </c>
       <c r="D109" t="n">
-        <v>61.9</v>
+        <v>59.1</v>
       </c>
       <c r="E109" t="n">
-        <v>17.2</v>
+        <v>31.1</v>
       </c>
       <c r="F109" t="n">
-        <v>20</v>
+        <v>39.4</v>
       </c>
       <c r="G109" t="n">
-        <v>5.4</v>
+        <v>14.3</v>
       </c>
       <c r="H109" t="n">
-        <v>44.8</v>
+        <v>48.5</v>
       </c>
       <c r="I109" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J109" t="n">
-        <v>15.6</v>
+        <v>28</v>
       </c>
       <c r="K109" t="n">
-        <v>2.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>151</v>
+        <v>276</v>
       </c>
       <c r="B110" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C110" t="n">
-        <v>51.6</v>
+        <v>60</v>
       </c>
       <c r="D110" t="n">
-        <v>59.1</v>
+        <v>60.4</v>
       </c>
       <c r="E110" t="n">
-        <v>31.1</v>
+        <v>21</v>
       </c>
       <c r="F110" t="n">
-        <v>39.4</v>
+        <v>26.3</v>
       </c>
       <c r="G110" t="n">
-        <v>14.3</v>
+        <v>11.1</v>
       </c>
       <c r="H110" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="I110" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
       <c r="J110" t="n">
-        <v>28</v>
+        <v>20.9</v>
       </c>
       <c r="K110" t="n">
-        <v>7.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B111" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C111" t="n">
-        <v>60</v>
+        <v>52.6</v>
       </c>
       <c r="D111" t="n">
-        <v>60.4</v>
+        <v>56.2</v>
       </c>
       <c r="E111" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F111" t="n">
-        <v>26.3</v>
+        <v>10</v>
       </c>
       <c r="G111" t="n">
-        <v>11.1</v>
+        <v>15.8</v>
       </c>
       <c r="H111" t="n">
         <v>50</v>
       </c>
       <c r="I111" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J111" t="n">
-        <v>20.9</v>
+        <v>15.2</v>
       </c>
       <c r="K111" t="n">
-        <v>2.8</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B112" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C112" t="n">
-        <v>52.6</v>
+        <v>61.3</v>
       </c>
       <c r="D112" t="n">
-        <v>56.2</v>
+        <v>63.9</v>
       </c>
       <c r="E112" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="F112" t="n">
-        <v>10</v>
+        <v>54.4</v>
       </c>
       <c r="G112" t="n">
-        <v>15.8</v>
+        <v>9</v>
       </c>
       <c r="H112" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="I112" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
-        <v>15.2</v>
+        <v>29.2</v>
       </c>
       <c r="K112" t="n">
-        <v>-10.5</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B113" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C113" t="n">
-        <v>61.3</v>
+        <v>59.7</v>
       </c>
       <c r="D113" t="n">
-        <v>63.9</v>
+        <v>61.8</v>
       </c>
       <c r="E113" t="n">
-        <v>28.5</v>
+        <v>20</v>
       </c>
       <c r="F113" t="n">
-        <v>54.4</v>
+        <v>51.5</v>
       </c>
       <c r="G113" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="H113" t="n">
-        <v>39.1</v>
+        <v>39.4</v>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>29.2</v>
+        <v>34.7</v>
       </c>
       <c r="K113" t="n">
-        <v>18.9</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B114" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C114" t="n">
-        <v>59.7</v>
+        <v>44</v>
       </c>
       <c r="D114" t="n">
-        <v>61.8</v>
+        <v>56.3</v>
       </c>
       <c r="E114" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="F114" t="n">
-        <v>51.5</v>
+        <v>38.5</v>
       </c>
       <c r="G114" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="H114" t="n">
-        <v>39.4</v>
+        <v>50</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J114" t="n">
-        <v>34.7</v>
+        <v>26.5</v>
       </c>
       <c r="K114" t="n">
-        <v>16.1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B115" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C115" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D115" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E115" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F115" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H115" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I115" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J115" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K115" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B116" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C116" t="n">
-        <v>38.9</v>
+        <v>59.2</v>
       </c>
       <c r="D116" t="n">
-        <v>52</v>
+        <v>62.2</v>
       </c>
       <c r="E116" t="n">
-        <v>16.3</v>
+        <v>21.3</v>
       </c>
       <c r="F116" t="n">
-        <v>33.3</v>
+        <v>26.9</v>
       </c>
       <c r="G116" t="n">
-        <v>27.8</v>
+        <v>6.8</v>
       </c>
       <c r="H116" t="n">
-        <v>22.2</v>
+        <v>59.4</v>
       </c>
       <c r="I116" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J116" t="n">
-        <v>31</v>
+        <v>20.5</v>
       </c>
       <c r="K116" t="n">
-        <v>-11.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C117" t="n">
-        <v>59.2</v>
+        <v>57.9</v>
       </c>
       <c r="D117" t="n">
-        <v>62.2</v>
+        <v>59.8</v>
       </c>
       <c r="E117" t="n">
-        <v>21.3</v>
+        <v>24.6</v>
       </c>
       <c r="F117" t="n">
-        <v>26.9</v>
+        <v>38.9</v>
       </c>
       <c r="G117" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H117" t="n">
-        <v>59.4</v>
+        <v>42</v>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>8.6</v>
       </c>
       <c r="J117" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="K117" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B118" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="C118" t="n">
-        <v>57.9</v>
+        <v>70.8</v>
       </c>
       <c r="D118" t="n">
-        <v>59.8</v>
+        <v>64.4</v>
       </c>
       <c r="E118" t="n">
-        <v>24.6</v>
+        <v>27.3</v>
       </c>
       <c r="F118" t="n">
-        <v>38.9</v>
+        <v>63.6</v>
       </c>
       <c r="G118" t="n">
-        <v>6</v>
+        <v>8.3</v>
       </c>
       <c r="H118" t="n">
-        <v>42</v>
+        <v>76.9</v>
       </c>
       <c r="I118" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>18.5</v>
+        <v>28.9</v>
       </c>
       <c r="K118" t="n">
-        <v>7.9</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B119" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C119" t="n">
-        <v>70.8</v>
+        <v>62.4</v>
       </c>
       <c r="D119" t="n">
-        <v>64.4</v>
+        <v>67.5</v>
       </c>
       <c r="E119" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="F119" t="n">
-        <v>63.6</v>
+        <v>44.3</v>
       </c>
       <c r="G119" t="n">
-        <v>8.3</v>
+        <v>2.4</v>
       </c>
       <c r="H119" t="n">
-        <v>76.9</v>
+        <v>48.4</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>28.9</v>
+        <v>20.7</v>
       </c>
       <c r="K119" t="n">
-        <v>20.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B120" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C120" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="D120" t="n">
-        <v>67.5</v>
+        <v>64.8</v>
       </c>
       <c r="E120" t="n">
-        <v>22.6</v>
+        <v>11.2</v>
       </c>
       <c r="F120" t="n">
-        <v>44.3</v>
+        <v>32.4</v>
       </c>
       <c r="G120" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="H120" t="n">
-        <v>48.4</v>
+        <v>29.6</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J120" t="n">
-        <v>20.7</v>
+        <v>19.6</v>
       </c>
       <c r="K120" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B121" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C121" t="n">
-        <v>60.7</v>
+        <v>60.4</v>
       </c>
       <c r="D121" t="n">
-        <v>64.8</v>
+        <v>64.6</v>
       </c>
       <c r="E121" t="n">
-        <v>11.2</v>
+        <v>33.8</v>
       </c>
       <c r="F121" t="n">
-        <v>32.4</v>
+        <v>71.9</v>
       </c>
       <c r="G121" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H121" t="n">
-        <v>29.6</v>
+        <v>50</v>
       </c>
       <c r="I121" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="J121" t="n">
-        <v>19.6</v>
+        <v>43.6</v>
       </c>
       <c r="K121" t="n">
-        <v>5.7</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="B122" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C122" t="n">
-        <v>60.4</v>
+        <v>59.4</v>
       </c>
       <c r="D122" t="n">
-        <v>64.6</v>
+        <v>60.3</v>
       </c>
       <c r="E122" t="n">
-        <v>33.8</v>
+        <v>10.3</v>
       </c>
       <c r="F122" t="n">
-        <v>71.9</v>
+        <v>29</v>
       </c>
       <c r="G122" t="n">
-        <v>6.4</v>
+        <v>8.8</v>
       </c>
       <c r="H122" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I122" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J122" t="n">
-        <v>43.6</v>
+        <v>22.6</v>
       </c>
       <c r="K122" t="n">
-        <v>44.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>213</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C123" t="n">
-        <v>59.4</v>
+        <v>67.3</v>
       </c>
       <c r="D123" t="n">
-        <v>60.3</v>
+        <v>63.7</v>
       </c>
       <c r="E123" t="n">
-        <v>10.3</v>
+        <v>28.4</v>
       </c>
       <c r="F123" t="n">
-        <v>29</v>
+        <v>45.9</v>
       </c>
       <c r="G123" t="n">
-        <v>8.8</v>
+        <v>7.3</v>
       </c>
       <c r="H123" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
       <c r="I123" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="J123" t="n">
-        <v>22.6</v>
+        <v>46.8</v>
       </c>
       <c r="K123" t="n">
-        <v>4.4</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B124" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C124" t="n">
-        <v>67.3</v>
+        <v>84.6</v>
       </c>
       <c r="D124" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="E124" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="E124"/>
+      <c r="F124" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I124" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J124" t="n">
         <v>28.4</v>
       </c>
-      <c r="F124" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G124" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H124" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I124" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J124" t="n">
-        <v>46.8</v>
-      </c>
       <c r="K124" t="n">
-        <v>23.6</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B125" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C125" t="n">
-        <v>84.6</v>
+        <v>50</v>
       </c>
       <c r="D125" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E125"/>
+        <v>45.1</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
       <c r="F125" t="n">
-        <v>47.1</v>
+        <v>25</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H125" t="n">
-        <v>45.2</v>
+        <v>37.5</v>
       </c>
       <c r="I125" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J125" t="n">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="K125" t="n">
-        <v>19.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B126" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C126" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D126" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F126" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G126" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H126" t="n">
         <v>50</v>
       </c>
-      <c r="D126" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>25</v>
-      </c>
-      <c r="G126" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H126" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I126" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J126" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K126" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C127" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D127" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E127" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F127" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G127" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H127" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I127" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K127" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B128" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C128" t="n">
-        <v>65.8</v>
+        <v>51.4</v>
       </c>
       <c r="D128" t="n">
-        <v>67.5</v>
+        <v>60.8</v>
       </c>
       <c r="E128" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F128" t="n">
-        <v>38.1</v>
+        <v>40</v>
       </c>
       <c r="G128" t="n">
-        <v>7.9</v>
+        <v>10.1</v>
       </c>
       <c r="H128" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="J128" t="n">
-        <v>26.8</v>
+        <v>22</v>
       </c>
       <c r="K128" t="n">
-        <v>13.2</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B129" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C129" t="n">
-        <v>51.4</v>
+        <v>66.7</v>
       </c>
       <c r="D129" t="n">
-        <v>60.8</v>
+        <v>56.7</v>
       </c>
       <c r="E129" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F129" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G129" t="n">
-        <v>10.1</v>
+        <v>22.2</v>
       </c>
       <c r="H129" t="n">
-        <v>54.1</v>
+        <v>20</v>
       </c>
       <c r="I129" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K129" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B130" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C130" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D130" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E130" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F130" t="n">
         <v>50</v>
       </c>
       <c r="G130" t="n">
-        <v>22.2</v>
+        <v>4</v>
       </c>
       <c r="H130" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J130" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K130" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B131" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C131" t="n">
-        <v>69.5</v>
+        <v>63</v>
       </c>
       <c r="D131" t="n">
-        <v>70.3</v>
+        <v>64.4</v>
       </c>
       <c r="E131" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F131" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="G131" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="H131" t="n">
-        <v>41.9</v>
+        <v>45.7</v>
       </c>
       <c r="I131" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J131" t="n">
-        <v>26.3</v>
+        <v>21.8</v>
       </c>
       <c r="K131" t="n">
-        <v>18.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="s">
-        <v>298</v>
-      </c>
+      <c r="A132"/>
       <c r="B132" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="C132" t="n">
-        <v>63</v>
+        <v>58.2</v>
       </c>
       <c r="D132" t="n">
-        <v>64.4</v>
+        <v>61.1</v>
       </c>
       <c r="E132" t="n">
-        <v>27</v>
+        <v>21.2</v>
       </c>
       <c r="F132" t="n">
-        <v>44.4</v>
+        <v>37</v>
       </c>
       <c r="G132" t="n">
-        <v>5.4</v>
+        <v>11.3</v>
       </c>
       <c r="H132" t="n">
-        <v>45.7</v>
+        <v>45.4</v>
       </c>
       <c r="I132" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J132" t="n">
-        <v>21.8</v>
+        <v>25.2</v>
       </c>
       <c r="K132" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133"/>
-      <c r="B133" t="s">
-        <v>176</v>
-      </c>
-      <c r="C133" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="D133" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="E133" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F133" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="G133" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H133" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I133" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J133" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="K133" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -640,9 +640,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jose Arias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kade Kodak</t>
   </si>
   <si>
     <t xml:space="preserve">Kade Kozak</t>
@@ -1005,8 +1002,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K138" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K138"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K137" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K137"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -8298,29 +8295,31 @@
         <v>46</v>
       </c>
       <c r="C31" t="n">
-        <v>61.5</v>
+        <v>50.9</v>
       </c>
       <c r="D31" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="E31"/>
+        <v>57.1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>22.4</v>
+      </c>
       <c r="F31" t="n">
-        <v>38.5</v>
+        <v>43.5</v>
       </c>
       <c r="G31" t="n">
-        <v>7.7</v>
+        <v>15.8</v>
       </c>
       <c r="H31" t="n">
-        <v>31.2</v>
+        <v>51.5</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="K31" t="n">
-        <v>11.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="32">
@@ -8331,31 +8330,31 @@
         <v>46</v>
       </c>
       <c r="C32" t="n">
-        <v>41.9</v>
+        <v>59.6</v>
       </c>
       <c r="D32" t="n">
-        <v>50.5</v>
+        <v>58.8</v>
       </c>
       <c r="E32" t="n">
-        <v>22.4</v>
+        <v>19.6</v>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>17.6</v>
       </c>
       <c r="G32" t="n">
-        <v>22.6</v>
+        <v>13.3</v>
       </c>
       <c r="H32" t="n">
-        <v>70.6</v>
+        <v>42.9</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
-        <v>19.4</v>
+        <v>23.1</v>
       </c>
       <c r="K32" t="n">
-        <v>-6.5</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="33">
@@ -8366,101 +8365,101 @@
         <v>46</v>
       </c>
       <c r="C33" t="n">
-        <v>59.6</v>
+        <v>56.7</v>
       </c>
       <c r="D33" t="n">
-        <v>58.8</v>
+        <v>60.8</v>
       </c>
       <c r="E33" t="n">
-        <v>19.6</v>
+        <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>17.6</v>
+        <v>41.7</v>
       </c>
       <c r="G33" t="n">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="H33" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>6.7</v>
       </c>
       <c r="J33" t="n">
-        <v>23.1</v>
+        <v>27.8</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.9</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
       </c>
       <c r="C34" t="n">
-        <v>56.7</v>
+        <v>45</v>
       </c>
       <c r="D34" t="n">
-        <v>60.8</v>
+        <v>57.9</v>
       </c>
       <c r="E34" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G34" t="n">
         <v>10</v>
       </c>
-      <c r="F34" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3.3</v>
-      </c>
       <c r="H34" t="n">
-        <v>41.2</v>
+        <v>37.5</v>
       </c>
       <c r="I34" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="K34" t="n">
-        <v>16.7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="D35" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="F35" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H35" t="n">
         <v>46</v>
       </c>
-      <c r="C35" t="n">
-        <v>45</v>
-      </c>
-      <c r="D35" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="E35" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F35" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="G35" t="n">
-        <v>10</v>
-      </c>
-      <c r="H35" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="J35" t="n">
-        <v>27.5</v>
+        <v>18.8</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="36">
@@ -8471,31 +8470,31 @@
         <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>52.5</v>
+        <v>55.6</v>
       </c>
       <c r="D36" t="n">
-        <v>59.1</v>
+        <v>60.6</v>
       </c>
       <c r="E36" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="F36" t="n">
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="H36" t="n">
-        <v>46</v>
+        <v>28.6</v>
       </c>
       <c r="I36" t="n">
-        <v>8.3</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>18.8</v>
+        <v>6.7</v>
       </c>
       <c r="K36" t="n">
-        <v>2.5</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="37">
@@ -8506,31 +8505,29 @@
         <v>53</v>
       </c>
       <c r="C37" t="n">
-        <v>55.6</v>
+        <v>25</v>
       </c>
       <c r="D37" t="n">
-        <v>60.6</v>
+        <v>60</v>
       </c>
       <c r="E37" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>28.6</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H37"/>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>6.7</v>
+        <v>66.7</v>
       </c>
       <c r="K37" t="n">
-        <v>-11.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -8541,99 +8538,101 @@
         <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>52.3</v>
       </c>
       <c r="D38" t="n">
-        <v>60</v>
+        <v>56.9</v>
       </c>
       <c r="E38" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="F38" t="n">
-        <v>75</v>
+        <v>34.4</v>
       </c>
       <c r="G38" t="n">
-        <v>25</v>
-      </c>
-      <c r="H38"/>
+        <v>12.1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>45.7</v>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>66.7</v>
+        <v>22.7</v>
       </c>
       <c r="K38" t="n">
-        <v>50</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>216</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
         <v>53</v>
       </c>
       <c r="C39" t="n">
-        <v>52.3</v>
+        <v>47.8</v>
       </c>
       <c r="D39" t="n">
-        <v>56.9</v>
+        <v>53.7</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>12.1</v>
       </c>
       <c r="F39" t="n">
-        <v>34.4</v>
+        <v>28.6</v>
       </c>
       <c r="G39" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="H39" t="n">
-        <v>45.7</v>
+        <v>53.3</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J39" t="n">
-        <v>22.7</v>
+        <v>19.4</v>
       </c>
       <c r="K39" t="n">
-        <v>4.6</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>216</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
       </c>
       <c r="C40" t="n">
-        <v>47.8</v>
+        <v>49.5</v>
       </c>
       <c r="D40" t="n">
-        <v>53.7</v>
+        <v>56.3</v>
       </c>
       <c r="E40" t="n">
-        <v>12.1</v>
+        <v>15.3</v>
       </c>
       <c r="F40" t="n">
-        <v>28.6</v>
+        <v>34.1</v>
       </c>
       <c r="G40" t="n">
-        <v>15.2</v>
+        <v>10.5</v>
       </c>
       <c r="H40" t="n">
-        <v>53.3</v>
+        <v>56.1</v>
       </c>
       <c r="I40" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
-        <v>19.4</v>
+        <v>24.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-2.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="41">
@@ -8644,31 +8643,31 @@
         <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>49.5</v>
+        <v>60.9</v>
       </c>
       <c r="D41" t="n">
-        <v>56.3</v>
+        <v>63.1</v>
       </c>
       <c r="E41" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="F41" t="n">
-        <v>34.1</v>
+        <v>20.7</v>
       </c>
       <c r="G41" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="H41" t="n">
-        <v>56.1</v>
+        <v>34</v>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
-        <v>24.1</v>
+        <v>20.2</v>
       </c>
       <c r="K41" t="n">
-        <v>3.8</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="42">
@@ -8679,31 +8678,31 @@
         <v>53</v>
       </c>
       <c r="C42" t="n">
-        <v>60.9</v>
+        <v>54.8</v>
       </c>
       <c r="D42" t="n">
-        <v>63.1</v>
+        <v>64.3</v>
       </c>
       <c r="E42" t="n">
-        <v>16.2</v>
+        <v>23.7</v>
       </c>
       <c r="F42" t="n">
-        <v>20.7</v>
+        <v>50</v>
       </c>
       <c r="G42" t="n">
-        <v>10.1</v>
+        <v>6.5</v>
       </c>
       <c r="H42" t="n">
-        <v>34</v>
+        <v>38.1</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="J42" t="n">
-        <v>20.2</v>
+        <v>20.8</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.4</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="43">
@@ -8714,31 +8713,29 @@
         <v>53</v>
       </c>
       <c r="C43" t="n">
-        <v>54.8</v>
+        <v>100</v>
       </c>
       <c r="D43" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="E43" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43"/>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>50</v>
       </c>
-      <c r="G43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H43" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="I43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>20.8</v>
-      </c>
       <c r="K43" t="n">
-        <v>16.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -8749,29 +8746,31 @@
         <v>53</v>
       </c>
       <c r="C44" t="n">
-        <v>100</v>
+        <v>67.1</v>
       </c>
       <c r="D44" t="n">
-        <v>50</v>
+        <v>64.6</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>51.6</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44"/>
+        <v>2.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>61.7</v>
+      </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>18.5</v>
       </c>
       <c r="K44" t="n">
-        <v>100</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="45">
@@ -8782,31 +8781,31 @@
         <v>53</v>
       </c>
       <c r="C45" t="n">
-        <v>67.1</v>
+        <v>50</v>
       </c>
       <c r="D45" t="n">
-        <v>64.6</v>
+        <v>62.5</v>
       </c>
       <c r="E45" t="n">
-        <v>15.2</v>
+        <v>35.3</v>
       </c>
       <c r="F45" t="n">
-        <v>51.6</v>
+        <v>40</v>
       </c>
       <c r="G45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>61.7</v>
+        <v>40</v>
       </c>
       <c r="I45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>18.5</v>
+        <v>28.6</v>
       </c>
       <c r="K45" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
@@ -8817,31 +8816,31 @@
         <v>53</v>
       </c>
       <c r="C46" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="D46" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="F46" t="n">
         <v>50</v>
       </c>
-      <c r="D46" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="E46" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="F46" t="n">
-        <v>40</v>
-      </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="H46" t="n">
-        <v>40</v>
+        <v>48.9</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="K46" t="n">
-        <v>25</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="47">
@@ -8852,31 +8851,31 @@
         <v>53</v>
       </c>
       <c r="C47" t="n">
-        <v>60.6</v>
+        <v>64</v>
       </c>
       <c r="D47" t="n">
-        <v>64.3</v>
+        <v>68.4</v>
       </c>
       <c r="E47" t="n">
-        <v>16.5</v>
+        <v>23.3</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>46.3</v>
       </c>
       <c r="G47" t="n">
-        <v>11.3</v>
+        <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>48.9</v>
+        <v>33.3</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J47" t="n">
-        <v>28.8</v>
+        <v>28.1</v>
       </c>
       <c r="K47" t="n">
-        <v>9.8</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="48">
@@ -8887,31 +8886,31 @@
         <v>53</v>
       </c>
       <c r="C48" t="n">
-        <v>64</v>
+        <v>55.8</v>
       </c>
       <c r="D48" t="n">
-        <v>68.4</v>
+        <v>60.8</v>
       </c>
       <c r="E48" t="n">
-        <v>23.3</v>
+        <v>19.1</v>
       </c>
       <c r="F48" t="n">
-        <v>46.3</v>
+        <v>42.3</v>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="H48" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J48" t="n">
-        <v>28.1</v>
+        <v>27.6</v>
       </c>
       <c r="K48" t="n">
-        <v>22.1</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="49">
@@ -8922,31 +8921,31 @@
         <v>53</v>
       </c>
       <c r="C49" t="n">
-        <v>55.8</v>
+        <v>50</v>
       </c>
       <c r="D49" t="n">
-        <v>60.8</v>
+        <v>63.2</v>
       </c>
       <c r="E49" t="n">
-        <v>19.1</v>
+        <v>12.5</v>
       </c>
       <c r="F49" t="n">
-        <v>42.3</v>
+        <v>33.3</v>
       </c>
       <c r="G49" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="H49" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="I49" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>27.6</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>13.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
@@ -8957,31 +8956,31 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D50" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
       <c r="E50" t="n">
-        <v>12.5</v>
+        <v>16.3</v>
       </c>
       <c r="F50" t="n">
-        <v>33.3</v>
+        <v>43.8</v>
       </c>
       <c r="G50" t="n">
-        <v>10</v>
+        <v>6.1</v>
       </c>
       <c r="H50" t="n">
-        <v>28.6</v>
+        <v>52.8</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="J50" t="n">
-        <v>35</v>
+        <v>26.6</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="51">
@@ -8992,31 +8991,29 @@
         <v>53</v>
       </c>
       <c r="C51" t="n">
-        <v>58</v>
+        <v>44.4</v>
       </c>
       <c r="D51" t="n">
-        <v>64</v>
-      </c>
-      <c r="E51" t="n">
-        <v>16.3</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E51"/>
       <c r="F51" t="n">
-        <v>43.8</v>
+        <v>25</v>
       </c>
       <c r="G51" t="n">
-        <v>6.1</v>
+        <v>33.3</v>
       </c>
       <c r="H51" t="n">
-        <v>52.8</v>
+        <v>20</v>
       </c>
       <c r="I51" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="K51" t="n">
-        <v>20.7</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="52">
@@ -9027,29 +9024,31 @@
         <v>53</v>
       </c>
       <c r="C52" t="n">
-        <v>44.4</v>
+        <v>51</v>
       </c>
       <c r="D52" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E52"/>
+        <v>56.4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>15.8</v>
+      </c>
       <c r="F52" t="n">
-        <v>25</v>
+        <v>23.2</v>
       </c>
       <c r="G52" t="n">
-        <v>33.3</v>
+        <v>10.3</v>
       </c>
       <c r="H52" t="n">
-        <v>20</v>
+        <v>38.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J52" t="n">
-        <v>27.3</v>
+        <v>13.9</v>
       </c>
       <c r="K52" t="n">
-        <v>-22.2</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="53">
@@ -9057,34 +9056,34 @@
         <v>229</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C53" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>56.4</v>
+        <v>57.4</v>
       </c>
       <c r="E53" t="n">
-        <v>15.8</v>
+        <v>16.9</v>
       </c>
       <c r="F53" t="n">
-        <v>23.2</v>
+        <v>35.6</v>
       </c>
       <c r="G53" t="n">
-        <v>10.3</v>
+        <v>13.6</v>
       </c>
       <c r="H53" t="n">
-        <v>38.2</v>
+        <v>31.2</v>
       </c>
       <c r="I53" t="n">
-        <v>6.8</v>
+        <v>2.3</v>
       </c>
       <c r="J53" t="n">
-        <v>13.9</v>
+        <v>28.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="54">
@@ -9095,31 +9094,31 @@
         <v>71</v>
       </c>
       <c r="C54" t="n">
-        <v>60</v>
+        <v>72.9</v>
       </c>
       <c r="D54" t="n">
-        <v>57.4</v>
+        <v>75.3</v>
       </c>
       <c r="E54" t="n">
-        <v>16.9</v>
+        <v>43.6</v>
       </c>
       <c r="F54" t="n">
-        <v>35.6</v>
+        <v>75</v>
       </c>
       <c r="G54" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>31.2</v>
+        <v>41.7</v>
       </c>
       <c r="I54" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J54" t="n">
-        <v>28.4</v>
+        <v>43.3</v>
       </c>
       <c r="K54" t="n">
-        <v>4.6</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="55">
@@ -9130,31 +9129,31 @@
         <v>71</v>
       </c>
       <c r="C55" t="n">
-        <v>72.9</v>
+        <v>59.2</v>
       </c>
       <c r="D55" t="n">
-        <v>75.3</v>
+        <v>59.6</v>
       </c>
       <c r="E55" t="n">
-        <v>43.6</v>
+        <v>15.4</v>
       </c>
       <c r="F55" t="n">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H55" t="n">
-        <v>41.7</v>
+        <v>47.8</v>
       </c>
       <c r="I55" t="n">
         <v>2.1</v>
       </c>
       <c r="J55" t="n">
-        <v>43.3</v>
+        <v>34</v>
       </c>
       <c r="K55" t="n">
-        <v>38.3</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="56">
@@ -9165,31 +9164,29 @@
         <v>71</v>
       </c>
       <c r="C56" t="n">
-        <v>59.2</v>
+        <v>66.7</v>
       </c>
       <c r="D56" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>15.4</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E56"/>
       <c r="F56" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="G56" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>47.8</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="K56" t="n">
-        <v>14.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
@@ -9200,29 +9197,31 @@
         <v>71</v>
       </c>
       <c r="C57" t="n">
-        <v>66.7</v>
+        <v>65.9</v>
       </c>
       <c r="D57" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E57"/>
+        <v>68.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>22</v>
+      </c>
       <c r="F57" t="n">
-        <v>33.3</v>
+        <v>38.3</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>42.1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>22.3</v>
       </c>
       <c r="K57" t="n">
-        <v>33.3</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="58">
@@ -9233,31 +9232,31 @@
         <v>71</v>
       </c>
       <c r="C58" t="n">
-        <v>65.9</v>
+        <v>55.3</v>
       </c>
       <c r="D58" t="n">
-        <v>68.2</v>
+        <v>60.1</v>
       </c>
       <c r="E58" t="n">
         <v>22</v>
       </c>
       <c r="F58" t="n">
-        <v>38.3</v>
+        <v>44.4</v>
       </c>
       <c r="G58" t="n">
-        <v>3.7</v>
+        <v>13.2</v>
       </c>
       <c r="H58" t="n">
-        <v>42.1</v>
+        <v>41.1</v>
       </c>
       <c r="I58" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
-        <v>22.3</v>
+        <v>36.4</v>
       </c>
       <c r="K58" t="n">
-        <v>14.2</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="59">
@@ -9268,31 +9267,31 @@
         <v>71</v>
       </c>
       <c r="C59" t="n">
-        <v>55.3</v>
+        <v>72.4</v>
       </c>
       <c r="D59" t="n">
-        <v>60.1</v>
+        <v>59.2</v>
       </c>
       <c r="E59" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F59" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="G59" t="n">
-        <v>13.2</v>
+        <v>20.7</v>
       </c>
       <c r="H59" t="n">
-        <v>41.1</v>
+        <v>33.3</v>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>36.4</v>
+        <v>42.4</v>
       </c>
       <c r="K59" t="n">
-        <v>8.7</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="60">
@@ -9303,31 +9302,31 @@
         <v>71</v>
       </c>
       <c r="C60" t="n">
-        <v>72.4</v>
+        <v>61.7</v>
       </c>
       <c r="D60" t="n">
-        <v>59.2</v>
+        <v>63.1</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>23.4</v>
       </c>
       <c r="F60" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G60" t="n">
-        <v>20.7</v>
+        <v>8.1</v>
       </c>
       <c r="H60" t="n">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J60" t="n">
-        <v>42.4</v>
+        <v>15.7</v>
       </c>
       <c r="K60" t="n">
-        <v>10.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="61">
@@ -9338,31 +9337,31 @@
         <v>71</v>
       </c>
       <c r="C61" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="D61" t="n">
-        <v>63.1</v>
+        <v>64.7</v>
       </c>
       <c r="E61" t="n">
-        <v>23.4</v>
+        <v>18.5</v>
       </c>
       <c r="F61" t="n">
-        <v>34</v>
+        <v>44.7</v>
       </c>
       <c r="G61" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="H61" t="n">
-        <v>34.6</v>
+        <v>62</v>
       </c>
       <c r="I61" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J61" t="n">
-        <v>15.7</v>
+        <v>33.6</v>
       </c>
       <c r="K61" t="n">
-        <v>4.1</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="62">
@@ -9373,31 +9372,31 @@
         <v>71</v>
       </c>
       <c r="C62" t="n">
-        <v>61.8</v>
+        <v>56.5</v>
       </c>
       <c r="D62" t="n">
-        <v>64.7</v>
+        <v>61.6</v>
       </c>
       <c r="E62" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="F62" t="n">
-        <v>44.7</v>
+        <v>42.9</v>
       </c>
       <c r="G62" t="n">
-        <v>6.5</v>
+        <v>8.7</v>
       </c>
       <c r="H62" t="n">
-        <v>62</v>
+        <v>56.2</v>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="J62" t="n">
-        <v>33.6</v>
+        <v>23.8</v>
       </c>
       <c r="K62" t="n">
-        <v>15.6</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="63">
@@ -9408,31 +9407,31 @@
         <v>71</v>
       </c>
       <c r="C63" t="n">
-        <v>56.5</v>
+        <v>65.7</v>
       </c>
       <c r="D63" t="n">
-        <v>61.6</v>
+        <v>66.9</v>
       </c>
       <c r="E63" t="n">
-        <v>6.5</v>
+        <v>29.4</v>
       </c>
       <c r="F63" t="n">
-        <v>42.9</v>
+        <v>33.9</v>
       </c>
       <c r="G63" t="n">
-        <v>8.7</v>
+        <v>5</v>
       </c>
       <c r="H63" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="I63" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J63" t="n">
-        <v>23.8</v>
+        <v>19.6</v>
       </c>
       <c r="K63" t="n">
-        <v>10.9</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="64">
@@ -9443,171 +9442,171 @@
         <v>71</v>
       </c>
       <c r="C64" t="n">
-        <v>65.7</v>
+        <v>63.8</v>
       </c>
       <c r="D64" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="E64" t="n">
-        <v>29.4</v>
+        <v>33.3</v>
       </c>
       <c r="F64" t="n">
-        <v>33.9</v>
+        <v>38.1</v>
       </c>
       <c r="G64" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="H64" t="n">
-        <v>55.8</v>
+        <v>19.4</v>
       </c>
       <c r="I64" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>19.6</v>
+        <v>20.5</v>
       </c>
       <c r="K64" t="n">
-        <v>9.3</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>241</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
         <v>71</v>
       </c>
       <c r="C65" t="n">
-        <v>63.8</v>
+        <v>30</v>
       </c>
       <c r="D65" t="n">
-        <v>64.6</v>
+        <v>60.6</v>
       </c>
       <c r="E65" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="F65" t="n">
-        <v>38.1</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>19.4</v>
+        <v>25</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J65" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>13.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="B66" t="s">
         <v>71</v>
       </c>
       <c r="C66" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D66" t="n">
-        <v>60.6</v>
+        <v>51.9</v>
       </c>
       <c r="E66" t="n">
+        <v>25</v>
+      </c>
+      <c r="F66" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="G66" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="H66" t="n">
         <v>46.7</v>
       </c>
-      <c r="F66" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>25</v>
-      </c>
       <c r="I66" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>32.5</v>
       </c>
       <c r="K66" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>242</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
         <v>71</v>
       </c>
       <c r="C67" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9</v>
+        <v>57.1</v>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F67" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>22.2</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>46.7</v>
+        <v>20</v>
       </c>
       <c r="I67" t="n">
-        <v>11.1</v>
+        <v>40</v>
       </c>
       <c r="J67" t="n">
-        <v>32.5</v>
+        <v>14.3</v>
       </c>
       <c r="K67" t="n">
-        <v>-7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>242</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C68" t="n">
-        <v>40</v>
+        <v>70.8</v>
       </c>
       <c r="D68" t="n">
-        <v>57.1</v>
+        <v>70.6</v>
       </c>
       <c r="E68" t="n">
-        <v>37.5</v>
+        <v>18</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>44.1</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H68" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J68" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="K68" t="n">
         <v>20</v>
-      </c>
-      <c r="I68" t="n">
-        <v>40</v>
-      </c>
-      <c r="J68" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -9618,31 +9617,31 @@
         <v>93</v>
       </c>
       <c r="C69" t="n">
-        <v>70.8</v>
+        <v>69</v>
       </c>
       <c r="D69" t="n">
-        <v>70.6</v>
+        <v>67.1</v>
       </c>
       <c r="E69" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="F69" t="n">
-        <v>44.1</v>
+        <v>33.3</v>
       </c>
       <c r="G69" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="H69" t="n">
-        <v>52.5</v>
+        <v>36.4</v>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="J69" t="n">
-        <v>23.3</v>
+        <v>7.5</v>
       </c>
       <c r="K69" t="n">
-        <v>20</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="70">
@@ -9653,31 +9652,31 @@
         <v>93</v>
       </c>
       <c r="C70" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="D70" t="n">
-        <v>67.1</v>
+        <v>68.3</v>
       </c>
       <c r="E70" t="n">
-        <v>17.9</v>
+        <v>26.5</v>
       </c>
       <c r="F70" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="G70" t="n">
-        <v>3.4</v>
+        <v>9.1</v>
       </c>
       <c r="H70" t="n">
-        <v>36.4</v>
+        <v>38.9</v>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="K70" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -9688,31 +9687,31 @@
         <v>93</v>
       </c>
       <c r="C71" t="n">
-        <v>50</v>
+        <v>56.4</v>
       </c>
       <c r="D71" t="n">
-        <v>68.3</v>
+        <v>61.5</v>
       </c>
       <c r="E71" t="n">
-        <v>26.5</v>
+        <v>20.5</v>
       </c>
       <c r="F71" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="G71" t="n">
-        <v>9.1</v>
+        <v>12.8</v>
       </c>
       <c r="H71" t="n">
-        <v>38.9</v>
+        <v>48</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J71" t="n">
-        <v>8.9</v>
+        <v>19.3</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="72">
@@ -9723,31 +9722,31 @@
         <v>93</v>
       </c>
       <c r="C72" t="n">
-        <v>56.4</v>
+        <v>59.5</v>
       </c>
       <c r="D72" t="n">
-        <v>61.5</v>
+        <v>62.8</v>
       </c>
       <c r="E72" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="F72" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G72" t="n">
-        <v>12.8</v>
+        <v>16.2</v>
       </c>
       <c r="H72" t="n">
-        <v>48</v>
+        <v>52.6</v>
       </c>
       <c r="I72" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>19.3</v>
+        <v>27.5</v>
       </c>
       <c r="K72" t="n">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="73">
@@ -9758,31 +9757,31 @@
         <v>93</v>
       </c>
       <c r="C73" t="n">
-        <v>59.5</v>
+        <v>61.1</v>
       </c>
       <c r="D73" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="E73" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="F73" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G73" t="n">
-        <v>16.2</v>
+        <v>7.1</v>
       </c>
       <c r="H73" t="n">
-        <v>52.6</v>
+        <v>56.5</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
-        <v>27.5</v>
+        <v>36.2</v>
       </c>
       <c r="K73" t="n">
-        <v>5.4</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="74">
@@ -9793,31 +9792,31 @@
         <v>93</v>
       </c>
       <c r="C74" t="n">
-        <v>61.1</v>
+        <v>66.9</v>
       </c>
       <c r="D74" t="n">
-        <v>63</v>
+        <v>61.6</v>
       </c>
       <c r="E74" t="n">
-        <v>17.6</v>
+        <v>29.7</v>
       </c>
       <c r="F74" t="n">
-        <v>55</v>
+        <v>59.5</v>
       </c>
       <c r="G74" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="H74" t="n">
-        <v>56.5</v>
+        <v>54</v>
       </c>
       <c r="I74" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>36.2</v>
+        <v>41.3</v>
       </c>
       <c r="K74" t="n">
-        <v>22.1</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="75">
@@ -9828,31 +9827,31 @@
         <v>93</v>
       </c>
       <c r="C75" t="n">
-        <v>66.9</v>
+        <v>57.1</v>
       </c>
       <c r="D75" t="n">
-        <v>61.6</v>
+        <v>66.7</v>
       </c>
       <c r="E75" t="n">
-        <v>29.7</v>
+        <v>34.5</v>
       </c>
       <c r="F75" t="n">
-        <v>59.5</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="H75" t="n">
-        <v>54</v>
+        <v>47.8</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J75" t="n">
-        <v>41.3</v>
+        <v>22.7</v>
       </c>
       <c r="K75" t="n">
-        <v>28.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="76">
@@ -9863,31 +9862,31 @@
         <v>93</v>
       </c>
       <c r="C76" t="n">
-        <v>57.1</v>
+        <v>72.7</v>
       </c>
       <c r="D76" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="E76" t="n">
-        <v>34.5</v>
+        <v>21.7</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>38.5</v>
       </c>
       <c r="G76" t="n">
-        <v>7.1</v>
+        <v>13.6</v>
       </c>
       <c r="H76" t="n">
-        <v>47.8</v>
+        <v>46.2</v>
       </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>22.7</v>
+        <v>30.6</v>
       </c>
       <c r="K76" t="n">
-        <v>3.6</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="77">
@@ -9898,31 +9897,31 @@
         <v>93</v>
       </c>
       <c r="C77" t="n">
-        <v>72.7</v>
+        <v>68.3</v>
       </c>
       <c r="D77" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E77" t="n">
-        <v>21.7</v>
+        <v>26.9</v>
       </c>
       <c r="F77" t="n">
         <v>38.5</v>
       </c>
       <c r="G77" t="n">
-        <v>13.6</v>
+        <v>7.3</v>
       </c>
       <c r="H77" t="n">
-        <v>46.2</v>
+        <v>56.7</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J77" t="n">
-        <v>30.6</v>
+        <v>25</v>
       </c>
       <c r="K77" t="n">
-        <v>9.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
@@ -9933,31 +9932,31 @@
         <v>93</v>
       </c>
       <c r="C78" t="n">
-        <v>68.3</v>
+        <v>61.7</v>
       </c>
       <c r="D78" t="n">
-        <v>69</v>
+        <v>63.5</v>
       </c>
       <c r="E78" t="n">
-        <v>26.9</v>
+        <v>25.7</v>
       </c>
       <c r="F78" t="n">
-        <v>38.5</v>
+        <v>54.3</v>
       </c>
       <c r="G78" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H78" t="n">
-        <v>56.7</v>
+        <v>40.6</v>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
-        <v>25</v>
+        <v>30.3</v>
       </c>
       <c r="K78" t="n">
-        <v>11</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="79">
@@ -9968,31 +9967,31 @@
         <v>93</v>
       </c>
       <c r="C79" t="n">
-        <v>61.7</v>
+        <v>65.9</v>
       </c>
       <c r="D79" t="n">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="E79" t="n">
-        <v>25.7</v>
+        <v>23.1</v>
       </c>
       <c r="F79" t="n">
-        <v>54.3</v>
+        <v>44.4</v>
       </c>
       <c r="G79" t="n">
-        <v>7.4</v>
+        <v>9.3</v>
       </c>
       <c r="H79" t="n">
-        <v>40.6</v>
+        <v>52</v>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J79" t="n">
-        <v>30.3</v>
+        <v>22.5</v>
       </c>
       <c r="K79" t="n">
-        <v>19.6</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="80">
@@ -10000,34 +9999,34 @@
         <v>254</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C80" t="n">
-        <v>65.9</v>
+        <v>42</v>
       </c>
       <c r="D80" t="n">
-        <v>63.4</v>
+        <v>44.7</v>
       </c>
       <c r="E80" t="n">
-        <v>23.1</v>
+        <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="G80" t="n">
-        <v>9.3</v>
+        <v>31.9</v>
       </c>
       <c r="H80" t="n">
-        <v>52</v>
+        <v>41.4</v>
       </c>
       <c r="I80" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
-        <v>22.5</v>
+        <v>30.4</v>
       </c>
       <c r="K80" t="n">
-        <v>9.3</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="81">
@@ -10038,101 +10037,99 @@
         <v>107</v>
       </c>
       <c r="C81" t="n">
-        <v>42</v>
+        <v>67.9</v>
       </c>
       <c r="D81" t="n">
-        <v>44.7</v>
+        <v>63.4</v>
       </c>
       <c r="E81" t="n">
-        <v>6.3</v>
+        <v>26</v>
       </c>
       <c r="F81" t="n">
-        <v>46.4</v>
+        <v>46.5</v>
       </c>
       <c r="G81" t="n">
-        <v>31.9</v>
+        <v>10.5</v>
       </c>
       <c r="H81" t="n">
-        <v>41.4</v>
+        <v>53.7</v>
       </c>
       <c r="I81" t="n">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="J81" t="n">
-        <v>30.4</v>
+        <v>29.9</v>
       </c>
       <c r="K81" t="n">
-        <v>-13.1</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
       </c>
       <c r="C82" t="n">
-        <v>67.9</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>63.4</v>
+        <v>53.5</v>
       </c>
       <c r="E82" t="n">
-        <v>26</v>
+        <v>10.1</v>
       </c>
       <c r="F82" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="G82" t="n">
-        <v>10.5</v>
+        <v>13.6</v>
       </c>
       <c r="H82" t="n">
-        <v>53.7</v>
+        <v>38.5</v>
       </c>
       <c r="I82" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
-        <v>29.9</v>
+        <v>22.1</v>
       </c>
       <c r="K82" t="n">
-        <v>12.8</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
       </c>
       <c r="C83" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="D83" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="E83" t="n">
-        <v>10.1</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E83"/>
       <c r="F83" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>13.6</v>
+        <v>42.9</v>
       </c>
       <c r="H83" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="I83" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>22.1</v>
+        <v>14.3</v>
       </c>
       <c r="K83" t="n">
-        <v>6.1</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="84">
@@ -10143,29 +10140,31 @@
         <v>107</v>
       </c>
       <c r="C84" t="n">
-        <v>28.6</v>
+        <v>68.8</v>
       </c>
       <c r="D84" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E84"/>
+        <v>64.9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>22.2</v>
+      </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G84" t="n">
-        <v>42.9</v>
+        <v>18.8</v>
       </c>
       <c r="H84" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>14.3</v>
+        <v>21.4</v>
       </c>
       <c r="K84" t="n">
-        <v>-42.9</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="85">
@@ -10176,171 +10175,171 @@
         <v>107</v>
       </c>
       <c r="C85" t="n">
-        <v>68.8</v>
+        <v>48.6</v>
       </c>
       <c r="D85" t="n">
-        <v>64.9</v>
+        <v>56.4</v>
       </c>
       <c r="E85" t="n">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="F85" t="n">
-        <v>25</v>
+        <v>41.5</v>
       </c>
       <c r="G85" t="n">
-        <v>18.8</v>
+        <v>14.9</v>
       </c>
       <c r="H85" t="n">
-        <v>50</v>
+        <v>32.6</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J85" t="n">
-        <v>21.4</v>
+        <v>33.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-6.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>259</v>
+        <v>109</v>
       </c>
       <c r="B86" t="s">
         <v>107</v>
       </c>
       <c r="C86" t="n">
-        <v>48.6</v>
+        <v>57.4</v>
       </c>
       <c r="D86" t="n">
-        <v>56.4</v>
+        <v>59.1</v>
       </c>
       <c r="E86" t="n">
-        <v>22.6</v>
+        <v>19.1</v>
       </c>
       <c r="F86" t="n">
-        <v>41.5</v>
+        <v>24.2</v>
       </c>
       <c r="G86" t="n">
-        <v>14.9</v>
+        <v>6.5</v>
       </c>
       <c r="H86" t="n">
-        <v>32.6</v>
+        <v>42.2</v>
       </c>
       <c r="I86" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
-        <v>33.6</v>
+        <v>22.5</v>
       </c>
       <c r="K86" t="n">
-        <v>8.1</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>109</v>
+        <v>259</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
       </c>
       <c r="C87" t="n">
-        <v>57.4</v>
+        <v>71.4</v>
       </c>
       <c r="D87" t="n">
-        <v>59.1</v>
+        <v>70.6</v>
       </c>
       <c r="E87" t="n">
-        <v>19.1</v>
+        <v>22.2</v>
       </c>
       <c r="F87" t="n">
-        <v>24.2</v>
+        <v>28.6</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="H87" t="n">
-        <v>42.2</v>
+        <v>45.5</v>
       </c>
       <c r="I87" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
-        <v>22.5</v>
+        <v>10.7</v>
       </c>
       <c r="K87" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
       </c>
       <c r="C88" t="n">
-        <v>71.4</v>
+        <v>63</v>
       </c>
       <c r="D88" t="n">
-        <v>70.6</v>
+        <v>66.4</v>
       </c>
       <c r="E88" t="n">
-        <v>22.2</v>
+        <v>27.9</v>
       </c>
       <c r="F88" t="n">
-        <v>28.6</v>
+        <v>39.3</v>
       </c>
       <c r="G88" t="n">
-        <v>7.1</v>
+        <v>5</v>
       </c>
       <c r="H88" t="n">
-        <v>45.5</v>
+        <v>44.1</v>
       </c>
       <c r="I88" t="n">
-        <v>7.1</v>
+        <v>4.5</v>
       </c>
       <c r="J88" t="n">
-        <v>10.7</v>
+        <v>22.6</v>
       </c>
       <c r="K88" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>220</v>
+        <v>260</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
       </c>
       <c r="C89" t="n">
-        <v>63</v>
+        <v>54.5</v>
       </c>
       <c r="D89" t="n">
-        <v>66.4</v>
+        <v>55.6</v>
       </c>
       <c r="E89" t="n">
-        <v>27.9</v>
+        <v>10.4</v>
       </c>
       <c r="F89" t="n">
-        <v>39.3</v>
+        <v>29.4</v>
       </c>
       <c r="G89" t="n">
-        <v>5</v>
+        <v>15.2</v>
       </c>
       <c r="H89" t="n">
-        <v>44.1</v>
+        <v>45</v>
       </c>
       <c r="I89" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="J89" t="n">
-        <v>22.6</v>
+        <v>26.6</v>
       </c>
       <c r="K89" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -10351,31 +10350,29 @@
         <v>107</v>
       </c>
       <c r="C90" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="D90" t="n">
         <v>54.5</v>
       </c>
-      <c r="D90" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="E90" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="E90"/>
       <c r="F90" t="n">
-        <v>29.4</v>
+        <v>23.8</v>
       </c>
       <c r="G90" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="H90" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I90" t="n">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="J90" t="n">
-        <v>26.6</v>
+        <v>43.1</v>
       </c>
       <c r="K90" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="91">
@@ -10386,29 +10383,31 @@
         <v>107</v>
       </c>
       <c r="C91" t="n">
-        <v>34.6</v>
+        <v>67.3</v>
       </c>
       <c r="D91" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E91"/>
+        <v>65.4</v>
+      </c>
+      <c r="E91" t="n">
+        <v>27.7</v>
+      </c>
       <c r="F91" t="n">
-        <v>23.8</v>
+        <v>39.3</v>
       </c>
       <c r="G91" t="n">
-        <v>15.4</v>
+        <v>9</v>
       </c>
       <c r="H91" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="I91" t="n">
-        <v>7.7</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
-        <v>43.1</v>
+        <v>29</v>
       </c>
       <c r="K91" t="n">
-        <v>3.8</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="92">
@@ -10419,31 +10418,31 @@
         <v>107</v>
       </c>
       <c r="C92" t="n">
-        <v>67.3</v>
+        <v>62.1</v>
       </c>
       <c r="D92" t="n">
-        <v>65.4</v>
+        <v>61.2</v>
       </c>
       <c r="E92" t="n">
-        <v>27.7</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
-        <v>39.3</v>
+        <v>25</v>
       </c>
       <c r="G92" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="H92" t="n">
-        <v>46.7</v>
+        <v>48.6</v>
       </c>
       <c r="I92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>29</v>
+        <v>23.2</v>
       </c>
       <c r="K92" t="n">
-        <v>10.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="93">
@@ -10454,31 +10453,31 @@
         <v>107</v>
       </c>
       <c r="C93" t="n">
-        <v>62.1</v>
+        <v>52.6</v>
       </c>
       <c r="D93" t="n">
-        <v>61.2</v>
+        <v>55.8</v>
       </c>
       <c r="E93" t="n">
-        <v>14</v>
+        <v>25.6</v>
       </c>
       <c r="F93" t="n">
-        <v>25</v>
+        <v>37.9</v>
       </c>
       <c r="G93" t="n">
-        <v>10.3</v>
+        <v>12.4</v>
       </c>
       <c r="H93" t="n">
-        <v>48.6</v>
+        <v>30</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="J93" t="n">
-        <v>23.2</v>
+        <v>24.9</v>
       </c>
       <c r="K93" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="94">
@@ -10489,31 +10488,31 @@
         <v>107</v>
       </c>
       <c r="C94" t="n">
-        <v>52.6</v>
+        <v>75</v>
       </c>
       <c r="D94" t="n">
-        <v>55.8</v>
+        <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>25.6</v>
+        <v>12.1</v>
       </c>
       <c r="F94" t="n">
-        <v>37.9</v>
+        <v>37.5</v>
       </c>
       <c r="G94" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>30</v>
+        <v>53.8</v>
       </c>
       <c r="I94" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J94" t="n">
-        <v>24.9</v>
+        <v>26.9</v>
       </c>
       <c r="K94" t="n">
-        <v>3.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="95">
@@ -10524,31 +10523,31 @@
         <v>107</v>
       </c>
       <c r="C95" t="n">
-        <v>75</v>
+        <v>55.2</v>
       </c>
       <c r="D95" t="n">
-        <v>65</v>
+        <v>61.1</v>
       </c>
       <c r="E95" t="n">
-        <v>12.1</v>
+        <v>23.4</v>
       </c>
       <c r="F95" t="n">
-        <v>37.5</v>
+        <v>38.3</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="n">
-        <v>53.8</v>
+        <v>50.7</v>
       </c>
       <c r="I95" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J95" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="K95" t="n">
-        <v>18.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="96">
@@ -10556,34 +10555,34 @@
         <v>267</v>
       </c>
       <c r="B96" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C96" t="n">
-        <v>55.2</v>
+        <v>74.2</v>
       </c>
       <c r="D96" t="n">
-        <v>61.1</v>
+        <v>69.7</v>
       </c>
       <c r="E96" t="n">
-        <v>23.4</v>
+        <v>39.1</v>
       </c>
       <c r="F96" t="n">
-        <v>38.3</v>
+        <v>33.3</v>
       </c>
       <c r="G96" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="H96" t="n">
-        <v>50.7</v>
+        <v>52.2</v>
       </c>
       <c r="I96" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="K96" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="97">
@@ -10594,31 +10593,31 @@
         <v>128</v>
       </c>
       <c r="C97" t="n">
-        <v>74.2</v>
+        <v>61.9</v>
       </c>
       <c r="D97" t="n">
-        <v>69.7</v>
+        <v>57.3</v>
       </c>
       <c r="E97" t="n">
-        <v>39.1</v>
+        <v>15.4</v>
       </c>
       <c r="F97" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="G97" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="H97" t="n">
-        <v>52.2</v>
+        <v>39.3</v>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J97" t="n">
-        <v>22.9</v>
+        <v>32.4</v>
       </c>
       <c r="K97" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="98">
@@ -10629,31 +10628,31 @@
         <v>128</v>
       </c>
       <c r="C98" t="n">
-        <v>61.9</v>
+        <v>57.5</v>
       </c>
       <c r="D98" t="n">
-        <v>57.3</v>
+        <v>64.6</v>
       </c>
       <c r="E98" t="n">
-        <v>15.4</v>
+        <v>30</v>
       </c>
       <c r="F98" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="G98" t="n">
-        <v>14.3</v>
+        <v>6.7</v>
       </c>
       <c r="H98" t="n">
-        <v>39.3</v>
+        <v>50</v>
       </c>
       <c r="I98" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J98" t="n">
-        <v>32.4</v>
+        <v>21.8</v>
       </c>
       <c r="K98" t="n">
-        <v>4.7</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="99">
@@ -10664,31 +10663,31 @@
         <v>128</v>
       </c>
       <c r="C99" t="n">
-        <v>57.5</v>
+        <v>59.7</v>
       </c>
       <c r="D99" t="n">
-        <v>64.6</v>
+        <v>64.4</v>
       </c>
       <c r="E99" t="n">
-        <v>30</v>
+        <v>32.3</v>
       </c>
       <c r="F99" t="n">
-        <v>40.8</v>
+        <v>48.6</v>
       </c>
       <c r="G99" t="n">
-        <v>6.7</v>
+        <v>11.9</v>
       </c>
       <c r="H99" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I99" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
-        <v>21.8</v>
+        <v>31.2</v>
       </c>
       <c r="K99" t="n">
-        <v>8.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100">
@@ -10699,31 +10698,31 @@
         <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>59.7</v>
+        <v>65.3</v>
       </c>
       <c r="D100" t="n">
-        <v>64.4</v>
+        <v>67.2</v>
       </c>
       <c r="E100" t="n">
-        <v>32.3</v>
+        <v>33.8</v>
       </c>
       <c r="F100" t="n">
-        <v>48.6</v>
+        <v>64</v>
       </c>
       <c r="G100" t="n">
-        <v>11.9</v>
+        <v>6.1</v>
       </c>
       <c r="H100" t="n">
-        <v>59</v>
+        <v>55.2</v>
       </c>
       <c r="I100" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>31.2</v>
+        <v>31.8</v>
       </c>
       <c r="K100" t="n">
-        <v>15</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="101">
@@ -10734,31 +10733,31 @@
         <v>128</v>
       </c>
       <c r="C101" t="n">
-        <v>65.3</v>
+        <v>60.6</v>
       </c>
       <c r="D101" t="n">
-        <v>67.2</v>
+        <v>64.6</v>
       </c>
       <c r="E101" t="n">
-        <v>33.8</v>
+        <v>21.7</v>
       </c>
       <c r="F101" t="n">
-        <v>64</v>
+        <v>25.7</v>
       </c>
       <c r="G101" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H101" t="n">
-        <v>55.2</v>
+        <v>67.9</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J101" t="n">
-        <v>31.8</v>
+        <v>19.3</v>
       </c>
       <c r="K101" t="n">
-        <v>26.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="102">
@@ -10769,31 +10768,31 @@
         <v>128</v>
       </c>
       <c r="C102" t="n">
-        <v>60.6</v>
+        <v>72.2</v>
       </c>
       <c r="D102" t="n">
-        <v>64.6</v>
+        <v>67.9</v>
       </c>
       <c r="E102" t="n">
-        <v>21.7</v>
+        <v>34.3</v>
       </c>
       <c r="F102" t="n">
-        <v>25.7</v>
+        <v>50</v>
       </c>
       <c r="G102" t="n">
-        <v>5.9</v>
+        <v>11.1</v>
       </c>
       <c r="H102" t="n">
-        <v>67.9</v>
+        <v>50</v>
       </c>
       <c r="I102" t="n">
-        <v>2.9</v>
+        <v>5.6</v>
       </c>
       <c r="J102" t="n">
-        <v>19.3</v>
+        <v>38.7</v>
       </c>
       <c r="K102" t="n">
-        <v>7.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="103">
@@ -10804,31 +10803,31 @@
         <v>128</v>
       </c>
       <c r="C103" t="n">
-        <v>72.2</v>
+        <v>66.3</v>
       </c>
       <c r="D103" t="n">
-        <v>67.9</v>
+        <v>65.8</v>
       </c>
       <c r="E103" t="n">
-        <v>34.3</v>
+        <v>23.1</v>
       </c>
       <c r="F103" t="n">
-        <v>50</v>
+        <v>37.2</v>
       </c>
       <c r="G103" t="n">
-        <v>11.1</v>
+        <v>9.4</v>
       </c>
       <c r="H103" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
       <c r="I103" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
-        <v>38.7</v>
+        <v>21.5</v>
       </c>
       <c r="K103" t="n">
-        <v>16.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="104">
@@ -10839,31 +10838,31 @@
         <v>128</v>
       </c>
       <c r="C104" t="n">
-        <v>66.3</v>
+        <v>67.6</v>
       </c>
       <c r="D104" t="n">
-        <v>65.8</v>
+        <v>70.2</v>
       </c>
       <c r="E104" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="F104" t="n">
-        <v>37.2</v>
+        <v>48</v>
       </c>
       <c r="G104" t="n">
-        <v>9.4</v>
+        <v>0.5</v>
       </c>
       <c r="H104" t="n">
-        <v>41.3</v>
+        <v>44</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="K104" t="n">
-        <v>6.4</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="105">
@@ -10874,31 +10873,31 @@
         <v>128</v>
       </c>
       <c r="C105" t="n">
-        <v>67.6</v>
+        <v>64.4</v>
       </c>
       <c r="D105" t="n">
-        <v>70.2</v>
+        <v>61.4</v>
       </c>
       <c r="E105" t="n">
-        <v>22.7</v>
+        <v>13.4</v>
       </c>
       <c r="F105" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="G105" t="n">
-        <v>0.5</v>
+        <v>16.4</v>
       </c>
       <c r="H105" t="n">
-        <v>44</v>
+        <v>32.3</v>
       </c>
       <c r="I105" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J105" t="n">
-        <v>21.6</v>
+        <v>36.4</v>
       </c>
       <c r="K105" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="106">
@@ -10906,34 +10905,34 @@
         <v>277</v>
       </c>
       <c r="B106" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="C106" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D106" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E106" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F106" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H106" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J106" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="107">
@@ -10944,101 +10943,101 @@
         <v>144</v>
       </c>
       <c r="C107" t="n">
-        <v>33.3</v>
+        <v>54.3</v>
       </c>
       <c r="D107" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="E107" t="n">
-        <v>36.4</v>
+        <v>17.4</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="G107" t="n">
-        <v>33.3</v>
+        <v>14.3</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I107" t="n">
-        <v>33.3</v>
+        <v>2.9</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K107" t="n">
-        <v>-33.3</v>
+        <v>-8.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>279</v>
+        <v>145</v>
       </c>
       <c r="B108" t="s">
         <v>144</v>
       </c>
       <c r="C108" t="n">
-        <v>54.3</v>
+        <v>51.6</v>
       </c>
       <c r="D108" t="n">
-        <v>56.1</v>
+        <v>58.9</v>
       </c>
       <c r="E108" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="F108" t="n">
-        <v>15.4</v>
+        <v>40.9</v>
       </c>
       <c r="G108" t="n">
-        <v>14.3</v>
+        <v>12.9</v>
       </c>
       <c r="H108" t="n">
-        <v>40</v>
+        <v>44.4</v>
       </c>
       <c r="I108" t="n">
-        <v>2.9</v>
+        <v>8.1</v>
       </c>
       <c r="J108" t="n">
-        <v>17</v>
+        <v>24.4</v>
       </c>
       <c r="K108" t="n">
-        <v>-8.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>145</v>
+        <v>279</v>
       </c>
       <c r="B109" t="s">
         <v>144</v>
       </c>
       <c r="C109" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D109" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E109" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F109" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9</v>
+        <v>8.3</v>
       </c>
       <c r="H109" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I109" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J109" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K109" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="110">
@@ -11049,31 +11048,29 @@
         <v>144</v>
       </c>
       <c r="C110" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D110" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E110" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F110" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F110"/>
       <c r="G110" t="n">
-        <v>8.3</v>
+        <v>25</v>
       </c>
       <c r="H110" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="111">
@@ -11084,29 +11081,31 @@
         <v>144</v>
       </c>
       <c r="C111" t="n">
-        <v>50</v>
+        <v>67.3</v>
       </c>
       <c r="D111" t="n">
-        <v>45.5</v>
+        <v>62.6</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111"/>
+        <v>26.4</v>
+      </c>
+      <c r="F111" t="n">
+        <v>25</v>
+      </c>
       <c r="G111" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>50.7</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>23.6</v>
       </c>
       <c r="K111" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="112">
@@ -11117,101 +11116,101 @@
         <v>144</v>
       </c>
       <c r="C112" t="n">
-        <v>67.3</v>
+        <v>51.2</v>
       </c>
       <c r="D112" t="n">
-        <v>62.6</v>
+        <v>60.8</v>
       </c>
       <c r="E112" t="n">
-        <v>26.4</v>
+        <v>15.8</v>
       </c>
       <c r="F112" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="G112" t="n">
-        <v>12.9</v>
+        <v>4.7</v>
       </c>
       <c r="H112" t="n">
-        <v>50.7</v>
+        <v>38.2</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J112" t="n">
-        <v>23.6</v>
+        <v>15.3</v>
       </c>
       <c r="K112" t="n">
-        <v>-1</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>283</v>
+        <v>156</v>
       </c>
       <c r="B113" t="s">
         <v>144</v>
       </c>
       <c r="C113" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="D113" t="n">
-        <v>60.8</v>
+        <v>59.1</v>
       </c>
       <c r="E113" t="n">
-        <v>15.8</v>
+        <v>31.1</v>
       </c>
       <c r="F113" t="n">
-        <v>23.5</v>
+        <v>39.4</v>
       </c>
       <c r="G113" t="n">
-        <v>4.7</v>
+        <v>14.3</v>
       </c>
       <c r="H113" t="n">
-        <v>38.2</v>
+        <v>48.5</v>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="J113" t="n">
-        <v>15.3</v>
+        <v>28</v>
       </c>
       <c r="K113" t="n">
-        <v>4.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>156</v>
+        <v>283</v>
       </c>
       <c r="B114" t="s">
         <v>144</v>
       </c>
       <c r="C114" t="n">
-        <v>51.6</v>
+        <v>57.9</v>
       </c>
       <c r="D114" t="n">
-        <v>59.1</v>
+        <v>58.3</v>
       </c>
       <c r="E114" t="n">
-        <v>31.1</v>
+        <v>21</v>
       </c>
       <c r="F114" t="n">
-        <v>39.4</v>
+        <v>25</v>
       </c>
       <c r="G114" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="H114" t="n">
-        <v>48.5</v>
+        <v>48.1</v>
       </c>
       <c r="I114" t="n">
-        <v>7.9</v>
+        <v>2.6</v>
       </c>
       <c r="J114" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K114" t="n">
-        <v>7.9</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="115">
@@ -11222,31 +11221,31 @@
         <v>144</v>
       </c>
       <c r="C115" t="n">
-        <v>57.9</v>
+        <v>52.6</v>
       </c>
       <c r="D115" t="n">
-        <v>58.3</v>
+        <v>56.2</v>
       </c>
       <c r="E115" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G115" t="n">
-        <v>15.4</v>
+        <v>15.8</v>
       </c>
       <c r="H115" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="I115" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J115" t="n">
-        <v>20</v>
+        <v>15.2</v>
       </c>
       <c r="K115" t="n">
-        <v>-2.6</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="116">
@@ -11257,31 +11256,31 @@
         <v>144</v>
       </c>
       <c r="C116" t="n">
-        <v>52.6</v>
+        <v>62.8</v>
       </c>
       <c r="D116" t="n">
-        <v>56.2</v>
+        <v>64.3</v>
       </c>
       <c r="E116" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
       <c r="F116" t="n">
-        <v>10</v>
+        <v>54.4</v>
       </c>
       <c r="G116" t="n">
-        <v>15.8</v>
+        <v>8.8</v>
       </c>
       <c r="H116" t="n">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="I116" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
-        <v>15.2</v>
+        <v>28.3</v>
       </c>
       <c r="K116" t="n">
-        <v>-10.5</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="117">
@@ -11292,31 +11291,31 @@
         <v>144</v>
       </c>
       <c r="C117" t="n">
-        <v>62.8</v>
+        <v>58.7</v>
       </c>
       <c r="D117" t="n">
-        <v>64.3</v>
+        <v>61</v>
       </c>
       <c r="E117" t="n">
-        <v>28.5</v>
+        <v>20</v>
       </c>
       <c r="F117" t="n">
-        <v>54.4</v>
+        <v>48.6</v>
       </c>
       <c r="G117" t="n">
-        <v>8.8</v>
+        <v>10.7</v>
       </c>
       <c r="H117" t="n">
-        <v>41.5</v>
+        <v>42.9</v>
       </c>
       <c r="I117" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>28.3</v>
+        <v>33.6</v>
       </c>
       <c r="K117" t="n">
-        <v>18.2</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="118">
@@ -11327,31 +11326,31 @@
         <v>144</v>
       </c>
       <c r="C118" t="n">
-        <v>58.7</v>
+        <v>44</v>
       </c>
       <c r="D118" t="n">
-        <v>61</v>
+        <v>56.3</v>
       </c>
       <c r="E118" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="F118" t="n">
-        <v>48.6</v>
+        <v>38.5</v>
       </c>
       <c r="G118" t="n">
-        <v>10.7</v>
+        <v>8</v>
       </c>
       <c r="H118" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J118" t="n">
-        <v>33.6</v>
+        <v>26.5</v>
       </c>
       <c r="K118" t="n">
-        <v>13.3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
@@ -11362,31 +11361,31 @@
         <v>144</v>
       </c>
       <c r="C119" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D119" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E119" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F119" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G119" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H119" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I119" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J119" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K119" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="120">
@@ -11397,31 +11396,31 @@
         <v>144</v>
       </c>
       <c r="C120" t="n">
-        <v>38.9</v>
+        <v>60.1</v>
       </c>
       <c r="D120" t="n">
-        <v>52</v>
+        <v>62.9</v>
       </c>
       <c r="E120" t="n">
-        <v>16.3</v>
+        <v>22.7</v>
       </c>
       <c r="F120" t="n">
-        <v>33.3</v>
+        <v>26.3</v>
       </c>
       <c r="G120" t="n">
-        <v>27.8</v>
+        <v>6.7</v>
       </c>
       <c r="H120" t="n">
-        <v>22.2</v>
+        <v>56.3</v>
       </c>
       <c r="I120" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="K120" t="n">
         <v>5.6</v>
-      </c>
-      <c r="J120" t="n">
-        <v>31</v>
-      </c>
-      <c r="K120" t="n">
-        <v>-11.1</v>
       </c>
     </row>
     <row r="121">
@@ -11432,31 +11431,31 @@
         <v>144</v>
       </c>
       <c r="C121" t="n">
-        <v>60.1</v>
+        <v>57.5</v>
       </c>
       <c r="D121" t="n">
-        <v>62.9</v>
+        <v>59</v>
       </c>
       <c r="E121" t="n">
-        <v>22.7</v>
+        <v>24.5</v>
       </c>
       <c r="F121" t="n">
-        <v>26.3</v>
+        <v>38.6</v>
       </c>
       <c r="G121" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H121" t="n">
-        <v>56.3</v>
+        <v>41.7</v>
       </c>
       <c r="I121" t="n">
-        <v>3.1</v>
+        <v>8.2</v>
       </c>
       <c r="J121" t="n">
-        <v>20.9</v>
+        <v>18.1</v>
       </c>
       <c r="K121" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="122">
@@ -11464,34 +11463,34 @@
         <v>291</v>
       </c>
       <c r="B122" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C122" t="n">
-        <v>57.5</v>
+        <v>70.8</v>
       </c>
       <c r="D122" t="n">
-        <v>59</v>
+        <v>64.4</v>
       </c>
       <c r="E122" t="n">
-        <v>24.5</v>
+        <v>27.3</v>
       </c>
       <c r="F122" t="n">
-        <v>38.6</v>
+        <v>63.6</v>
       </c>
       <c r="G122" t="n">
-        <v>7.5</v>
+        <v>8.3</v>
       </c>
       <c r="H122" t="n">
-        <v>41.7</v>
+        <v>76.9</v>
       </c>
       <c r="I122" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="J122" t="n">
-        <v>18.1</v>
+        <v>28.9</v>
       </c>
       <c r="K122" t="n">
-        <v>6.3</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="123">
@@ -11502,31 +11501,31 @@
         <v>166</v>
       </c>
       <c r="C123" t="n">
-        <v>70.8</v>
+        <v>62.4</v>
       </c>
       <c r="D123" t="n">
-        <v>64.4</v>
+        <v>67.5</v>
       </c>
       <c r="E123" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="F123" t="n">
-        <v>63.6</v>
+        <v>44.3</v>
       </c>
       <c r="G123" t="n">
-        <v>8.3</v>
+        <v>2.4</v>
       </c>
       <c r="H123" t="n">
-        <v>76.9</v>
+        <v>48.4</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>28.9</v>
+        <v>20.7</v>
       </c>
       <c r="K123" t="n">
-        <v>20.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="124">
@@ -11537,31 +11536,31 @@
         <v>166</v>
       </c>
       <c r="C124" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="D124" t="n">
-        <v>67.5</v>
+        <v>64.8</v>
       </c>
       <c r="E124" t="n">
-        <v>22.6</v>
+        <v>11.2</v>
       </c>
       <c r="F124" t="n">
-        <v>44.3</v>
+        <v>32.4</v>
       </c>
       <c r="G124" t="n">
-        <v>2.4</v>
+        <v>6.7</v>
       </c>
       <c r="H124" t="n">
-        <v>48.4</v>
+        <v>29.6</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J124" t="n">
-        <v>20.7</v>
+        <v>19.6</v>
       </c>
       <c r="K124" t="n">
-        <v>14</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="125">
@@ -11575,98 +11574,98 @@
         <v>60.7</v>
       </c>
       <c r="D125" t="n">
-        <v>64.8</v>
+        <v>63.9</v>
       </c>
       <c r="E125" t="n">
-        <v>11.2</v>
+        <v>33.8</v>
       </c>
       <c r="F125" t="n">
-        <v>32.4</v>
+        <v>68.4</v>
       </c>
       <c r="G125" t="n">
-        <v>6.7</v>
+        <v>9.1</v>
       </c>
       <c r="H125" t="n">
-        <v>29.6</v>
+        <v>55.6</v>
       </c>
       <c r="I125" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J125" t="n">
-        <v>19.6</v>
+        <v>40.9</v>
       </c>
       <c r="K125" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
         <v>166</v>
       </c>
       <c r="C126" t="n">
-        <v>60.7</v>
+        <v>60</v>
       </c>
       <c r="D126" t="n">
-        <v>63.9</v>
+        <v>58.8</v>
       </c>
       <c r="E126" t="n">
-        <v>33.8</v>
+        <v>10.3</v>
       </c>
       <c r="F126" t="n">
-        <v>68.4</v>
+        <v>29.4</v>
       </c>
       <c r="G126" t="n">
-        <v>9.1</v>
+        <v>10.8</v>
       </c>
       <c r="H126" t="n">
-        <v>55.6</v>
+        <v>37.7</v>
       </c>
       <c r="I126" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J126" t="n">
-        <v>40.9</v>
+        <v>22.7</v>
       </c>
       <c r="K126" t="n">
-        <v>40</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="B127" t="s">
         <v>166</v>
       </c>
       <c r="C127" t="n">
-        <v>60</v>
+        <v>67.3</v>
       </c>
       <c r="D127" t="n">
-        <v>58.8</v>
+        <v>63.7</v>
       </c>
       <c r="E127" t="n">
-        <v>10.3</v>
+        <v>28.4</v>
       </c>
       <c r="F127" t="n">
-        <v>29.4</v>
+        <v>45.9</v>
       </c>
       <c r="G127" t="n">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="H127" t="n">
-        <v>37.7</v>
+        <v>46.7</v>
       </c>
       <c r="I127" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="J127" t="n">
-        <v>22.7</v>
+        <v>46.8</v>
       </c>
       <c r="K127" t="n">
-        <v>2.7</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="128">
@@ -11677,31 +11676,29 @@
         <v>166</v>
       </c>
       <c r="C128" t="n">
-        <v>67.3</v>
+        <v>84.6</v>
       </c>
       <c r="D128" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="E128" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="E128"/>
+      <c r="F128" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J128" t="n">
         <v>28.4</v>
       </c>
-      <c r="F128" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="G128" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H128" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I128" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J128" t="n">
-        <v>46.8</v>
-      </c>
       <c r="K128" t="n">
-        <v>23.6</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="129">
@@ -11712,29 +11709,31 @@
         <v>166</v>
       </c>
       <c r="C129" t="n">
-        <v>84.6</v>
+        <v>50</v>
       </c>
       <c r="D129" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E129"/>
+        <v>45.1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
       <c r="F129" t="n">
-        <v>47.1</v>
+        <v>25</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H129" t="n">
-        <v>45.2</v>
+        <v>37.5</v>
       </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J129" t="n">
-        <v>28.4</v>
+        <v>31.2</v>
       </c>
       <c r="K129" t="n">
-        <v>19.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="130">
@@ -11745,31 +11744,31 @@
         <v>166</v>
       </c>
       <c r="C130" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D130" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E130" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G130" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H130" t="n">
         <v>50</v>
       </c>
-      <c r="D130" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>25</v>
-      </c>
-      <c r="G130" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H130" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I130" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J130" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K130" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="131">
@@ -11780,31 +11779,31 @@
         <v>166</v>
       </c>
       <c r="C131" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D131" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E131" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F131" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G131" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H131" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I131" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J131" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K131" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="132">
@@ -11815,31 +11814,31 @@
         <v>166</v>
       </c>
       <c r="C132" t="n">
-        <v>65.8</v>
+        <v>50.9</v>
       </c>
       <c r="D132" t="n">
-        <v>67.5</v>
+        <v>60.7</v>
       </c>
       <c r="E132" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F132" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G132" t="n">
-        <v>7.9</v>
+        <v>9.6</v>
       </c>
       <c r="H132" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="I132" t="n">
         <v>2.6</v>
       </c>
       <c r="J132" t="n">
-        <v>26.8</v>
+        <v>21.7</v>
       </c>
       <c r="K132" t="n">
-        <v>13.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="133">
@@ -11850,31 +11849,31 @@
         <v>166</v>
       </c>
       <c r="C133" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="D133" t="n">
-        <v>60.7</v>
+        <v>56.7</v>
       </c>
       <c r="E133" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F133" t="n">
-        <v>38.6</v>
+        <v>50</v>
       </c>
       <c r="G133" t="n">
-        <v>9.6</v>
+        <v>22.2</v>
       </c>
       <c r="H133" t="n">
-        <v>54.4</v>
+        <v>20</v>
       </c>
       <c r="I133" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K133" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -11885,31 +11884,31 @@
         <v>166</v>
       </c>
       <c r="C134" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D134" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E134" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F134" t="n">
         <v>50</v>
       </c>
       <c r="G134" t="n">
-        <v>22.2</v>
+        <v>4</v>
       </c>
       <c r="H134" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="135">
@@ -11920,31 +11919,31 @@
         <v>166</v>
       </c>
       <c r="C135" t="n">
-        <v>69.5</v>
+        <v>63</v>
       </c>
       <c r="D135" t="n">
-        <v>70.3</v>
+        <v>64.4</v>
       </c>
       <c r="E135" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F135" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="G135" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="H135" t="n">
-        <v>41.9</v>
+        <v>45.7</v>
       </c>
       <c r="I135" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J135" t="n">
-        <v>26.3</v>
+        <v>21.8</v>
       </c>
       <c r="K135" t="n">
-        <v>18.2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136">
@@ -11955,97 +11954,62 @@
         <v>166</v>
       </c>
       <c r="C136" t="n">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="D136" t="n">
-        <v>64.4</v>
-      </c>
-      <c r="E136" t="n">
-        <v>27</v>
-      </c>
+        <v>57.6</v>
+      </c>
+      <c r="E136"/>
       <c r="F136" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="G136" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="H136" t="n">
-        <v>45.7</v>
+        <v>68.8</v>
       </c>
       <c r="I136" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>21.8</v>
+        <v>16.7</v>
       </c>
       <c r="K136" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
-        <v>305</v>
-      </c>
+      <c r="A137"/>
       <c r="B137" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C137" t="n">
-        <v>44</v>
+        <v>58.1</v>
       </c>
       <c r="D137" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E137"/>
+        <v>61</v>
+      </c>
+      <c r="E137" t="n">
+        <v>21</v>
+      </c>
       <c r="F137" t="n">
-        <v>33.3</v>
+        <v>36.1</v>
       </c>
       <c r="G137" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H137" t="n">
-        <v>68.8</v>
+        <v>45.2</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
-        <v>16.7</v>
+        <v>24.9</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138"/>
-      <c r="B138" t="s">
-        <v>181</v>
-      </c>
-      <c r="C138" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="D138" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="E138" t="n">
-        <v>21</v>
-      </c>
-      <c r="F138" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="G138" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H138" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="I138" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J138" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="K138" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -487,9 +487,6 @@
   </si>
   <si>
     <t xml:space="preserve">Marcus Knecht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Knecht</t>
   </si>
   <si>
     <t xml:space="preserve">Matt Brandt</t>
@@ -982,8 +979,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K174" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K174"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K173" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K173"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -6365,31 +6362,31 @@
         <v>144</v>
       </c>
       <c r="C150" t="n">
-        <v>67.6</v>
+        <v>68.7</v>
       </c>
       <c r="D150" t="n">
-        <v>30.1</v>
+        <v>28.8</v>
       </c>
       <c r="E150" t="n">
-        <v>37.5</v>
+        <v>39.9</v>
       </c>
       <c r="F150" t="n">
-        <v>30.1</v>
+        <v>28.8</v>
       </c>
       <c r="G150" t="n">
-        <v>31.3</v>
+        <v>30.3</v>
       </c>
       <c r="H150" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I150" t="n">
-        <v>38.2</v>
+        <v>36.7</v>
       </c>
       <c r="J150" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
       <c r="K150" t="n">
-        <v>47.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="151">
@@ -6400,101 +6397,101 @@
         <v>144</v>
       </c>
       <c r="C151" t="n">
-        <v>81.8</v>
+        <v>64.7</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E151" t="n">
-        <v>81.8</v>
+        <v>39.7</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G151" t="n">
-        <v>11.1</v>
+        <v>21.4</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="I151" t="n">
-        <v>20</v>
+        <v>60.3</v>
       </c>
       <c r="J151" t="n">
-        <v>40</v>
+        <v>22.4</v>
       </c>
       <c r="K151" t="n">
-        <v>20</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="B152" t="s">
         <v>144</v>
       </c>
       <c r="C152" t="n">
-        <v>64.7</v>
+        <v>56.1</v>
       </c>
       <c r="D152" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="E152" t="n">
-        <v>39.7</v>
+        <v>36.9</v>
       </c>
       <c r="F152" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="G152" t="n">
-        <v>21.4</v>
+        <v>22.5</v>
       </c>
       <c r="H152" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>60.3</v>
+        <v>40.5</v>
       </c>
       <c r="J152" t="n">
-        <v>22.4</v>
+        <v>27</v>
       </c>
       <c r="K152" t="n">
-        <v>28.1</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>115</v>
+        <v>159</v>
       </c>
       <c r="B153" t="s">
         <v>144</v>
       </c>
       <c r="C153" t="n">
-        <v>56.1</v>
+        <v>78.6</v>
       </c>
       <c r="D153" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="E153" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="F153" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="G153" t="n">
-        <v>22.5</v>
+        <v>28.9</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>40.5</v>
+        <v>57.1</v>
       </c>
       <c r="J153" t="n">
-        <v>27</v>
+        <v>14.3</v>
       </c>
       <c r="K153" t="n">
-        <v>40.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="154">
@@ -6505,31 +6502,31 @@
         <v>144</v>
       </c>
       <c r="C154" t="n">
-        <v>78.6</v>
+        <v>62.1</v>
       </c>
       <c r="D154" t="n">
-        <v>39.1</v>
+        <v>10.6</v>
       </c>
       <c r="E154" t="n">
-        <v>39.5</v>
+        <v>51.5</v>
       </c>
       <c r="F154" t="n">
-        <v>39.1</v>
+        <v>10.6</v>
       </c>
       <c r="G154" t="n">
-        <v>28.9</v>
+        <v>11.8</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="I154" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J154" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="K154" t="n">
-        <v>14.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="155">
@@ -6540,31 +6537,31 @@
         <v>144</v>
       </c>
       <c r="C155" t="n">
-        <v>62.1</v>
+        <v>63.2</v>
       </c>
       <c r="D155" t="n">
-        <v>10.6</v>
+        <v>45</v>
       </c>
       <c r="E155" t="n">
-        <v>51.5</v>
+        <v>18.2</v>
       </c>
       <c r="F155" t="n">
-        <v>10.6</v>
+        <v>45</v>
       </c>
       <c r="G155" t="n">
-        <v>11.8</v>
+        <v>26.9</v>
       </c>
       <c r="H155" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I155" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K155" t="n">
-        <v>32.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="156">
@@ -6575,31 +6572,31 @@
         <v>144</v>
       </c>
       <c r="C156" t="n">
-        <v>63.2</v>
+        <v>74.1</v>
       </c>
       <c r="D156" t="n">
-        <v>45</v>
+        <v>12.8</v>
       </c>
       <c r="E156" t="n">
-        <v>18.2</v>
+        <v>61.3</v>
       </c>
       <c r="F156" t="n">
-        <v>45</v>
+        <v>12.8</v>
       </c>
       <c r="G156" t="n">
-        <v>26.9</v>
+        <v>25.2</v>
       </c>
       <c r="H156" t="n">
-        <v>7.7</v>
+        <v>16.5</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="J156" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="K156" t="n">
-        <v>25</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="157">
@@ -6610,31 +6607,31 @@
         <v>144</v>
       </c>
       <c r="C157" t="n">
-        <v>74.1</v>
+        <v>74.6</v>
       </c>
       <c r="D157" t="n">
-        <v>12.8</v>
+        <v>25.3</v>
       </c>
       <c r="E157" t="n">
-        <v>61.3</v>
+        <v>49.3</v>
       </c>
       <c r="F157" t="n">
-        <v>12.8</v>
+        <v>25.3</v>
       </c>
       <c r="G157" t="n">
-        <v>25.2</v>
+        <v>8.9</v>
       </c>
       <c r="H157" t="n">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="I157" t="n">
-        <v>32.8</v>
+        <v>47.2</v>
       </c>
       <c r="J157" t="n">
-        <v>34.5</v>
+        <v>22.2</v>
       </c>
       <c r="K157" t="n">
-        <v>36.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="158">
@@ -6642,69 +6639,69 @@
         <v>164</v>
       </c>
       <c r="B158" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C158" t="n">
-        <v>74.6</v>
+        <v>70.5</v>
       </c>
       <c r="D158" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="E158" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F158" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="G158" t="n">
-        <v>8.9</v>
+        <v>37.7</v>
       </c>
       <c r="H158" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="I158" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="J158" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="K158" t="n">
-        <v>33.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" t="s">
         <v>165</v>
       </c>
-      <c r="B159" t="s">
-        <v>166</v>
-      </c>
       <c r="C159" t="n">
-        <v>70.5</v>
+        <v>66.9</v>
       </c>
       <c r="D159" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="E159" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="F159" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="G159" t="n">
-        <v>37.7</v>
+        <v>15.9</v>
       </c>
       <c r="H159" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="I159" t="n">
-        <v>51.9</v>
+        <v>57.7</v>
       </c>
       <c r="J159" t="n">
-        <v>21.2</v>
+        <v>18.3</v>
       </c>
       <c r="K159" t="n">
-        <v>39.1</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="160">
@@ -6712,34 +6709,34 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C160" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="D160" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="E160" t="n">
-        <v>45.6</v>
+        <v>47.9</v>
       </c>
       <c r="F160" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="G160" t="n">
-        <v>15.9</v>
+        <v>37.7</v>
       </c>
       <c r="H160" t="n">
-        <v>6.7</v>
+        <v>12.5</v>
       </c>
       <c r="I160" t="n">
-        <v>57.7</v>
+        <v>29.6</v>
       </c>
       <c r="J160" t="n">
-        <v>18.3</v>
+        <v>48.1</v>
       </c>
       <c r="K160" t="n">
-        <v>43.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="161">
@@ -6747,34 +6744,34 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C161" t="n">
-        <v>64.6</v>
+        <v>59</v>
       </c>
       <c r="D161" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E161" t="n">
-        <v>47.9</v>
+        <v>37.9</v>
       </c>
       <c r="F161" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G161" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="H161" t="n">
         <v>12.5</v>
       </c>
       <c r="I161" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="J161" t="n">
-        <v>48.1</v>
+        <v>36.8</v>
       </c>
       <c r="K161" t="n">
-        <v>38.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="162">
@@ -6782,34 +6779,34 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C162" t="n">
-        <v>59</v>
+        <v>65.9</v>
       </c>
       <c r="D162" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="E162" t="n">
-        <v>37.9</v>
+        <v>50.4</v>
       </c>
       <c r="F162" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="G162" t="n">
-        <v>34.5</v>
+        <v>9.5</v>
       </c>
       <c r="H162" t="n">
-        <v>12.5</v>
+        <v>15.8</v>
       </c>
       <c r="I162" t="n">
-        <v>31.6</v>
+        <v>63.6</v>
       </c>
       <c r="J162" t="n">
-        <v>36.8</v>
+        <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>29.4</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="163">
@@ -6817,34 +6814,34 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C163" t="n">
-        <v>65.9</v>
+        <v>80</v>
       </c>
       <c r="D163" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E163" t="n">
-        <v>50.4</v>
+        <v>64</v>
       </c>
       <c r="F163" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G163" t="n">
-        <v>9.5</v>
+        <v>23.7</v>
       </c>
       <c r="H163" t="n">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="I163" t="n">
-        <v>63.6</v>
+        <v>36.1</v>
       </c>
       <c r="J163" t="n">
-        <v>17</v>
+        <v>33.7</v>
       </c>
       <c r="K163" t="n">
-        <v>39.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="164">
@@ -6852,34 +6849,34 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C164" t="n">
-        <v>80</v>
+        <v>55.2</v>
       </c>
       <c r="D164" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="E164" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="F164" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="G164" t="n">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="H164" t="n">
-        <v>10.5</v>
+        <v>12.9</v>
       </c>
       <c r="I164" t="n">
-        <v>36.1</v>
+        <v>52.1</v>
       </c>
       <c r="J164" t="n">
-        <v>33.7</v>
+        <v>22.9</v>
       </c>
       <c r="K164" t="n">
-        <v>47.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="165">
@@ -6887,34 +6884,34 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C165" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="D165" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>36.9</v>
+        <v>75</v>
       </c>
       <c r="F165" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>27</v>
+        <v>66.7</v>
       </c>
       <c r="H165" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>52.1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -6922,34 +6919,34 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C166" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E166" t="n">
-        <v>75</v>
+        <v>37.7</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="G166" t="n">
-        <v>66.7</v>
+        <v>13.2</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="167">
@@ -6957,34 +6954,34 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C167" t="n">
-        <v>56.2</v>
+        <v>61.3</v>
       </c>
       <c r="D167" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="E167" t="n">
-        <v>37.7</v>
+        <v>40.6</v>
       </c>
       <c r="F167" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="G167" t="n">
-        <v>13.2</v>
+        <v>9.5</v>
       </c>
       <c r="H167" t="n">
-        <v>18.7</v>
+        <v>7.6</v>
       </c>
       <c r="I167" t="n">
-        <v>36.5</v>
+        <v>60.4</v>
       </c>
       <c r="J167" t="n">
-        <v>30.2</v>
+        <v>17.8</v>
       </c>
       <c r="K167" t="n">
-        <v>48.3</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="168">
@@ -6992,34 +6989,34 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C168" t="n">
-        <v>61.3</v>
+        <v>71.2</v>
       </c>
       <c r="D168" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="E168" t="n">
-        <v>40.6</v>
+        <v>54.6</v>
       </c>
       <c r="F168" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="G168" t="n">
-        <v>9.5</v>
+        <v>25</v>
       </c>
       <c r="H168" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="I168" t="n">
-        <v>60.4</v>
+        <v>35.8</v>
       </c>
       <c r="J168" t="n">
-        <v>17.8</v>
+        <v>30.9</v>
       </c>
       <c r="K168" t="n">
-        <v>28.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="169">
@@ -7027,34 +7024,34 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C169" t="n">
-        <v>71.2</v>
+        <v>78</v>
       </c>
       <c r="D169" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="E169" t="n">
-        <v>54.6</v>
+        <v>47.3</v>
       </c>
       <c r="F169" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="G169" t="n">
-        <v>25</v>
+        <v>39.4</v>
       </c>
       <c r="H169" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I169" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="J169" t="n">
-        <v>30.9</v>
+        <v>22.7</v>
       </c>
       <c r="K169" t="n">
-        <v>56.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="170">
@@ -7062,34 +7059,34 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C170" t="n">
-        <v>78</v>
+        <v>73.6</v>
       </c>
       <c r="D170" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="E170" t="n">
-        <v>47.3</v>
+        <v>53.6</v>
       </c>
       <c r="F170" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="G170" t="n">
-        <v>39.4</v>
+        <v>18.9</v>
       </c>
       <c r="H170" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="I170" t="n">
-        <v>36.4</v>
+        <v>30.8</v>
       </c>
       <c r="J170" t="n">
-        <v>22.7</v>
+        <v>30.8</v>
       </c>
       <c r="K170" t="n">
-        <v>68.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="171">
@@ -7097,57 +7094,51 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C171" t="n">
-        <v>73.6</v>
+        <v>37.5</v>
       </c>
       <c r="D171" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E171" t="n">
-        <v>53.6</v>
+        <v>4.2</v>
       </c>
       <c r="F171" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G171" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I171" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J171" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K171" t="n">
-        <v>47.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I171"/>
+      <c r="J171"/>
+      <c r="K171"/>
     </row>
     <row r="172">
       <c r="A172" t="s">
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C172" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>33.3</v>
       </c>
       <c r="E172" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F172" t="n">
         <v>33.3</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7157,65 +7148,36 @@
       <c r="K172"/>
     </row>
     <row r="173">
-      <c r="A173" t="s">
+      <c r="A173"/>
+      <c r="B173" t="s">
         <v>180</v>
       </c>
-      <c r="B173" t="s">
-        <v>166</v>
-      </c>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>69.3</v>
       </c>
       <c r="D173" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="E173" t="n">
-        <v>-33.3</v>
+        <v>46.4</v>
       </c>
       <c r="F173" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="G173" t="n">
-        <v>100</v>
+        <v>26.8</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173"/>
-      <c r="J173"/>
-      <c r="K173"/>
-    </row>
-    <row r="174">
-      <c r="A174"/>
-      <c r="B174" t="s">
-        <v>181</v>
-      </c>
-      <c r="C174" t="n">
-        <v>69.4</v>
-      </c>
-      <c r="D174" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E174" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="F174" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="G174" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H174" t="n">
-        <v>9</v>
-      </c>
-      <c r="I174" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="J174" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="K174" t="n">
-        <v>37.3</v>
+        <v>9.1</v>
+      </c>
+      <c r="I173" t="n">
+        <v>47</v>
+      </c>
+      <c r="J173" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>37.4</v>
       </c>
     </row>
   </sheetData>
@@ -7247,22 +7209,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7271,18 +7233,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7317,7 +7279,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7387,7 +7349,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7457,7 +7419,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7492,7 +7454,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7527,7 +7489,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7597,7 +7559,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7632,7 +7594,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7667,7 +7629,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7702,7 +7664,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7770,7 +7732,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7803,7 +7765,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7836,7 +7798,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7869,7 +7831,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
@@ -7904,7 +7866,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B20" t="s">
         <v>46</v>
@@ -7939,7 +7901,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s">
         <v>46</v>
@@ -8009,7 +7971,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
@@ -8044,7 +8006,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
@@ -8079,7 +8041,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
@@ -8114,7 +8076,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
@@ -8149,7 +8111,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -8184,7 +8146,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -8219,7 +8181,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -8254,7 +8216,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -8289,7 +8251,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
@@ -8324,7 +8286,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -8359,7 +8321,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -8394,7 +8356,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -8429,7 +8391,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
@@ -8464,7 +8426,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -8499,7 +8461,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
@@ -8532,7 +8494,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
@@ -8602,7 +8564,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
@@ -8637,7 +8599,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
@@ -8672,7 +8634,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
@@ -8707,7 +8669,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -8740,7 +8702,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
@@ -8775,7 +8737,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
@@ -8810,7 +8772,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
@@ -8845,7 +8807,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -8880,7 +8842,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -8915,7 +8877,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
         <v>53</v>
@@ -8950,7 +8912,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -8985,7 +8947,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
         <v>53</v>
@@ -9018,7 +8980,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
         <v>53</v>
@@ -9053,7 +9015,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B53" t="s">
         <v>71</v>
@@ -9088,7 +9050,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B54" t="s">
         <v>71</v>
@@ -9123,7 +9085,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
         <v>71</v>
@@ -9158,7 +9120,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
         <v>71</v>
@@ -9191,7 +9153,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
         <v>71</v>
@@ -9226,7 +9188,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B58" t="s">
         <v>71</v>
@@ -9261,7 +9223,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
         <v>71</v>
@@ -9296,7 +9258,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
         <v>71</v>
@@ -9331,7 +9293,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
         <v>71</v>
@@ -9366,7 +9328,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B62" t="s">
         <v>71</v>
@@ -9401,7 +9363,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B63" t="s">
         <v>71</v>
@@ -9436,7 +9398,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B64" t="s">
         <v>71</v>
@@ -9506,7 +9468,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B66" t="s">
         <v>71</v>
@@ -9576,7 +9538,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B68" t="s">
         <v>93</v>
@@ -9611,7 +9573,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B69" t="s">
         <v>93</v>
@@ -9646,7 +9608,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
         <v>93</v>
@@ -9681,7 +9643,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B71" t="s">
         <v>93</v>
@@ -9716,7 +9678,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
         <v>93</v>
@@ -9751,7 +9713,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
         <v>93</v>
@@ -9786,7 +9748,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
         <v>93</v>
@@ -9821,7 +9783,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s">
         <v>93</v>
@@ -9856,7 +9818,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
         <v>93</v>
@@ -9891,7 +9853,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
         <v>93</v>
@@ -9926,7 +9888,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
         <v>93</v>
@@ -9961,7 +9923,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
         <v>93</v>
@@ -9996,7 +9958,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B80" t="s">
         <v>107</v>
@@ -10031,7 +9993,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
@@ -10066,7 +10028,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
@@ -10101,7 +10063,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
@@ -10134,7 +10096,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
         <v>107</v>
@@ -10169,7 +10131,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B85" t="s">
         <v>107</v>
@@ -10239,7 +10201,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
@@ -10274,7 +10236,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
@@ -10309,7 +10271,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
@@ -10344,7 +10306,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
         <v>107</v>
@@ -10377,7 +10339,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B91" t="s">
         <v>107</v>
@@ -10412,7 +10374,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B92" t="s">
         <v>107</v>
@@ -10447,7 +10409,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
         <v>107</v>
@@ -10482,7 +10444,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B94" t="s">
         <v>107</v>
@@ -10517,7 +10479,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B95" t="s">
         <v>107</v>
@@ -10552,7 +10514,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B96" t="s">
         <v>128</v>
@@ -10587,7 +10549,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
@@ -10622,7 +10584,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
@@ -10657,7 +10619,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
@@ -10692,7 +10654,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s">
         <v>128</v>
@@ -10727,7 +10689,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
@@ -10762,7 +10724,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
@@ -10797,7 +10759,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B103" t="s">
         <v>128</v>
@@ -10832,7 +10794,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B104" t="s">
         <v>128</v>
@@ -10867,7 +10829,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B105" t="s">
         <v>128</v>
@@ -10902,7 +10864,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B106" t="s">
         <v>144</v>
@@ -10937,7 +10899,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B107" t="s">
         <v>144</v>
@@ -11007,7 +10969,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B109" t="s">
         <v>144</v>
@@ -11042,7 +11004,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B110" t="s">
         <v>144</v>
@@ -11075,7 +11037,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B111" t="s">
         <v>144</v>
@@ -11110,7 +11072,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B112" t="s">
         <v>144</v>
@@ -11180,7 +11142,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B114" t="s">
         <v>144</v>
@@ -11215,7 +11177,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
         <v>144</v>
@@ -11250,7 +11212,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B116" t="s">
         <v>144</v>
@@ -11285,7 +11247,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
         <v>144</v>
@@ -11320,7 +11282,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
         <v>144</v>
@@ -11355,7 +11317,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
         <v>144</v>
@@ -11390,7 +11352,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
         <v>144</v>
@@ -11425,7 +11387,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B121" t="s">
         <v>144</v>
@@ -11460,10 +11422,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B122" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C122" t="n">
         <v>70.8</v>
@@ -11495,10 +11457,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C123" t="n">
         <v>62.4</v>
@@ -11530,10 +11492,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C124" t="n">
         <v>60.7</v>
@@ -11565,10 +11527,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B125" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C125" t="n">
         <v>60.7</v>
@@ -11600,10 +11562,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B126" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C126" t="n">
         <v>60</v>
@@ -11635,10 +11597,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C127" t="n">
         <v>67.3</v>
@@ -11670,10 +11632,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B128" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C128" t="n">
         <v>84.6</v>
@@ -11703,10 +11665,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B129" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C129" t="n">
         <v>50</v>
@@ -11738,10 +11700,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B130" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C130" t="n">
         <v>61.3</v>
@@ -11773,10 +11735,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C131" t="n">
         <v>65.8</v>
@@ -11808,10 +11770,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B132" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C132" t="n">
         <v>50.9</v>
@@ -11843,10 +11805,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B133" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C133" t="n">
         <v>66.7</v>
@@ -11878,10 +11840,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C134" t="n">
         <v>69.5</v>
@@ -11913,10 +11875,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B135" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C135" t="n">
         <v>63</v>
@@ -11948,10 +11910,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B136" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C136" t="n">
         <v>44</v>
@@ -11982,7 +11944,7 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C137" t="n">
         <v>58.1</v>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -444,13 +444,10 @@
     <t xml:space="preserve">Xavier Whittle</t>
   </si>
   <si>
-    <t xml:space="preserve">Ben Sitarenios</t>
+    <t xml:space="preserve">Benjamin Sitarenios</t>
   </si>
   <si>
     <t xml:space="preserve">Toronto Maple Leafs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benjamin Sitarenios</t>
   </si>
   <si>
     <t xml:space="preserve">Benjamin Sterritt</t>
@@ -979,8 +976,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K173" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K173"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K172" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K172"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -5919,25 +5916,31 @@
         <v>144</v>
       </c>
       <c r="C137" t="n">
-        <v>100</v>
-      </c>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
+        <v>78.9</v>
+      </c>
+      <c r="D137" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E137" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F137" t="n">
+        <v>27.3</v>
+      </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="J137" t="n">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="138">
@@ -5948,31 +5951,31 @@
         <v>144</v>
       </c>
       <c r="C138" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="D138" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="E138" t="n">
-        <v>50.5</v>
+        <v>6.7</v>
       </c>
       <c r="F138" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="G138" t="n">
-        <v>17.6</v>
+        <v>33.3</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I138" t="n">
-        <v>42.9</v>
+        <v>25</v>
       </c>
       <c r="J138" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K138" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -5983,31 +5986,31 @@
         <v>144</v>
       </c>
       <c r="C139" t="n">
-        <v>66.7</v>
+        <v>64.4</v>
       </c>
       <c r="D139" t="n">
-        <v>60</v>
+        <v>20.9</v>
       </c>
       <c r="E139" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="G139" t="n">
+        <v>17</v>
+      </c>
+      <c r="H139" t="n">
         <v>6.7</v>
       </c>
-      <c r="F139" t="n">
-        <v>60</v>
-      </c>
-      <c r="G139" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="H139" t="n">
-        <v>11.1</v>
-      </c>
       <c r="I139" t="n">
-        <v>25</v>
+        <v>47.6</v>
       </c>
       <c r="J139" t="n">
-        <v>25</v>
+        <v>21.4</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="140">
@@ -6018,31 +6021,31 @@
         <v>144</v>
       </c>
       <c r="C140" t="n">
-        <v>64.4</v>
+        <v>35</v>
       </c>
       <c r="D140" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="E140" t="n">
-        <v>43.5</v>
+        <v>21.7</v>
       </c>
       <c r="F140" t="n">
-        <v>20.9</v>
+        <v>13.3</v>
       </c>
       <c r="G140" t="n">
-        <v>17</v>
+        <v>33.3</v>
       </c>
       <c r="H140" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="J140" t="n">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>43.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6053,31 +6056,31 @@
         <v>144</v>
       </c>
       <c r="C141" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="D141" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
       <c r="E141" t="n">
-        <v>21.7</v>
+        <v>37.1</v>
       </c>
       <c r="F141" t="n">
-        <v>13.3</v>
+        <v>33.9</v>
       </c>
       <c r="G141" t="n">
-        <v>33.3</v>
+        <v>30.6</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I141" t="n">
-        <v>50</v>
+        <v>48.4</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="142">
@@ -6088,31 +6091,25 @@
         <v>144</v>
       </c>
       <c r="C142" t="n">
-        <v>71</v>
-      </c>
-      <c r="D142" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="E142" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="F142" t="n">
-        <v>33.9</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
       <c r="G142" t="n">
-        <v>30.6</v>
+        <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>48.4</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>22.6</v>
+        <v>100</v>
       </c>
       <c r="K142" t="n">
-        <v>35.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -6123,25 +6120,31 @@
         <v>144</v>
       </c>
       <c r="C143" t="n">
-        <v>100</v>
-      </c>
-      <c r="D143"/>
-      <c r="E143"/>
-      <c r="F143"/>
+        <v>72.4</v>
+      </c>
+      <c r="D143" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="F143" t="n">
+        <v>27.6</v>
+      </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>31.3</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J143" t="n">
-        <v>100</v>
+        <v>31.1</v>
       </c>
       <c r="K143" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="144">
@@ -6152,31 +6155,31 @@
         <v>144</v>
       </c>
       <c r="C144" t="n">
-        <v>72.4</v>
+        <v>52.9</v>
       </c>
       <c r="D144" t="n">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="E144" t="n">
-        <v>44.8</v>
+        <v>24.9</v>
       </c>
       <c r="F144" t="n">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="G144" t="n">
-        <v>31.3</v>
+        <v>11.1</v>
       </c>
       <c r="H144" t="n">
-        <v>10.8</v>
+        <v>30</v>
       </c>
       <c r="I144" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J144" t="n">
-        <v>31.1</v>
+        <v>33.3</v>
       </c>
       <c r="K144" t="n">
-        <v>38.6</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="145">
@@ -6187,31 +6190,31 @@
         <v>144</v>
       </c>
       <c r="C145" t="n">
-        <v>52.9</v>
+        <v>64.7</v>
       </c>
       <c r="D145" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="E145" t="n">
-        <v>24.9</v>
+        <v>39.2</v>
       </c>
       <c r="F145" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
       <c r="G145" t="n">
-        <v>11.1</v>
+        <v>18.6</v>
       </c>
       <c r="H145" t="n">
-        <v>30</v>
+        <v>8.1</v>
       </c>
       <c r="I145" t="n">
-        <v>50</v>
+        <v>58.9</v>
       </c>
       <c r="J145" t="n">
-        <v>33.3</v>
+        <v>16.1</v>
       </c>
       <c r="K145" t="n">
-        <v>16.7</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="146">
@@ -6222,31 +6225,31 @@
         <v>144</v>
       </c>
       <c r="C146" t="n">
-        <v>64.7</v>
+        <v>66.7</v>
       </c>
       <c r="D146" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>39.2</v>
+        <v>66.7</v>
       </c>
       <c r="F146" t="n">
-        <v>25.5</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="H146" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>58.9</v>
+        <v>75</v>
       </c>
       <c r="J146" t="n">
-        <v>16.1</v>
+        <v>25</v>
       </c>
       <c r="K146" t="n">
-        <v>32.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -6257,31 +6260,31 @@
         <v>144</v>
       </c>
       <c r="C147" t="n">
-        <v>66.7</v>
+        <v>67.5</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="E147" t="n">
-        <v>66.7</v>
+        <v>46.8</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>20.7</v>
       </c>
       <c r="G147" t="n">
-        <v>18.2</v>
+        <v>31.9</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="I147" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
       <c r="J147" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="148">
@@ -6292,31 +6295,31 @@
         <v>144</v>
       </c>
       <c r="C148" t="n">
-        <v>67.5</v>
+        <v>50</v>
       </c>
       <c r="D148" t="n">
-        <v>20.7</v>
+        <v>14.3</v>
       </c>
       <c r="E148" t="n">
-        <v>46.8</v>
+        <v>35.7</v>
       </c>
       <c r="F148" t="n">
-        <v>20.7</v>
+        <v>14.3</v>
       </c>
       <c r="G148" t="n">
-        <v>31.9</v>
+        <v>28.6</v>
       </c>
       <c r="H148" t="n">
-        <v>6.9</v>
+        <v>12.5</v>
       </c>
       <c r="I148" t="n">
-        <v>73.7</v>
+        <v>75</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K148" t="n">
-        <v>42.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="149">
@@ -6327,31 +6330,31 @@
         <v>144</v>
       </c>
       <c r="C149" t="n">
-        <v>50</v>
+        <v>68.7</v>
       </c>
       <c r="D149" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="E149" t="n">
-        <v>35.7</v>
+        <v>39.9</v>
       </c>
       <c r="F149" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="G149" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="H149" t="n">
-        <v>12.5</v>
+        <v>6.1</v>
       </c>
       <c r="I149" t="n">
-        <v>75</v>
+        <v>36.7</v>
       </c>
       <c r="J149" t="n">
-        <v>25</v>
+        <v>28.3</v>
       </c>
       <c r="K149" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="150">
@@ -6362,101 +6365,101 @@
         <v>144</v>
       </c>
       <c r="C150" t="n">
-        <v>68.7</v>
+        <v>64.7</v>
       </c>
       <c r="D150" t="n">
-        <v>28.8</v>
+        <v>25</v>
       </c>
       <c r="E150" t="n">
-        <v>39.9</v>
+        <v>39.7</v>
       </c>
       <c r="F150" t="n">
-        <v>28.8</v>
+        <v>25</v>
       </c>
       <c r="G150" t="n">
-        <v>30.3</v>
+        <v>21.4</v>
       </c>
       <c r="H150" t="n">
-        <v>6.1</v>
+        <v>1.3</v>
       </c>
       <c r="I150" t="n">
-        <v>36.7</v>
+        <v>60.3</v>
       </c>
       <c r="J150" t="n">
-        <v>28.3</v>
+        <v>22.4</v>
       </c>
       <c r="K150" t="n">
-        <v>45</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="B151" t="s">
         <v>144</v>
       </c>
       <c r="C151" t="n">
-        <v>64.7</v>
+        <v>56.1</v>
       </c>
       <c r="D151" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="E151" t="n">
-        <v>39.7</v>
+        <v>36.9</v>
       </c>
       <c r="F151" t="n">
-        <v>25</v>
+        <v>19.2</v>
       </c>
       <c r="G151" t="n">
-        <v>21.4</v>
+        <v>22.5</v>
       </c>
       <c r="H151" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>60.3</v>
+        <v>40.5</v>
       </c>
       <c r="J151" t="n">
-        <v>22.4</v>
+        <v>27</v>
       </c>
       <c r="K151" t="n">
-        <v>28.1</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>115</v>
+        <v>158</v>
       </c>
       <c r="B152" t="s">
         <v>144</v>
       </c>
       <c r="C152" t="n">
-        <v>56.1</v>
+        <v>78.6</v>
       </c>
       <c r="D152" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="E152" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="F152" t="n">
-        <v>19.2</v>
+        <v>39.1</v>
       </c>
       <c r="G152" t="n">
-        <v>22.5</v>
+        <v>28.9</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>40.5</v>
+        <v>57.1</v>
       </c>
       <c r="J152" t="n">
-        <v>27</v>
+        <v>14.3</v>
       </c>
       <c r="K152" t="n">
-        <v>40.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="153">
@@ -6467,31 +6470,31 @@
         <v>144</v>
       </c>
       <c r="C153" t="n">
-        <v>78.6</v>
+        <v>62.1</v>
       </c>
       <c r="D153" t="n">
-        <v>39.1</v>
+        <v>10.6</v>
       </c>
       <c r="E153" t="n">
-        <v>39.5</v>
+        <v>51.5</v>
       </c>
       <c r="F153" t="n">
-        <v>39.1</v>
+        <v>10.6</v>
       </c>
       <c r="G153" t="n">
-        <v>28.9</v>
+        <v>11.8</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="I153" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="J153" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="K153" t="n">
-        <v>14.3</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="154">
@@ -6502,31 +6505,31 @@
         <v>144</v>
       </c>
       <c r="C154" t="n">
-        <v>62.1</v>
+        <v>63.2</v>
       </c>
       <c r="D154" t="n">
-        <v>10.6</v>
+        <v>45</v>
       </c>
       <c r="E154" t="n">
-        <v>51.5</v>
+        <v>18.2</v>
       </c>
       <c r="F154" t="n">
-        <v>10.6</v>
+        <v>45</v>
       </c>
       <c r="G154" t="n">
-        <v>11.8</v>
+        <v>26.9</v>
       </c>
       <c r="H154" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="I154" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K154" t="n">
-        <v>32.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="155">
@@ -6537,31 +6540,31 @@
         <v>144</v>
       </c>
       <c r="C155" t="n">
-        <v>63.2</v>
+        <v>74.1</v>
       </c>
       <c r="D155" t="n">
-        <v>45</v>
+        <v>12.8</v>
       </c>
       <c r="E155" t="n">
-        <v>18.2</v>
+        <v>61.3</v>
       </c>
       <c r="F155" t="n">
-        <v>45</v>
+        <v>12.8</v>
       </c>
       <c r="G155" t="n">
-        <v>26.9</v>
+        <v>25.2</v>
       </c>
       <c r="H155" t="n">
-        <v>7.7</v>
+        <v>16.5</v>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>32.8</v>
       </c>
       <c r="J155" t="n">
-        <v>25</v>
+        <v>34.5</v>
       </c>
       <c r="K155" t="n">
-        <v>25</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="156">
@@ -6572,31 +6575,31 @@
         <v>144</v>
       </c>
       <c r="C156" t="n">
-        <v>74.1</v>
+        <v>74.6</v>
       </c>
       <c r="D156" t="n">
-        <v>12.8</v>
+        <v>25.3</v>
       </c>
       <c r="E156" t="n">
-        <v>61.3</v>
+        <v>49.3</v>
       </c>
       <c r="F156" t="n">
-        <v>12.8</v>
+        <v>25.3</v>
       </c>
       <c r="G156" t="n">
-        <v>25.2</v>
+        <v>8.9</v>
       </c>
       <c r="H156" t="n">
-        <v>16.5</v>
+        <v>2.3</v>
       </c>
       <c r="I156" t="n">
-        <v>32.8</v>
+        <v>47.2</v>
       </c>
       <c r="J156" t="n">
-        <v>34.5</v>
+        <v>22.2</v>
       </c>
       <c r="K156" t="n">
-        <v>36.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="157">
@@ -6604,69 +6607,69 @@
         <v>163</v>
       </c>
       <c r="B157" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C157" t="n">
-        <v>74.6</v>
+        <v>70.5</v>
       </c>
       <c r="D157" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="E157" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F157" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="G157" t="n">
-        <v>8.9</v>
+        <v>37.7</v>
       </c>
       <c r="H157" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="I157" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="J157" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="K157" t="n">
-        <v>33.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" t="s">
         <v>164</v>
       </c>
-      <c r="B158" t="s">
-        <v>165</v>
-      </c>
       <c r="C158" t="n">
-        <v>70.5</v>
+        <v>66.9</v>
       </c>
       <c r="D158" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="E158" t="n">
-        <v>50</v>
+        <v>45.6</v>
       </c>
       <c r="F158" t="n">
-        <v>20.5</v>
+        <v>21.3</v>
       </c>
       <c r="G158" t="n">
-        <v>37.7</v>
+        <v>15.9</v>
       </c>
       <c r="H158" t="n">
-        <v>9.1</v>
+        <v>6.7</v>
       </c>
       <c r="I158" t="n">
-        <v>51.9</v>
+        <v>57.7</v>
       </c>
       <c r="J158" t="n">
-        <v>21.2</v>
+        <v>18.3</v>
       </c>
       <c r="K158" t="n">
-        <v>39.1</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="159">
@@ -6674,34 +6677,34 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C159" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="D159" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="E159" t="n">
-        <v>45.6</v>
+        <v>47.9</v>
       </c>
       <c r="F159" t="n">
-        <v>21.3</v>
+        <v>16.7</v>
       </c>
       <c r="G159" t="n">
-        <v>15.9</v>
+        <v>37.7</v>
       </c>
       <c r="H159" t="n">
-        <v>6.7</v>
+        <v>12.5</v>
       </c>
       <c r="I159" t="n">
-        <v>57.7</v>
+        <v>29.6</v>
       </c>
       <c r="J159" t="n">
-        <v>18.3</v>
+        <v>48.1</v>
       </c>
       <c r="K159" t="n">
-        <v>43.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="160">
@@ -6709,34 +6712,34 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160" t="n">
-        <v>64.6</v>
+        <v>59</v>
       </c>
       <c r="D160" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E160" t="n">
-        <v>47.9</v>
+        <v>37.9</v>
       </c>
       <c r="F160" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G160" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="H160" t="n">
         <v>12.5</v>
       </c>
       <c r="I160" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="J160" t="n">
-        <v>48.1</v>
+        <v>36.8</v>
       </c>
       <c r="K160" t="n">
-        <v>38.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="161">
@@ -6744,34 +6747,34 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C161" t="n">
-        <v>59</v>
+        <v>65.9</v>
       </c>
       <c r="D161" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="E161" t="n">
-        <v>37.9</v>
+        <v>50.4</v>
       </c>
       <c r="F161" t="n">
-        <v>21.1</v>
+        <v>15.5</v>
       </c>
       <c r="G161" t="n">
-        <v>34.5</v>
+        <v>9.5</v>
       </c>
       <c r="H161" t="n">
-        <v>12.5</v>
+        <v>15.8</v>
       </c>
       <c r="I161" t="n">
-        <v>31.6</v>
+        <v>63.6</v>
       </c>
       <c r="J161" t="n">
-        <v>36.8</v>
+        <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>29.4</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="162">
@@ -6779,34 +6782,34 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C162" t="n">
-        <v>65.9</v>
+        <v>80</v>
       </c>
       <c r="D162" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="E162" t="n">
-        <v>50.4</v>
+        <v>64</v>
       </c>
       <c r="F162" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="G162" t="n">
-        <v>9.5</v>
+        <v>23.7</v>
       </c>
       <c r="H162" t="n">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="I162" t="n">
-        <v>63.6</v>
+        <v>36.1</v>
       </c>
       <c r="J162" t="n">
-        <v>17</v>
+        <v>33.7</v>
       </c>
       <c r="K162" t="n">
-        <v>39.3</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="163">
@@ -6814,34 +6817,34 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C163" t="n">
-        <v>80</v>
+        <v>55.2</v>
       </c>
       <c r="D163" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="E163" t="n">
-        <v>64</v>
+        <v>36.9</v>
       </c>
       <c r="F163" t="n">
-        <v>16</v>
+        <v>18.3</v>
       </c>
       <c r="G163" t="n">
-        <v>23.7</v>
+        <v>27</v>
       </c>
       <c r="H163" t="n">
-        <v>10.5</v>
+        <v>12.9</v>
       </c>
       <c r="I163" t="n">
-        <v>36.1</v>
+        <v>52.1</v>
       </c>
       <c r="J163" t="n">
-        <v>33.7</v>
+        <v>22.9</v>
       </c>
       <c r="K163" t="n">
-        <v>47.4</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="164">
@@ -6849,34 +6852,34 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C164" t="n">
-        <v>55.2</v>
+        <v>75</v>
       </c>
       <c r="D164" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>36.9</v>
+        <v>75</v>
       </c>
       <c r="F164" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>27</v>
+        <v>66.7</v>
       </c>
       <c r="H164" t="n">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>52.1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>22.9</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>29.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -6884,34 +6887,34 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C165" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="E165" t="n">
-        <v>75</v>
+        <v>37.7</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="G165" t="n">
-        <v>66.7</v>
+        <v>13.2</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>18.7</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>36.5</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="166">
@@ -6919,34 +6922,34 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C166" t="n">
-        <v>56.2</v>
+        <v>61.3</v>
       </c>
       <c r="D166" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="E166" t="n">
-        <v>37.7</v>
+        <v>40.6</v>
       </c>
       <c r="F166" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="G166" t="n">
-        <v>13.2</v>
+        <v>9.5</v>
       </c>
       <c r="H166" t="n">
-        <v>18.7</v>
+        <v>7.6</v>
       </c>
       <c r="I166" t="n">
-        <v>36.5</v>
+        <v>60.4</v>
       </c>
       <c r="J166" t="n">
-        <v>30.2</v>
+        <v>17.8</v>
       </c>
       <c r="K166" t="n">
-        <v>48.3</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="167">
@@ -6954,34 +6957,34 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C167" t="n">
-        <v>61.3</v>
+        <v>71.2</v>
       </c>
       <c r="D167" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="E167" t="n">
-        <v>40.6</v>
+        <v>54.6</v>
       </c>
       <c r="F167" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="G167" t="n">
-        <v>9.5</v>
+        <v>25</v>
       </c>
       <c r="H167" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="I167" t="n">
-        <v>60.4</v>
+        <v>35.8</v>
       </c>
       <c r="J167" t="n">
-        <v>17.8</v>
+        <v>30.9</v>
       </c>
       <c r="K167" t="n">
-        <v>28.9</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="168">
@@ -6989,34 +6992,34 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C168" t="n">
-        <v>71.2</v>
+        <v>78</v>
       </c>
       <c r="D168" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="E168" t="n">
-        <v>54.6</v>
+        <v>47.3</v>
       </c>
       <c r="F168" t="n">
-        <v>16.6</v>
+        <v>30.7</v>
       </c>
       <c r="G168" t="n">
-        <v>25</v>
+        <v>39.4</v>
       </c>
       <c r="H168" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I168" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="J168" t="n">
-        <v>30.9</v>
+        <v>22.7</v>
       </c>
       <c r="K168" t="n">
-        <v>56.2</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="169">
@@ -7024,34 +7027,34 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C169" t="n">
-        <v>78</v>
+        <v>73.6</v>
       </c>
       <c r="D169" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="E169" t="n">
-        <v>47.3</v>
+        <v>53.6</v>
       </c>
       <c r="F169" t="n">
-        <v>30.7</v>
+        <v>20</v>
       </c>
       <c r="G169" t="n">
-        <v>39.4</v>
+        <v>18.9</v>
       </c>
       <c r="H169" t="n">
-        <v>8</v>
+        <v>11.2</v>
       </c>
       <c r="I169" t="n">
-        <v>36.4</v>
+        <v>30.8</v>
       </c>
       <c r="J169" t="n">
-        <v>22.7</v>
+        <v>30.8</v>
       </c>
       <c r="K169" t="n">
-        <v>68.2</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="170">
@@ -7059,57 +7062,51 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C170" t="n">
-        <v>73.6</v>
+        <v>37.5</v>
       </c>
       <c r="D170" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E170" t="n">
-        <v>53.6</v>
+        <v>4.2</v>
       </c>
       <c r="F170" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="G170" t="n">
-        <v>18.9</v>
+        <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I170" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J170" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="K170" t="n">
-        <v>47.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I170"/>
+      <c r="J170"/>
+      <c r="K170"/>
     </row>
     <row r="171">
       <c r="A171" t="s">
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C171" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D171" t="n">
         <v>33.3</v>
       </c>
       <c r="E171" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F171" t="n">
         <v>33.3</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7119,65 +7116,36 @@
       <c r="K171"/>
     </row>
     <row r="172">
-      <c r="A172" t="s">
+      <c r="A172"/>
+      <c r="B172" t="s">
         <v>179</v>
       </c>
-      <c r="B172" t="s">
-        <v>165</v>
-      </c>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>69.1</v>
       </c>
       <c r="D172" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="E172" t="n">
-        <v>-33.3</v>
+        <v>46.5</v>
       </c>
       <c r="F172" t="n">
-        <v>33.3</v>
+        <v>22.7</v>
       </c>
       <c r="G172" t="n">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172"/>
-      <c r="J172"/>
-      <c r="K172"/>
-    </row>
-    <row r="173">
-      <c r="A173"/>
-      <c r="B173" t="s">
-        <v>180</v>
-      </c>
-      <c r="C173" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="D173" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E173" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="F173" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G173" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="H173" t="n">
         <v>9.1</v>
       </c>
-      <c r="I173" t="n">
-        <v>47</v>
-      </c>
-      <c r="J173" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="K173" t="n">
-        <v>37.4</v>
+      <c r="I172" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="J172" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K172" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
@@ -7209,22 +7177,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7233,18 +7201,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7279,7 +7247,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7349,7 +7317,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7419,7 +7387,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7454,7 +7422,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7489,7 +7457,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7559,7 +7527,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7594,7 +7562,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7629,7 +7597,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7664,7 +7632,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7732,7 +7700,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -7765,7 +7733,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
@@ -7798,7 +7766,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -7831,7 +7799,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
         <v>46</v>
@@ -7866,7 +7834,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B20" t="s">
         <v>46</v>
@@ -7901,7 +7869,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
         <v>46</v>
@@ -7971,7 +7939,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
@@ -8006,7 +7974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
@@ -8041,7 +8009,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B25" t="s">
         <v>46</v>
@@ -8076,7 +8044,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
@@ -8111,7 +8079,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s">
         <v>46</v>
@@ -8146,7 +8114,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
         <v>46</v>
@@ -8181,7 +8149,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -8216,7 +8184,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B30" t="s">
         <v>46</v>
@@ -8251,7 +8219,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
@@ -8286,7 +8254,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
@@ -8321,7 +8289,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
@@ -8356,7 +8324,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s">
         <v>46</v>
@@ -8391,7 +8359,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B35" t="s">
         <v>53</v>
@@ -8426,7 +8394,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
         <v>53</v>
@@ -8461,7 +8429,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B37" t="s">
         <v>53</v>
@@ -8494,7 +8462,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B38" t="s">
         <v>53</v>
@@ -8564,7 +8532,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s">
         <v>53</v>
@@ -8599,7 +8567,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
@@ -8634,7 +8602,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
@@ -8669,7 +8637,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B43" t="s">
         <v>53</v>
@@ -8702,7 +8670,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" t="s">
         <v>53</v>
@@ -8737,7 +8705,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B45" t="s">
         <v>53</v>
@@ -8772,7 +8740,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s">
         <v>53</v>
@@ -8807,7 +8775,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B47" t="s">
         <v>53</v>
@@ -8842,7 +8810,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B48" t="s">
         <v>53</v>
@@ -8877,7 +8845,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
         <v>53</v>
@@ -8912,7 +8880,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
         <v>53</v>
@@ -8947,7 +8915,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51" t="s">
         <v>53</v>
@@ -8980,7 +8948,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
         <v>53</v>
@@ -9015,7 +8983,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
         <v>71</v>
@@ -9050,7 +9018,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s">
         <v>71</v>
@@ -9085,7 +9053,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s">
         <v>71</v>
@@ -9120,7 +9088,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
         <v>71</v>
@@ -9153,7 +9121,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B57" t="s">
         <v>71</v>
@@ -9188,7 +9156,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
         <v>71</v>
@@ -9223,7 +9191,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s">
         <v>71</v>
@@ -9258,7 +9226,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B60" t="s">
         <v>71</v>
@@ -9293,7 +9261,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
         <v>71</v>
@@ -9328,7 +9296,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
         <v>71</v>
@@ -9363,7 +9331,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B63" t="s">
         <v>71</v>
@@ -9398,7 +9366,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B64" t="s">
         <v>71</v>
@@ -9468,7 +9436,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B66" t="s">
         <v>71</v>
@@ -9538,7 +9506,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B68" t="s">
         <v>93</v>
@@ -9573,7 +9541,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B69" t="s">
         <v>93</v>
@@ -9608,7 +9576,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>93</v>
@@ -9643,7 +9611,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>93</v>
@@ -9678,7 +9646,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
         <v>93</v>
@@ -9713,7 +9681,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s">
         <v>93</v>
@@ -9748,7 +9716,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
         <v>93</v>
@@ -9783,7 +9751,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>93</v>
@@ -9818,7 +9786,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>93</v>
@@ -9853,7 +9821,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
         <v>93</v>
@@ -9888,7 +9856,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s">
         <v>93</v>
@@ -9923,7 +9891,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
         <v>93</v>
@@ -9958,7 +9926,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B80" t="s">
         <v>107</v>
@@ -9993,7 +9961,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
@@ -10028,7 +9996,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
@@ -10063,7 +10031,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
@@ -10096,7 +10064,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" t="s">
         <v>107</v>
@@ -10131,7 +10099,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B85" t="s">
         <v>107</v>
@@ -10201,7 +10169,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
@@ -10236,7 +10204,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
@@ -10271,7 +10239,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
@@ -10306,7 +10274,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B90" t="s">
         <v>107</v>
@@ -10339,7 +10307,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B91" t="s">
         <v>107</v>
@@ -10374,7 +10342,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B92" t="s">
         <v>107</v>
@@ -10409,7 +10377,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B93" t="s">
         <v>107</v>
@@ -10444,7 +10412,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
         <v>107</v>
@@ -10479,7 +10447,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B95" t="s">
         <v>107</v>
@@ -10514,7 +10482,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B96" t="s">
         <v>128</v>
@@ -10549,7 +10517,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
@@ -10584,7 +10552,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
@@ -10619,7 +10587,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
@@ -10654,7 +10622,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B100" t="s">
         <v>128</v>
@@ -10689,7 +10657,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
@@ -10724,7 +10692,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
@@ -10759,7 +10727,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
         <v>128</v>
@@ -10794,7 +10762,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s">
         <v>128</v>
@@ -10829,7 +10797,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B105" t="s">
         <v>128</v>
@@ -10864,7 +10832,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B106" t="s">
         <v>144</v>
@@ -10899,7 +10867,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
         <v>144</v>
@@ -10934,7 +10902,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B108" t="s">
         <v>144</v>
@@ -10969,7 +10937,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
         <v>144</v>
@@ -11004,7 +10972,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B110" t="s">
         <v>144</v>
@@ -11037,7 +11005,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B111" t="s">
         <v>144</v>
@@ -11072,7 +11040,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B112" t="s">
         <v>144</v>
@@ -11107,7 +11075,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B113" t="s">
         <v>144</v>
@@ -11142,7 +11110,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B114" t="s">
         <v>144</v>
@@ -11177,7 +11145,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B115" t="s">
         <v>144</v>
@@ -11212,7 +11180,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B116" t="s">
         <v>144</v>
@@ -11247,7 +11215,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B117" t="s">
         <v>144</v>
@@ -11282,7 +11250,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B118" t="s">
         <v>144</v>
@@ -11317,7 +11285,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B119" t="s">
         <v>144</v>
@@ -11352,7 +11320,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B120" t="s">
         <v>144</v>
@@ -11387,7 +11355,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
         <v>144</v>
@@ -11422,10 +11390,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C122" t="n">
         <v>70.8</v>
@@ -11457,10 +11425,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C123" t="n">
         <v>62.4</v>
@@ -11492,10 +11460,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C124" t="n">
         <v>60.7</v>
@@ -11527,10 +11495,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C125" t="n">
         <v>60.7</v>
@@ -11562,10 +11530,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C126" t="n">
         <v>60</v>
@@ -11597,10 +11565,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C127" t="n">
         <v>67.3</v>
@@ -11632,10 +11600,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C128" t="n">
         <v>84.6</v>
@@ -11665,10 +11633,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C129" t="n">
         <v>50</v>
@@ -11700,10 +11668,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C130" t="n">
         <v>61.3</v>
@@ -11735,10 +11703,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C131" t="n">
         <v>65.8</v>
@@ -11770,10 +11738,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C132" t="n">
         <v>50.9</v>
@@ -11805,10 +11773,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C133" t="n">
         <v>66.7</v>
@@ -11840,10 +11808,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B134" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C134" t="n">
         <v>69.5</v>
@@ -11875,10 +11843,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B135" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C135" t="n">
         <v>63</v>
@@ -11910,10 +11878,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B136" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C136" t="n">
         <v>44</v>
@@ -11944,7 +11912,7 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C137" t="n">
         <v>58.1</v>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -475,9 +475,6 @@
   </si>
   <si>
     <t xml:space="preserve">Cooper Tomkinson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crix Taveras</t>
   </si>
   <si>
     <t xml:space="preserve">Crixtian Taveras</t>
@@ -1006,8 +1003,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K179" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K179"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K178" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K178"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -6282,25 +6279,31 @@
         <v>150</v>
       </c>
       <c r="C147" t="n">
-        <v>80</v>
-      </c>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147"/>
+        <v>73.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="E147" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F147" t="n">
+        <v>25.3</v>
+      </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>30.4</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="I147" t="n">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="K147" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -6311,31 +6314,25 @@
         <v>150</v>
       </c>
       <c r="C148" t="n">
-        <v>73.1</v>
-      </c>
-      <c r="D148" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E148" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="F148" t="n">
-        <v>25.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
       <c r="G148" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>23.5</v>
+        <v>100</v>
       </c>
       <c r="K148" t="n">
-        <v>38.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6346,25 +6343,31 @@
         <v>150</v>
       </c>
       <c r="C149" t="n">
-        <v>100</v>
-      </c>
-      <c r="D149"/>
-      <c r="E149"/>
-      <c r="F149"/>
+        <v>74.8</v>
+      </c>
+      <c r="D149" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="F149" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>45.3</v>
       </c>
       <c r="J149" t="n">
-        <v>100</v>
+        <v>26.4</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="150">
@@ -6375,31 +6378,31 @@
         <v>150</v>
       </c>
       <c r="C150" t="n">
-        <v>74.8</v>
+        <v>55.6</v>
       </c>
       <c r="D150" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="E150" t="n">
-        <v>48.7</v>
+        <v>29.7</v>
       </c>
       <c r="F150" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="G150" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H150" t="n">
-        <v>9.4</v>
+        <v>27.3</v>
       </c>
       <c r="I150" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="J150" t="n">
-        <v>26.4</v>
+        <v>28.6</v>
       </c>
       <c r="K150" t="n">
-        <v>40.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="151">
@@ -6410,31 +6413,31 @@
         <v>150</v>
       </c>
       <c r="C151" t="n">
-        <v>55.6</v>
+        <v>65.9</v>
       </c>
       <c r="D151" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="E151" t="n">
-        <v>29.7</v>
+        <v>41.4</v>
       </c>
       <c r="F151" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="G151" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="H151" t="n">
-        <v>27.3</v>
+        <v>7.2</v>
       </c>
       <c r="I151" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="J151" t="n">
-        <v>28.6</v>
+        <v>15.4</v>
       </c>
       <c r="K151" t="n">
-        <v>14.3</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="152">
@@ -6445,31 +6448,31 @@
         <v>150</v>
       </c>
       <c r="C152" t="n">
-        <v>65.9</v>
+        <v>66.7</v>
       </c>
       <c r="D152" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>41.4</v>
+        <v>66.7</v>
       </c>
       <c r="F152" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="H152" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="J152" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="K152" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -6480,31 +6483,31 @@
         <v>150</v>
       </c>
       <c r="C153" t="n">
-        <v>66.7</v>
+        <v>71</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E153" t="n">
-        <v>66.7</v>
+        <v>51.6</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G153" t="n">
-        <v>18.2</v>
+        <v>25.7</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I153" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J153" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="154">
@@ -6515,31 +6518,31 @@
         <v>150</v>
       </c>
       <c r="C154" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D154" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E154" t="n">
-        <v>51.6</v>
+        <v>35.7</v>
       </c>
       <c r="F154" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G154" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
       <c r="H154" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="I154" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K154" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155">
@@ -6550,31 +6553,31 @@
         <v>150</v>
       </c>
       <c r="C155" t="n">
-        <v>50</v>
+        <v>68.7</v>
       </c>
       <c r="D155" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="E155" t="n">
-        <v>35.7</v>
+        <v>39.9</v>
       </c>
       <c r="F155" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="G155" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="H155" t="n">
-        <v>12.5</v>
+        <v>6.1</v>
       </c>
       <c r="I155" t="n">
-        <v>75</v>
+        <v>36.7</v>
       </c>
       <c r="J155" t="n">
-        <v>25</v>
+        <v>28.3</v>
       </c>
       <c r="K155" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="156">
@@ -6585,101 +6588,101 @@
         <v>150</v>
       </c>
       <c r="C156" t="n">
-        <v>68.7</v>
+        <v>65.5</v>
       </c>
       <c r="D156" t="n">
-        <v>28.8</v>
+        <v>23.2</v>
       </c>
       <c r="E156" t="n">
-        <v>39.9</v>
+        <v>42.3</v>
       </c>
       <c r="F156" t="n">
-        <v>28.8</v>
+        <v>23.2</v>
       </c>
       <c r="G156" t="n">
-        <v>30.3</v>
+        <v>20</v>
       </c>
       <c r="H156" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="I156" t="n">
-        <v>36.7</v>
+        <v>60.6</v>
       </c>
       <c r="J156" t="n">
-        <v>28.3</v>
+        <v>24.2</v>
       </c>
       <c r="K156" t="n">
-        <v>45</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="B157" t="s">
         <v>150</v>
       </c>
       <c r="C157" t="n">
-        <v>65.5</v>
+        <v>56.1</v>
       </c>
       <c r="D157" t="n">
-        <v>23.2</v>
+        <v>19.2</v>
       </c>
       <c r="E157" t="n">
-        <v>42.3</v>
+        <v>36.9</v>
       </c>
       <c r="F157" t="n">
-        <v>23.2</v>
+        <v>19.2</v>
       </c>
       <c r="G157" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="H157" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>60.6</v>
+        <v>40.5</v>
       </c>
       <c r="J157" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
       <c r="K157" t="n">
-        <v>29.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="B158" t="s">
         <v>150</v>
       </c>
       <c r="C158" t="n">
-        <v>56.1</v>
+        <v>81.4</v>
       </c>
       <c r="D158" t="n">
-        <v>19.2</v>
+        <v>35.2</v>
       </c>
       <c r="E158" t="n">
-        <v>36.9</v>
+        <v>46.2</v>
       </c>
       <c r="F158" t="n">
-        <v>19.2</v>
+        <v>35.2</v>
       </c>
       <c r="G158" t="n">
-        <v>22.5</v>
+        <v>30.5</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I158" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="J158" t="n">
-        <v>27</v>
+        <v>18.2</v>
       </c>
       <c r="K158" t="n">
-        <v>40.5</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="159">
@@ -6690,31 +6693,31 @@
         <v>150</v>
       </c>
       <c r="C159" t="n">
-        <v>81.4</v>
+        <v>60.3</v>
       </c>
       <c r="D159" t="n">
-        <v>35.2</v>
+        <v>9.3</v>
       </c>
       <c r="E159" t="n">
-        <v>46.2</v>
+        <v>51</v>
       </c>
       <c r="F159" t="n">
-        <v>35.2</v>
+        <v>9.3</v>
       </c>
       <c r="G159" t="n">
-        <v>30.5</v>
+        <v>11.4</v>
       </c>
       <c r="H159" t="n">
-        <v>3.3</v>
+        <v>11.2</v>
       </c>
       <c r="I159" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="J159" t="n">
-        <v>18.2</v>
+        <v>10.8</v>
       </c>
       <c r="K159" t="n">
-        <v>40.9</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="160">
@@ -6725,31 +6728,31 @@
         <v>150</v>
       </c>
       <c r="C160" t="n">
-        <v>60.3</v>
+        <v>63.2</v>
       </c>
       <c r="D160" t="n">
-        <v>9.3</v>
+        <v>45</v>
       </c>
       <c r="E160" t="n">
-        <v>51</v>
+        <v>18.2</v>
       </c>
       <c r="F160" t="n">
-        <v>9.3</v>
+        <v>45</v>
       </c>
       <c r="G160" t="n">
-        <v>11.4</v>
+        <v>26.9</v>
       </c>
       <c r="H160" t="n">
-        <v>11.2</v>
+        <v>7.7</v>
       </c>
       <c r="I160" t="n">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>10.8</v>
+        <v>25</v>
       </c>
       <c r="K160" t="n">
-        <v>34.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161">
@@ -6760,31 +6763,31 @@
         <v>150</v>
       </c>
       <c r="C161" t="n">
-        <v>63.2</v>
+        <v>74.4</v>
       </c>
       <c r="D161" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E161" t="n">
-        <v>18.2</v>
+        <v>62.4</v>
       </c>
       <c r="F161" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G161" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="H161" t="n">
-        <v>7.7</v>
+        <v>16</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="J161" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K161" t="n">
-        <v>25</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="162">
@@ -6795,31 +6798,31 @@
         <v>150</v>
       </c>
       <c r="C162" t="n">
-        <v>74.4</v>
+        <v>74.6</v>
       </c>
       <c r="D162" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="E162" t="n">
-        <v>62.4</v>
+        <v>49.3</v>
       </c>
       <c r="F162" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="G162" t="n">
-        <v>23.9</v>
+        <v>8.9</v>
       </c>
       <c r="H162" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="I162" t="n">
-        <v>32.3</v>
+        <v>47.2</v>
       </c>
       <c r="J162" t="n">
-        <v>35.4</v>
+        <v>22.2</v>
       </c>
       <c r="K162" t="n">
-        <v>36.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="163">
@@ -6827,69 +6830,69 @@
         <v>169</v>
       </c>
       <c r="B163" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C163" t="n">
-        <v>74.6</v>
+        <v>70.5</v>
       </c>
       <c r="D163" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="E163" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F163" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="G163" t="n">
-        <v>8.9</v>
+        <v>37.7</v>
       </c>
       <c r="H163" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="I163" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="J163" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="K163" t="n">
-        <v>33.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" t="s">
         <v>170</v>
       </c>
-      <c r="B164" t="s">
-        <v>171</v>
-      </c>
       <c r="C164" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D164" t="n">
         <v>20.5</v>
       </c>
       <c r="E164" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F164" t="n">
         <v>20.5</v>
       </c>
       <c r="G164" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H164" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="I164" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J164" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K164" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="165">
@@ -6897,34 +6900,34 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C165" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D165" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E165" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F165" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G165" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H165" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I165" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J165" t="n">
         <v>48.1</v>
       </c>
-      <c r="F165" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G165" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H165" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I165" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J165" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K165" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="166">
@@ -6932,34 +6935,34 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C166" t="n">
-        <v>64.6</v>
+        <v>59</v>
       </c>
       <c r="D166" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E166" t="n">
-        <v>47.9</v>
+        <v>38.2</v>
       </c>
       <c r="F166" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="G166" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="H166" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="I166" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="J166" t="n">
-        <v>48.1</v>
+        <v>36.8</v>
       </c>
       <c r="K166" t="n">
-        <v>38.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="167">
@@ -6967,34 +6970,34 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C167" t="n">
-        <v>59</v>
+        <v>66.3</v>
       </c>
       <c r="D167" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="E167" t="n">
-        <v>38.2</v>
+        <v>51.5</v>
       </c>
       <c r="F167" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="G167" t="n">
-        <v>34.5</v>
+        <v>9.3</v>
       </c>
       <c r="H167" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="I167" t="n">
-        <v>31.6</v>
+        <v>62.6</v>
       </c>
       <c r="J167" t="n">
-        <v>36.8</v>
+        <v>16.5</v>
       </c>
       <c r="K167" t="n">
-        <v>29.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="168">
@@ -7002,34 +7005,34 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C168" t="n">
-        <v>66.3</v>
+        <v>80.8</v>
       </c>
       <c r="D168" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="E168" t="n">
-        <v>51.5</v>
+        <v>65.3</v>
       </c>
       <c r="F168" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G168" t="n">
-        <v>9.3</v>
+        <v>22.7</v>
       </c>
       <c r="H168" t="n">
-        <v>16.8</v>
+        <v>10.1</v>
       </c>
       <c r="I168" t="n">
-        <v>62.6</v>
+        <v>38.6</v>
       </c>
       <c r="J168" t="n">
-        <v>16.5</v>
+        <v>31.8</v>
       </c>
       <c r="K168" t="n">
-        <v>37.9</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="169">
@@ -7037,34 +7040,34 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C169" t="n">
-        <v>80.8</v>
+        <v>55.6</v>
       </c>
       <c r="D169" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="E169" t="n">
-        <v>65.3</v>
+        <v>36.9</v>
       </c>
       <c r="F169" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="G169" t="n">
-        <v>22.7</v>
+        <v>26.8</v>
       </c>
       <c r="H169" t="n">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="I169" t="n">
-        <v>38.6</v>
+        <v>51</v>
       </c>
       <c r="J169" t="n">
-        <v>31.8</v>
+        <v>21.6</v>
       </c>
       <c r="K169" t="n">
-        <v>48.2</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="170">
@@ -7072,34 +7075,34 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C170" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D170" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
-        <v>36.9</v>
+        <v>75</v>
       </c>
       <c r="F170" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>26.8</v>
+        <v>66.7</v>
       </c>
       <c r="H170" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="I170" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J170" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -7107,34 +7110,34 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C171" t="n">
-        <v>75</v>
+        <v>56.3</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="E171" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="G171" t="n">
-        <v>66.7</v>
+        <v>12.7</v>
       </c>
       <c r="H171" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="J171" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="K171" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="172">
@@ -7142,34 +7145,34 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C172" t="n">
-        <v>56.3</v>
+        <v>61.5</v>
       </c>
       <c r="D172" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="E172" t="n">
-        <v>38.5</v>
+        <v>41.3</v>
       </c>
       <c r="F172" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="G172" t="n">
-        <v>12.7</v>
+        <v>9.1</v>
       </c>
       <c r="H172" t="n">
-        <v>17.9</v>
+        <v>7.2</v>
       </c>
       <c r="I172" t="n">
-        <v>34.8</v>
+        <v>60</v>
       </c>
       <c r="J172" t="n">
-        <v>31.8</v>
+        <v>18.1</v>
       </c>
       <c r="K172" t="n">
-        <v>47.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="173">
@@ -7177,34 +7180,34 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C173" t="n">
-        <v>61.5</v>
+        <v>71.4</v>
       </c>
       <c r="D173" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="E173" t="n">
-        <v>41.3</v>
+        <v>54.4</v>
       </c>
       <c r="F173" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="G173" t="n">
-        <v>9.1</v>
+        <v>25.1</v>
       </c>
       <c r="H173" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="I173" t="n">
-        <v>60</v>
+        <v>36.5</v>
       </c>
       <c r="J173" t="n">
-        <v>18.1</v>
+        <v>29.4</v>
       </c>
       <c r="K173" t="n">
-        <v>29</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="174">
@@ -7212,34 +7215,34 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C174" t="n">
-        <v>71.4</v>
+        <v>76.7</v>
       </c>
       <c r="D174" t="n">
-        <v>17</v>
+        <v>30.1</v>
       </c>
       <c r="E174" t="n">
-        <v>54.4</v>
+        <v>46.6</v>
       </c>
       <c r="F174" t="n">
-        <v>17</v>
+        <v>30.1</v>
       </c>
       <c r="G174" t="n">
-        <v>25.1</v>
+        <v>40.7</v>
       </c>
       <c r="H174" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="I174" t="n">
-        <v>36.5</v>
+        <v>39.1</v>
       </c>
       <c r="J174" t="n">
-        <v>29.4</v>
+        <v>21.7</v>
       </c>
       <c r="K174" t="n">
-        <v>57.1</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="175">
@@ -7247,34 +7250,34 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C175" t="n">
-        <v>76.7</v>
+        <v>74.5</v>
       </c>
       <c r="D175" t="n">
-        <v>30.1</v>
+        <v>19.9</v>
       </c>
       <c r="E175" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="F175" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G175" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H175" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I175" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J175" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K175" t="n">
         <v>46.6</v>
-      </c>
-      <c r="F175" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="G175" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="H175" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I175" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="J175" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K175" t="n">
-        <v>65.2</v>
       </c>
     </row>
     <row r="176">
@@ -7282,57 +7285,51 @@
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C176" t="n">
-        <v>74.5</v>
+        <v>37.5</v>
       </c>
       <c r="D176" t="n">
-        <v>19.9</v>
+        <v>33.3</v>
       </c>
       <c r="E176" t="n">
-        <v>54.6</v>
+        <v>4.2</v>
       </c>
       <c r="F176" t="n">
-        <v>19.9</v>
+        <v>33.3</v>
       </c>
       <c r="G176" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I176" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J176" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K176" t="n">
-        <v>46.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I176"/>
+      <c r="J176"/>
+      <c r="K176"/>
     </row>
     <row r="177">
       <c r="A177" t="s">
         <v>184</v>
       </c>
       <c r="B177" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C177" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
         <v>33.3</v>
       </c>
       <c r="E177" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F177" t="n">
         <v>33.3</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -7342,65 +7339,36 @@
       <c r="K177"/>
     </row>
     <row r="178">
-      <c r="A178" t="s">
+      <c r="A178"/>
+      <c r="B178" t="s">
         <v>185</v>
       </c>
-      <c r="B178" t="s">
-        <v>171</v>
-      </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D178" t="n">
-        <v>33.3</v>
+        <v>21.7</v>
       </c>
       <c r="E178" t="n">
-        <v>-33.3</v>
+        <v>47.5</v>
       </c>
       <c r="F178" t="n">
-        <v>33.3</v>
+        <v>21.7</v>
       </c>
       <c r="G178" t="n">
-        <v>100</v>
+        <v>27.1</v>
       </c>
       <c r="H178" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178"/>
-      <c r="J178"/>
-      <c r="K178"/>
-    </row>
-    <row r="179">
-      <c r="A179"/>
-      <c r="B179" t="s">
-        <v>186</v>
-      </c>
-      <c r="C179" t="n">
-        <v>69.1</v>
-      </c>
-      <c r="D179" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="E179" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F179" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G179" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="H179" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I179" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="J179" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="K179" t="n">
-        <v>38</v>
+        <v>9.2</v>
+      </c>
+      <c r="I178" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J178" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K178" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
@@ -7432,22 +7400,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7456,18 +7424,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7502,7 +7470,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7572,7 +7540,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7642,7 +7610,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7677,7 +7645,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7712,7 +7680,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7782,7 +7750,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7817,7 +7785,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7852,7 +7820,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7887,7 +7855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7955,7 +7923,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -7988,7 +7956,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
@@ -8021,7 +7989,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -8054,7 +8022,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -8089,7 +8057,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -8124,7 +8092,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
@@ -8194,7 +8162,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -8229,7 +8197,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -8264,7 +8232,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
@@ -8299,7 +8267,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -8334,7 +8302,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -8369,7 +8337,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -8404,7 +8372,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -8439,7 +8407,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -8474,7 +8442,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -8509,7 +8477,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -8544,7 +8512,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -8579,7 +8547,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -8614,7 +8582,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -8649,7 +8617,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -8684,7 +8652,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -8717,7 +8685,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -8787,7 +8755,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -8822,7 +8790,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -8857,7 +8825,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
@@ -8892,7 +8860,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -8925,7 +8893,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -8960,7 +8928,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -8995,7 +8963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -9030,7 +8998,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -9065,7 +9033,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -9100,7 +9068,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -9135,7 +9103,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -9170,7 +9138,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -9205,7 +9173,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
         <v>54</v>
@@ -9240,7 +9208,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s">
         <v>54</v>
@@ -9273,7 +9241,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
@@ -9308,7 +9276,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s">
         <v>72</v>
@@ -9343,7 +9311,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s">
         <v>72</v>
@@ -9378,7 +9346,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s">
         <v>72</v>
@@ -9413,7 +9381,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B58" t="s">
         <v>72</v>
@@ -9446,7 +9414,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B59" t="s">
         <v>72</v>
@@ -9481,7 +9449,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B60" t="s">
         <v>72</v>
@@ -9516,7 +9484,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B61" t="s">
         <v>72</v>
@@ -9551,7 +9519,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B62" t="s">
         <v>72</v>
@@ -9586,7 +9554,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B63" t="s">
         <v>72</v>
@@ -9621,7 +9589,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B64" t="s">
         <v>72</v>
@@ -9656,7 +9624,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B65" t="s">
         <v>72</v>
@@ -9691,7 +9659,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B66" t="s">
         <v>72</v>
@@ -9761,7 +9729,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B68" t="s">
         <v>72</v>
@@ -9831,7 +9799,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B70" t="s">
         <v>96</v>
@@ -9866,7 +9834,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B71" t="s">
         <v>96</v>
@@ -9901,7 +9869,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B72" t="s">
         <v>96</v>
@@ -9936,7 +9904,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B73" t="s">
         <v>96</v>
@@ -9971,7 +9939,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B74" t="s">
         <v>96</v>
@@ -10006,7 +9974,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B75" t="s">
         <v>96</v>
@@ -10041,7 +10009,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
         <v>96</v>
@@ -10076,7 +10044,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B77" t="s">
         <v>96</v>
@@ -10111,7 +10079,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B78" t="s">
         <v>96</v>
@@ -10146,7 +10114,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B79" t="s">
         <v>96</v>
@@ -10181,7 +10149,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B80" t="s">
         <v>96</v>
@@ -10216,7 +10184,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B81" t="s">
         <v>96</v>
@@ -10249,7 +10217,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B82" t="s">
         <v>96</v>
@@ -10284,7 +10252,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B83" t="s">
         <v>110</v>
@@ -10319,7 +10287,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B84" t="s">
         <v>110</v>
@@ -10354,7 +10322,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B85" t="s">
         <v>110</v>
@@ -10389,7 +10357,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B86" t="s">
         <v>110</v>
@@ -10422,7 +10390,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B87" t="s">
         <v>110</v>
@@ -10457,7 +10425,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B88" t="s">
         <v>110</v>
@@ -10562,7 +10530,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B91" t="s">
         <v>110</v>
@@ -10597,7 +10565,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B92" t="s">
         <v>110</v>
@@ -10632,7 +10600,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B93" t="s">
         <v>110</v>
@@ -10665,7 +10633,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B94" t="s">
         <v>110</v>
@@ -10700,7 +10668,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B95" t="s">
         <v>110</v>
@@ -10735,7 +10703,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B96" t="s">
         <v>110</v>
@@ -10770,7 +10738,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B97" t="s">
         <v>110</v>
@@ -10805,7 +10773,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B98" t="s">
         <v>110</v>
@@ -10840,7 +10808,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B99" t="s">
         <v>133</v>
@@ -10875,7 +10843,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B100" t="s">
         <v>133</v>
@@ -10910,7 +10878,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B101" t="s">
         <v>133</v>
@@ -10945,7 +10913,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B102" t="s">
         <v>133</v>
@@ -10980,7 +10948,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B103" t="s">
         <v>133</v>
@@ -11015,7 +10983,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B104" t="s">
         <v>133</v>
@@ -11050,7 +11018,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B105" t="s">
         <v>133</v>
@@ -11085,7 +11053,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B106" t="s">
         <v>133</v>
@@ -11120,7 +11088,7 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B107" t="s">
         <v>133</v>
@@ -11155,7 +11123,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B108" t="s">
         <v>133</v>
@@ -11190,7 +11158,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B109" t="s">
         <v>133</v>
@@ -11225,7 +11193,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B110" t="s">
         <v>150</v>
@@ -11260,7 +11228,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B111" t="s">
         <v>150</v>
@@ -11330,7 +11298,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B113" t="s">
         <v>150</v>
@@ -11365,7 +11333,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B114" t="s">
         <v>150</v>
@@ -11398,7 +11366,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B115" t="s">
         <v>150</v>
@@ -11433,7 +11401,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B116" t="s">
         <v>150</v>
@@ -11468,7 +11436,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B117" t="s">
         <v>150</v>
@@ -11503,7 +11471,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B118" t="s">
         <v>150</v>
@@ -11538,7 +11506,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B119" t="s">
         <v>150</v>
@@ -11573,7 +11541,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B120" t="s">
         <v>150</v>
@@ -11608,7 +11576,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B121" t="s">
         <v>150</v>
@@ -11643,7 +11611,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B122" t="s">
         <v>150</v>
@@ -11678,7 +11646,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B123" t="s">
         <v>150</v>
@@ -11713,7 +11681,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B124" t="s">
         <v>150</v>
@@ -11748,7 +11716,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B125" t="s">
         <v>150</v>
@@ -11783,10 +11751,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B126" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C126" t="n">
         <v>72.5</v>
@@ -11818,10 +11786,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B127" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C127" t="n">
         <v>62.4</v>
@@ -11853,10 +11821,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B128" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C128" t="n">
         <v>60.7</v>
@@ -11888,10 +11856,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B129" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C129" t="n">
         <v>58.2</v>
@@ -11923,10 +11891,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C130" t="n">
         <v>60</v>
@@ -11958,10 +11926,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C131" t="n">
         <v>67.3</v>
@@ -11993,10 +11961,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C132" t="n">
         <v>84.6</v>
@@ -12026,10 +11994,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C133" t="n">
         <v>50</v>
@@ -12061,10 +12029,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B134" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C134" t="n">
         <v>61.3</v>
@@ -12096,10 +12064,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C135" t="n">
         <v>65.8</v>
@@ -12131,10 +12099,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C136" t="n">
         <v>50.9</v>
@@ -12166,10 +12134,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C137" t="n">
         <v>66.7</v>
@@ -12201,10 +12169,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B138" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C138" t="n">
         <v>69.5</v>
@@ -12236,10 +12204,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C139" t="n">
         <v>63</v>
@@ -12271,10 +12239,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C140" t="n">
         <v>44</v>
@@ -12305,7 +12273,7 @@
     <row r="141">
       <c r="A141"/>
       <c r="B141" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C141" t="n">
         <v>58.4</v>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="311">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -946,9 +946,6 @@
   </si>
   <si>
     <t xml:space="preserve">Yoilan Quinonez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yolian Quinonez</t>
   </si>
 </sst>
 </file>
@@ -1023,8 +1020,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K141" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K141"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K140" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K140"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -12210,96 +12207,63 @@
         <v>170</v>
       </c>
       <c r="C139" t="n">
+        <v>59</v>
+      </c>
+      <c r="D139" t="n">
         <v>63</v>
-      </c>
-      <c r="D139" t="n">
-        <v>64.4</v>
       </c>
       <c r="E139" t="n">
         <v>27</v>
       </c>
       <c r="F139" t="n">
-        <v>44.4</v>
+        <v>42.2</v>
       </c>
       <c r="G139" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="H139" t="n">
+        <v>50</v>
+      </c>
+      <c r="I139" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J139" t="n">
+        <v>21</v>
+      </c>
+      <c r="K139" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140"/>
+      <c r="B140" t="s">
+        <v>185</v>
+      </c>
+      <c r="C140" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="D140" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="E140" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F140" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H140" t="n">
         <v>45.7</v>
       </c>
-      <c r="I139" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J139" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K139" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>311</v>
-      </c>
-      <c r="B140" t="s">
-        <v>170</v>
-      </c>
-      <c r="C140" t="n">
-        <v>44</v>
-      </c>
-      <c r="D140" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E140"/>
-      <c r="F140" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G140" t="n">
-        <v>12</v>
-      </c>
-      <c r="H140" t="n">
-        <v>68.8</v>
-      </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J140" t="n">
-        <v>16.7</v>
+        <v>24.8</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141"/>
-      <c r="B141" t="s">
-        <v>185</v>
-      </c>
-      <c r="C141" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="D141" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="E141" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F141" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G141" t="n">
-        <v>11</v>
-      </c>
-      <c r="H141" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="I141" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J141" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K141" t="n">
         <v>7.9</v>
       </c>
     </row>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -192,12 +192,12 @@
     <t xml:space="preserve">Greyson Barrett</t>
   </si>
   <si>
+    <t xml:space="preserve">Iyad Anasari</t>
+  </si>
+  <si>
     <t xml:space="preserve">Iyad Ansari</t>
   </si>
   <si>
-    <t xml:space="preserve">Iyan Ansari</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jayden Valle</t>
   </si>
   <si>
@@ -690,22 +690,13 @@
     <t xml:space="preserve">Garret Day</t>
   </si>
   <si>
-    <t xml:space="preserve">Konsta Korikka</t>
-  </si>
-  <si>
     <t xml:space="preserve">Konsta Kurikka</t>
   </si>
   <si>
     <t xml:space="preserve">Mizuki Akatsuka</t>
   </si>
   <si>
-    <t xml:space="preserve">Mizuki Akatzuka</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ryoya Oe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryoya Oye</t>
   </si>
   <si>
     <t xml:space="preserve">Shane Gustafson</t>
@@ -1020,8 +1011,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K140" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K137" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K137"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -3145,31 +3136,31 @@
         <v>54</v>
       </c>
       <c r="C56" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="D56" t="n">
-        <v>26.3</v>
+        <v>37.5</v>
       </c>
       <c r="E56" t="n">
-        <v>40.4</v>
+        <v>42.5</v>
       </c>
       <c r="F56" t="n">
-        <v>26.3</v>
+        <v>37.5</v>
       </c>
       <c r="G56" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>27.8</v>
+        <v>33.3</v>
       </c>
       <c r="J56" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="K56" t="n">
-        <v>23.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="57">
@@ -3180,31 +3171,31 @@
         <v>54</v>
       </c>
       <c r="C57" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="D57" t="n">
-        <v>37.5</v>
+        <v>26.3</v>
       </c>
       <c r="E57" t="n">
-        <v>42.5</v>
+        <v>40.4</v>
       </c>
       <c r="F57" t="n">
-        <v>37.5</v>
+        <v>26.3</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I57" t="n">
-        <v>33.3</v>
+        <v>27.8</v>
       </c>
       <c r="J57" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="K57" t="n">
-        <v>33.3</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="58">
@@ -8931,31 +8922,31 @@
         <v>54</v>
       </c>
       <c r="C45" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D45" t="n">
-        <v>62.5</v>
+        <v>61.8</v>
       </c>
       <c r="E45" t="n">
-        <v>35.3</v>
+        <v>18.4</v>
       </c>
       <c r="F45" t="n">
-        <v>40</v>
+        <v>48.6</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="H45" t="n">
-        <v>40</v>
+        <v>47.3</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
-        <v>28.6</v>
+        <v>27.3</v>
       </c>
       <c r="K45" t="n">
-        <v>25</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="46">
@@ -8966,31 +8957,31 @@
         <v>54</v>
       </c>
       <c r="C46" t="n">
-        <v>57.7</v>
+        <v>60.4</v>
       </c>
       <c r="D46" t="n">
-        <v>61.8</v>
+        <v>66.4</v>
       </c>
       <c r="E46" t="n">
-        <v>15.5</v>
+        <v>20.3</v>
       </c>
       <c r="F46" t="n">
-        <v>50</v>
+        <v>44.8</v>
       </c>
       <c r="G46" t="n">
-        <v>12.8</v>
+        <v>4.8</v>
       </c>
       <c r="H46" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="I46" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J46" t="n">
-        <v>27.2</v>
+        <v>25.9</v>
       </c>
       <c r="K46" t="n">
-        <v>6.4</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="47">
@@ -9001,31 +8992,31 @@
         <v>54</v>
       </c>
       <c r="C47" t="n">
-        <v>64</v>
+        <v>56.9</v>
       </c>
       <c r="D47" t="n">
-        <v>68.4</v>
+        <v>61.8</v>
       </c>
       <c r="E47" t="n">
-        <v>23.3</v>
+        <v>19.5</v>
       </c>
       <c r="F47" t="n">
-        <v>46.3</v>
+        <v>42.4</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="H47" t="n">
-        <v>33.3</v>
+        <v>44.2</v>
       </c>
       <c r="I47" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J47" t="n">
-        <v>28.1</v>
+        <v>30.4</v>
       </c>
       <c r="K47" t="n">
-        <v>22.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="48">
@@ -9036,31 +9027,31 @@
         <v>54</v>
       </c>
       <c r="C48" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>56.9</v>
+        <v>80</v>
       </c>
       <c r="E48" t="n">
-        <v>9.1</v>
+        <v>50</v>
       </c>
       <c r="F48" t="n">
-        <v>35.7</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -9071,31 +9062,31 @@
         <v>54</v>
       </c>
       <c r="C49" t="n">
-        <v>58.2</v>
+        <v>58</v>
       </c>
       <c r="D49" t="n">
-        <v>61.5</v>
+        <v>64</v>
       </c>
       <c r="E49" t="n">
-        <v>21.1</v>
+        <v>16.3</v>
       </c>
       <c r="F49" t="n">
-        <v>44.4</v>
+        <v>43.8</v>
       </c>
       <c r="G49" t="n">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="H49" t="n">
-        <v>47.2</v>
+        <v>52.8</v>
       </c>
       <c r="I49" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="J49" t="n">
-        <v>29.3</v>
+        <v>26.6</v>
       </c>
       <c r="K49" t="n">
-        <v>14.8</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="50">
@@ -9106,31 +9097,29 @@
         <v>54</v>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="D50" t="n">
-        <v>63.2</v>
-      </c>
-      <c r="E50" t="n">
-        <v>12.5</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E50"/>
       <c r="F50" t="n">
+        <v>25</v>
+      </c>
+      <c r="G50" t="n">
         <v>33.3</v>
       </c>
-      <c r="G50" t="n">
-        <v>10</v>
-      </c>
       <c r="H50" t="n">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>35</v>
+        <v>27.3</v>
       </c>
       <c r="K50" t="n">
-        <v>10</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="51">
@@ -9141,31 +9130,31 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="D51" t="n">
-        <v>80</v>
+        <v>56.4</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>15.8</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H51" t="n">
-        <v>60</v>
+        <v>38.2</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="52">
@@ -9173,34 +9162,34 @@
         <v>232</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C52" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>64</v>
+        <v>57.4</v>
       </c>
       <c r="E52" t="n">
-        <v>16.3</v>
+        <v>16.9</v>
       </c>
       <c r="F52" t="n">
-        <v>43.8</v>
+        <v>35.6</v>
       </c>
       <c r="G52" t="n">
-        <v>6.1</v>
+        <v>13.6</v>
       </c>
       <c r="H52" t="n">
-        <v>52.8</v>
+        <v>31.2</v>
       </c>
       <c r="I52" t="n">
-        <v>8.5</v>
+        <v>2.3</v>
       </c>
       <c r="J52" t="n">
-        <v>26.6</v>
+        <v>28.4</v>
       </c>
       <c r="K52" t="n">
-        <v>20.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="53">
@@ -9208,32 +9197,34 @@
         <v>233</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C53" t="n">
-        <v>44.4</v>
+        <v>72.9</v>
       </c>
       <c r="D53" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E53"/>
+        <v>75.3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>43.6</v>
+      </c>
       <c r="F53" t="n">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="G53" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>41.7</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="J53" t="n">
-        <v>27.3</v>
+        <v>43.3</v>
       </c>
       <c r="K53" t="n">
-        <v>-22.2</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="54">
@@ -9241,34 +9232,34 @@
         <v>234</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C54" t="n">
-        <v>51</v>
+        <v>58.9</v>
       </c>
       <c r="D54" t="n">
-        <v>56.4</v>
+        <v>60.2</v>
       </c>
       <c r="E54" t="n">
-        <v>15.8</v>
+        <v>14.5</v>
       </c>
       <c r="F54" t="n">
-        <v>23.2</v>
+        <v>44.7</v>
       </c>
       <c r="G54" t="n">
-        <v>10.3</v>
+        <v>14.5</v>
       </c>
       <c r="H54" t="n">
-        <v>38.2</v>
+        <v>50</v>
       </c>
       <c r="I54" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
-        <v>13.9</v>
+        <v>33.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-1.4</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="55">
@@ -9279,31 +9270,29 @@
         <v>72</v>
       </c>
       <c r="C55" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="D55" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="E55" t="n">
-        <v>16.9</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E55"/>
       <c r="F55" t="n">
-        <v>35.6</v>
+        <v>33.3</v>
       </c>
       <c r="G55" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>31.2</v>
+        <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>28.4</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>4.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="56">
@@ -9314,31 +9303,31 @@
         <v>72</v>
       </c>
       <c r="C56" t="n">
-        <v>72.9</v>
+        <v>67.1</v>
       </c>
       <c r="D56" t="n">
-        <v>75.3</v>
+        <v>68.8</v>
       </c>
       <c r="E56" t="n">
-        <v>43.6</v>
+        <v>20.7</v>
       </c>
       <c r="F56" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H56" t="n">
-        <v>41.7</v>
+        <v>42.5</v>
       </c>
       <c r="I56" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J56" t="n">
-        <v>43.3</v>
+        <v>22.8</v>
       </c>
       <c r="K56" t="n">
-        <v>38.3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -9349,31 +9338,31 @@
         <v>72</v>
       </c>
       <c r="C57" t="n">
-        <v>58.9</v>
+        <v>55.3</v>
       </c>
       <c r="D57" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="E57" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="F57" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="G57" t="n">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="H57" t="n">
-        <v>50</v>
+        <v>41.1</v>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J57" t="n">
-        <v>33.3</v>
+        <v>36.4</v>
       </c>
       <c r="K57" t="n">
-        <v>16.4</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="58">
@@ -9384,29 +9373,31 @@
         <v>72</v>
       </c>
       <c r="C58" t="n">
-        <v>66.7</v>
+        <v>72.4</v>
       </c>
       <c r="D58" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E58"/>
+        <v>59.2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>12</v>
+      </c>
       <c r="F58" t="n">
+        <v>50</v>
+      </c>
+      <c r="G58" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H58" t="n">
         <v>33.3</v>
       </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>100</v>
-      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>25</v>
+        <v>42.4</v>
       </c>
       <c r="K58" t="n">
-        <v>33.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="59">
@@ -9417,31 +9408,31 @@
         <v>72</v>
       </c>
       <c r="C59" t="n">
-        <v>67.1</v>
+        <v>61.7</v>
       </c>
       <c r="D59" t="n">
-        <v>68.8</v>
+        <v>63.1</v>
       </c>
       <c r="E59" t="n">
-        <v>20.7</v>
+        <v>23.4</v>
       </c>
       <c r="F59" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G59" t="n">
-        <v>3.8</v>
+        <v>8.1</v>
       </c>
       <c r="H59" t="n">
-        <v>42.5</v>
+        <v>34.6</v>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="J59" t="n">
-        <v>22.8</v>
+        <v>15.7</v>
       </c>
       <c r="K59" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="60">
@@ -9452,31 +9443,31 @@
         <v>72</v>
       </c>
       <c r="C60" t="n">
-        <v>55.3</v>
+        <v>61.8</v>
       </c>
       <c r="D60" t="n">
-        <v>60.1</v>
+        <v>64.7</v>
       </c>
       <c r="E60" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="F60" t="n">
-        <v>44.4</v>
+        <v>44.7</v>
       </c>
       <c r="G60" t="n">
-        <v>13.2</v>
+        <v>6.5</v>
       </c>
       <c r="H60" t="n">
-        <v>41.1</v>
+        <v>62</v>
       </c>
       <c r="I60" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J60" t="n">
-        <v>36.4</v>
+        <v>33.6</v>
       </c>
       <c r="K60" t="n">
-        <v>8.7</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="61">
@@ -9487,31 +9478,31 @@
         <v>72</v>
       </c>
       <c r="C61" t="n">
-        <v>72.4</v>
+        <v>56.5</v>
       </c>
       <c r="D61" t="n">
-        <v>59.2</v>
+        <v>61.6</v>
       </c>
       <c r="E61" t="n">
-        <v>12</v>
+        <v>6.5</v>
       </c>
       <c r="F61" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G61" t="n">
-        <v>20.7</v>
+        <v>8.7</v>
       </c>
       <c r="H61" t="n">
-        <v>33.3</v>
+        <v>56.2</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J61" t="n">
-        <v>42.4</v>
+        <v>23.8</v>
       </c>
       <c r="K61" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="62">
@@ -9522,31 +9513,31 @@
         <v>72</v>
       </c>
       <c r="C62" t="n">
-        <v>61.7</v>
+        <v>65.7</v>
       </c>
       <c r="D62" t="n">
-        <v>63.1</v>
+        <v>66.9</v>
       </c>
       <c r="E62" t="n">
-        <v>23.4</v>
+        <v>29.4</v>
       </c>
       <c r="F62" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="G62" t="n">
-        <v>8.1</v>
+        <v>5</v>
       </c>
       <c r="H62" t="n">
-        <v>34.6</v>
+        <v>55.8</v>
       </c>
       <c r="I62" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J62" t="n">
-        <v>15.7</v>
+        <v>19.6</v>
       </c>
       <c r="K62" t="n">
-        <v>4.1</v>
+        <v>9.3</v>
       </c>
     </row>
     <row r="63">
@@ -9557,238 +9548,238 @@
         <v>72</v>
       </c>
       <c r="C63" t="n">
-        <v>61.8</v>
+        <v>64.2</v>
       </c>
       <c r="D63" t="n">
-        <v>64.7</v>
+        <v>65.1</v>
       </c>
       <c r="E63" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="F63" t="n">
-        <v>44.7</v>
+        <v>37.5</v>
       </c>
       <c r="G63" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H63" t="n">
-        <v>62</v>
+        <v>22.9</v>
       </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="J63" t="n">
-        <v>33.6</v>
+        <v>19.1</v>
       </c>
       <c r="K63" t="n">
-        <v>15.6</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>244</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
         <v>72</v>
       </c>
       <c r="C64" t="n">
-        <v>56.5</v>
+        <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>61.6</v>
+        <v>60.6</v>
       </c>
       <c r="E64" t="n">
-        <v>6.5</v>
+        <v>46.7</v>
       </c>
       <c r="F64" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>8.7</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>56.2</v>
+        <v>25</v>
       </c>
       <c r="I64" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="J64" t="n">
-        <v>23.8</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B65" t="s">
         <v>72</v>
       </c>
       <c r="C65" t="n">
-        <v>65.7</v>
+        <v>38.7</v>
       </c>
       <c r="D65" t="n">
-        <v>66.9</v>
+        <v>51.7</v>
       </c>
       <c r="E65" t="n">
-        <v>29.4</v>
+        <v>18.5</v>
       </c>
       <c r="F65" t="n">
-        <v>33.9</v>
+        <v>28.6</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>22.6</v>
       </c>
       <c r="H65" t="n">
-        <v>55.8</v>
+        <v>50</v>
       </c>
       <c r="I65" t="n">
-        <v>4.3</v>
+        <v>9.7</v>
       </c>
       <c r="J65" t="n">
-        <v>19.6</v>
+        <v>31.1</v>
       </c>
       <c r="K65" t="n">
-        <v>9.3</v>
+        <v>-9.7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>246</v>
+        <v>92</v>
       </c>
       <c r="B66" t="s">
         <v>72</v>
       </c>
       <c r="C66" t="n">
-        <v>64.2</v>
+        <v>40</v>
       </c>
       <c r="D66" t="n">
-        <v>65.1</v>
+        <v>57.1</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="F66" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="I66" t="n">
-        <v>1.9</v>
+        <v>40</v>
       </c>
       <c r="J66" t="n">
-        <v>19.1</v>
+        <v>14.3</v>
       </c>
       <c r="K66" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>90</v>
+        <v>245</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C67" t="n">
-        <v>30</v>
+        <v>73.4</v>
       </c>
       <c r="D67" t="n">
-        <v>60.6</v>
+        <v>71.9</v>
       </c>
       <c r="E67" t="n">
-        <v>46.7</v>
+        <v>16.4</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>41.5</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>48.1</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>1.3</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B68" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C68" t="n">
-        <v>38.7</v>
+        <v>69</v>
       </c>
       <c r="D68" t="n">
-        <v>51.7</v>
+        <v>67.1</v>
       </c>
       <c r="E68" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="F68" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="G68" t="n">
-        <v>22.6</v>
+        <v>3.4</v>
       </c>
       <c r="H68" t="n">
-        <v>50</v>
+        <v>36.4</v>
       </c>
       <c r="I68" t="n">
-        <v>9.7</v>
+        <v>3.4</v>
       </c>
       <c r="J68" t="n">
-        <v>31.1</v>
+        <v>7.5</v>
       </c>
       <c r="K68" t="n">
-        <v>-9.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>247</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="C69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D69" t="n">
-        <v>57.1</v>
+        <v>68.3</v>
       </c>
       <c r="E69" t="n">
-        <v>37.5</v>
+        <v>26.5</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>38.9</v>
       </c>
       <c r="I69" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>14.3</v>
+        <v>8.9</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -9802,31 +9793,31 @@
         <v>96</v>
       </c>
       <c r="C70" t="n">
-        <v>73.4</v>
+        <v>56.4</v>
       </c>
       <c r="D70" t="n">
-        <v>71.9</v>
+        <v>61.5</v>
       </c>
       <c r="E70" t="n">
-        <v>16.4</v>
+        <v>20.5</v>
       </c>
       <c r="F70" t="n">
-        <v>41.5</v>
+        <v>40</v>
       </c>
       <c r="G70" t="n">
-        <v>2.5</v>
+        <v>12.8</v>
       </c>
       <c r="H70" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J70" t="n">
-        <v>23</v>
+        <v>19.3</v>
       </c>
       <c r="K70" t="n">
-        <v>19</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="71">
@@ -9837,31 +9828,31 @@
         <v>96</v>
       </c>
       <c r="C71" t="n">
-        <v>69</v>
+        <v>54.8</v>
       </c>
       <c r="D71" t="n">
-        <v>67.1</v>
+        <v>62.4</v>
       </c>
       <c r="E71" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="F71" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G71" t="n">
-        <v>3.4</v>
+        <v>14.3</v>
       </c>
       <c r="H71" t="n">
-        <v>36.4</v>
+        <v>54.2</v>
       </c>
       <c r="I71" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>7.5</v>
+        <v>25.5</v>
       </c>
       <c r="K71" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="72">
@@ -9872,31 +9863,31 @@
         <v>96</v>
       </c>
       <c r="C72" t="n">
-        <v>50</v>
+        <v>61.1</v>
       </c>
       <c r="D72" t="n">
-        <v>68.3</v>
+        <v>63</v>
       </c>
       <c r="E72" t="n">
-        <v>26.5</v>
+        <v>17.6</v>
       </c>
       <c r="F72" t="n">
-        <v>16.7</v>
+        <v>55</v>
       </c>
       <c r="G72" t="n">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
       <c r="H72" t="n">
-        <v>38.9</v>
+        <v>56.5</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
-        <v>8.9</v>
+        <v>36.2</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="73">
@@ -9907,31 +9898,31 @@
         <v>96</v>
       </c>
       <c r="C73" t="n">
-        <v>56.4</v>
+        <v>62.1</v>
       </c>
       <c r="D73" t="n">
         <v>61.5</v>
       </c>
       <c r="E73" t="n">
-        <v>20.5</v>
+        <v>26.6</v>
       </c>
       <c r="F73" t="n">
-        <v>40</v>
+        <v>57.3</v>
       </c>
       <c r="G73" t="n">
-        <v>12.8</v>
+        <v>7.2</v>
       </c>
       <c r="H73" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>19.3</v>
+        <v>39.5</v>
       </c>
       <c r="K73" t="n">
-        <v>2.6</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="74">
@@ -9942,31 +9933,31 @@
         <v>96</v>
       </c>
       <c r="C74" t="n">
-        <v>54.8</v>
+        <v>57.1</v>
       </c>
       <c r="D74" t="n">
-        <v>62.4</v>
+        <v>66.7</v>
       </c>
       <c r="E74" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F74" t="n">
         <v>20</v>
       </c>
-      <c r="F74" t="n">
-        <v>50</v>
-      </c>
       <c r="G74" t="n">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="H74" t="n">
-        <v>54.2</v>
+        <v>47.8</v>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J74" t="n">
-        <v>25.5</v>
+        <v>22.7</v>
       </c>
       <c r="K74" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="75">
@@ -9977,31 +9968,31 @@
         <v>96</v>
       </c>
       <c r="C75" t="n">
-        <v>61.1</v>
+        <v>72.7</v>
       </c>
       <c r="D75" t="n">
-        <v>63</v>
+        <v>66.2</v>
       </c>
       <c r="E75" t="n">
-        <v>17.6</v>
+        <v>21.7</v>
       </c>
       <c r="F75" t="n">
-        <v>55</v>
+        <v>38.5</v>
       </c>
       <c r="G75" t="n">
-        <v>7.1</v>
+        <v>13.6</v>
       </c>
       <c r="H75" t="n">
-        <v>56.5</v>
+        <v>46.2</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>36.2</v>
+        <v>30.6</v>
       </c>
       <c r="K75" t="n">
-        <v>22.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="76">
@@ -10012,31 +10003,31 @@
         <v>96</v>
       </c>
       <c r="C76" t="n">
-        <v>62.1</v>
+        <v>69.4</v>
       </c>
       <c r="D76" t="n">
-        <v>61.5</v>
+        <v>69.9</v>
       </c>
       <c r="E76" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="F76" t="n">
-        <v>57.3</v>
+        <v>44.9</v>
       </c>
       <c r="G76" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H76" t="n">
-        <v>54</v>
+        <v>51.9</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
-        <v>39.5</v>
+        <v>25.1</v>
       </c>
       <c r="K76" t="n">
-        <v>29.5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
@@ -10047,31 +10038,31 @@
         <v>96</v>
       </c>
       <c r="C77" t="n">
-        <v>57.1</v>
+        <v>61.7</v>
       </c>
       <c r="D77" t="n">
-        <v>66.7</v>
+        <v>63.5</v>
       </c>
       <c r="E77" t="n">
-        <v>34.5</v>
+        <v>25.7</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>54.3</v>
       </c>
       <c r="G77" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H77" t="n">
-        <v>47.8</v>
+        <v>40.6</v>
       </c>
       <c r="I77" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J77" t="n">
-        <v>22.7</v>
+        <v>30.3</v>
       </c>
       <c r="K77" t="n">
-        <v>3.6</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="78">
@@ -10082,31 +10073,29 @@
         <v>96</v>
       </c>
       <c r="C78" t="n">
-        <v>72.7</v>
+        <v>33.3</v>
       </c>
       <c r="D78" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="E78" t="n">
-        <v>21.7</v>
-      </c>
+        <v>64.3</v>
+      </c>
+      <c r="E78"/>
       <c r="F78" t="n">
-        <v>38.5</v>
+        <v>100</v>
       </c>
       <c r="G78" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>30.6</v>
+        <v>40</v>
       </c>
       <c r="K78" t="n">
-        <v>9.1</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="79">
@@ -10117,31 +10106,31 @@
         <v>96</v>
       </c>
       <c r="C79" t="n">
-        <v>69.4</v>
+        <v>63.3</v>
       </c>
       <c r="D79" t="n">
-        <v>69.9</v>
+        <v>62.7</v>
       </c>
       <c r="E79" t="n">
-        <v>26.9</v>
+        <v>21.1</v>
       </c>
       <c r="F79" t="n">
-        <v>44.9</v>
+        <v>42.1</v>
       </c>
       <c r="G79" t="n">
-        <v>7.4</v>
+        <v>9.8</v>
       </c>
       <c r="H79" t="n">
-        <v>51.9</v>
+        <v>60</v>
       </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
-        <v>25.1</v>
+        <v>20.5</v>
       </c>
       <c r="K79" t="n">
-        <v>13</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="80">
@@ -10149,34 +10138,34 @@
         <v>258</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C80" t="n">
-        <v>61.7</v>
+        <v>42</v>
       </c>
       <c r="D80" t="n">
-        <v>63.5</v>
+        <v>44.7</v>
       </c>
       <c r="E80" t="n">
-        <v>25.7</v>
+        <v>6.3</v>
       </c>
       <c r="F80" t="n">
-        <v>54.3</v>
+        <v>46.4</v>
       </c>
       <c r="G80" t="n">
-        <v>7.4</v>
+        <v>31.9</v>
       </c>
       <c r="H80" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="I80" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="J80" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="K80" t="n">
-        <v>19.6</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="81">
@@ -10184,380 +10173,380 @@
         <v>259</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C81" t="n">
-        <v>33.3</v>
+        <v>67.9</v>
       </c>
       <c r="D81" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="E81"/>
+        <v>63.4</v>
+      </c>
+      <c r="E81" t="n">
+        <v>26</v>
+      </c>
       <c r="F81" t="n">
-        <v>100</v>
+        <v>46.5</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>53.7</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="J81" t="n">
-        <v>40</v>
+        <v>29.9</v>
       </c>
       <c r="K81" t="n">
-        <v>66.7</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C82" t="n">
-        <v>63.3</v>
+        <v>50</v>
       </c>
       <c r="D82" t="n">
-        <v>62.7</v>
+        <v>53.5</v>
       </c>
       <c r="E82" t="n">
-        <v>21.1</v>
+        <v>10.1</v>
       </c>
       <c r="F82" t="n">
-        <v>42.1</v>
+        <v>46.4</v>
       </c>
       <c r="G82" t="n">
-        <v>9.8</v>
+        <v>13.6</v>
       </c>
       <c r="H82" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J82" t="n">
-        <v>20.5</v>
+        <v>22.1</v>
       </c>
       <c r="K82" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B83" t="s">
         <v>110</v>
       </c>
       <c r="C83" t="n">
-        <v>42</v>
+        <v>28.6</v>
       </c>
       <c r="D83" t="n">
-        <v>44.7</v>
-      </c>
-      <c r="E83" t="n">
-        <v>6.3</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E83"/>
       <c r="F83" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>31.9</v>
+        <v>42.9</v>
       </c>
       <c r="H83" t="n">
-        <v>41.4</v>
+        <v>25</v>
       </c>
       <c r="I83" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>30.4</v>
+        <v>14.3</v>
       </c>
       <c r="K83" t="n">
-        <v>-13.1</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B84" t="s">
         <v>110</v>
       </c>
       <c r="C84" t="n">
-        <v>67.9</v>
+        <v>63.6</v>
       </c>
       <c r="D84" t="n">
-        <v>63.4</v>
+        <v>64.4</v>
       </c>
       <c r="E84" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="F84" t="n">
-        <v>46.5</v>
+        <v>31.2</v>
       </c>
       <c r="G84" t="n">
-        <v>10.5</v>
+        <v>12.1</v>
       </c>
       <c r="H84" t="n">
-        <v>53.7</v>
+        <v>39.1</v>
       </c>
       <c r="I84" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>29.9</v>
+        <v>24.6</v>
       </c>
       <c r="K84" t="n">
-        <v>12.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="B85" t="s">
         <v>110</v>
       </c>
       <c r="C85" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="D85" t="n">
-        <v>53.5</v>
+        <v>56.4</v>
       </c>
       <c r="E85" t="n">
-        <v>10.1</v>
+        <v>22.6</v>
       </c>
       <c r="F85" t="n">
-        <v>46.4</v>
+        <v>41.5</v>
       </c>
       <c r="G85" t="n">
-        <v>13.6</v>
+        <v>14.9</v>
       </c>
       <c r="H85" t="n">
-        <v>38.5</v>
+        <v>32.6</v>
       </c>
       <c r="I85" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J85" t="n">
-        <v>22.1</v>
+        <v>33.6</v>
       </c>
       <c r="K85" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>263</v>
+        <v>112</v>
       </c>
       <c r="B86" t="s">
         <v>110</v>
       </c>
       <c r="C86" t="n">
-        <v>28.6</v>
+        <v>57.4</v>
       </c>
       <c r="D86" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E86"/>
+        <v>59.1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>19.1</v>
+      </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="G86" t="n">
-        <v>42.9</v>
+        <v>6.5</v>
       </c>
       <c r="H86" t="n">
-        <v>25</v>
+        <v>42.2</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J86" t="n">
-        <v>14.3</v>
+        <v>22.5</v>
       </c>
       <c r="K86" t="n">
-        <v>-42.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>264</v>
+        <v>113</v>
       </c>
       <c r="B87" t="s">
         <v>110</v>
       </c>
       <c r="C87" t="n">
-        <v>63.6</v>
+        <v>71.4</v>
       </c>
       <c r="D87" t="n">
-        <v>64.4</v>
+        <v>70.6</v>
       </c>
       <c r="E87" t="n">
-        <v>25.5</v>
+        <v>22.2</v>
       </c>
       <c r="F87" t="n">
-        <v>31.2</v>
+        <v>28.6</v>
       </c>
       <c r="G87" t="n">
-        <v>12.1</v>
+        <v>7.1</v>
       </c>
       <c r="H87" t="n">
-        <v>39.1</v>
+        <v>45.5</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J87" t="n">
-        <v>24.6</v>
+        <v>10.7</v>
       </c>
       <c r="K87" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="B88" t="s">
         <v>110</v>
       </c>
       <c r="C88" t="n">
-        <v>48.6</v>
+        <v>61.5</v>
       </c>
       <c r="D88" t="n">
-        <v>56.4</v>
+        <v>66.1</v>
       </c>
       <c r="E88" t="n">
-        <v>22.6</v>
+        <v>27</v>
       </c>
       <c r="F88" t="n">
-        <v>41.5</v>
+        <v>38</v>
       </c>
       <c r="G88" t="n">
-        <v>14.9</v>
+        <v>5.5</v>
       </c>
       <c r="H88" t="n">
-        <v>32.6</v>
+        <v>44.5</v>
       </c>
       <c r="I88" t="n">
         <v>4.1</v>
       </c>
       <c r="J88" t="n">
-        <v>33.6</v>
+        <v>22.2</v>
       </c>
       <c r="K88" t="n">
-        <v>8.1</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="B89" t="s">
         <v>110</v>
       </c>
       <c r="C89" t="n">
-        <v>57.4</v>
+        <v>54.5</v>
       </c>
       <c r="D89" t="n">
-        <v>59.1</v>
+        <v>55.6</v>
       </c>
       <c r="E89" t="n">
-        <v>19.1</v>
+        <v>10.4</v>
       </c>
       <c r="F89" t="n">
-        <v>24.2</v>
+        <v>29.4</v>
       </c>
       <c r="G89" t="n">
-        <v>6.5</v>
+        <v>15.2</v>
       </c>
       <c r="H89" t="n">
-        <v>42.2</v>
+        <v>45</v>
       </c>
       <c r="I89" t="n">
-        <v>4.8</v>
+        <v>6.1</v>
       </c>
       <c r="J89" t="n">
-        <v>22.5</v>
+        <v>26.6</v>
       </c>
       <c r="K89" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>113</v>
+        <v>264</v>
       </c>
       <c r="B90" t="s">
         <v>110</v>
       </c>
       <c r="C90" t="n">
-        <v>71.4</v>
+        <v>34.6</v>
       </c>
       <c r="D90" t="n">
-        <v>70.6</v>
-      </c>
-      <c r="E90" t="n">
-        <v>22.2</v>
-      </c>
+        <v>54.5</v>
+      </c>
+      <c r="E90"/>
       <c r="F90" t="n">
-        <v>28.6</v>
+        <v>23.8</v>
       </c>
       <c r="G90" t="n">
-        <v>7.1</v>
+        <v>15.4</v>
       </c>
       <c r="H90" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="I90" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="J90" t="n">
-        <v>10.7</v>
+        <v>43.1</v>
       </c>
       <c r="K90" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="B91" t="s">
         <v>110</v>
       </c>
       <c r="C91" t="n">
-        <v>61.5</v>
+        <v>67.3</v>
       </c>
       <c r="D91" t="n">
-        <v>66.1</v>
+        <v>65.4</v>
       </c>
       <c r="E91" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="F91" t="n">
-        <v>38</v>
+        <v>39.3</v>
       </c>
       <c r="G91" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="H91" t="n">
-        <v>44.5</v>
+        <v>46.7</v>
       </c>
       <c r="I91" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
-        <v>22.2</v>
+        <v>29</v>
       </c>
       <c r="K91" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="92">
@@ -10568,31 +10557,31 @@
         <v>110</v>
       </c>
       <c r="C92" t="n">
-        <v>54.5</v>
+        <v>62.1</v>
       </c>
       <c r="D92" t="n">
-        <v>55.6</v>
+        <v>61.2</v>
       </c>
       <c r="E92" t="n">
-        <v>10.4</v>
+        <v>14</v>
       </c>
       <c r="F92" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="G92" t="n">
-        <v>15.2</v>
+        <v>10.3</v>
       </c>
       <c r="H92" t="n">
-        <v>45</v>
+        <v>48.6</v>
       </c>
       <c r="I92" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>26.6</v>
+        <v>23.2</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="93">
@@ -10603,29 +10592,31 @@
         <v>110</v>
       </c>
       <c r="C93" t="n">
-        <v>34.6</v>
+        <v>52.6</v>
       </c>
       <c r="D93" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E93"/>
+        <v>55.8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>25.6</v>
+      </c>
       <c r="F93" t="n">
-        <v>23.8</v>
+        <v>37.9</v>
       </c>
       <c r="G93" t="n">
-        <v>15.4</v>
+        <v>12.4</v>
       </c>
       <c r="H93" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I93" t="n">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="J93" t="n">
-        <v>43.1</v>
+        <v>24.9</v>
       </c>
       <c r="K93" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="94">
@@ -10636,31 +10627,31 @@
         <v>110</v>
       </c>
       <c r="C94" t="n">
-        <v>67.3</v>
+        <v>75</v>
       </c>
       <c r="D94" t="n">
-        <v>65.4</v>
+        <v>65</v>
       </c>
       <c r="E94" t="n">
-        <v>27.7</v>
+        <v>12.1</v>
       </c>
       <c r="F94" t="n">
-        <v>39.3</v>
+        <v>37.5</v>
       </c>
       <c r="G94" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>46.7</v>
+        <v>53.8</v>
       </c>
       <c r="I94" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="J94" t="n">
-        <v>29</v>
+        <v>26.9</v>
       </c>
       <c r="K94" t="n">
-        <v>10.8</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="95">
@@ -10671,31 +10662,31 @@
         <v>110</v>
       </c>
       <c r="C95" t="n">
-        <v>62.1</v>
+        <v>55.2</v>
       </c>
       <c r="D95" t="n">
-        <v>61.2</v>
+        <v>61.1</v>
       </c>
       <c r="E95" t="n">
-        <v>14</v>
+        <v>23.4</v>
       </c>
       <c r="F95" t="n">
-        <v>25</v>
+        <v>38.3</v>
       </c>
       <c r="G95" t="n">
-        <v>10.3</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="n">
-        <v>48.6</v>
+        <v>50.7</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J95" t="n">
-        <v>23.2</v>
+        <v>24.5</v>
       </c>
       <c r="K95" t="n">
-        <v>1.8</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="96">
@@ -10703,34 +10694,34 @@
         <v>270</v>
       </c>
       <c r="B96" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C96" t="n">
-        <v>52.6</v>
+        <v>74.2</v>
       </c>
       <c r="D96" t="n">
-        <v>55.8</v>
+        <v>69.7</v>
       </c>
       <c r="E96" t="n">
-        <v>25.6</v>
+        <v>39.1</v>
       </c>
       <c r="F96" t="n">
-        <v>37.9</v>
+        <v>33.3</v>
       </c>
       <c r="G96" t="n">
-        <v>12.4</v>
+        <v>9.4</v>
       </c>
       <c r="H96" t="n">
-        <v>30</v>
+        <v>52.2</v>
       </c>
       <c r="I96" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>24.9</v>
+        <v>22.9</v>
       </c>
       <c r="K96" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="97">
@@ -10738,34 +10729,34 @@
         <v>271</v>
       </c>
       <c r="B97" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C97" t="n">
-        <v>75</v>
+        <v>63.2</v>
       </c>
       <c r="D97" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E97" t="n">
-        <v>12.1</v>
+        <v>16.9</v>
       </c>
       <c r="F97" t="n">
-        <v>37.5</v>
+        <v>43.3</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="H97" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="I97" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J97" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="K97" t="n">
-        <v>18.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -10773,34 +10764,34 @@
         <v>272</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C98" t="n">
-        <v>55.2</v>
+        <v>58.7</v>
       </c>
       <c r="D98" t="n">
-        <v>61.1</v>
+        <v>64.2</v>
       </c>
       <c r="E98" t="n">
-        <v>23.4</v>
+        <v>26.6</v>
       </c>
       <c r="F98" t="n">
-        <v>38.3</v>
+        <v>36.8</v>
       </c>
       <c r="G98" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="H98" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="I98" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="J98" t="n">
-        <v>24.5</v>
+        <v>22.5</v>
       </c>
       <c r="K98" t="n">
-        <v>13.3</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="99">
@@ -10811,31 +10802,31 @@
         <v>133</v>
       </c>
       <c r="C99" t="n">
-        <v>74.2</v>
+        <v>63.4</v>
       </c>
       <c r="D99" t="n">
-        <v>69.7</v>
+        <v>65.5</v>
       </c>
       <c r="E99" t="n">
-        <v>39.1</v>
+        <v>30.1</v>
       </c>
       <c r="F99" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G99" t="n">
-        <v>9.4</v>
+        <v>9.8</v>
       </c>
       <c r="H99" t="n">
-        <v>52.2</v>
+        <v>60.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J99" t="n">
-        <v>22.9</v>
+        <v>33.5</v>
       </c>
       <c r="K99" t="n">
-        <v>6.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="100">
@@ -10846,31 +10837,31 @@
         <v>133</v>
       </c>
       <c r="C100" t="n">
-        <v>63.2</v>
+        <v>66.1</v>
       </c>
       <c r="D100" t="n">
-        <v>57</v>
+        <v>66.8</v>
       </c>
       <c r="E100" t="n">
-        <v>16.9</v>
+        <v>33.8</v>
       </c>
       <c r="F100" t="n">
-        <v>43.3</v>
+        <v>59.3</v>
       </c>
       <c r="G100" t="n">
-        <v>15.8</v>
+        <v>7.1</v>
       </c>
       <c r="H100" t="n">
-        <v>40</v>
+        <v>54.3</v>
       </c>
       <c r="I100" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J100" t="n">
-        <v>27</v>
+        <v>31.6</v>
       </c>
       <c r="K100" t="n">
-        <v>7</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="101">
@@ -10881,31 +10872,31 @@
         <v>133</v>
       </c>
       <c r="C101" t="n">
-        <v>58.7</v>
+        <v>80</v>
       </c>
       <c r="D101" t="n">
-        <v>64.2</v>
+        <v>75.8</v>
       </c>
       <c r="E101" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="F101" t="n">
-        <v>36.8</v>
+        <v>75</v>
       </c>
       <c r="G101" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>50</v>
+        <v>85.7</v>
       </c>
       <c r="I101" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="J101" t="n">
-        <v>22.5</v>
+        <v>33.3</v>
       </c>
       <c r="K101" t="n">
-        <v>8.4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
@@ -10916,31 +10907,31 @@
         <v>133</v>
       </c>
       <c r="C102" t="n">
-        <v>63.4</v>
+        <v>60.6</v>
       </c>
       <c r="D102" t="n">
-        <v>65.5</v>
+        <v>64.6</v>
       </c>
       <c r="E102" t="n">
-        <v>30.1</v>
+        <v>21.7</v>
       </c>
       <c r="F102" t="n">
-        <v>50</v>
+        <v>25.7</v>
       </c>
       <c r="G102" t="n">
-        <v>9.8</v>
+        <v>5.9</v>
       </c>
       <c r="H102" t="n">
-        <v>60.4</v>
+        <v>67.9</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J102" t="n">
-        <v>33.5</v>
+        <v>19.3</v>
       </c>
       <c r="K102" t="n">
-        <v>18.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="103">
@@ -10951,31 +10942,31 @@
         <v>133</v>
       </c>
       <c r="C103" t="n">
-        <v>66.1</v>
+        <v>69.2</v>
       </c>
       <c r="D103" t="n">
-        <v>66.8</v>
+        <v>68.2</v>
       </c>
       <c r="E103" t="n">
-        <v>33.8</v>
+        <v>33.3</v>
       </c>
       <c r="F103" t="n">
-        <v>59.3</v>
+        <v>54.5</v>
       </c>
       <c r="G103" t="n">
-        <v>7.1</v>
+        <v>10.3</v>
       </c>
       <c r="H103" t="n">
-        <v>54.3</v>
+        <v>47.8</v>
       </c>
       <c r="I103" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J103" t="n">
-        <v>31.6</v>
+        <v>38.8</v>
       </c>
       <c r="K103" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="104">
@@ -10986,31 +10977,31 @@
         <v>133</v>
       </c>
       <c r="C104" t="n">
-        <v>80</v>
+        <v>66.3</v>
       </c>
       <c r="D104" t="n">
-        <v>75.8</v>
+        <v>65.8</v>
       </c>
       <c r="E104" t="n">
-        <v>27.3</v>
+        <v>23.1</v>
       </c>
       <c r="F104" t="n">
-        <v>75</v>
+        <v>37.2</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H104" t="n">
-        <v>85.7</v>
+        <v>41.3</v>
       </c>
       <c r="I104" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>33.3</v>
+        <v>21.5</v>
       </c>
       <c r="K104" t="n">
-        <v>30</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="105">
@@ -11021,31 +11012,31 @@
         <v>133</v>
       </c>
       <c r="C105" t="n">
-        <v>60.6</v>
+        <v>66.9</v>
       </c>
       <c r="D105" t="n">
-        <v>64.6</v>
+        <v>69.5</v>
       </c>
       <c r="E105" t="n">
-        <v>21.7</v>
+        <v>19.9</v>
       </c>
       <c r="F105" t="n">
-        <v>25.7</v>
+        <v>46.4</v>
       </c>
       <c r="G105" t="n">
-        <v>5.9</v>
+        <v>0.9</v>
       </c>
       <c r="H105" t="n">
-        <v>67.9</v>
+        <v>44.3</v>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J105" t="n">
-        <v>19.3</v>
+        <v>20.7</v>
       </c>
       <c r="K105" t="n">
-        <v>7.3</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="106">
@@ -11056,31 +11047,31 @@
         <v>133</v>
       </c>
       <c r="C106" t="n">
-        <v>69.2</v>
+        <v>64.4</v>
       </c>
       <c r="D106" t="n">
-        <v>68.2</v>
+        <v>61.4</v>
       </c>
       <c r="E106" t="n">
-        <v>33.3</v>
+        <v>13.4</v>
       </c>
       <c r="F106" t="n">
-        <v>54.5</v>
+        <v>58</v>
       </c>
       <c r="G106" t="n">
-        <v>10.3</v>
+        <v>16.4</v>
       </c>
       <c r="H106" t="n">
-        <v>47.8</v>
+        <v>32.3</v>
       </c>
       <c r="I106" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J106" t="n">
-        <v>38.8</v>
+        <v>36.4</v>
       </c>
       <c r="K106" t="n">
-        <v>20.5</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="107">
@@ -11088,34 +11079,34 @@
         <v>281</v>
       </c>
       <c r="B107" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C107" t="n">
-        <v>66.3</v>
+        <v>33.3</v>
       </c>
       <c r="D107" t="n">
-        <v>65.8</v>
+        <v>56.2</v>
       </c>
       <c r="E107" t="n">
-        <v>23.1</v>
+        <v>36.4</v>
       </c>
       <c r="F107" t="n">
-        <v>37.2</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>9.4</v>
+        <v>33.3</v>
       </c>
       <c r="H107" t="n">
-        <v>41.3</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>33.3</v>
       </c>
       <c r="J107" t="n">
-        <v>21.5</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>6.4</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="108">
@@ -11123,174 +11114,172 @@
         <v>282</v>
       </c>
       <c r="B108" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C108" t="n">
-        <v>66.9</v>
+        <v>54.1</v>
       </c>
       <c r="D108" t="n">
-        <v>69.5</v>
+        <v>57.6</v>
       </c>
       <c r="E108" t="n">
-        <v>19.9</v>
+        <v>17</v>
       </c>
       <c r="F108" t="n">
-        <v>46.4</v>
+        <v>14.3</v>
       </c>
       <c r="G108" t="n">
-        <v>0.9</v>
+        <v>13.5</v>
       </c>
       <c r="H108" t="n">
-        <v>44.3</v>
+        <v>40.7</v>
       </c>
       <c r="I108" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
-        <v>20.7</v>
+        <v>16.1</v>
       </c>
       <c r="K108" t="n">
-        <v>21.3</v>
+        <v>-8.1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>283</v>
+        <v>149</v>
       </c>
       <c r="B109" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C109" t="n">
-        <v>64.4</v>
+        <v>51.6</v>
       </c>
       <c r="D109" t="n">
-        <v>61.4</v>
+        <v>58.9</v>
       </c>
       <c r="E109" t="n">
-        <v>13.4</v>
+        <v>16</v>
       </c>
       <c r="F109" t="n">
-        <v>58</v>
+        <v>40.9</v>
       </c>
       <c r="G109" t="n">
-        <v>16.4</v>
+        <v>12.9</v>
       </c>
       <c r="H109" t="n">
-        <v>32.3</v>
+        <v>44.4</v>
       </c>
       <c r="I109" t="n">
-        <v>2.7</v>
+        <v>8.1</v>
       </c>
       <c r="J109" t="n">
-        <v>36.4</v>
+        <v>24.4</v>
       </c>
       <c r="K109" t="n">
-        <v>23.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B110" t="s">
         <v>150</v>
       </c>
       <c r="C110" t="n">
-        <v>33.3</v>
+        <v>62</v>
       </c>
       <c r="D110" t="n">
-        <v>56.2</v>
+        <v>65.2</v>
       </c>
       <c r="E110" t="n">
-        <v>36.4</v>
+        <v>19.6</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="G110" t="n">
-        <v>33.3</v>
+        <v>8.3</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="I110" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>18.1</v>
       </c>
       <c r="K110" t="n">
-        <v>-33.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
         <v>150</v>
       </c>
       <c r="C111" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="D111" t="n">
-        <v>57.6</v>
+        <v>45.5</v>
       </c>
       <c r="E111" t="n">
-        <v>17</v>
-      </c>
-      <c r="F111" t="n">
-        <v>14.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F111"/>
       <c r="G111" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="H111" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>-8.1</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>149</v>
+        <v>285</v>
       </c>
       <c r="B112" t="s">
         <v>150</v>
       </c>
       <c r="C112" t="n">
-        <v>51.6</v>
+        <v>65.8</v>
       </c>
       <c r="D112" t="n">
-        <v>58.9</v>
+        <v>62</v>
       </c>
       <c r="E112" t="n">
-        <v>16</v>
+        <v>23.2</v>
       </c>
       <c r="F112" t="n">
-        <v>40.9</v>
+        <v>26.8</v>
       </c>
       <c r="G112" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H112" t="n">
-        <v>44.4</v>
+        <v>51.2</v>
       </c>
       <c r="I112" t="n">
-        <v>8.1</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="K112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -11301,96 +11290,98 @@
         <v>150</v>
       </c>
       <c r="C113" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D113" t="n">
-        <v>65.2</v>
+        <v>58.9</v>
       </c>
       <c r="E113" t="n">
-        <v>19.6</v>
+        <v>13.2</v>
       </c>
       <c r="F113" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
       <c r="G113" t="n">
-        <v>8.3</v>
+        <v>6.2</v>
       </c>
       <c r="H113" t="n">
-        <v>37.7</v>
+        <v>41.7</v>
       </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J113" t="n">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="K113" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>287</v>
+        <v>161</v>
       </c>
       <c r="B114" t="s">
         <v>150</v>
       </c>
       <c r="C114" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="D114" t="n">
-        <v>45.5</v>
+        <v>59.9</v>
       </c>
       <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114"/>
+        <v>30.4</v>
+      </c>
+      <c r="F114" t="n">
+        <v>42.9</v>
+      </c>
       <c r="G114" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>47.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="K114" t="n">
-        <v>-25</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B115" t="s">
         <v>150</v>
       </c>
       <c r="C115" t="n">
-        <v>65.8</v>
+        <v>63</v>
       </c>
       <c r="D115" t="n">
-        <v>62</v>
+        <v>59.5</v>
       </c>
       <c r="E115" t="n">
-        <v>23.2</v>
+        <v>19.5</v>
       </c>
       <c r="F115" t="n">
-        <v>26.8</v>
+        <v>33.3</v>
       </c>
       <c r="G115" t="n">
-        <v>13.5</v>
+        <v>17.4</v>
       </c>
       <c r="H115" t="n">
-        <v>51.2</v>
+        <v>48.3</v>
       </c>
       <c r="I115" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J115" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -11398,72 +11389,72 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B116" t="s">
         <v>150</v>
       </c>
       <c r="C116" t="n">
-        <v>51</v>
+        <v>52.6</v>
       </c>
       <c r="D116" t="n">
-        <v>58.9</v>
+        <v>56.2</v>
       </c>
       <c r="E116" t="n">
-        <v>13.2</v>
+        <v>30</v>
       </c>
       <c r="F116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G116" t="n">
-        <v>6.2</v>
+        <v>15.8</v>
       </c>
       <c r="H116" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="I116" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J116" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="K116" t="n">
-        <v>4.2</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>161</v>
+        <v>289</v>
       </c>
       <c r="B117" t="s">
         <v>150</v>
       </c>
       <c r="C117" t="n">
-        <v>51.5</v>
+        <v>65.2</v>
       </c>
       <c r="D117" t="n">
-        <v>59.9</v>
+        <v>64</v>
       </c>
       <c r="E117" t="n">
-        <v>30.4</v>
+        <v>22.9</v>
       </c>
       <c r="F117" t="n">
-        <v>42.9</v>
+        <v>51.9</v>
       </c>
       <c r="G117" t="n">
-        <v>13</v>
+        <v>9.9</v>
       </c>
       <c r="H117" t="n">
-        <v>47.2</v>
+        <v>39.2</v>
       </c>
       <c r="I117" t="n">
-        <v>7.2</v>
+        <v>3.1</v>
       </c>
       <c r="J117" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="K117" t="n">
-        <v>10.2</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="118">
@@ -11474,31 +11465,31 @@
         <v>150</v>
       </c>
       <c r="C118" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D118" t="n">
-        <v>59.5</v>
+        <v>60.6</v>
       </c>
       <c r="E118" t="n">
-        <v>19.5</v>
+        <v>17.4</v>
       </c>
       <c r="F118" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G118" t="n">
-        <v>17.4</v>
+        <v>10.6</v>
       </c>
       <c r="H118" t="n">
-        <v>48.3</v>
+        <v>40.4</v>
       </c>
       <c r="I118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>24.1</v>
+        <v>35.1</v>
       </c>
       <c r="K118" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="119">
@@ -11509,31 +11500,31 @@
         <v>150</v>
       </c>
       <c r="C119" t="n">
-        <v>52.6</v>
+        <v>44</v>
       </c>
       <c r="D119" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="E119" t="n">
-        <v>30</v>
+        <v>23.1</v>
       </c>
       <c r="F119" t="n">
-        <v>10</v>
+        <v>38.5</v>
       </c>
       <c r="G119" t="n">
-        <v>15.8</v>
+        <v>8</v>
       </c>
       <c r="H119" t="n">
         <v>50</v>
       </c>
       <c r="I119" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="J119" t="n">
-        <v>15.2</v>
+        <v>26.5</v>
       </c>
       <c r="K119" t="n">
-        <v>-10.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120">
@@ -11544,31 +11535,31 @@
         <v>150</v>
       </c>
       <c r="C120" t="n">
-        <v>65.2</v>
+        <v>38.9</v>
       </c>
       <c r="D120" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E120" t="n">
-        <v>22.9</v>
+        <v>16.3</v>
       </c>
       <c r="F120" t="n">
-        <v>51.9</v>
+        <v>33.3</v>
       </c>
       <c r="G120" t="n">
-        <v>9.9</v>
+        <v>27.8</v>
       </c>
       <c r="H120" t="n">
-        <v>39.2</v>
+        <v>22.2</v>
       </c>
       <c r="I120" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J120" t="n">
-        <v>26.9</v>
+        <v>31</v>
       </c>
       <c r="K120" t="n">
-        <v>16.2</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="121">
@@ -11579,31 +11570,31 @@
         <v>150</v>
       </c>
       <c r="C121" t="n">
-        <v>60</v>
+        <v>58.7</v>
       </c>
       <c r="D121" t="n">
-        <v>60.6</v>
+        <v>62.1</v>
       </c>
       <c r="E121" t="n">
-        <v>17.4</v>
+        <v>19.7</v>
       </c>
       <c r="F121" t="n">
-        <v>50</v>
+        <v>28.7</v>
       </c>
       <c r="G121" t="n">
-        <v>10.6</v>
+        <v>7.4</v>
       </c>
       <c r="H121" t="n">
-        <v>40.4</v>
+        <v>57</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J121" t="n">
-        <v>35.1</v>
+        <v>21.6</v>
       </c>
       <c r="K121" t="n">
-        <v>14.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="122">
@@ -11614,31 +11605,31 @@
         <v>150</v>
       </c>
       <c r="C122" t="n">
-        <v>44</v>
+        <v>57.5</v>
       </c>
       <c r="D122" t="n">
-        <v>56.3</v>
+        <v>59</v>
       </c>
       <c r="E122" t="n">
-        <v>23.1</v>
+        <v>24.5</v>
       </c>
       <c r="F122" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="G122" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="H122" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="I122" t="n">
-        <v>8</v>
+        <v>8.2</v>
       </c>
       <c r="J122" t="n">
-        <v>26.5</v>
+        <v>18.1</v>
       </c>
       <c r="K122" t="n">
-        <v>12</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="123">
@@ -11646,34 +11637,34 @@
         <v>295</v>
       </c>
       <c r="B123" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C123" t="n">
-        <v>38.9</v>
+        <v>72.5</v>
       </c>
       <c r="D123" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="E123" t="n">
-        <v>16.3</v>
+        <v>22.5</v>
       </c>
       <c r="F123" t="n">
-        <v>33.3</v>
+        <v>54.5</v>
       </c>
       <c r="G123" t="n">
-        <v>27.8</v>
+        <v>3.9</v>
       </c>
       <c r="H123" t="n">
-        <v>22.2</v>
+        <v>60</v>
       </c>
       <c r="I123" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>31</v>
+        <v>22.6</v>
       </c>
       <c r="K123" t="n">
-        <v>-11.1</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="124">
@@ -11681,34 +11672,34 @@
         <v>296</v>
       </c>
       <c r="B124" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C124" t="n">
-        <v>58.7</v>
+        <v>62.4</v>
       </c>
       <c r="D124" t="n">
-        <v>62.1</v>
+        <v>67.5</v>
       </c>
       <c r="E124" t="n">
-        <v>19.7</v>
+        <v>22.6</v>
       </c>
       <c r="F124" t="n">
-        <v>28.7</v>
+        <v>44.3</v>
       </c>
       <c r="G124" t="n">
-        <v>7.4</v>
+        <v>2.4</v>
       </c>
       <c r="H124" t="n">
-        <v>57</v>
+        <v>48.4</v>
       </c>
       <c r="I124" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="K124" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
@@ -11716,34 +11707,34 @@
         <v>297</v>
       </c>
       <c r="B125" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C125" t="n">
-        <v>57.5</v>
+        <v>60.7</v>
       </c>
       <c r="D125" t="n">
-        <v>59</v>
+        <v>64.8</v>
       </c>
       <c r="E125" t="n">
-        <v>24.5</v>
+        <v>11.2</v>
       </c>
       <c r="F125" t="n">
-        <v>38.6</v>
+        <v>32.4</v>
       </c>
       <c r="G125" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="H125" t="n">
-        <v>41.7</v>
+        <v>29.6</v>
       </c>
       <c r="I125" t="n">
-        <v>8.2</v>
+        <v>3.4</v>
       </c>
       <c r="J125" t="n">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="K125" t="n">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="126">
@@ -11754,171 +11745,169 @@
         <v>170</v>
       </c>
       <c r="C126" t="n">
-        <v>72.5</v>
+        <v>58.2</v>
       </c>
       <c r="D126" t="n">
-        <v>67</v>
+        <v>62.1</v>
       </c>
       <c r="E126" t="n">
-        <v>22.5</v>
+        <v>27.7</v>
       </c>
       <c r="F126" t="n">
-        <v>54.5</v>
+        <v>65.9</v>
       </c>
       <c r="G126" t="n">
-        <v>3.9</v>
+        <v>10.6</v>
       </c>
       <c r="H126" t="n">
-        <v>60</v>
+        <v>42.3</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J126" t="n">
-        <v>22.6</v>
+        <v>37</v>
       </c>
       <c r="K126" t="n">
-        <v>19.6</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="B127" t="s">
         <v>170</v>
       </c>
       <c r="C127" t="n">
-        <v>62.4</v>
+        <v>60</v>
       </c>
       <c r="D127" t="n">
-        <v>67.5</v>
+        <v>58.8</v>
       </c>
       <c r="E127" t="n">
-        <v>22.6</v>
+        <v>10.3</v>
       </c>
       <c r="F127" t="n">
-        <v>44.3</v>
+        <v>29.4</v>
       </c>
       <c r="G127" t="n">
-        <v>2.4</v>
+        <v>10.8</v>
       </c>
       <c r="H127" t="n">
-        <v>48.4</v>
+        <v>37.7</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J127" t="n">
-        <v>20.7</v>
+        <v>22.7</v>
       </c>
       <c r="K127" t="n">
-        <v>14</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B128" t="s">
         <v>170</v>
       </c>
       <c r="C128" t="n">
-        <v>60.7</v>
+        <v>67.3</v>
       </c>
       <c r="D128" t="n">
-        <v>64.8</v>
+        <v>63.7</v>
       </c>
       <c r="E128" t="n">
-        <v>11.2</v>
+        <v>28.4</v>
       </c>
       <c r="F128" t="n">
-        <v>32.4</v>
+        <v>45.9</v>
       </c>
       <c r="G128" t="n">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="H128" t="n">
-        <v>29.6</v>
+        <v>46.7</v>
       </c>
       <c r="I128" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J128" t="n">
-        <v>19.6</v>
+        <v>46.8</v>
       </c>
       <c r="K128" t="n">
-        <v>5.7</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B129" t="s">
         <v>170</v>
       </c>
       <c r="C129" t="n">
-        <v>58.2</v>
+        <v>84.6</v>
       </c>
       <c r="D129" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="E129" t="n">
-        <v>27.7</v>
-      </c>
+        <v>74.4</v>
+      </c>
+      <c r="E129"/>
       <c r="F129" t="n">
-        <v>65.9</v>
+        <v>47.1</v>
       </c>
       <c r="G129" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>42.3</v>
+        <v>45.2</v>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
-        <v>37</v>
+        <v>28.4</v>
       </c>
       <c r="K129" t="n">
-        <v>31.8</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="B130" t="s">
         <v>170</v>
       </c>
       <c r="C130" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D130" t="n">
-        <v>58.8</v>
+        <v>45.1</v>
       </c>
       <c r="E130" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="G130" t="n">
-        <v>10.8</v>
+        <v>30.8</v>
       </c>
       <c r="H130" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="I130" t="n">
-        <v>4.1</v>
+        <v>7.7</v>
       </c>
       <c r="J130" t="n">
-        <v>22.7</v>
+        <v>31.2</v>
       </c>
       <c r="K130" t="n">
-        <v>2.7</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="131">
@@ -11929,31 +11918,31 @@
         <v>170</v>
       </c>
       <c r="C131" t="n">
-        <v>67.3</v>
+        <v>61.3</v>
       </c>
       <c r="D131" t="n">
-        <v>63.7</v>
+        <v>64.8</v>
       </c>
       <c r="E131" t="n">
-        <v>28.4</v>
+        <v>23.6</v>
       </c>
       <c r="F131" t="n">
-        <v>45.9</v>
+        <v>31.8</v>
       </c>
       <c r="G131" t="n">
-        <v>7.3</v>
+        <v>16.1</v>
       </c>
       <c r="H131" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="I131" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J131" t="n">
-        <v>46.8</v>
+        <v>29.4</v>
       </c>
       <c r="K131" t="n">
-        <v>23.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="132">
@@ -11964,29 +11953,31 @@
         <v>170</v>
       </c>
       <c r="C132" t="n">
-        <v>84.6</v>
+        <v>65.8</v>
       </c>
       <c r="D132" t="n">
-        <v>74.4</v>
-      </c>
-      <c r="E132"/>
+        <v>67.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>36.4</v>
+      </c>
       <c r="F132" t="n">
-        <v>47.1</v>
+        <v>38.1</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="H132" t="n">
-        <v>45.2</v>
+        <v>53.8</v>
       </c>
       <c r="I132" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
-        <v>28.4</v>
+        <v>26.8</v>
       </c>
       <c r="K132" t="n">
-        <v>19.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="133">
@@ -11997,31 +11988,31 @@
         <v>170</v>
       </c>
       <c r="C133" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="D133" t="n">
-        <v>45.1</v>
+        <v>60.7</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="F133" t="n">
-        <v>25</v>
+        <v>38.6</v>
       </c>
       <c r="G133" t="n">
-        <v>30.8</v>
+        <v>9.6</v>
       </c>
       <c r="H133" t="n">
-        <v>37.5</v>
+        <v>54.4</v>
       </c>
       <c r="I133" t="n">
-        <v>7.7</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
-        <v>31.2</v>
+        <v>21.7</v>
       </c>
       <c r="K133" t="n">
-        <v>-23.1</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="134">
@@ -12032,31 +12023,31 @@
         <v>170</v>
       </c>
       <c r="C134" t="n">
-        <v>61.3</v>
+        <v>66.7</v>
       </c>
       <c r="D134" t="n">
-        <v>64.8</v>
+        <v>56.7</v>
       </c>
       <c r="E134" t="n">
-        <v>23.6</v>
+        <v>14.3</v>
       </c>
       <c r="F134" t="n">
-        <v>31.8</v>
+        <v>50</v>
       </c>
       <c r="G134" t="n">
-        <v>16.1</v>
+        <v>22.2</v>
       </c>
       <c r="H134" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="I134" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="K134" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -12067,31 +12058,31 @@
         <v>170</v>
       </c>
       <c r="C135" t="n">
-        <v>65.8</v>
+        <v>69.5</v>
       </c>
       <c r="D135" t="n">
-        <v>67.5</v>
+        <v>70.3</v>
       </c>
       <c r="E135" t="n">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="F135" t="n">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="G135" t="n">
-        <v>7.9</v>
+        <v>4</v>
       </c>
       <c r="H135" t="n">
-        <v>53.8</v>
+        <v>41.9</v>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
-        <v>26.8</v>
+        <v>26.3</v>
       </c>
       <c r="K135" t="n">
-        <v>13.2</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="136">
@@ -12102,169 +12093,64 @@
         <v>170</v>
       </c>
       <c r="C136" t="n">
-        <v>50.9</v>
+        <v>59</v>
       </c>
       <c r="D136" t="n">
-        <v>60.7</v>
+        <v>63</v>
       </c>
       <c r="E136" t="n">
-        <v>24.6</v>
+        <v>27</v>
       </c>
       <c r="F136" t="n">
-        <v>38.6</v>
+        <v>42.2</v>
       </c>
       <c r="G136" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="H136" t="n">
-        <v>54.4</v>
+        <v>50</v>
       </c>
       <c r="I136" t="n">
         <v>2.6</v>
       </c>
       <c r="J136" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="K136" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="s">
-        <v>308</v>
-      </c>
+      <c r="A137"/>
       <c r="B137" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="C137" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
       <c r="D137" t="n">
-        <v>56.7</v>
+        <v>61.3</v>
       </c>
       <c r="E137" t="n">
-        <v>14.3</v>
+        <v>20.7</v>
       </c>
       <c r="F137" t="n">
-        <v>50</v>
+        <v>36.5</v>
       </c>
       <c r="G137" t="n">
-        <v>22.2</v>
+        <v>11.2</v>
       </c>
       <c r="H137" t="n">
-        <v>20</v>
+        <v>45.9</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>309</v>
-      </c>
-      <c r="B138" t="s">
-        <v>170</v>
-      </c>
-      <c r="C138" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="D138" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="E138" t="n">
-        <v>25</v>
-      </c>
-      <c r="F138" t="n">
-        <v>50</v>
-      </c>
-      <c r="G138" t="n">
-        <v>4</v>
-      </c>
-      <c r="H138" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I138" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J138" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="K138" t="n">
-        <v>18.2</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>310</v>
-      </c>
-      <c r="B139" t="s">
-        <v>170</v>
-      </c>
-      <c r="C139" t="n">
-        <v>59</v>
-      </c>
-      <c r="D139" t="n">
-        <v>63</v>
-      </c>
-      <c r="E139" t="n">
-        <v>27</v>
-      </c>
-      <c r="F139" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="G139" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H139" t="n">
-        <v>50</v>
-      </c>
-      <c r="I139" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J139" t="n">
-        <v>21</v>
-      </c>
-      <c r="K139" t="n">
-        <v>9.4</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140"/>
-      <c r="B140" t="s">
-        <v>185</v>
-      </c>
-      <c r="C140" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="D140" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="E140" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F140" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G140" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H140" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I140" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J140" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K140" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="307">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -190,9 +190,6 @@
   </si>
   <si>
     <t xml:space="preserve">Greyson Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iyad Anasari</t>
   </si>
   <si>
     <t xml:space="preserve">Iyad Ansari</t>
@@ -991,8 +988,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K178" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K178"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K177" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K177"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -3136,31 +3133,31 @@
         <v>54</v>
       </c>
       <c r="C56" t="n">
-        <v>80</v>
+        <v>69.6</v>
       </c>
       <c r="D56" t="n">
-        <v>37.5</v>
+        <v>29.6</v>
       </c>
       <c r="E56" t="n">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="F56" t="n">
-        <v>37.5</v>
+        <v>29.6</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I56" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="J56" t="n">
-        <v>33.3</v>
+        <v>47.6</v>
       </c>
       <c r="K56" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
@@ -3170,32 +3167,28 @@
       <c r="B57" t="s">
         <v>54</v>
       </c>
-      <c r="C57" t="n">
-        <v>66.7</v>
-      </c>
+      <c r="C57"/>
       <c r="D57" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="E57" t="n">
-        <v>40.4</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E57"/>
       <c r="F57" t="n">
-        <v>26.3</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>27.8</v>
+        <v>100</v>
       </c>
       <c r="J57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>23.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -3205,28 +3198,32 @@
       <c r="B58" t="s">
         <v>54</v>
       </c>
-      <c r="C58"/>
+      <c r="C58" t="n">
+        <v>65.9</v>
+      </c>
       <c r="D58" t="n">
-        <v>100</v>
-      </c>
-      <c r="E58"/>
+        <v>23.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>42.5</v>
+      </c>
       <c r="F58" t="n">
-        <v>100</v>
+        <v>23.4</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="I58" t="n">
-        <v>100</v>
+        <v>53.6</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="K58" t="n">
-        <v>100</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="59">
@@ -3237,31 +3234,31 @@
         <v>54</v>
       </c>
       <c r="C59" t="n">
-        <v>65.9</v>
+        <v>77.3</v>
       </c>
       <c r="D59" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="E59" t="n">
-        <v>42.5</v>
+        <v>54.8</v>
       </c>
       <c r="F59" t="n">
-        <v>23.4</v>
+        <v>22.5</v>
       </c>
       <c r="G59" t="n">
-        <v>21.3</v>
+        <v>41.2</v>
       </c>
       <c r="H59" t="n">
-        <v>9.1</v>
+        <v>8.2</v>
       </c>
       <c r="I59" t="n">
-        <v>53.6</v>
+        <v>55.6</v>
       </c>
       <c r="J59" t="n">
-        <v>15.9</v>
+        <v>22.2</v>
       </c>
       <c r="K59" t="n">
-        <v>21.7</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="60">
@@ -3272,31 +3269,31 @@
         <v>54</v>
       </c>
       <c r="C60" t="n">
-        <v>77.3</v>
+        <v>79.6</v>
       </c>
       <c r="D60" t="n">
-        <v>22.5</v>
+        <v>36.8</v>
       </c>
       <c r="E60" t="n">
-        <v>54.8</v>
+        <v>42.8</v>
       </c>
       <c r="F60" t="n">
-        <v>22.5</v>
+        <v>36.8</v>
       </c>
       <c r="G60" t="n">
-        <v>41.2</v>
+        <v>38.1</v>
       </c>
       <c r="H60" t="n">
-        <v>8.2</v>
+        <v>7.1</v>
       </c>
       <c r="I60" t="n">
-        <v>55.6</v>
+        <v>48</v>
       </c>
       <c r="J60" t="n">
-        <v>22.2</v>
+        <v>32</v>
       </c>
       <c r="K60" t="n">
-        <v>25.9</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61">
@@ -3307,31 +3304,31 @@
         <v>54</v>
       </c>
       <c r="C61" t="n">
-        <v>79.6</v>
+        <v>50.7</v>
       </c>
       <c r="D61" t="n">
-        <v>36.8</v>
+        <v>17.9</v>
       </c>
       <c r="E61" t="n">
-        <v>42.8</v>
+        <v>32.8</v>
       </c>
       <c r="F61" t="n">
-        <v>36.8</v>
+        <v>17.9</v>
       </c>
       <c r="G61" t="n">
-        <v>38.1</v>
+        <v>18.3</v>
       </c>
       <c r="H61" t="n">
-        <v>7.1</v>
+        <v>17.1</v>
       </c>
       <c r="I61" t="n">
-        <v>48</v>
+        <v>38.5</v>
       </c>
       <c r="J61" t="n">
-        <v>32</v>
+        <v>30.8</v>
       </c>
       <c r="K61" t="n">
-        <v>44</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="62">
@@ -3342,31 +3339,31 @@
         <v>54</v>
       </c>
       <c r="C62" t="n">
-        <v>50.7</v>
+        <v>69.4</v>
       </c>
       <c r="D62" t="n">
-        <v>17.9</v>
+        <v>13.8</v>
       </c>
       <c r="E62" t="n">
-        <v>32.8</v>
+        <v>55.6</v>
       </c>
       <c r="F62" t="n">
-        <v>17.9</v>
+        <v>13.8</v>
       </c>
       <c r="G62" t="n">
-        <v>18.3</v>
+        <v>31.4</v>
       </c>
       <c r="H62" t="n">
-        <v>17.1</v>
+        <v>13.3</v>
       </c>
       <c r="I62" t="n">
-        <v>38.5</v>
+        <v>34.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30.8</v>
+        <v>41.8</v>
       </c>
       <c r="K62" t="n">
-        <v>16.7</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="63">
@@ -3380,28 +3377,28 @@
         <v>69.4</v>
       </c>
       <c r="D63" t="n">
-        <v>13.8</v>
+        <v>22</v>
       </c>
       <c r="E63" t="n">
-        <v>55.6</v>
+        <v>47.4</v>
       </c>
       <c r="F63" t="n">
-        <v>13.8</v>
+        <v>22</v>
       </c>
       <c r="G63" t="n">
-        <v>31.4</v>
+        <v>52</v>
       </c>
       <c r="H63" t="n">
-        <v>13.3</v>
+        <v>8</v>
       </c>
       <c r="I63" t="n">
-        <v>34.5</v>
+        <v>50</v>
       </c>
       <c r="J63" t="n">
-        <v>41.8</v>
+        <v>21.4</v>
       </c>
       <c r="K63" t="n">
-        <v>25.5</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="64">
@@ -3412,31 +3409,31 @@
         <v>54</v>
       </c>
       <c r="C64" t="n">
-        <v>69.4</v>
+        <v>70.4</v>
       </c>
       <c r="D64" t="n">
-        <v>22</v>
+        <v>15.3</v>
       </c>
       <c r="E64" t="n">
-        <v>47.4</v>
+        <v>55.1</v>
       </c>
       <c r="F64" t="n">
-        <v>22</v>
+        <v>15.3</v>
       </c>
       <c r="G64" t="n">
-        <v>52</v>
+        <v>21.6</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I64" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J64" t="n">
-        <v>21.4</v>
+        <v>15</v>
       </c>
       <c r="K64" t="n">
-        <v>28.6</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="65">
@@ -3447,31 +3444,31 @@
         <v>54</v>
       </c>
       <c r="C65" t="n">
-        <v>70.4</v>
+        <v>69.3</v>
       </c>
       <c r="D65" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E65" t="n">
-        <v>55.1</v>
+        <v>54.7</v>
       </c>
       <c r="F65" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="G65" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="H65" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="I65" t="n">
-        <v>62.5</v>
+        <v>38.8</v>
       </c>
       <c r="J65" t="n">
-        <v>15</v>
+        <v>32.8</v>
       </c>
       <c r="K65" t="n">
-        <v>22.5</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="66">
@@ -3482,31 +3479,31 @@
         <v>54</v>
       </c>
       <c r="C66" t="n">
-        <v>69.3</v>
+        <v>78.7</v>
       </c>
       <c r="D66" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="E66" t="n">
-        <v>54.7</v>
+        <v>66</v>
       </c>
       <c r="F66" t="n">
-        <v>14.6</v>
+        <v>12.7</v>
       </c>
       <c r="G66" t="n">
-        <v>25.6</v>
+        <v>34.7</v>
       </c>
       <c r="H66" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="I66" t="n">
-        <v>38.8</v>
+        <v>21.3</v>
       </c>
       <c r="J66" t="n">
-        <v>32.8</v>
+        <v>41</v>
       </c>
       <c r="K66" t="n">
-        <v>38.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="67">
@@ -3514,69 +3511,69 @@
         <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="C67" t="n">
-        <v>78.7</v>
+        <v>79.2</v>
       </c>
       <c r="D67" t="n">
-        <v>12.7</v>
+        <v>22.7</v>
       </c>
       <c r="E67" t="n">
-        <v>66</v>
+        <v>56.5</v>
       </c>
       <c r="F67" t="n">
-        <v>12.7</v>
+        <v>22.7</v>
       </c>
       <c r="G67" t="n">
-        <v>34.7</v>
+        <v>30.2</v>
       </c>
       <c r="H67" t="n">
-        <v>12.5</v>
+        <v>10.1</v>
       </c>
       <c r="I67" t="n">
-        <v>21.3</v>
+        <v>52.2</v>
       </c>
       <c r="J67" t="n">
-        <v>41</v>
+        <v>19.6</v>
       </c>
       <c r="K67" t="n">
-        <v>50.8</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68" t="s">
         <v>71</v>
       </c>
-      <c r="B68" t="s">
-        <v>72</v>
-      </c>
       <c r="C68" t="n">
-        <v>79.2</v>
+        <v>90.9</v>
       </c>
       <c r="D68" t="n">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>56.5</v>
+        <v>90.9</v>
       </c>
       <c r="F68" t="n">
-        <v>22.7</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>30.2</v>
+        <v>20</v>
       </c>
       <c r="H68" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>52.2</v>
+        <v>40</v>
       </c>
       <c r="J68" t="n">
-        <v>19.6</v>
+        <v>40</v>
       </c>
       <c r="K68" t="n">
-        <v>45.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69">
@@ -3584,34 +3581,34 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C69" t="n">
-        <v>90.9</v>
+        <v>79.1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="E69" t="n">
-        <v>90.9</v>
+        <v>49.5</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="G69" t="n">
-        <v>20</v>
+        <v>19.7</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="I69" t="n">
         <v>40</v>
       </c>
       <c r="J69" t="n">
-        <v>40</v>
+        <v>21.5</v>
       </c>
       <c r="K69" t="n">
-        <v>40</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="70">
@@ -3619,34 +3616,34 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" t="n">
-        <v>79.1</v>
+        <v>59.5</v>
       </c>
       <c r="D70" t="n">
-        <v>29.6</v>
+        <v>7.6</v>
       </c>
       <c r="E70" t="n">
-        <v>49.5</v>
+        <v>51.9</v>
       </c>
       <c r="F70" t="n">
-        <v>29.6</v>
+        <v>7.6</v>
       </c>
       <c r="G70" t="n">
-        <v>19.7</v>
+        <v>27.6</v>
       </c>
       <c r="H70" t="n">
-        <v>3.9</v>
+        <v>14.7</v>
       </c>
       <c r="I70" t="n">
-        <v>40</v>
+        <v>56.1</v>
       </c>
       <c r="J70" t="n">
-        <v>21.5</v>
+        <v>14.6</v>
       </c>
       <c r="K70" t="n">
-        <v>30.8</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="71">
@@ -3654,34 +3651,34 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C71" t="n">
-        <v>59.5</v>
+        <v>100</v>
       </c>
       <c r="D71" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="E71" t="n">
-        <v>51.9</v>
+        <v>80</v>
       </c>
       <c r="F71" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>27.6</v>
+        <v>43.8</v>
       </c>
       <c r="H71" t="n">
-        <v>14.7</v>
+        <v>22.2</v>
       </c>
       <c r="I71" t="n">
-        <v>56.1</v>
+        <v>40</v>
       </c>
       <c r="J71" t="n">
-        <v>14.6</v>
+        <v>60</v>
       </c>
       <c r="K71" t="n">
-        <v>32.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
@@ -3689,34 +3686,34 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>45.7</v>
       </c>
       <c r="E72" t="n">
-        <v>80</v>
+        <v>12.1</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>45.7</v>
       </c>
       <c r="G72" t="n">
-        <v>43.8</v>
+        <v>31</v>
       </c>
       <c r="H72" t="n">
-        <v>22.2</v>
+        <v>3.3</v>
       </c>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="J72" t="n">
-        <v>60</v>
+        <v>21.1</v>
       </c>
       <c r="K72" t="n">
-        <v>20</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="73">
@@ -3724,34 +3721,34 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C73" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
       <c r="D73" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="n">
-        <v>12.1</v>
+        <v>44.6</v>
       </c>
       <c r="F73" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="G73" t="n">
-        <v>31</v>
+        <v>14.3</v>
       </c>
       <c r="H73" t="n">
-        <v>3.3</v>
+        <v>16.7</v>
       </c>
       <c r="I73" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="J73" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74">
@@ -3759,34 +3756,34 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C74" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E74" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F74" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G74" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H74" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I74" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K74" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="75">
@@ -3794,34 +3791,34 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C75" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D75" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E75" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F75" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G75" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H75" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I75" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J75" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K75" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="76">
@@ -3829,34 +3826,34 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C76" t="n">
-        <v>72.4</v>
+        <v>45.5</v>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="E76" t="n">
-        <v>62.4</v>
+        <v>37.8</v>
       </c>
       <c r="F76" t="n">
-        <v>10</v>
+        <v>7.7</v>
       </c>
       <c r="G76" t="n">
-        <v>41.2</v>
+        <v>33.3</v>
       </c>
       <c r="H76" t="n">
-        <v>14.3</v>
+        <v>40</v>
       </c>
       <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
         <v>50</v>
       </c>
-      <c r="J76" t="n">
-        <v>30</v>
-      </c>
       <c r="K76" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -3864,34 +3861,34 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C77" t="n">
-        <v>45.5</v>
+        <v>73.5</v>
       </c>
       <c r="D77" t="n">
-        <v>7.7</v>
+        <v>21.2</v>
       </c>
       <c r="E77" t="n">
-        <v>37.8</v>
+        <v>52.3</v>
       </c>
       <c r="F77" t="n">
-        <v>7.7</v>
+        <v>21.2</v>
       </c>
       <c r="G77" t="n">
-        <v>33.3</v>
+        <v>23.9</v>
       </c>
       <c r="H77" t="n">
-        <v>40</v>
+        <v>14.9</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>19.7</v>
       </c>
       <c r="K77" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="78">
@@ -3899,34 +3896,34 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C78" t="n">
-        <v>73.5</v>
+        <v>81</v>
       </c>
       <c r="D78" t="n">
-        <v>21.2</v>
+        <v>16.1</v>
       </c>
       <c r="E78" t="n">
-        <v>52.3</v>
+        <v>64.9</v>
       </c>
       <c r="F78" t="n">
-        <v>21.2</v>
+        <v>16.1</v>
       </c>
       <c r="G78" t="n">
-        <v>23.9</v>
+        <v>24.7</v>
       </c>
       <c r="H78" t="n">
-        <v>14.9</v>
+        <v>11.4</v>
       </c>
       <c r="I78" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="J78" t="n">
-        <v>19.7</v>
+        <v>15.4</v>
       </c>
       <c r="K78" t="n">
-        <v>43.5</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="79">
@@ -3934,34 +3931,34 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C79" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D79" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="E79" t="n">
-        <v>64.9</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="G79" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="H79" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J79" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80">
@@ -3969,19 +3966,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C80" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D80" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E80" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G80" t="n">
         <v>25</v>
@@ -3990,13 +3987,13 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81">
@@ -4004,34 +4001,34 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C81" t="n">
-        <v>33.3</v>
+        <v>78.4</v>
       </c>
       <c r="D81" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>0</v>
+        <v>78.4</v>
       </c>
       <c r="F81" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>31.8</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I81" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K81" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="82">
@@ -4039,34 +4036,34 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C82" t="n">
-        <v>78.4</v>
+        <v>69.6</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="E82" t="n">
-        <v>78.4</v>
+        <v>36.3</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G82" t="n">
-        <v>31.8</v>
+        <v>20</v>
       </c>
       <c r="H82" t="n">
-        <v>17.6</v>
+        <v>11.8</v>
       </c>
       <c r="I82" t="n">
-        <v>62.5</v>
+        <v>46.2</v>
       </c>
       <c r="J82" t="n">
-        <v>12.5</v>
+        <v>30.8</v>
       </c>
       <c r="K82" t="n">
-        <v>12.5</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="83">
@@ -4074,34 +4071,34 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C83" t="n">
-        <v>69.6</v>
+        <v>87.5</v>
       </c>
       <c r="D83" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E83" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G83" t="n">
+        <v>60</v>
+      </c>
+      <c r="H83" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="I83" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J83" t="n">
         <v>33.3</v>
       </c>
-      <c r="E83" t="n">
-        <v>36.3</v>
-      </c>
-      <c r="F83" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G83" t="n">
-        <v>20</v>
-      </c>
-      <c r="H83" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I83" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="J83" t="n">
-        <v>30.8</v>
-      </c>
       <c r="K83" t="n">
-        <v>53.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -4109,34 +4106,34 @@
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C84" t="n">
-        <v>87.5</v>
+        <v>68.6</v>
       </c>
       <c r="D84" t="n">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
       <c r="E84" t="n">
-        <v>69.3</v>
+        <v>36.8</v>
       </c>
       <c r="F84" t="n">
-        <v>18.2</v>
+        <v>31.8</v>
       </c>
       <c r="G84" t="n">
-        <v>60</v>
+        <v>11.1</v>
       </c>
       <c r="H84" t="n">
-        <v>16.7</v>
+        <v>3.4</v>
       </c>
       <c r="I84" t="n">
-        <v>66.7</v>
+        <v>47.6</v>
       </c>
       <c r="J84" t="n">
-        <v>33.3</v>
+        <v>28.6</v>
       </c>
       <c r="K84" t="n">
-        <v>100</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="85">
@@ -4144,34 +4141,34 @@
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" t="n">
-        <v>68.6</v>
+        <v>67.2</v>
       </c>
       <c r="D85" t="n">
-        <v>31.8</v>
+        <v>17.4</v>
       </c>
       <c r="E85" t="n">
-        <v>36.8</v>
+        <v>49.8</v>
       </c>
       <c r="F85" t="n">
-        <v>31.8</v>
+        <v>17.4</v>
       </c>
       <c r="G85" t="n">
-        <v>11.1</v>
+        <v>27.4</v>
       </c>
       <c r="H85" t="n">
-        <v>3.4</v>
+        <v>9.4</v>
       </c>
       <c r="I85" t="n">
-        <v>47.6</v>
+        <v>42.4</v>
       </c>
       <c r="J85" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="K85" t="n">
-        <v>38.1</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="86">
@@ -4179,34 +4176,34 @@
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C86" t="n">
-        <v>67.2</v>
+        <v>81.1</v>
       </c>
       <c r="D86" t="n">
-        <v>17.4</v>
+        <v>35.2</v>
       </c>
       <c r="E86" t="n">
-        <v>49.8</v>
+        <v>45.9</v>
       </c>
       <c r="F86" t="n">
-        <v>17.4</v>
+        <v>35.2</v>
       </c>
       <c r="G86" t="n">
-        <v>27.4</v>
+        <v>22.9</v>
       </c>
       <c r="H86" t="n">
-        <v>9.4</v>
+        <v>2.7</v>
       </c>
       <c r="I86" t="n">
-        <v>42.4</v>
+        <v>39.8</v>
       </c>
       <c r="J86" t="n">
-        <v>30.3</v>
+        <v>38.6</v>
       </c>
       <c r="K86" t="n">
-        <v>43.1</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="87">
@@ -4214,34 +4211,34 @@
         <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C87" t="n">
-        <v>81.1</v>
+        <v>57.3</v>
       </c>
       <c r="D87" t="n">
-        <v>35.2</v>
+        <v>8.1</v>
       </c>
       <c r="E87" t="n">
-        <v>45.9</v>
+        <v>49.2</v>
       </c>
       <c r="F87" t="n">
-        <v>35.2</v>
+        <v>8.1</v>
       </c>
       <c r="G87" t="n">
-        <v>22.9</v>
+        <v>31.5</v>
       </c>
       <c r="H87" t="n">
-        <v>2.7</v>
+        <v>16</v>
       </c>
       <c r="I87" t="n">
-        <v>39.8</v>
+        <v>50</v>
       </c>
       <c r="J87" t="n">
-        <v>38.6</v>
+        <v>26.1</v>
       </c>
       <c r="K87" t="n">
-        <v>48.2</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="88">
@@ -4249,34 +4246,34 @@
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C88" t="n">
-        <v>57.3</v>
+        <v>66.7</v>
       </c>
       <c r="D88" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>49.2</v>
+        <v>66.7</v>
       </c>
       <c r="F88" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>31.5</v>
+        <v>26.7</v>
       </c>
       <c r="H88" t="n">
-        <v>16</v>
+        <v>15.8</v>
       </c>
       <c r="I88" t="n">
-        <v>50</v>
+        <v>27.3</v>
       </c>
       <c r="J88" t="n">
-        <v>26.1</v>
+        <v>36.4</v>
       </c>
       <c r="K88" t="n">
-        <v>23.3</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="89">
@@ -4284,34 +4281,34 @@
         <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C89" t="n">
-        <v>66.7</v>
+        <v>77.9</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="E89" t="n">
-        <v>66.7</v>
+        <v>60.7</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>17.2</v>
       </c>
       <c r="G89" t="n">
-        <v>26.7</v>
+        <v>32.7</v>
       </c>
       <c r="H89" t="n">
-        <v>15.8</v>
+        <v>10.7</v>
       </c>
       <c r="I89" t="n">
-        <v>27.3</v>
+        <v>46.2</v>
       </c>
       <c r="J89" t="n">
-        <v>36.4</v>
+        <v>28.8</v>
       </c>
       <c r="K89" t="n">
-        <v>54.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="90">
@@ -4319,69 +4316,69 @@
         <v>94</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="C90" t="n">
-        <v>77.9</v>
+        <v>85.7</v>
       </c>
       <c r="D90" t="n">
-        <v>17.2</v>
+        <v>15.3</v>
       </c>
       <c r="E90" t="n">
-        <v>60.7</v>
+        <v>70.4</v>
       </c>
       <c r="F90" t="n">
-        <v>17.2</v>
+        <v>15.3</v>
       </c>
       <c r="G90" t="n">
-        <v>32.7</v>
+        <v>37.7</v>
       </c>
       <c r="H90" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="I90" t="n">
-        <v>46.2</v>
+        <v>38.9</v>
       </c>
       <c r="J90" t="n">
-        <v>28.8</v>
+        <v>41.7</v>
       </c>
       <c r="K90" t="n">
-        <v>58.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
+        <v>96</v>
+      </c>
+      <c r="B91" t="s">
         <v>95</v>
       </c>
-      <c r="B91" t="s">
-        <v>96</v>
-      </c>
       <c r="C91" t="n">
-        <v>85.7</v>
+        <v>72.1</v>
       </c>
       <c r="D91" t="n">
-        <v>15.3</v>
+        <v>30.2</v>
       </c>
       <c r="E91" t="n">
-        <v>70.4</v>
+        <v>41.9</v>
       </c>
       <c r="F91" t="n">
-        <v>15.3</v>
+        <v>30.2</v>
       </c>
       <c r="G91" t="n">
-        <v>37.7</v>
+        <v>21.6</v>
       </c>
       <c r="H91" t="n">
-        <v>12.3</v>
+        <v>5.1</v>
       </c>
       <c r="I91" t="n">
-        <v>38.9</v>
+        <v>60.7</v>
       </c>
       <c r="J91" t="n">
-        <v>41.7</v>
+        <v>17.9</v>
       </c>
       <c r="K91" t="n">
-        <v>47.4</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="92">
@@ -4389,34 +4386,34 @@
         <v>97</v>
       </c>
       <c r="B92" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C92" t="n">
-        <v>72.1</v>
+        <v>72.6</v>
       </c>
       <c r="D92" t="n">
-        <v>30.2</v>
+        <v>28.9</v>
       </c>
       <c r="E92" t="n">
-        <v>41.9</v>
+        <v>43.7</v>
       </c>
       <c r="F92" t="n">
-        <v>30.2</v>
+        <v>28.9</v>
       </c>
       <c r="G92" t="n">
-        <v>21.6</v>
+        <v>34.4</v>
       </c>
       <c r="H92" t="n">
-        <v>5.1</v>
+        <v>8.8</v>
       </c>
       <c r="I92" t="n">
-        <v>60.7</v>
+        <v>40</v>
       </c>
       <c r="J92" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="K92" t="n">
-        <v>44.4</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="93">
@@ -4424,34 +4421,34 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C93" t="n">
-        <v>72.6</v>
+        <v>74.7</v>
       </c>
       <c r="D93" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="E93" t="n">
-        <v>43.7</v>
+        <v>45.9</v>
       </c>
       <c r="F93" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="G93" t="n">
-        <v>34.4</v>
+        <v>24.2</v>
       </c>
       <c r="H93" t="n">
-        <v>8.8</v>
+        <v>7.9</v>
       </c>
       <c r="I93" t="n">
-        <v>40</v>
+        <v>49.3</v>
       </c>
       <c r="J93" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="K93" t="n">
-        <v>58.2</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="94">
@@ -4459,34 +4456,34 @@
         <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C94" t="n">
-        <v>74.7</v>
+        <v>79.6</v>
       </c>
       <c r="D94" t="n">
-        <v>28.8</v>
+        <v>30.8</v>
       </c>
       <c r="E94" t="n">
-        <v>45.9</v>
+        <v>48.8</v>
       </c>
       <c r="F94" t="n">
-        <v>28.8</v>
+        <v>30.8</v>
       </c>
       <c r="G94" t="n">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
       <c r="H94" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>49.3</v>
+        <v>39</v>
       </c>
       <c r="J94" t="n">
-        <v>20.3</v>
+        <v>28</v>
       </c>
       <c r="K94" t="n">
-        <v>46.3</v>
+        <v>65.4</v>
       </c>
     </row>
     <row r="95">
@@ -4494,34 +4491,34 @@
         <v>100</v>
       </c>
       <c r="B95" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C95" t="n">
-        <v>79.6</v>
+        <v>72.2</v>
       </c>
       <c r="D95" t="n">
-        <v>30.8</v>
+        <v>18.4</v>
       </c>
       <c r="E95" t="n">
-        <v>48.8</v>
+        <v>53.8</v>
       </c>
       <c r="F95" t="n">
-        <v>30.8</v>
+        <v>18.4</v>
       </c>
       <c r="G95" t="n">
-        <v>25.5</v>
+        <v>27.4</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="I95" t="n">
-        <v>39</v>
+        <v>33.3</v>
       </c>
       <c r="J95" t="n">
-        <v>28</v>
+        <v>36.4</v>
       </c>
       <c r="K95" t="n">
-        <v>65.4</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="96">
@@ -4529,34 +4526,34 @@
         <v>101</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C96" t="n">
-        <v>72.2</v>
+        <v>70.8</v>
       </c>
       <c r="D96" t="n">
-        <v>18.4</v>
+        <v>22.2</v>
       </c>
       <c r="E96" t="n">
-        <v>53.8</v>
+        <v>48.6</v>
       </c>
       <c r="F96" t="n">
-        <v>18.4</v>
+        <v>22.2</v>
       </c>
       <c r="G96" t="n">
-        <v>27.4</v>
+        <v>30</v>
       </c>
       <c r="H96" t="n">
-        <v>10.4</v>
+        <v>6.2</v>
       </c>
       <c r="I96" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="J96" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K96" t="n">
         <v>33.3</v>
-      </c>
-      <c r="J96" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="K96" t="n">
-        <v>26.6</v>
       </c>
     </row>
     <row r="97">
@@ -4564,34 +4561,34 @@
         <v>102</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C97" t="n">
-        <v>70.8</v>
+        <v>40</v>
       </c>
       <c r="D97" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="E97" t="n">
-        <v>48.6</v>
+        <v>15</v>
       </c>
       <c r="F97" t="n">
-        <v>22.2</v>
+        <v>25</v>
       </c>
       <c r="G97" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H97" t="n">
-        <v>6.2</v>
+        <v>21.1</v>
       </c>
       <c r="I97" t="n">
-        <v>48.8</v>
+        <v>62.5</v>
       </c>
       <c r="J97" t="n">
-        <v>24.4</v>
+        <v>12.5</v>
       </c>
       <c r="K97" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
@@ -4599,34 +4596,34 @@
         <v>103</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C98" t="n">
-        <v>40</v>
+        <v>68.9</v>
       </c>
       <c r="D98" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="E98" t="n">
-        <v>15</v>
+        <v>43.3</v>
       </c>
       <c r="F98" t="n">
-        <v>25</v>
+        <v>25.6</v>
       </c>
       <c r="G98" t="n">
-        <v>36</v>
+        <v>17.7</v>
       </c>
       <c r="H98" t="n">
-        <v>21.1</v>
+        <v>7.6</v>
       </c>
       <c r="I98" t="n">
-        <v>62.5</v>
+        <v>56.9</v>
       </c>
       <c r="J98" t="n">
-        <v>12.5</v>
+        <v>19.4</v>
       </c>
       <c r="K98" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="99">
@@ -4634,34 +4631,34 @@
         <v>104</v>
       </c>
       <c r="B99" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C99" t="n">
-        <v>68.9</v>
+        <v>72.5</v>
       </c>
       <c r="D99" t="n">
-        <v>25.6</v>
+        <v>32.4</v>
       </c>
       <c r="E99" t="n">
-        <v>43.3</v>
+        <v>40.1</v>
       </c>
       <c r="F99" t="n">
-        <v>25.6</v>
+        <v>32.4</v>
       </c>
       <c r="G99" t="n">
-        <v>17.7</v>
+        <v>26</v>
       </c>
       <c r="H99" t="n">
-        <v>7.6</v>
+        <v>9.3</v>
       </c>
       <c r="I99" t="n">
-        <v>56.9</v>
+        <v>44.4</v>
       </c>
       <c r="J99" t="n">
-        <v>19.4</v>
+        <v>37</v>
       </c>
       <c r="K99" t="n">
-        <v>41.7</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="100">
@@ -4669,34 +4666,34 @@
         <v>105</v>
       </c>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C100" t="n">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="D100" t="n">
-        <v>32.4</v>
+        <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>40.1</v>
+        <v>50</v>
       </c>
       <c r="F100" t="n">
-        <v>32.4</v>
+        <v>30</v>
       </c>
       <c r="G100" t="n">
-        <v>26</v>
+        <v>27.3</v>
       </c>
       <c r="H100" t="n">
-        <v>9.3</v>
+        <v>20</v>
       </c>
       <c r="I100" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="J100" t="n">
-        <v>37</v>
+        <v>11.1</v>
       </c>
       <c r="K100" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="101">
@@ -4704,34 +4701,34 @@
         <v>106</v>
       </c>
       <c r="B101" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C101" t="n">
-        <v>80</v>
+        <v>62.2</v>
       </c>
       <c r="D101" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="F101" t="n">
-        <v>30</v>
+        <v>15.5</v>
       </c>
       <c r="G101" t="n">
-        <v>27.3</v>
+        <v>22.5</v>
       </c>
       <c r="H101" t="n">
-        <v>20</v>
+        <v>12.3</v>
       </c>
       <c r="I101" t="n">
-        <v>66.7</v>
+        <v>61.9</v>
       </c>
       <c r="J101" t="n">
-        <v>11.1</v>
+        <v>15.9</v>
       </c>
       <c r="K101" t="n">
-        <v>33.3</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="102">
@@ -4739,34 +4736,34 @@
         <v>107</v>
       </c>
       <c r="B102" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C102" t="n">
-        <v>62.2</v>
+        <v>53.6</v>
       </c>
       <c r="D102" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="E102" t="n">
-        <v>46.7</v>
+        <v>38</v>
       </c>
       <c r="F102" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="G102" t="n">
-        <v>22.5</v>
+        <v>30.9</v>
       </c>
       <c r="H102" t="n">
-        <v>12.3</v>
+        <v>7.3</v>
       </c>
       <c r="I102" t="n">
-        <v>61.9</v>
+        <v>67.7</v>
       </c>
       <c r="J102" t="n">
-        <v>15.9</v>
+        <v>25.8</v>
       </c>
       <c r="K102" t="n">
-        <v>39.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="103">
@@ -4774,57 +4771,51 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C103" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="D103" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="E103" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="G103" t="n">
-        <v>30.9</v>
+        <v>100</v>
       </c>
       <c r="H103" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I103" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J103" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K103" t="n">
-        <v>26.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
     </row>
     <row r="104">
       <c r="A104" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" t="s">
         <v>109</v>
       </c>
-      <c r="B104" t="s">
-        <v>110</v>
-      </c>
       <c r="C104" t="n">
+        <v>100</v>
+      </c>
+      <c r="D104" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F104" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G104" t="n">
         <v>50</v>
-      </c>
-      <c r="D104" t="n">
-        <v>50</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>50</v>
-      </c>
-      <c r="G104" t="n">
-        <v>100</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4835,66 +4826,72 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C105" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D105" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="E105" t="n">
-        <v>66.7</v>
+        <v>47</v>
       </c>
       <c r="F105" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="G105" t="n">
-        <v>50</v>
+        <v>25.4</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105"/>
-      <c r="J105"/>
-      <c r="K105"/>
+        <v>12.5</v>
+      </c>
+      <c r="I105" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J105" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C106" t="n">
-        <v>57.8</v>
+        <v>71.4</v>
       </c>
       <c r="D106" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="E106" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
       <c r="F106" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="G106" t="n">
-        <v>25.4</v>
+        <v>16.7</v>
       </c>
       <c r="H106" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I106" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4902,34 +4899,34 @@
         <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C107" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D107" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E107" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="H107" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -4937,34 +4934,28 @@
         <v>113</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C108" t="n">
-        <v>75</v>
-      </c>
-      <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="n">
-        <v>75</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H108" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -4972,28 +4963,34 @@
         <v>114</v>
       </c>
       <c r="B109" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
-      </c>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
+        <v>60</v>
+      </c>
+      <c r="D109" t="n">
+        <v>40</v>
+      </c>
+      <c r="E109" t="n">
+        <v>20</v>
+      </c>
+      <c r="F109" t="n">
+        <v>40</v>
+      </c>
       <c r="G109" t="n">
-        <v>50</v>
+        <v>28.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="K109" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -5001,34 +4998,34 @@
         <v>115</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C110" t="n">
-        <v>60</v>
+        <v>77.1</v>
       </c>
       <c r="D110" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="E110" t="n">
-        <v>20</v>
+        <v>36.3</v>
       </c>
       <c r="F110" t="n">
-        <v>40</v>
+        <v>40.8</v>
       </c>
       <c r="G110" t="n">
-        <v>28.8</v>
+        <v>41.6</v>
       </c>
       <c r="H110" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="I110" t="n">
-        <v>39.1</v>
+        <v>51.5</v>
       </c>
       <c r="J110" t="n">
-        <v>26.1</v>
+        <v>15.2</v>
       </c>
       <c r="K110" t="n">
-        <v>13</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="111">
@@ -5036,34 +5033,34 @@
         <v>116</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C111" t="n">
-        <v>77.1</v>
+        <v>73.3</v>
       </c>
       <c r="D111" t="n">
-        <v>40.8</v>
+        <v>20.8</v>
       </c>
       <c r="E111" t="n">
-        <v>36.3</v>
+        <v>52.5</v>
       </c>
       <c r="F111" t="n">
-        <v>40.8</v>
+        <v>20.8</v>
       </c>
       <c r="G111" t="n">
-        <v>41.6</v>
+        <v>14.8</v>
       </c>
       <c r="H111" t="n">
-        <v>10</v>
+        <v>8.2</v>
       </c>
       <c r="I111" t="n">
-        <v>51.5</v>
+        <v>45.2</v>
       </c>
       <c r="J111" t="n">
-        <v>15.2</v>
+        <v>20.5</v>
       </c>
       <c r="K111" t="n">
-        <v>37.5</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="112">
@@ -5071,34 +5068,26 @@
         <v>117</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
-      </c>
-      <c r="C112" t="n">
-        <v>73.3</v>
-      </c>
-      <c r="D112" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="E112" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="F112" t="n">
-        <v>20.8</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
       <c r="G112" t="n">
-        <v>14.8</v>
+        <v>22.2</v>
       </c>
       <c r="H112" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>45.2</v>
+        <v>50</v>
       </c>
       <c r="J112" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>29.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5106,26 +5095,34 @@
         <v>118</v>
       </c>
       <c r="B113" t="s">
-        <v>110</v>
-      </c>
-      <c r="C113"/>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
+        <v>109</v>
+      </c>
+      <c r="C113" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>9.7</v>
+      </c>
+      <c r="E113" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="F113" t="n">
+        <v>9.7</v>
+      </c>
       <c r="G113" t="n">
-        <v>22.2</v>
+        <v>31.8</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="I113" t="n">
-        <v>50</v>
+        <v>27.6</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>36.2</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="114">
@@ -5133,34 +5130,34 @@
         <v>119</v>
       </c>
       <c r="B114" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="D114" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="E114" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="F114" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="G114" t="n">
-        <v>31.8</v>
+        <v>46.7</v>
       </c>
       <c r="H114" t="n">
-        <v>22.4</v>
+        <v>30</v>
       </c>
       <c r="I114" t="n">
-        <v>27.6</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>40.4</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="115">
@@ -5168,25 +5165,25 @@
         <v>120</v>
       </c>
       <c r="B115" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C115" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D115" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="F115" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -5195,7 +5192,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5203,34 +5200,26 @@
         <v>121</v>
       </c>
       <c r="B116" t="s">
-        <v>110</v>
-      </c>
-      <c r="C116" t="n">
+        <v>109</v>
+      </c>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
         <v>100</v>
       </c>
-      <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
         <v>100</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5238,26 +5227,34 @@
         <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>110</v>
-      </c>
-      <c r="C117"/>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
+        <v>109</v>
+      </c>
+      <c r="C117" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="D117" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E117" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F117" t="n">
+        <v>26.5</v>
+      </c>
       <c r="G117" t="n">
-        <v>16.7</v>
+        <v>22.1</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>9.2</v>
       </c>
       <c r="I117" t="n">
-        <v>100</v>
+        <v>42.9</v>
       </c>
       <c r="J117" t="n">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="K117" t="n">
-        <v>100</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="118">
@@ -5265,34 +5262,34 @@
         <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C118" t="n">
-        <v>70.7</v>
+        <v>80</v>
       </c>
       <c r="D118" t="n">
-        <v>26.5</v>
+        <v>25.8</v>
       </c>
       <c r="E118" t="n">
-        <v>44.2</v>
+        <v>54.2</v>
       </c>
       <c r="F118" t="n">
-        <v>26.5</v>
+        <v>25.8</v>
       </c>
       <c r="G118" t="n">
-        <v>22.1</v>
+        <v>33.9</v>
       </c>
       <c r="H118" t="n">
-        <v>9.2</v>
+        <v>7.8</v>
       </c>
       <c r="I118" t="n">
-        <v>42.9</v>
+        <v>33.9</v>
       </c>
       <c r="J118" t="n">
-        <v>28.6</v>
+        <v>32.2</v>
       </c>
       <c r="K118" t="n">
-        <v>48.1</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="119">
@@ -5300,34 +5297,34 @@
         <v>124</v>
       </c>
       <c r="B119" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C119" t="n">
-        <v>80</v>
+        <v>71.4</v>
       </c>
       <c r="D119" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="E119" t="n">
-        <v>54.2</v>
+        <v>35.7</v>
       </c>
       <c r="F119" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="G119" t="n">
-        <v>33.9</v>
+        <v>5.3</v>
       </c>
       <c r="H119" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="I119" t="n">
-        <v>33.9</v>
+        <v>42.9</v>
       </c>
       <c r="J119" t="n">
-        <v>32.2</v>
+        <v>14.3</v>
       </c>
       <c r="K119" t="n">
-        <v>49.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="120">
@@ -5335,34 +5332,34 @@
         <v>125</v>
       </c>
       <c r="B120" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C120" t="n">
-        <v>71.4</v>
+        <v>57</v>
       </c>
       <c r="D120" t="n">
-        <v>35.7</v>
+        <v>19.3</v>
       </c>
       <c r="E120" t="n">
-        <v>35.7</v>
+        <v>37.7</v>
       </c>
       <c r="F120" t="n">
-        <v>35.7</v>
+        <v>19.3</v>
       </c>
       <c r="G120" t="n">
-        <v>5.3</v>
+        <v>29.4</v>
       </c>
       <c r="H120" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="I120" t="n">
-        <v>42.9</v>
+        <v>36</v>
       </c>
       <c r="J120" t="n">
-        <v>14.3</v>
+        <v>36</v>
       </c>
       <c r="K120" t="n">
-        <v>33.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="121">
@@ -5370,34 +5367,34 @@
         <v>126</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C121" t="n">
-        <v>57</v>
+        <v>79.3</v>
       </c>
       <c r="D121" t="n">
-        <v>19.3</v>
+        <v>26.9</v>
       </c>
       <c r="E121" t="n">
-        <v>37.7</v>
+        <v>52.4</v>
       </c>
       <c r="F121" t="n">
-        <v>19.3</v>
+        <v>26.9</v>
       </c>
       <c r="G121" t="n">
-        <v>29.4</v>
+        <v>36.1</v>
       </c>
       <c r="H121" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="I121" t="n">
-        <v>36</v>
+        <v>40.4</v>
       </c>
       <c r="J121" t="n">
-        <v>36</v>
+        <v>26.9</v>
       </c>
       <c r="K121" t="n">
-        <v>44</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="122">
@@ -5405,34 +5402,34 @@
         <v>127</v>
       </c>
       <c r="B122" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C122" t="n">
-        <v>79.3</v>
+        <v>67.2</v>
       </c>
       <c r="D122" t="n">
-        <v>26.9</v>
+        <v>16.8</v>
       </c>
       <c r="E122" t="n">
-        <v>52.4</v>
+        <v>50.4</v>
       </c>
       <c r="F122" t="n">
-        <v>26.9</v>
+        <v>16.8</v>
       </c>
       <c r="G122" t="n">
-        <v>36.1</v>
+        <v>16.3</v>
       </c>
       <c r="H122" t="n">
-        <v>9.4</v>
+        <v>9.2</v>
       </c>
       <c r="I122" t="n">
-        <v>40.4</v>
+        <v>40.2</v>
       </c>
       <c r="J122" t="n">
-        <v>26.9</v>
+        <v>19.5</v>
       </c>
       <c r="K122" t="n">
-        <v>40.4</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="123">
@@ -5440,34 +5437,26 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>110</v>
-      </c>
-      <c r="C123" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="D123" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="E123" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="F123" t="n">
-        <v>16.8</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
       <c r="G123" t="n">
-        <v>16.3</v>
+        <v>22.2</v>
       </c>
       <c r="H123" t="n">
-        <v>9.2</v>
+        <v>20</v>
       </c>
       <c r="I123" t="n">
-        <v>40.2</v>
+        <v>33.3</v>
       </c>
       <c r="J123" t="n">
-        <v>19.5</v>
+        <v>66.7</v>
       </c>
       <c r="K123" t="n">
-        <v>44.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124">
@@ -5475,26 +5464,34 @@
         <v>129</v>
       </c>
       <c r="B124" t="s">
-        <v>110</v>
-      </c>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
+        <v>109</v>
+      </c>
+      <c r="C124" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E124" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>22.5</v>
+      </c>
       <c r="G124" t="n">
-        <v>22.2</v>
+        <v>19.7</v>
       </c>
       <c r="H124" t="n">
-        <v>20</v>
+        <v>10.7</v>
       </c>
       <c r="I124" t="n">
-        <v>33.3</v>
+        <v>43.2</v>
       </c>
       <c r="J124" t="n">
-        <v>66.7</v>
+        <v>23</v>
       </c>
       <c r="K124" t="n">
-        <v>100</v>
+        <v>39.2</v>
       </c>
     </row>
     <row r="125">
@@ -5502,34 +5499,34 @@
         <v>130</v>
       </c>
       <c r="B125" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C125" t="n">
-        <v>56.2</v>
+        <v>65.3</v>
       </c>
       <c r="D125" t="n">
-        <v>22.5</v>
+        <v>17</v>
       </c>
       <c r="E125" t="n">
-        <v>33.7</v>
+        <v>48.3</v>
       </c>
       <c r="F125" t="n">
-        <v>22.5</v>
+        <v>17</v>
       </c>
       <c r="G125" t="n">
-        <v>19.7</v>
+        <v>23</v>
       </c>
       <c r="H125" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="I125" t="n">
-        <v>43.2</v>
+        <v>54.2</v>
       </c>
       <c r="J125" t="n">
-        <v>23</v>
+        <v>27.1</v>
       </c>
       <c r="K125" t="n">
-        <v>39.2</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="126">
@@ -5537,69 +5534,61 @@
         <v>131</v>
       </c>
       <c r="B126" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C126" t="n">
-        <v>65.3</v>
+        <v>66.2</v>
       </c>
       <c r="D126" t="n">
-        <v>17</v>
+        <v>36.1</v>
       </c>
       <c r="E126" t="n">
-        <v>48.3</v>
+        <v>30.1</v>
       </c>
       <c r="F126" t="n">
-        <v>17</v>
+        <v>36.1</v>
       </c>
       <c r="G126" t="n">
-        <v>23</v>
+        <v>27.9</v>
       </c>
       <c r="H126" t="n">
-        <v>10.8</v>
+        <v>7.3</v>
       </c>
       <c r="I126" t="n">
-        <v>54.2</v>
+        <v>40.7</v>
       </c>
       <c r="J126" t="n">
-        <v>27.1</v>
+        <v>33.3</v>
       </c>
       <c r="K126" t="n">
-        <v>52.5</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" t="s">
         <v>132</v>
       </c>
-      <c r="B127" t="s">
-        <v>133</v>
-      </c>
-      <c r="C127" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="D127" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="E127" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="F127" t="n">
-        <v>36.1</v>
-      </c>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
       <c r="G127" t="n">
-        <v>27.9</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="J127" t="n">
         <v>33.3</v>
       </c>
       <c r="K127" t="n">
-        <v>48.1</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="128">
@@ -5607,26 +5596,34 @@
         <v>134</v>
       </c>
       <c r="B128" t="s">
-        <v>133</v>
-      </c>
-      <c r="C128"/>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
+        <v>132</v>
+      </c>
+      <c r="C128" t="n">
+        <v>80</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>80</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K128" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5634,34 +5631,34 @@
         <v>135</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C129" t="n">
-        <v>80</v>
+        <v>69.5</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="E129" t="n">
-        <v>80</v>
+        <v>46.3</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>23.2</v>
       </c>
       <c r="G129" t="n">
-        <v>25</v>
+        <v>13.2</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>40.7</v>
       </c>
       <c r="J129" t="n">
-        <v>100</v>
+        <v>31.5</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="130">
@@ -5669,34 +5666,34 @@
         <v>136</v>
       </c>
       <c r="B130" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C130" t="n">
-        <v>69.5</v>
+        <v>65.9</v>
       </c>
       <c r="D130" t="n">
-        <v>23.2</v>
+        <v>26.1</v>
       </c>
       <c r="E130" t="n">
-        <v>46.3</v>
+        <v>39.8</v>
       </c>
       <c r="F130" t="n">
-        <v>23.2</v>
+        <v>26.1</v>
       </c>
       <c r="G130" t="n">
-        <v>13.2</v>
+        <v>31.7</v>
       </c>
       <c r="H130" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="I130" t="n">
-        <v>40.7</v>
+        <v>42.6</v>
       </c>
       <c r="J130" t="n">
-        <v>31.5</v>
+        <v>23.4</v>
       </c>
       <c r="K130" t="n">
-        <v>51.9</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="131">
@@ -5704,34 +5701,34 @@
         <v>137</v>
       </c>
       <c r="B131" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C131" t="n">
-        <v>65.9</v>
+        <v>79.6</v>
       </c>
       <c r="D131" t="n">
-        <v>26.1</v>
+        <v>32.8</v>
       </c>
       <c r="E131" t="n">
-        <v>39.8</v>
+        <v>46.8</v>
       </c>
       <c r="F131" t="n">
-        <v>26.1</v>
+        <v>32.8</v>
       </c>
       <c r="G131" t="n">
-        <v>31.7</v>
+        <v>25.9</v>
       </c>
       <c r="H131" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="I131" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="J131" t="n">
-        <v>23.4</v>
+        <v>26.2</v>
       </c>
       <c r="K131" t="n">
-        <v>44.7</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="132">
@@ -5739,34 +5736,34 @@
         <v>138</v>
       </c>
       <c r="B132" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C132" t="n">
-        <v>79.6</v>
+        <v>54.1</v>
       </c>
       <c r="D132" t="n">
-        <v>32.8</v>
+        <v>25.4</v>
       </c>
       <c r="E132" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="F132" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G132" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="H132" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="I132" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J132" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="K132" t="n">
         <v>46.8</v>
-      </c>
-      <c r="F132" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="G132" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H132" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="I132" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="J132" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="K132" t="n">
-        <v>30.4</v>
       </c>
     </row>
     <row r="133">
@@ -5774,34 +5771,34 @@
         <v>139</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C133" t="n">
-        <v>54.1</v>
+        <v>55.9</v>
       </c>
       <c r="D133" t="n">
-        <v>25.4</v>
+        <v>20.9</v>
       </c>
       <c r="E133" t="n">
-        <v>28.7</v>
+        <v>35</v>
       </c>
       <c r="F133" t="n">
-        <v>25.4</v>
+        <v>20.9</v>
       </c>
       <c r="G133" t="n">
-        <v>21.9</v>
+        <v>8.8</v>
       </c>
       <c r="H133" t="n">
-        <v>8.3</v>
+        <v>10.4</v>
       </c>
       <c r="I133" t="n">
-        <v>61.7</v>
+        <v>62.5</v>
       </c>
       <c r="J133" t="n">
-        <v>12.8</v>
+        <v>11.4</v>
       </c>
       <c r="K133" t="n">
-        <v>46.8</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="134">
@@ -5809,34 +5806,34 @@
         <v>140</v>
       </c>
       <c r="B134" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C134" t="n">
-        <v>55.9</v>
+        <v>80</v>
       </c>
       <c r="D134" t="n">
-        <v>20.9</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="n">
-        <v>35</v>
+        <v>68.9</v>
       </c>
       <c r="F134" t="n">
-        <v>20.9</v>
+        <v>11.1</v>
       </c>
       <c r="G134" t="n">
-        <v>8.8</v>
+        <v>39.5</v>
       </c>
       <c r="H134" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="I134" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="J134" t="n">
-        <v>11.4</v>
+        <v>9.1</v>
       </c>
       <c r="K134" t="n">
-        <v>25.3</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="135">
@@ -5844,34 +5841,34 @@
         <v>141</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C135" t="n">
-        <v>80</v>
+        <v>70.9</v>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="E135" t="n">
-        <v>68.9</v>
+        <v>43.6</v>
       </c>
       <c r="F135" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="G135" t="n">
-        <v>39.5</v>
+        <v>21</v>
       </c>
       <c r="H135" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="I135" t="n">
-        <v>63.6</v>
+        <v>39</v>
       </c>
       <c r="J135" t="n">
-        <v>9.1</v>
+        <v>30.5</v>
       </c>
       <c r="K135" t="n">
-        <v>45.5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136">
@@ -5879,34 +5876,34 @@
         <v>142</v>
       </c>
       <c r="B136" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C136" t="n">
-        <v>70.9</v>
+        <v>70</v>
       </c>
       <c r="D136" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="E136" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="F136" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G136" t="n">
-        <v>21</v>
+        <v>14.8</v>
       </c>
       <c r="H136" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="I136" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="J136" t="n">
-        <v>30.5</v>
+        <v>30</v>
       </c>
       <c r="K136" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137">
@@ -5914,34 +5911,34 @@
         <v>143</v>
       </c>
       <c r="B137" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C137" t="n">
-        <v>70</v>
+        <v>56.9</v>
       </c>
       <c r="D137" t="n">
-        <v>26.7</v>
+        <v>20.7</v>
       </c>
       <c r="E137" t="n">
-        <v>43.3</v>
+        <v>36.2</v>
       </c>
       <c r="F137" t="n">
-        <v>26.7</v>
+        <v>20.7</v>
       </c>
       <c r="G137" t="n">
-        <v>14.8</v>
+        <v>17.2</v>
       </c>
       <c r="H137" t="n">
-        <v>12.5</v>
+        <v>14.3</v>
       </c>
       <c r="I137" t="n">
-        <v>60</v>
+        <v>54.2</v>
       </c>
       <c r="J137" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K137" t="n">
-        <v>10</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="138">
@@ -5949,34 +5946,34 @@
         <v>144</v>
       </c>
       <c r="B138" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C138" t="n">
-        <v>56.9</v>
+        <v>72.4</v>
       </c>
       <c r="D138" t="n">
-        <v>20.7</v>
+        <v>22.5</v>
       </c>
       <c r="E138" t="n">
-        <v>36.2</v>
+        <v>49.9</v>
       </c>
       <c r="F138" t="n">
-        <v>20.7</v>
+        <v>22.5</v>
       </c>
       <c r="G138" t="n">
-        <v>17.2</v>
+        <v>31.8</v>
       </c>
       <c r="H138" t="n">
-        <v>14.3</v>
+        <v>11</v>
       </c>
       <c r="I138" t="n">
-        <v>54.2</v>
+        <v>47.9</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>18.3</v>
       </c>
       <c r="K138" t="n">
-        <v>56.5</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="139">
@@ -5984,34 +5981,34 @@
         <v>145</v>
       </c>
       <c r="B139" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C139" t="n">
-        <v>72.4</v>
+        <v>76.7</v>
       </c>
       <c r="D139" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="E139" t="n">
-        <v>49.9</v>
+        <v>51.7</v>
       </c>
       <c r="F139" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="G139" t="n">
-        <v>31.8</v>
+        <v>33.1</v>
       </c>
       <c r="H139" t="n">
-        <v>11</v>
+        <v>8.7</v>
       </c>
       <c r="I139" t="n">
-        <v>47.9</v>
+        <v>36.8</v>
       </c>
       <c r="J139" t="n">
-        <v>18.3</v>
+        <v>27.6</v>
       </c>
       <c r="K139" t="n">
-        <v>40.3</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="140">
@@ -6019,34 +6016,34 @@
         <v>146</v>
       </c>
       <c r="B140" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C140" t="n">
-        <v>76.7</v>
+        <v>73</v>
       </c>
       <c r="D140" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="E140" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="F140" t="n">
-        <v>25</v>
+        <v>22.2</v>
       </c>
       <c r="G140" t="n">
-        <v>33.1</v>
+        <v>25.2</v>
       </c>
       <c r="H140" t="n">
-        <v>8.7</v>
+        <v>8.6</v>
       </c>
       <c r="I140" t="n">
-        <v>36.8</v>
+        <v>40.2</v>
       </c>
       <c r="J140" t="n">
-        <v>27.6</v>
+        <v>34.5</v>
       </c>
       <c r="K140" t="n">
-        <v>41.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="141">
@@ -6054,34 +6051,34 @@
         <v>147</v>
       </c>
       <c r="B141" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C141" t="n">
-        <v>73</v>
+        <v>68.2</v>
       </c>
       <c r="D141" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="E141" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="F141" t="n">
-        <v>22.2</v>
+        <v>18.2</v>
       </c>
       <c r="G141" t="n">
-        <v>25.2</v>
+        <v>21.5</v>
       </c>
       <c r="H141" t="n">
-        <v>8.6</v>
+        <v>11.9</v>
       </c>
       <c r="I141" t="n">
-        <v>40.2</v>
+        <v>48.3</v>
       </c>
       <c r="J141" t="n">
-        <v>34.5</v>
+        <v>17.2</v>
       </c>
       <c r="K141" t="n">
-        <v>49.4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142">
@@ -6089,69 +6086,69 @@
         <v>148</v>
       </c>
       <c r="B142" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C142" t="n">
-        <v>68.2</v>
+        <v>73.9</v>
       </c>
       <c r="D142" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="E142" t="n">
-        <v>50</v>
+        <v>46.6</v>
       </c>
       <c r="F142" t="n">
-        <v>18.2</v>
+        <v>27.3</v>
       </c>
       <c r="G142" t="n">
-        <v>21.5</v>
+        <v>15</v>
       </c>
       <c r="H142" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>48.3</v>
+        <v>30</v>
       </c>
       <c r="J142" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="K142" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" t="s">
         <v>149</v>
       </c>
-      <c r="B143" t="s">
-        <v>150</v>
-      </c>
       <c r="C143" t="n">
-        <v>73.9</v>
+        <v>66.7</v>
       </c>
       <c r="D143" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="E143" t="n">
-        <v>46.6</v>
+        <v>6.7</v>
       </c>
       <c r="F143" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="G143" t="n">
-        <v>15</v>
+        <v>33.3</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I143" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J143" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K143" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -6159,34 +6156,34 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C144" t="n">
-        <v>66.7</v>
+        <v>65.2</v>
       </c>
       <c r="D144" t="n">
-        <v>60</v>
+        <v>19.2</v>
       </c>
       <c r="E144" t="n">
-        <v>6.7</v>
+        <v>46</v>
       </c>
       <c r="F144" t="n">
-        <v>60</v>
+        <v>19.2</v>
       </c>
       <c r="G144" t="n">
-        <v>33.3</v>
+        <v>15.7</v>
       </c>
       <c r="H144" t="n">
-        <v>11.1</v>
+        <v>5.6</v>
       </c>
       <c r="I144" t="n">
-        <v>25</v>
+        <v>42.3</v>
       </c>
       <c r="J144" t="n">
         <v>25</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="145">
@@ -6194,34 +6191,34 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C145" t="n">
-        <v>65.2</v>
+        <v>35</v>
       </c>
       <c r="D145" t="n">
-        <v>19.2</v>
+        <v>13.3</v>
       </c>
       <c r="E145" t="n">
-        <v>46</v>
+        <v>21.7</v>
       </c>
       <c r="F145" t="n">
-        <v>19.2</v>
+        <v>13.3</v>
       </c>
       <c r="G145" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="H145" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
       <c r="J145" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>41.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6229,34 +6226,34 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C146" t="n">
-        <v>35</v>
+        <v>73.5</v>
       </c>
       <c r="D146" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="E146" t="n">
-        <v>21.7</v>
+        <v>48.2</v>
       </c>
       <c r="F146" t="n">
-        <v>13.3</v>
+        <v>25.3</v>
       </c>
       <c r="G146" t="n">
-        <v>33.3</v>
+        <v>30.4</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="I146" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147">
@@ -6264,34 +6261,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C147" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="D147" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="E147" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="F147" t="n">
-        <v>25.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
       <c r="G147" t="n">
-        <v>30.4</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>51.4</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>22.9</v>
+        <v>100</v>
       </c>
       <c r="K147" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6299,28 +6290,34 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C148" t="n">
-        <v>100</v>
-      </c>
-      <c r="D148"/>
-      <c r="E148"/>
-      <c r="F148"/>
+        <v>74.8</v>
+      </c>
+      <c r="D148" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="E148" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="F148" t="n">
+        <v>26.1</v>
+      </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>45.3</v>
       </c>
       <c r="J148" t="n">
-        <v>100</v>
+        <v>26.4</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="149">
@@ -6328,34 +6325,34 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C149" t="n">
-        <v>74.8</v>
+        <v>55.6</v>
       </c>
       <c r="D149" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="E149" t="n">
-        <v>48.7</v>
+        <v>29.7</v>
       </c>
       <c r="F149" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="G149" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H149" t="n">
-        <v>9.4</v>
+        <v>27.3</v>
       </c>
       <c r="I149" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="J149" t="n">
-        <v>26.4</v>
+        <v>28.6</v>
       </c>
       <c r="K149" t="n">
-        <v>40.4</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="150">
@@ -6363,34 +6360,34 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C150" t="n">
-        <v>55.6</v>
+        <v>65.9</v>
       </c>
       <c r="D150" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="E150" t="n">
-        <v>29.7</v>
+        <v>41.4</v>
       </c>
       <c r="F150" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="G150" t="n">
-        <v>10</v>
+        <v>19.2</v>
       </c>
       <c r="H150" t="n">
-        <v>27.3</v>
+        <v>7.2</v>
       </c>
       <c r="I150" t="n">
-        <v>42.9</v>
+        <v>53.8</v>
       </c>
       <c r="J150" t="n">
-        <v>28.6</v>
+        <v>15.4</v>
       </c>
       <c r="K150" t="n">
-        <v>14.3</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="151">
@@ -6398,34 +6395,34 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C151" t="n">
-        <v>65.9</v>
+        <v>66.7</v>
       </c>
       <c r="D151" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>41.4</v>
+        <v>66.7</v>
       </c>
       <c r="F151" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="H151" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="J151" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="K151" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6433,34 +6430,34 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C152" t="n">
-        <v>66.7</v>
+        <v>71</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E152" t="n">
-        <v>66.7</v>
+        <v>51.6</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G152" t="n">
-        <v>18.2</v>
+        <v>25.7</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="I152" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J152" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="153">
@@ -6468,34 +6465,34 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C153" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D153" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E153" t="n">
-        <v>51.6</v>
+        <v>35.7</v>
       </c>
       <c r="F153" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G153" t="n">
-        <v>25.7</v>
+        <v>28.6</v>
       </c>
       <c r="H153" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="I153" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K153" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="154">
@@ -6503,34 +6500,34 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C154" t="n">
-        <v>50</v>
+        <v>68.7</v>
       </c>
       <c r="D154" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="E154" t="n">
-        <v>35.7</v>
+        <v>39.9</v>
       </c>
       <c r="F154" t="n">
-        <v>14.3</v>
+        <v>28.8</v>
       </c>
       <c r="G154" t="n">
-        <v>28.6</v>
+        <v>30.3</v>
       </c>
       <c r="H154" t="n">
-        <v>12.5</v>
+        <v>6.1</v>
       </c>
       <c r="I154" t="n">
-        <v>75</v>
+        <v>36.7</v>
       </c>
       <c r="J154" t="n">
-        <v>25</v>
+        <v>28.3</v>
       </c>
       <c r="K154" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="155">
@@ -6538,104 +6535,104 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C155" t="n">
-        <v>68.7</v>
+        <v>65.5</v>
       </c>
       <c r="D155" t="n">
-        <v>28.8</v>
+        <v>23.2</v>
       </c>
       <c r="E155" t="n">
-        <v>39.9</v>
+        <v>42.3</v>
       </c>
       <c r="F155" t="n">
-        <v>28.8</v>
+        <v>23.2</v>
       </c>
       <c r="G155" t="n">
-        <v>30.3</v>
+        <v>20</v>
       </c>
       <c r="H155" t="n">
-        <v>6.1</v>
+        <v>1.1</v>
       </c>
       <c r="I155" t="n">
-        <v>36.7</v>
+        <v>60.6</v>
       </c>
       <c r="J155" t="n">
-        <v>28.3</v>
+        <v>24.2</v>
       </c>
       <c r="K155" t="n">
-        <v>45</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="B156" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C156" t="n">
-        <v>65.5</v>
+        <v>56.1</v>
       </c>
       <c r="D156" t="n">
-        <v>23.2</v>
+        <v>19.2</v>
       </c>
       <c r="E156" t="n">
-        <v>42.3</v>
+        <v>36.9</v>
       </c>
       <c r="F156" t="n">
-        <v>23.2</v>
+        <v>19.2</v>
       </c>
       <c r="G156" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="H156" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>60.6</v>
+        <v>40.5</v>
       </c>
       <c r="J156" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
       <c r="K156" t="n">
-        <v>29.2</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>120</v>
+        <v>163</v>
       </c>
       <c r="B157" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C157" t="n">
-        <v>56.1</v>
+        <v>81.4</v>
       </c>
       <c r="D157" t="n">
-        <v>19.2</v>
+        <v>35.2</v>
       </c>
       <c r="E157" t="n">
-        <v>36.9</v>
+        <v>46.2</v>
       </c>
       <c r="F157" t="n">
-        <v>19.2</v>
+        <v>35.2</v>
       </c>
       <c r="G157" t="n">
-        <v>22.5</v>
+        <v>30.5</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I157" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="J157" t="n">
-        <v>27</v>
+        <v>18.2</v>
       </c>
       <c r="K157" t="n">
-        <v>40.5</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="158">
@@ -6643,34 +6640,34 @@
         <v>164</v>
       </c>
       <c r="B158" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C158" t="n">
-        <v>81.4</v>
+        <v>60.3</v>
       </c>
       <c r="D158" t="n">
-        <v>35.2</v>
+        <v>9.3</v>
       </c>
       <c r="E158" t="n">
-        <v>46.2</v>
+        <v>51</v>
       </c>
       <c r="F158" t="n">
-        <v>35.2</v>
+        <v>9.3</v>
       </c>
       <c r="G158" t="n">
-        <v>30.5</v>
+        <v>11.4</v>
       </c>
       <c r="H158" t="n">
-        <v>3.3</v>
+        <v>11.2</v>
       </c>
       <c r="I158" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="J158" t="n">
-        <v>18.2</v>
+        <v>10.8</v>
       </c>
       <c r="K158" t="n">
-        <v>40.9</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="159">
@@ -6678,34 +6675,34 @@
         <v>165</v>
       </c>
       <c r="B159" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C159" t="n">
-        <v>60.3</v>
+        <v>63.2</v>
       </c>
       <c r="D159" t="n">
-        <v>9.3</v>
+        <v>45</v>
       </c>
       <c r="E159" t="n">
-        <v>51</v>
+        <v>18.2</v>
       </c>
       <c r="F159" t="n">
-        <v>9.3</v>
+        <v>45</v>
       </c>
       <c r="G159" t="n">
-        <v>11.4</v>
+        <v>26.9</v>
       </c>
       <c r="H159" t="n">
-        <v>11.2</v>
+        <v>7.7</v>
       </c>
       <c r="I159" t="n">
-        <v>50.8</v>
+        <v>0</v>
       </c>
       <c r="J159" t="n">
-        <v>10.8</v>
+        <v>25</v>
       </c>
       <c r="K159" t="n">
-        <v>34.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160">
@@ -6713,34 +6710,34 @@
         <v>166</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C160" t="n">
-        <v>63.2</v>
+        <v>74.4</v>
       </c>
       <c r="D160" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E160" t="n">
-        <v>18.2</v>
+        <v>62.4</v>
       </c>
       <c r="F160" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="G160" t="n">
-        <v>26.9</v>
+        <v>23.9</v>
       </c>
       <c r="H160" t="n">
-        <v>7.7</v>
+        <v>16</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="J160" t="n">
-        <v>25</v>
+        <v>35.4</v>
       </c>
       <c r="K160" t="n">
-        <v>25</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="161">
@@ -6748,34 +6745,34 @@
         <v>167</v>
       </c>
       <c r="B161" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C161" t="n">
-        <v>74.4</v>
+        <v>74.6</v>
       </c>
       <c r="D161" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="E161" t="n">
-        <v>62.4</v>
+        <v>49.3</v>
       </c>
       <c r="F161" t="n">
-        <v>12</v>
+        <v>25.3</v>
       </c>
       <c r="G161" t="n">
-        <v>23.9</v>
+        <v>8.9</v>
       </c>
       <c r="H161" t="n">
-        <v>16</v>
+        <v>2.3</v>
       </c>
       <c r="I161" t="n">
-        <v>32.3</v>
+        <v>47.2</v>
       </c>
       <c r="J161" t="n">
-        <v>35.4</v>
+        <v>22.2</v>
       </c>
       <c r="K161" t="n">
-        <v>36.9</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="162">
@@ -6783,69 +6780,69 @@
         <v>168</v>
       </c>
       <c r="B162" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C162" t="n">
-        <v>74.6</v>
+        <v>70.5</v>
       </c>
       <c r="D162" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="E162" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F162" t="n">
-        <v>25.3</v>
+        <v>20.5</v>
       </c>
       <c r="G162" t="n">
-        <v>8.9</v>
+        <v>37.7</v>
       </c>
       <c r="H162" t="n">
-        <v>2.3</v>
+        <v>9.1</v>
       </c>
       <c r="I162" t="n">
-        <v>47.2</v>
+        <v>51.9</v>
       </c>
       <c r="J162" t="n">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="K162" t="n">
-        <v>33.3</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" t="s">
         <v>169</v>
       </c>
-      <c r="B163" t="s">
-        <v>170</v>
-      </c>
       <c r="C163" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D163" t="n">
         <v>20.5</v>
       </c>
       <c r="E163" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F163" t="n">
         <v>20.5</v>
       </c>
       <c r="G163" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H163" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="I163" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J163" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K163" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="164">
@@ -6853,34 +6850,34 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C164" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D164" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E164" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F164" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G164" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H164" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I164" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J164" t="n">
         <v>48.1</v>
       </c>
-      <c r="F164" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G164" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H164" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I164" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J164" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K164" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="165">
@@ -6888,34 +6885,34 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C165" t="n">
-        <v>64.6</v>
+        <v>59</v>
       </c>
       <c r="D165" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="E165" t="n">
-        <v>47.9</v>
+        <v>38.2</v>
       </c>
       <c r="F165" t="n">
-        <v>16.7</v>
+        <v>20.8</v>
       </c>
       <c r="G165" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="H165" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="I165" t="n">
-        <v>29.6</v>
+        <v>31.6</v>
       </c>
       <c r="J165" t="n">
-        <v>48.1</v>
+        <v>36.8</v>
       </c>
       <c r="K165" t="n">
-        <v>38.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="166">
@@ -6923,34 +6920,34 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C166" t="n">
-        <v>59</v>
+        <v>66.3</v>
       </c>
       <c r="D166" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="E166" t="n">
-        <v>38.2</v>
+        <v>51.5</v>
       </c>
       <c r="F166" t="n">
-        <v>20.8</v>
+        <v>14.8</v>
       </c>
       <c r="G166" t="n">
-        <v>34.5</v>
+        <v>9.3</v>
       </c>
       <c r="H166" t="n">
-        <v>14.6</v>
+        <v>16.8</v>
       </c>
       <c r="I166" t="n">
-        <v>31.6</v>
+        <v>62.6</v>
       </c>
       <c r="J166" t="n">
-        <v>36.8</v>
+        <v>16.5</v>
       </c>
       <c r="K166" t="n">
-        <v>29.4</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="167">
@@ -6958,34 +6955,34 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C167" t="n">
-        <v>66.3</v>
+        <v>80.8</v>
       </c>
       <c r="D167" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="E167" t="n">
-        <v>51.5</v>
+        <v>65.3</v>
       </c>
       <c r="F167" t="n">
-        <v>14.8</v>
+        <v>15.5</v>
       </c>
       <c r="G167" t="n">
-        <v>9.3</v>
+        <v>22.7</v>
       </c>
       <c r="H167" t="n">
-        <v>16.8</v>
+        <v>10.1</v>
       </c>
       <c r="I167" t="n">
-        <v>62.6</v>
+        <v>38.6</v>
       </c>
       <c r="J167" t="n">
-        <v>16.5</v>
+        <v>31.8</v>
       </c>
       <c r="K167" t="n">
-        <v>37.9</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="168">
@@ -6993,34 +6990,34 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C168" t="n">
-        <v>80.8</v>
+        <v>55.6</v>
       </c>
       <c r="D168" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="E168" t="n">
-        <v>65.3</v>
+        <v>36.9</v>
       </c>
       <c r="F168" t="n">
-        <v>15.5</v>
+        <v>18.7</v>
       </c>
       <c r="G168" t="n">
-        <v>22.7</v>
+        <v>26.8</v>
       </c>
       <c r="H168" t="n">
-        <v>10.1</v>
+        <v>12.4</v>
       </c>
       <c r="I168" t="n">
-        <v>38.6</v>
+        <v>51</v>
       </c>
       <c r="J168" t="n">
-        <v>31.8</v>
+        <v>21.6</v>
       </c>
       <c r="K168" t="n">
-        <v>48.2</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="169">
@@ -7028,34 +7025,34 @@
         <v>176</v>
       </c>
       <c r="B169" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C169" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D169" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="E169" t="n">
-        <v>36.9</v>
+        <v>75</v>
       </c>
       <c r="F169" t="n">
-        <v>18.7</v>
+        <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>26.8</v>
+        <v>66.7</v>
       </c>
       <c r="H169" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>21.6</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>27.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -7063,34 +7060,34 @@
         <v>177</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C170" t="n">
-        <v>75</v>
+        <v>56.3</v>
       </c>
       <c r="D170" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="E170" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="F170" t="n">
-        <v>0</v>
+        <v>17.8</v>
       </c>
       <c r="G170" t="n">
-        <v>66.7</v>
+        <v>12.7</v>
       </c>
       <c r="H170" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="I170" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="J170" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="K170" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="171">
@@ -7098,34 +7095,34 @@
         <v>178</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C171" t="n">
-        <v>56.3</v>
+        <v>61.5</v>
       </c>
       <c r="D171" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="E171" t="n">
-        <v>38.5</v>
+        <v>41.3</v>
       </c>
       <c r="F171" t="n">
-        <v>17.8</v>
+        <v>20.2</v>
       </c>
       <c r="G171" t="n">
-        <v>12.7</v>
+        <v>9.1</v>
       </c>
       <c r="H171" t="n">
-        <v>17.9</v>
+        <v>7.2</v>
       </c>
       <c r="I171" t="n">
-        <v>34.8</v>
+        <v>60</v>
       </c>
       <c r="J171" t="n">
-        <v>31.8</v>
+        <v>18.1</v>
       </c>
       <c r="K171" t="n">
-        <v>47.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="172">
@@ -7133,34 +7130,34 @@
         <v>179</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C172" t="n">
-        <v>61.5</v>
+        <v>71.4</v>
       </c>
       <c r="D172" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="E172" t="n">
-        <v>41.3</v>
+        <v>54.4</v>
       </c>
       <c r="F172" t="n">
-        <v>20.2</v>
+        <v>17</v>
       </c>
       <c r="G172" t="n">
-        <v>9.1</v>
+        <v>25.1</v>
       </c>
       <c r="H172" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="I172" t="n">
-        <v>60</v>
+        <v>36.5</v>
       </c>
       <c r="J172" t="n">
-        <v>18.1</v>
+        <v>29.4</v>
       </c>
       <c r="K172" t="n">
-        <v>29</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="173">
@@ -7168,34 +7165,34 @@
         <v>180</v>
       </c>
       <c r="B173" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C173" t="n">
-        <v>71.4</v>
+        <v>76.7</v>
       </c>
       <c r="D173" t="n">
-        <v>17</v>
+        <v>30.1</v>
       </c>
       <c r="E173" t="n">
-        <v>54.4</v>
+        <v>46.6</v>
       </c>
       <c r="F173" t="n">
-        <v>17</v>
+        <v>30.1</v>
       </c>
       <c r="G173" t="n">
-        <v>25.1</v>
+        <v>40.7</v>
       </c>
       <c r="H173" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="I173" t="n">
-        <v>36.5</v>
+        <v>39.1</v>
       </c>
       <c r="J173" t="n">
-        <v>29.4</v>
+        <v>21.7</v>
       </c>
       <c r="K173" t="n">
-        <v>57.1</v>
+        <v>65.2</v>
       </c>
     </row>
     <row r="174">
@@ -7203,34 +7200,34 @@
         <v>181</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C174" t="n">
-        <v>76.7</v>
+        <v>74.5</v>
       </c>
       <c r="D174" t="n">
-        <v>30.1</v>
+        <v>19.9</v>
       </c>
       <c r="E174" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="F174" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="G174" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H174" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I174" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J174" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K174" t="n">
         <v>46.6</v>
-      </c>
-      <c r="F174" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="G174" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="H174" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I174" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="J174" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="K174" t="n">
-        <v>65.2</v>
       </c>
     </row>
     <row r="175">
@@ -7238,57 +7235,51 @@
         <v>182</v>
       </c>
       <c r="B175" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C175" t="n">
-        <v>74.5</v>
+        <v>37.5</v>
       </c>
       <c r="D175" t="n">
-        <v>19.9</v>
+        <v>33.3</v>
       </c>
       <c r="E175" t="n">
-        <v>54.6</v>
+        <v>4.2</v>
       </c>
       <c r="F175" t="n">
-        <v>19.9</v>
+        <v>33.3</v>
       </c>
       <c r="G175" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="I175" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="J175" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K175" t="n">
-        <v>46.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I175"/>
+      <c r="J175"/>
+      <c r="K175"/>
     </row>
     <row r="176">
       <c r="A176" t="s">
         <v>183</v>
       </c>
       <c r="B176" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C176" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D176" t="n">
         <v>33.3</v>
       </c>
       <c r="E176" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F176" t="n">
         <v>33.3</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -7298,64 +7289,35 @@
       <c r="K176"/>
     </row>
     <row r="177">
-      <c r="A177" t="s">
+      <c r="A177"/>
+      <c r="B177" t="s">
         <v>184</v>
       </c>
-      <c r="B177" t="s">
-        <v>170</v>
-      </c>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="D177" t="n">
-        <v>33.3</v>
+        <v>21.6</v>
       </c>
       <c r="E177" t="n">
-        <v>-33.3</v>
+        <v>47.5</v>
       </c>
       <c r="F177" t="n">
-        <v>33.3</v>
+        <v>21.6</v>
       </c>
       <c r="G177" t="n">
-        <v>100</v>
+        <v>27.2</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177"/>
-      <c r="J177"/>
-      <c r="K177"/>
-    </row>
-    <row r="178">
-      <c r="A178"/>
-      <c r="B178" t="s">
-        <v>185</v>
-      </c>
-      <c r="C178" t="n">
-        <v>69</v>
-      </c>
-      <c r="D178" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="E178" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F178" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G178" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H178" t="n">
         <v>9.2</v>
       </c>
-      <c r="I178" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J178" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="K178" t="n">
+      <c r="I177" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="J177" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K177" t="n">
         <v>37.6</v>
       </c>
     </row>
@@ -7388,22 +7350,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>188</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7412,18 +7374,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7458,7 +7420,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7528,7 +7490,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -7563,7 +7525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7598,7 +7560,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7633,7 +7595,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7668,7 +7630,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7738,7 +7700,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -7773,7 +7735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7808,7 +7770,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7843,7 +7805,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7911,7 +7873,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
@@ -7944,7 +7906,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
@@ -7977,7 +7939,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
@@ -8010,7 +7972,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
@@ -8045,7 +8007,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
@@ -8080,7 +8042,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
@@ -8150,7 +8112,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
@@ -8185,7 +8147,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
         <v>47</v>
@@ -8220,7 +8182,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B25" t="s">
         <v>47</v>
@@ -8255,7 +8217,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B26" t="s">
         <v>47</v>
@@ -8290,7 +8252,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s">
         <v>47</v>
@@ -8325,7 +8287,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
         <v>47</v>
@@ -8360,7 +8322,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
         <v>47</v>
@@ -8395,7 +8357,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B30" t="s">
         <v>47</v>
@@ -8430,7 +8392,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B31" t="s">
         <v>47</v>
@@ -8465,7 +8427,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
@@ -8500,7 +8462,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -8535,7 +8497,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B34" t="s">
         <v>47</v>
@@ -8570,7 +8532,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
         <v>54</v>
@@ -8605,7 +8567,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
         <v>54</v>
@@ -8640,7 +8602,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B37" t="s">
         <v>54</v>
@@ -8673,7 +8635,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
         <v>54</v>
@@ -8743,7 +8705,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B40" t="s">
         <v>54</v>
@@ -8778,7 +8740,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
         <v>54</v>
@@ -8813,7 +8775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
         <v>54</v>
@@ -8848,7 +8810,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s">
         <v>54</v>
@@ -8881,7 +8843,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B44" t="s">
         <v>54</v>
@@ -8916,7 +8878,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s">
         <v>54</v>
@@ -8951,7 +8913,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s">
         <v>54</v>
@@ -8986,7 +8948,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
         <v>54</v>
@@ -9021,7 +8983,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -9056,7 +9018,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
         <v>54</v>
@@ -9091,7 +9053,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
         <v>54</v>
@@ -9124,7 +9086,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
         <v>54</v>
@@ -9159,10 +9121,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C52" t="n">
         <v>60</v>
@@ -9194,10 +9156,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C53" t="n">
         <v>72.9</v>
@@ -9229,10 +9191,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C54" t="n">
         <v>58.9</v>
@@ -9264,10 +9226,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C55" t="n">
         <v>66.7</v>
@@ -9297,10 +9259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C56" t="n">
         <v>67.1</v>
@@ -9332,10 +9294,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C57" t="n">
         <v>55.3</v>
@@ -9367,10 +9329,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C58" t="n">
         <v>72.4</v>
@@ -9402,10 +9364,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C59" t="n">
         <v>61.7</v>
@@ -9437,10 +9399,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B60" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C60" t="n">
         <v>61.8</v>
@@ -9472,10 +9434,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" t="n">
         <v>56.5</v>
@@ -9507,10 +9469,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C62" t="n">
         <v>65.7</v>
@@ -9542,10 +9504,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" t="n">
         <v>64.2</v>
@@ -9577,10 +9539,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" t="n">
         <v>30</v>
@@ -9612,10 +9574,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" t="n">
         <v>38.7</v>
@@ -9647,10 +9609,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C66" t="n">
         <v>40</v>
@@ -9682,10 +9644,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C67" t="n">
         <v>73.4</v>
@@ -9717,10 +9679,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C68" t="n">
         <v>69</v>
@@ -9752,10 +9714,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C69" t="n">
         <v>50</v>
@@ -9787,10 +9749,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C70" t="n">
         <v>56.4</v>
@@ -9822,10 +9784,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C71" t="n">
         <v>54.8</v>
@@ -9857,10 +9819,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C72" t="n">
         <v>61.1</v>
@@ -9892,10 +9854,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C73" t="n">
         <v>62.1</v>
@@ -9927,10 +9889,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C74" t="n">
         <v>57.1</v>
@@ -9962,10 +9924,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C75" t="n">
         <v>72.7</v>
@@ -9997,10 +9959,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" t="n">
         <v>69.4</v>
@@ -10032,10 +9994,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C77" t="n">
         <v>61.7</v>
@@ -10067,10 +10029,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C78" t="n">
         <v>33.3</v>
@@ -10100,10 +10062,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C79" t="n">
         <v>63.3</v>
@@ -10135,10 +10097,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C80" t="n">
         <v>42</v>
@@ -10170,10 +10132,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C81" t="n">
         <v>67.9</v>
@@ -10205,10 +10167,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B82" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C82" t="n">
         <v>50</v>
@@ -10240,10 +10202,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C83" t="n">
         <v>28.6</v>
@@ -10273,10 +10235,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B84" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C84" t="n">
         <v>63.6</v>
@@ -10308,10 +10270,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C85" t="n">
         <v>48.6</v>
@@ -10343,10 +10305,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C86" t="n">
         <v>57.4</v>
@@ -10378,10 +10340,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C87" t="n">
         <v>71.4</v>
@@ -10413,10 +10375,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C88" t="n">
         <v>61.5</v>
@@ -10448,10 +10410,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C89" t="n">
         <v>54.5</v>
@@ -10483,10 +10445,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C90" t="n">
         <v>34.6</v>
@@ -10516,10 +10478,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C91" t="n">
         <v>67.3</v>
@@ -10551,10 +10513,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C92" t="n">
         <v>62.1</v>
@@ -10586,10 +10548,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C93" t="n">
         <v>52.6</v>
@@ -10621,10 +10583,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B94" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C94" t="n">
         <v>75</v>
@@ -10656,10 +10618,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C95" t="n">
         <v>55.2</v>
@@ -10691,10 +10653,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C96" t="n">
         <v>74.2</v>
@@ -10726,10 +10688,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B97" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C97" t="n">
         <v>63.2</v>
@@ -10761,10 +10723,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B98" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C98" t="n">
         <v>58.7</v>
@@ -10796,10 +10758,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C99" t="n">
         <v>63.4</v>
@@ -10831,10 +10793,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B100" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C100" t="n">
         <v>66.1</v>
@@ -10866,10 +10828,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B101" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C101" t="n">
         <v>80</v>
@@ -10901,10 +10863,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C102" t="n">
         <v>60.6</v>
@@ -10936,10 +10898,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B103" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C103" t="n">
         <v>69.2</v>
@@ -10971,10 +10933,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B104" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C104" t="n">
         <v>66.3</v>
@@ -11006,10 +10968,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B105" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C105" t="n">
         <v>66.9</v>
@@ -11041,10 +11003,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B106" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C106" t="n">
         <v>64.4</v>
@@ -11076,10 +11038,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C107" t="n">
         <v>33.3</v>
@@ -11111,10 +11073,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B108" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C108" t="n">
         <v>54.1</v>
@@ -11146,10 +11108,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
+        <v>148</v>
+      </c>
+      <c r="B109" t="s">
         <v>149</v>
-      </c>
-      <c r="B109" t="s">
-        <v>150</v>
       </c>
       <c r="C109" t="n">
         <v>51.6</v>
@@ -11181,10 +11143,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C110" t="n">
         <v>62</v>
@@ -11216,10 +11178,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B111" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C111" t="n">
         <v>50</v>
@@ -11249,10 +11211,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B112" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C112" t="n">
         <v>65.8</v>
@@ -11284,10 +11246,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B113" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C113" t="n">
         <v>51</v>
@@ -11319,10 +11281,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B114" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C114" t="n">
         <v>51.5</v>
@@ -11354,10 +11316,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B115" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C115" t="n">
         <v>63</v>
@@ -11389,10 +11351,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B116" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C116" t="n">
         <v>52.6</v>
@@ -11424,10 +11386,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C117" t="n">
         <v>65.2</v>
@@ -11459,10 +11421,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B118" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C118" t="n">
         <v>60</v>
@@ -11494,10 +11456,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B119" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C119" t="n">
         <v>44</v>
@@ -11529,10 +11491,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B120" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C120" t="n">
         <v>38.9</v>
@@ -11564,10 +11526,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B121" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C121" t="n">
         <v>58.7</v>
@@ -11599,10 +11561,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B122" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C122" t="n">
         <v>57.5</v>
@@ -11634,10 +11596,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B123" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C123" t="n">
         <v>72.5</v>
@@ -11669,10 +11631,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B124" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C124" t="n">
         <v>62.4</v>
@@ -11704,10 +11666,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B125" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C125" t="n">
         <v>60.7</v>
@@ -11739,10 +11701,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B126" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C126" t="n">
         <v>58.2</v>
@@ -11774,10 +11736,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C127" t="n">
         <v>60</v>
@@ -11809,10 +11771,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C128" t="n">
         <v>67.3</v>
@@ -11844,10 +11806,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B129" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C129" t="n">
         <v>84.6</v>
@@ -11877,10 +11839,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B130" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C130" t="n">
         <v>50</v>
@@ -11912,10 +11874,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C131" t="n">
         <v>61.3</v>
@@ -11947,10 +11909,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B132" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C132" t="n">
         <v>65.8</v>
@@ -11982,10 +11944,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B133" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C133" t="n">
         <v>50.9</v>
@@ -12017,10 +11979,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B134" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C134" t="n">
         <v>66.7</v>
@@ -12052,10 +12014,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B135" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C135" t="n">
         <v>69.5</v>
@@ -12087,10 +12049,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B136" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C136" t="n">
         <v>59</v>
@@ -12123,7 +12085,7 @@
     <row r="137">
       <c r="A137"/>
       <c r="B137" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C137" t="n">
         <v>58.7</v>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -156,9 +156,6 @@
     <t xml:space="preserve">Tim Holyk</t>
   </si>
   <si>
-    <t xml:space="preserve">Unknown</t>
-  </si>
-  <si>
     <t xml:space="preserve">Walker Hultgren</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t xml:space="preserve">Rafael Gross</t>
   </si>
   <si>
-    <t xml:space="preserve">Raffi Gross</t>
-  </si>
-  <si>
     <t xml:space="preserve">Samuele Bruno</t>
   </si>
   <si>
@@ -679,9 +673,6 @@
   </si>
   <si>
     <t xml:space="preserve">Eric Pettipiece</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evan Elliottt</t>
   </si>
   <si>
     <t xml:space="preserve">Garret Day</t>
@@ -982,8 +973,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K166" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K166"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K164" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K164"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -1002,8 +993,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K136" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K136"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K135" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K135"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -2374,7 +2365,7 @@
         <v>17.1</v>
       </c>
       <c r="G31" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H31" t="n">
         <v>11.6</v>
@@ -2536,86 +2527,102 @@
       <c r="B36" t="s">
         <v>33</v>
       </c>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
+      <c r="C36" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>25</v>
+      </c>
+      <c r="E36" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>25</v>
+      </c>
       <c r="G36" t="n">
-        <v>100</v>
-      </c>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
+        <v>28.2</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="J36" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C37" t="n">
-        <v>74.2</v>
+        <v>76.1</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="E37" t="n">
-        <v>49.2</v>
+        <v>54.4</v>
       </c>
       <c r="F37" t="n">
-        <v>25</v>
+        <v>21.7</v>
       </c>
       <c r="G37" t="n">
-        <v>28.2</v>
+        <v>34.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="I37" t="n">
-        <v>45.8</v>
+        <v>63.2</v>
       </c>
       <c r="J37" t="n">
-        <v>29.2</v>
+        <v>23.7</v>
       </c>
       <c r="K37" t="n">
-        <v>37.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>50</v>
+      </c>
+      <c r="B38" t="s">
         <v>49</v>
       </c>
-      <c r="B38" t="s">
-        <v>50</v>
-      </c>
       <c r="C38" t="n">
-        <v>76.1</v>
+        <v>65.3</v>
       </c>
       <c r="D38" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="E38" t="n">
-        <v>54.4</v>
+        <v>47.8</v>
       </c>
       <c r="F38" t="n">
-        <v>21.7</v>
+        <v>17.5</v>
       </c>
       <c r="G38" t="n">
-        <v>34.8</v>
+        <v>17.6</v>
       </c>
       <c r="H38" t="n">
-        <v>10.5</v>
+        <v>6.9</v>
       </c>
       <c r="I38" t="n">
-        <v>63.2</v>
+        <v>40.7</v>
       </c>
       <c r="J38" t="n">
-        <v>23.7</v>
+        <v>31.9</v>
       </c>
       <c r="K38" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="39">
@@ -2623,34 +2630,34 @@
         <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>65.3</v>
+        <v>78.9</v>
       </c>
       <c r="D39" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="E39" t="n">
-        <v>47.8</v>
+        <v>65.6</v>
       </c>
       <c r="F39" t="n">
-        <v>17.5</v>
+        <v>13.3</v>
       </c>
       <c r="G39" t="n">
         <v>17.6</v>
       </c>
       <c r="H39" t="n">
-        <v>6.9</v>
+        <v>12.5</v>
       </c>
       <c r="I39" t="n">
-        <v>40.7</v>
+        <v>66.7</v>
       </c>
       <c r="J39" t="n">
-        <v>31.9</v>
+        <v>16.7</v>
       </c>
       <c r="K39" t="n">
-        <v>45.1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40">
@@ -2658,34 +2665,28 @@
         <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
-        <v>78.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>65.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40"/>
       <c r="G40" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="J40" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2693,28 +2694,34 @@
         <v>53</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>100</v>
-      </c>
-      <c r="D41"/>
-      <c r="E41"/>
-      <c r="F41"/>
+        <v>72.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14.3</v>
+      </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I41" t="n">
-        <v>100</v>
+        <v>51.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="42">
@@ -2722,34 +2729,34 @@
         <v>54</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="n">
-        <v>72.4</v>
+        <v>78.5</v>
       </c>
       <c r="D42" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="E42" t="n">
-        <v>58.1</v>
+        <v>51.4</v>
       </c>
       <c r="F42" t="n">
-        <v>14.3</v>
+        <v>27.1</v>
       </c>
       <c r="G42" t="n">
-        <v>12.9</v>
+        <v>25.4</v>
       </c>
       <c r="H42" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>51.9</v>
+        <v>48.2</v>
       </c>
       <c r="J42" t="n">
-        <v>24.7</v>
+        <v>31.3</v>
       </c>
       <c r="K42" t="n">
-        <v>25.9</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="43">
@@ -2757,34 +2764,34 @@
         <v>55</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>78.5</v>
+        <v>67.3</v>
       </c>
       <c r="D43" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="E43" t="n">
-        <v>51.4</v>
+        <v>39.2</v>
       </c>
       <c r="F43" t="n">
-        <v>27.1</v>
+        <v>28.1</v>
       </c>
       <c r="G43" t="n">
-        <v>25.4</v>
+        <v>13.2</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="I43" t="n">
-        <v>48.2</v>
+        <v>36</v>
       </c>
       <c r="J43" t="n">
-        <v>31.3</v>
+        <v>40</v>
       </c>
       <c r="K43" t="n">
-        <v>38.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="44">
@@ -2792,34 +2799,30 @@
         <v>56</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" t="n">
-        <v>67.3</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="C44"/>
       <c r="D44" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>39.2</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E44"/>
       <c r="F44" t="n">
-        <v>28.1</v>
+        <v>100</v>
       </c>
       <c r="G44" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="J44" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>29.2</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -2827,30 +2830,34 @@
         <v>57</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45"/>
+        <v>49</v>
+      </c>
+      <c r="C45" t="n">
+        <v>65.7</v>
+      </c>
       <c r="D45" t="n">
-        <v>100</v>
-      </c>
-      <c r="E45"/>
+        <v>25.8</v>
+      </c>
+      <c r="E45" t="n">
+        <v>39.9</v>
+      </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>25.8</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>8.3</v>
       </c>
       <c r="I45" t="n">
-        <v>100</v>
+        <v>53.2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="K45" t="n">
-        <v>100</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="46">
@@ -2858,34 +2865,34 @@
         <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>65.7</v>
+        <v>77.3</v>
       </c>
       <c r="D46" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="E46" t="n">
-        <v>39.9</v>
+        <v>54.8</v>
       </c>
       <c r="F46" t="n">
-        <v>25.8</v>
+        <v>22.5</v>
       </c>
       <c r="G46" t="n">
-        <v>22</v>
+        <v>41.2</v>
       </c>
       <c r="H46" t="n">
-        <v>8.3</v>
+        <v>8.2</v>
       </c>
       <c r="I46" t="n">
-        <v>53.2</v>
+        <v>55.6</v>
       </c>
       <c r="J46" t="n">
-        <v>15.6</v>
+        <v>22.2</v>
       </c>
       <c r="K46" t="n">
-        <v>20.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="47">
@@ -2893,34 +2900,34 @@
         <v>59</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>77.3</v>
+        <v>79.4</v>
       </c>
       <c r="D47" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="E47" t="n">
-        <v>54.8</v>
+        <v>42.4</v>
       </c>
       <c r="F47" t="n">
-        <v>22.5</v>
+        <v>37</v>
       </c>
       <c r="G47" t="n">
-        <v>41.2</v>
+        <v>39.1</v>
       </c>
       <c r="H47" t="n">
-        <v>8.2</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>55.6</v>
+        <v>48.1</v>
       </c>
       <c r="J47" t="n">
-        <v>22.2</v>
+        <v>29.6</v>
       </c>
       <c r="K47" t="n">
-        <v>25.9</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="48">
@@ -2928,34 +2935,34 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" t="n">
-        <v>79.4</v>
+        <v>50.7</v>
       </c>
       <c r="D48" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="E48" t="n">
-        <v>42.4</v>
+        <v>32.8</v>
       </c>
       <c r="F48" t="n">
-        <v>37</v>
+        <v>17.9</v>
       </c>
       <c r="G48" t="n">
-        <v>39.1</v>
+        <v>18.3</v>
       </c>
       <c r="H48" t="n">
-        <v>7</v>
+        <v>17.1</v>
       </c>
       <c r="I48" t="n">
-        <v>48.1</v>
+        <v>38.5</v>
       </c>
       <c r="J48" t="n">
-        <v>29.6</v>
+        <v>30.8</v>
       </c>
       <c r="K48" t="n">
-        <v>40.7</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="49">
@@ -2963,34 +2970,34 @@
         <v>61</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>50.7</v>
+        <v>69.3</v>
       </c>
       <c r="D49" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="E49" t="n">
-        <v>32.8</v>
+        <v>54.5</v>
       </c>
       <c r="F49" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="G49" t="n">
-        <v>18.3</v>
+        <v>31.2</v>
       </c>
       <c r="H49" t="n">
-        <v>17.1</v>
+        <v>12.5</v>
       </c>
       <c r="I49" t="n">
-        <v>38.5</v>
+        <v>36.7</v>
       </c>
       <c r="J49" t="n">
-        <v>30.8</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
-        <v>16.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -2998,34 +3005,34 @@
         <v>62</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>69.3</v>
+        <v>68.1</v>
       </c>
       <c r="D50" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="E50" t="n">
-        <v>54.5</v>
+        <v>42.6</v>
       </c>
       <c r="F50" t="n">
-        <v>14.8</v>
+        <v>25.5</v>
       </c>
       <c r="G50" t="n">
-        <v>31.2</v>
+        <v>51.6</v>
       </c>
       <c r="H50" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="I50" t="n">
-        <v>36.7</v>
+        <v>47.1</v>
       </c>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>17.6</v>
       </c>
       <c r="K50" t="n">
-        <v>25</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="51">
@@ -3033,34 +3040,34 @@
         <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C51" t="n">
-        <v>68.1</v>
+        <v>70.7</v>
       </c>
       <c r="D51" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="E51" t="n">
-        <v>42.6</v>
+        <v>56.4</v>
       </c>
       <c r="F51" t="n">
-        <v>25.5</v>
+        <v>14.3</v>
       </c>
       <c r="G51" t="n">
-        <v>51.6</v>
+        <v>21.6</v>
       </c>
       <c r="H51" t="n">
-        <v>6.5</v>
+        <v>13.3</v>
       </c>
       <c r="I51" t="n">
-        <v>47.1</v>
+        <v>61.9</v>
       </c>
       <c r="J51" t="n">
-        <v>17.6</v>
+        <v>14.3</v>
       </c>
       <c r="K51" t="n">
-        <v>29.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="52">
@@ -3068,34 +3075,34 @@
         <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C52" t="n">
-        <v>70.7</v>
+        <v>69.3</v>
       </c>
       <c r="D52" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="E52" t="n">
-        <v>56.4</v>
+        <v>54.7</v>
       </c>
       <c r="F52" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="G52" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="H52" t="n">
-        <v>13.3</v>
+        <v>9.6</v>
       </c>
       <c r="I52" t="n">
-        <v>61.9</v>
+        <v>38.8</v>
       </c>
       <c r="J52" t="n">
-        <v>14.3</v>
+        <v>32.8</v>
       </c>
       <c r="K52" t="n">
-        <v>21.4</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="53">
@@ -3103,34 +3110,34 @@
         <v>65</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C53" t="n">
-        <v>69.3</v>
+        <v>77.8</v>
       </c>
       <c r="D53" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="E53" t="n">
-        <v>54.7</v>
+        <v>65.6</v>
       </c>
       <c r="F53" t="n">
-        <v>14.6</v>
+        <v>12.2</v>
       </c>
       <c r="G53" t="n">
-        <v>25.6</v>
+        <v>33.8</v>
       </c>
       <c r="H53" t="n">
-        <v>9.6</v>
+        <v>13.6</v>
       </c>
       <c r="I53" t="n">
-        <v>38.8</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>32.8</v>
+        <v>41.5</v>
       </c>
       <c r="K53" t="n">
-        <v>38.8</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="54">
@@ -3138,69 +3145,69 @@
         <v>66</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
-        <v>77.8</v>
+        <v>76.8</v>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="E54" t="n">
-        <v>65.6</v>
+        <v>53.5</v>
       </c>
       <c r="F54" t="n">
-        <v>12.2</v>
+        <v>23.3</v>
       </c>
       <c r="G54" t="n">
-        <v>33.8</v>
+        <v>30.6</v>
       </c>
       <c r="H54" t="n">
-        <v>13.6</v>
+        <v>10.4</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>52.1</v>
       </c>
       <c r="J54" t="n">
-        <v>41.5</v>
+        <v>18.8</v>
       </c>
       <c r="K54" t="n">
-        <v>50.8</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
         <v>67</v>
       </c>
-      <c r="B55" t="s">
-        <v>68</v>
-      </c>
       <c r="C55" t="n">
-        <v>76.8</v>
+        <v>78.9</v>
       </c>
       <c r="D55" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="E55" t="n">
-        <v>53.5</v>
+        <v>45.6</v>
       </c>
       <c r="F55" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="G55" t="n">
-        <v>30.6</v>
+        <v>23.5</v>
       </c>
       <c r="H55" t="n">
-        <v>10.4</v>
+        <v>4.2</v>
       </c>
       <c r="I55" t="n">
-        <v>52.1</v>
+        <v>40.8</v>
       </c>
       <c r="J55" t="n">
-        <v>18.8</v>
+        <v>22.4</v>
       </c>
       <c r="K55" t="n">
-        <v>43.8</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="56">
@@ -3208,34 +3215,34 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>78.9</v>
+        <v>59.6</v>
       </c>
       <c r="D56" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="E56" t="n">
-        <v>45.6</v>
+        <v>46.3</v>
       </c>
       <c r="F56" t="n">
-        <v>33.3</v>
+        <v>13.3</v>
       </c>
       <c r="G56" t="n">
-        <v>23.5</v>
+        <v>26.1</v>
       </c>
       <c r="H56" t="n">
-        <v>4.2</v>
+        <v>13.6</v>
       </c>
       <c r="I56" t="n">
-        <v>40.8</v>
+        <v>54.9</v>
       </c>
       <c r="J56" t="n">
-        <v>22.4</v>
+        <v>17.6</v>
       </c>
       <c r="K56" t="n">
-        <v>32.9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57">
@@ -3243,34 +3250,34 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
-        <v>59.6</v>
+        <v>69.2</v>
       </c>
       <c r="D57" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E57" t="n">
-        <v>46.3</v>
+        <v>52.5</v>
       </c>
       <c r="F57" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="G57" t="n">
-        <v>26.1</v>
+        <v>42.9</v>
       </c>
       <c r="H57" t="n">
-        <v>13.6</v>
+        <v>23.1</v>
       </c>
       <c r="I57" t="n">
-        <v>54.9</v>
+        <v>42.9</v>
       </c>
       <c r="J57" t="n">
-        <v>17.6</v>
+        <v>57.1</v>
       </c>
       <c r="K57" t="n">
-        <v>34</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="58">
@@ -3278,98 +3285,98 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
-        <v>69.2</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="E58" t="n">
-        <v>52.5</v>
+        <v>-100</v>
       </c>
       <c r="F58" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="I58" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J58" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>28.6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59">
       <c r="A59" t="s">
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>57.8</v>
       </c>
       <c r="D59" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="E59" t="n">
-        <v>-100</v>
+        <v>12.1</v>
       </c>
       <c r="F59" t="n">
-        <v>100</v>
+        <v>45.7</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>31</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59"/>
-      <c r="J59"/>
-      <c r="K59"/>
+        <v>3.4</v>
+      </c>
+      <c r="I59" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>42.1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
-        <v>57.8</v>
+        <v>57.1</v>
       </c>
       <c r="D60" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="n">
-        <v>12.1</v>
+        <v>44.6</v>
       </c>
       <c r="F60" t="n">
-        <v>45.7</v>
+        <v>12.5</v>
       </c>
       <c r="G60" t="n">
-        <v>31</v>
+        <v>14.3</v>
       </c>
       <c r="H60" t="n">
-        <v>3.4</v>
+        <v>16.7</v>
       </c>
       <c r="I60" t="n">
-        <v>47.4</v>
+        <v>100</v>
       </c>
       <c r="J60" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>42.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61">
@@ -3377,34 +3384,34 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>57.1</v>
+        <v>78.7</v>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="E61" t="n">
-        <v>44.6</v>
+        <v>55.1</v>
       </c>
       <c r="F61" t="n">
-        <v>12.5</v>
+        <v>23.6</v>
       </c>
       <c r="G61" t="n">
-        <v>14.3</v>
+        <v>38.1</v>
       </c>
       <c r="H61" t="n">
-        <v>16.7</v>
+        <v>9.4</v>
       </c>
       <c r="I61" t="n">
-        <v>100</v>
+        <v>41.3</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -3412,34 +3419,34 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>78.7</v>
+        <v>72.4</v>
       </c>
       <c r="D62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="E62" t="n">
-        <v>55.1</v>
+        <v>62.4</v>
       </c>
       <c r="F62" t="n">
-        <v>23.6</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
-        <v>38.1</v>
+        <v>41.2</v>
       </c>
       <c r="H62" t="n">
-        <v>9.4</v>
+        <v>14.3</v>
       </c>
       <c r="I62" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
       <c r="J62" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63">
@@ -3447,34 +3454,34 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>72.4</v>
+        <v>46.4</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="n">
-        <v>62.4</v>
+        <v>33.2</v>
       </c>
       <c r="F63" t="n">
-        <v>10</v>
+        <v>13.2</v>
       </c>
       <c r="G63" t="n">
-        <v>41.2</v>
+        <v>14.3</v>
       </c>
       <c r="H63" t="n">
-        <v>14.3</v>
+        <v>20</v>
       </c>
       <c r="I63" t="n">
+        <v>30</v>
+      </c>
+      <c r="J63" t="n">
+        <v>40</v>
+      </c>
+      <c r="K63" t="n">
         <v>50</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3482,34 +3489,34 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>46.4</v>
+        <v>70.2</v>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="E64" t="n">
-        <v>33.2</v>
+        <v>52.4</v>
       </c>
       <c r="F64" t="n">
-        <v>13.2</v>
+        <v>17.8</v>
       </c>
       <c r="G64" t="n">
-        <v>14.3</v>
+        <v>23.5</v>
       </c>
       <c r="H64" t="n">
-        <v>20</v>
+        <v>15.7</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>50.6</v>
       </c>
       <c r="J64" t="n">
-        <v>40</v>
+        <v>20.8</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="65">
@@ -3517,34 +3524,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="E65" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>17.8</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
       <c r="G65" t="n">
-        <v>23.5</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>50.6</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>20.8</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
-        <v>41.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -3552,28 +3553,34 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
+        <v>81</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>64.9</v>
+      </c>
+      <c r="F66" t="n">
+        <v>16.1</v>
+      </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J66" t="n">
-        <v>50</v>
+        <v>15.4</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="67">
@@ -3581,34 +3588,34 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C67" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D67" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="E67" t="n">
-        <v>64.9</v>
+        <v>50</v>
       </c>
       <c r="F67" t="n">
-        <v>16.1</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="H67" t="n">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J67" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>57.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -3616,19 +3623,19 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="D68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="G68" t="n">
         <v>25</v>
@@ -3637,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -3651,34 +3658,34 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C69" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G69" t="n">
         <v>33.3</v>
       </c>
-      <c r="D69" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25</v>
-      </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I69" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="K69" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="70">
@@ -3686,34 +3693,34 @@
         <v>83</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C70" t="n">
-        <v>74.4</v>
+        <v>69.6</v>
       </c>
       <c r="D70" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="E70" t="n">
-        <v>71.3</v>
+        <v>36.3</v>
       </c>
       <c r="F70" t="n">
-        <v>3.1</v>
+        <v>33.3</v>
       </c>
       <c r="G70" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H70" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="I70" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
       <c r="J70" t="n">
-        <v>11.1</v>
+        <v>30.8</v>
       </c>
       <c r="K70" t="n">
-        <v>11.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="71">
@@ -3721,34 +3728,34 @@
         <v>84</v>
       </c>
       <c r="B71" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C71" t="n">
-        <v>69.6</v>
+        <v>61.1</v>
       </c>
       <c r="D71" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="E71" t="n">
-        <v>36.3</v>
+        <v>38</v>
       </c>
       <c r="F71" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="G71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
-        <v>11.8</v>
+        <v>14.3</v>
       </c>
       <c r="I71" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
       <c r="J71" t="n">
-        <v>30.8</v>
+        <v>37.5</v>
       </c>
       <c r="K71" t="n">
-        <v>53.8</v>
+        <v>71.4</v>
       </c>
     </row>
     <row r="72">
@@ -3756,34 +3763,34 @@
         <v>85</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>68.6</v>
       </c>
       <c r="D72" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="E72" t="n">
-        <v>38</v>
+        <v>36.8</v>
       </c>
       <c r="F72" t="n">
-        <v>23.1</v>
+        <v>31.8</v>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="H72" t="n">
-        <v>14.3</v>
+        <v>3.4</v>
       </c>
       <c r="I72" t="n">
-        <v>37.5</v>
+        <v>47.6</v>
       </c>
       <c r="J72" t="n">
-        <v>37.5</v>
+        <v>28.6</v>
       </c>
       <c r="K72" t="n">
-        <v>71.4</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="73">
@@ -3791,34 +3798,34 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C73" t="n">
-        <v>68.6</v>
+        <v>66.4</v>
       </c>
       <c r="D73" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="E73" t="n">
-        <v>36.8</v>
+        <v>51.5</v>
       </c>
       <c r="F73" t="n">
-        <v>31.8</v>
+        <v>14.9</v>
       </c>
       <c r="G73" t="n">
-        <v>11.1</v>
+        <v>27.3</v>
       </c>
       <c r="H73" t="n">
-        <v>3.4</v>
+        <v>10.3</v>
       </c>
       <c r="I73" t="n">
-        <v>47.6</v>
+        <v>38.7</v>
       </c>
       <c r="J73" t="n">
-        <v>28.6</v>
+        <v>34.7</v>
       </c>
       <c r="K73" t="n">
-        <v>38.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="74">
@@ -3826,34 +3833,34 @@
         <v>87</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" t="n">
-        <v>66.4</v>
+        <v>80.8</v>
       </c>
       <c r="D74" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="E74" t="n">
-        <v>51.5</v>
+        <v>47.5</v>
       </c>
       <c r="F74" t="n">
-        <v>14.9</v>
+        <v>33.3</v>
       </c>
       <c r="G74" t="n">
-        <v>27.3</v>
+        <v>26.1</v>
       </c>
       <c r="H74" t="n">
-        <v>10.3</v>
+        <v>3.2</v>
       </c>
       <c r="I74" t="n">
-        <v>38.7</v>
+        <v>42.9</v>
       </c>
       <c r="J74" t="n">
-        <v>34.7</v>
+        <v>35.2</v>
       </c>
       <c r="K74" t="n">
-        <v>47.3</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="75">
@@ -3861,34 +3868,34 @@
         <v>88</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C75" t="n">
-        <v>80.8</v>
+        <v>56.1</v>
       </c>
       <c r="D75" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="E75" t="n">
-        <v>47.5</v>
+        <v>46.3</v>
       </c>
       <c r="F75" t="n">
-        <v>33.3</v>
+        <v>9.8</v>
       </c>
       <c r="G75" t="n">
-        <v>26.1</v>
+        <v>30.6</v>
       </c>
       <c r="H75" t="n">
-        <v>3.2</v>
+        <v>17.7</v>
       </c>
       <c r="I75" t="n">
-        <v>42.9</v>
+        <v>54.5</v>
       </c>
       <c r="J75" t="n">
-        <v>35.2</v>
+        <v>21.8</v>
       </c>
       <c r="K75" t="n">
-        <v>50.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="76">
@@ -3896,34 +3903,34 @@
         <v>89</v>
       </c>
       <c r="B76" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C76" t="n">
-        <v>56.1</v>
+        <v>66.7</v>
       </c>
       <c r="D76" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>46.3</v>
+        <v>66.7</v>
       </c>
       <c r="F76" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>30.6</v>
+        <v>26.7</v>
       </c>
       <c r="H76" t="n">
-        <v>17.7</v>
+        <v>16.7</v>
       </c>
       <c r="I76" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="K76" t="n">
         <v>54.5</v>
-      </c>
-      <c r="J76" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="K76" t="n">
-        <v>30.8</v>
       </c>
     </row>
     <row r="77">
@@ -3931,34 +3938,34 @@
         <v>90</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C77" t="n">
-        <v>66.7</v>
+        <v>77.3</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="E77" t="n">
-        <v>66.7</v>
+        <v>58.7</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="G77" t="n">
-        <v>26.7</v>
+        <v>30.4</v>
       </c>
       <c r="H77" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="I77" t="n">
-        <v>27.3</v>
+        <v>46.9</v>
       </c>
       <c r="J77" t="n">
-        <v>36.4</v>
+        <v>29.7</v>
       </c>
       <c r="K77" t="n">
-        <v>54.5</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="78">
@@ -3966,69 +3973,69 @@
         <v>91</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C78" t="n">
-        <v>77.3</v>
+        <v>85.7</v>
       </c>
       <c r="D78" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="E78" t="n">
-        <v>58.7</v>
+        <v>70.4</v>
       </c>
       <c r="F78" t="n">
-        <v>18.6</v>
+        <v>15.3</v>
       </c>
       <c r="G78" t="n">
-        <v>30.4</v>
+        <v>37.7</v>
       </c>
       <c r="H78" t="n">
-        <v>10.3</v>
+        <v>12.5</v>
       </c>
       <c r="I78" t="n">
-        <v>46.9</v>
+        <v>38.9</v>
       </c>
       <c r="J78" t="n">
-        <v>29.7</v>
+        <v>41.7</v>
       </c>
       <c r="K78" t="n">
-        <v>58.5</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
+        <v>93</v>
+      </c>
+      <c r="B79" t="s">
         <v>92</v>
       </c>
-      <c r="B79" t="s">
-        <v>93</v>
-      </c>
       <c r="C79" t="n">
-        <v>85.7</v>
+        <v>72.6</v>
       </c>
       <c r="D79" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>70.4</v>
+        <v>42.6</v>
       </c>
       <c r="F79" t="n">
-        <v>15.3</v>
+        <v>30</v>
       </c>
       <c r="G79" t="n">
-        <v>37.7</v>
+        <v>20.4</v>
       </c>
       <c r="H79" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="I79" t="n">
-        <v>38.9</v>
+        <v>59.1</v>
       </c>
       <c r="J79" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="K79" t="n">
-        <v>47.4</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="80">
@@ -4036,34 +4043,34 @@
         <v>94</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C80" t="n">
-        <v>72.6</v>
+        <v>72.2</v>
       </c>
       <c r="D80" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="E80" t="n">
-        <v>42.6</v>
+        <v>44.3</v>
       </c>
       <c r="F80" t="n">
-        <v>30</v>
+        <v>27.9</v>
       </c>
       <c r="G80" t="n">
-        <v>20.4</v>
+        <v>31.7</v>
       </c>
       <c r="H80" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="I80" t="n">
-        <v>59.1</v>
+        <v>41.3</v>
       </c>
       <c r="J80" t="n">
-        <v>16.7</v>
+        <v>21.3</v>
       </c>
       <c r="K80" t="n">
-        <v>42.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="81">
@@ -4071,34 +4078,34 @@
         <v>95</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C81" t="n">
-        <v>72.2</v>
+        <v>76.5</v>
       </c>
       <c r="D81" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="E81" t="n">
-        <v>44.3</v>
+        <v>46.9</v>
       </c>
       <c r="F81" t="n">
-        <v>27.9</v>
+        <v>29.6</v>
       </c>
       <c r="G81" t="n">
-        <v>31.7</v>
+        <v>26</v>
       </c>
       <c r="H81" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I81" t="n">
-        <v>41.3</v>
+        <v>45.5</v>
       </c>
       <c r="J81" t="n">
-        <v>21.3</v>
+        <v>23.4</v>
       </c>
       <c r="K81" t="n">
-        <v>57.1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82">
@@ -4106,34 +4113,34 @@
         <v>96</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C82" t="n">
-        <v>76.5</v>
+        <v>78.6</v>
       </c>
       <c r="D82" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>46.9</v>
+        <v>78.6</v>
       </c>
       <c r="F82" t="n">
-        <v>29.6</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="H82" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="I82" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>23.4</v>
+        <v>37.5</v>
       </c>
       <c r="K82" t="n">
-        <v>48</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="83">
@@ -4141,34 +4148,34 @@
         <v>97</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C83" t="n">
-        <v>78.6</v>
+        <v>78.9</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="E83" t="n">
-        <v>78.6</v>
+        <v>48.2</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>30.7</v>
       </c>
       <c r="G83" t="n">
-        <v>5.3</v>
+        <v>25.7</v>
       </c>
       <c r="H83" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>43.5</v>
       </c>
       <c r="J83" t="n">
-        <v>37.5</v>
+        <v>27.2</v>
       </c>
       <c r="K83" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="84">
@@ -4176,34 +4183,34 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C84" t="n">
-        <v>78.9</v>
+        <v>73.8</v>
       </c>
       <c r="D84" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="E84" t="n">
-        <v>48.2</v>
+        <v>56</v>
       </c>
       <c r="F84" t="n">
-        <v>30.7</v>
+        <v>17.8</v>
       </c>
       <c r="G84" t="n">
-        <v>25.7</v>
+        <v>26.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I84" t="n">
-        <v>43.5</v>
+        <v>32.9</v>
       </c>
       <c r="J84" t="n">
-        <v>27.2</v>
+        <v>39.7</v>
       </c>
       <c r="K84" t="n">
-        <v>63.6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
@@ -4211,34 +4218,34 @@
         <v>99</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C85" t="n">
-        <v>73.8</v>
+        <v>72.2</v>
       </c>
       <c r="D85" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="E85" t="n">
-        <v>56</v>
+        <v>50.9</v>
       </c>
       <c r="F85" t="n">
-        <v>17.8</v>
+        <v>21.3</v>
       </c>
       <c r="G85" t="n">
-        <v>26.6</v>
+        <v>30</v>
       </c>
       <c r="H85" t="n">
-        <v>11.3</v>
+        <v>6.8</v>
       </c>
       <c r="I85" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="J85" t="n">
-        <v>39.7</v>
+        <v>24.5</v>
       </c>
       <c r="K85" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
@@ -4246,34 +4253,34 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C86" t="n">
-        <v>72.2</v>
+        <v>40</v>
       </c>
       <c r="D86" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
-        <v>50.9</v>
+        <v>15</v>
       </c>
       <c r="F86" t="n">
-        <v>21.3</v>
+        <v>25</v>
       </c>
       <c r="G86" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>6.8</v>
+        <v>21.1</v>
       </c>
       <c r="I86" t="n">
-        <v>42.9</v>
+        <v>62.5</v>
       </c>
       <c r="J86" t="n">
-        <v>24.5</v>
+        <v>12.5</v>
       </c>
       <c r="K86" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87">
@@ -4281,34 +4288,34 @@
         <v>101</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87" t="n">
-        <v>40</v>
+        <v>70.8</v>
       </c>
       <c r="D87" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="E87" t="n">
-        <v>15</v>
+        <v>44.1</v>
       </c>
       <c r="F87" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
       <c r="G87" t="n">
-        <v>36</v>
+        <v>18.4</v>
       </c>
       <c r="H87" t="n">
-        <v>21.1</v>
+        <v>6.9</v>
       </c>
       <c r="I87" t="n">
-        <v>62.5</v>
+        <v>54.3</v>
       </c>
       <c r="J87" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="K87" t="n">
-        <v>50</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="88">
@@ -4316,34 +4323,34 @@
         <v>102</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88" t="n">
-        <v>70.8</v>
+        <v>72.5</v>
       </c>
       <c r="D88" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="E88" t="n">
-        <v>44.1</v>
+        <v>40.1</v>
       </c>
       <c r="F88" t="n">
-        <v>26.7</v>
+        <v>32.4</v>
       </c>
       <c r="G88" t="n">
-        <v>18.4</v>
+        <v>26</v>
       </c>
       <c r="H88" t="n">
-        <v>6.9</v>
+        <v>9.3</v>
       </c>
       <c r="I88" t="n">
-        <v>54.3</v>
+        <v>44.4</v>
       </c>
       <c r="J88" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="K88" t="n">
-        <v>39.5</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="89">
@@ -4351,34 +4358,34 @@
         <v>103</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>72.5</v>
+        <v>83.3</v>
       </c>
       <c r="D89" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="E89" t="n">
-        <v>40.1</v>
+        <v>56</v>
       </c>
       <c r="F89" t="n">
-        <v>32.4</v>
+        <v>27.3</v>
       </c>
       <c r="G89" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="H89" t="n">
-        <v>9.3</v>
+        <v>20</v>
       </c>
       <c r="I89" t="n">
-        <v>44.4</v>
+        <v>70</v>
       </c>
       <c r="J89" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="K89" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
@@ -4386,34 +4393,34 @@
         <v>104</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C90" t="n">
-        <v>83.3</v>
+        <v>65.2</v>
       </c>
       <c r="D90" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="E90" t="n">
-        <v>56</v>
+        <v>50.7</v>
       </c>
       <c r="F90" t="n">
-        <v>27.3</v>
+        <v>14.5</v>
       </c>
       <c r="G90" t="n">
-        <v>26.1</v>
+        <v>21.2</v>
       </c>
       <c r="H90" t="n">
-        <v>20</v>
+        <v>12.1</v>
       </c>
       <c r="I90" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="J90" t="n">
-        <v>10</v>
+        <v>14.1</v>
       </c>
       <c r="K90" t="n">
-        <v>40</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="91">
@@ -4421,34 +4428,34 @@
         <v>105</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C91" t="n">
-        <v>65.2</v>
+        <v>53.6</v>
       </c>
       <c r="D91" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="E91" t="n">
-        <v>50.7</v>
+        <v>38</v>
       </c>
       <c r="F91" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="G91" t="n">
-        <v>21.2</v>
+        <v>30.9</v>
       </c>
       <c r="H91" t="n">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
       <c r="I91" t="n">
-        <v>62</v>
+        <v>67.7</v>
       </c>
       <c r="J91" t="n">
-        <v>14.1</v>
+        <v>25.8</v>
       </c>
       <c r="K91" t="n">
-        <v>42.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="92">
@@ -4456,57 +4463,51 @@
         <v>106</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C92" t="n">
-        <v>53.6</v>
+        <v>50</v>
       </c>
       <c r="D92" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>15.6</v>
+        <v>50</v>
       </c>
       <c r="G92" t="n">
-        <v>30.9</v>
+        <v>100</v>
       </c>
       <c r="H92" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I92" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="J92" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="K92" t="n">
-        <v>26.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I92"/>
+      <c r="J92"/>
+      <c r="K92"/>
     </row>
     <row r="93">
       <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" t="s">
         <v>107</v>
       </c>
-      <c r="B93" t="s">
-        <v>108</v>
-      </c>
       <c r="C93" t="n">
+        <v>100</v>
+      </c>
+      <c r="D93" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G93" t="n">
         <v>50</v>
-      </c>
-      <c r="D93" t="n">
-        <v>50</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="n">
-        <v>50</v>
-      </c>
-      <c r="G93" t="n">
-        <v>100</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4517,66 +4518,72 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>109</v>
+        <v>37</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C94" t="n">
-        <v>100</v>
+        <v>57.8</v>
       </c>
       <c r="D94" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="E94" t="n">
-        <v>66.7</v>
+        <v>47</v>
       </c>
       <c r="F94" t="n">
-        <v>33.3</v>
+        <v>10.8</v>
       </c>
       <c r="G94" t="n">
-        <v>50</v>
+        <v>25.4</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94"/>
-      <c r="J94"/>
-      <c r="K94"/>
+        <v>12.5</v>
+      </c>
+      <c r="I94" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J94" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="K94" t="n">
+        <v>45.5</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C95" t="n">
-        <v>57.8</v>
+        <v>71.4</v>
       </c>
       <c r="D95" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="E95" t="n">
-        <v>47</v>
+        <v>51.4</v>
       </c>
       <c r="F95" t="n">
-        <v>10.8</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>25.4</v>
+        <v>16.7</v>
       </c>
       <c r="H95" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="I95" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>27.3</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4584,34 +4591,34 @@
         <v>110</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C96" t="n">
-        <v>71.4</v>
+        <v>75</v>
       </c>
       <c r="D96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>51.4</v>
+        <v>75</v>
       </c>
       <c r="F96" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>16.7</v>
+        <v>40</v>
       </c>
       <c r="H96" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97">
@@ -4619,34 +4626,28 @@
         <v>111</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" t="n">
-        <v>75</v>
-      </c>
-      <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="n">
-        <v>75</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
       <c r="G97" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H97" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4654,28 +4655,34 @@
         <v>112</v>
       </c>
       <c r="B98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C98" t="n">
-        <v>50</v>
-      </c>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
+        <v>60</v>
+      </c>
+      <c r="D98" t="n">
+        <v>40</v>
+      </c>
+      <c r="E98" t="n">
+        <v>20</v>
+      </c>
+      <c r="F98" t="n">
+        <v>40</v>
+      </c>
       <c r="G98" t="n">
-        <v>50</v>
+        <v>28.8</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -4683,34 +4690,34 @@
         <v>113</v>
       </c>
       <c r="B99" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C99" t="n">
-        <v>60</v>
+        <v>75.9</v>
       </c>
       <c r="D99" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="E99" t="n">
-        <v>20</v>
+        <v>37.2</v>
       </c>
       <c r="F99" t="n">
-        <v>40</v>
+        <v>38.7</v>
       </c>
       <c r="G99" t="n">
-        <v>28.8</v>
+        <v>42.4</v>
       </c>
       <c r="H99" t="n">
-        <v>2.8</v>
+        <v>9.4</v>
       </c>
       <c r="I99" t="n">
-        <v>39.1</v>
+        <v>54.3</v>
       </c>
       <c r="J99" t="n">
-        <v>26.1</v>
+        <v>14.3</v>
       </c>
       <c r="K99" t="n">
-        <v>13</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="100">
@@ -4718,34 +4725,34 @@
         <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C100" t="n">
-        <v>75.9</v>
+        <v>73.2</v>
       </c>
       <c r="D100" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="E100" t="n">
-        <v>37.2</v>
+        <v>51.2</v>
       </c>
       <c r="F100" t="n">
-        <v>38.7</v>
+        <v>22</v>
       </c>
       <c r="G100" t="n">
-        <v>42.4</v>
+        <v>14.7</v>
       </c>
       <c r="H100" t="n">
-        <v>9.4</v>
+        <v>8.1</v>
       </c>
       <c r="I100" t="n">
-        <v>54.3</v>
+        <v>45.5</v>
       </c>
       <c r="J100" t="n">
-        <v>14.3</v>
+        <v>19.5</v>
       </c>
       <c r="K100" t="n">
-        <v>38.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="101">
@@ -4753,34 +4760,34 @@
         <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C101" t="n">
-        <v>73.2</v>
+        <v>65.5</v>
       </c>
       <c r="D101" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="E101" t="n">
-        <v>51.2</v>
+        <v>55.8</v>
       </c>
       <c r="F101" t="n">
-        <v>22</v>
+        <v>9.7</v>
       </c>
       <c r="G101" t="n">
-        <v>14.7</v>
+        <v>31.4</v>
       </c>
       <c r="H101" t="n">
-        <v>8.1</v>
+        <v>21.8</v>
       </c>
       <c r="I101" t="n">
-        <v>45.5</v>
+        <v>28.3</v>
       </c>
       <c r="J101" t="n">
-        <v>19.5</v>
+        <v>35</v>
       </c>
       <c r="K101" t="n">
-        <v>27.6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102">
@@ -4788,34 +4795,34 @@
         <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C102" t="n">
-        <v>65.5</v>
+        <v>66.7</v>
       </c>
       <c r="D102" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="E102" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="F102" t="n">
-        <v>9.7</v>
+        <v>18.2</v>
       </c>
       <c r="G102" t="n">
-        <v>31.4</v>
+        <v>46.7</v>
       </c>
       <c r="H102" t="n">
-        <v>21.8</v>
+        <v>33.3</v>
       </c>
       <c r="I102" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>39</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="103">
@@ -4823,25 +4830,25 @@
         <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C103" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="D103" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="E103" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="F103" t="n">
-        <v>18.2</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>46.7</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
@@ -4850,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -4858,34 +4865,26 @@
         <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>108</v>
-      </c>
-      <c r="C104" t="n">
+        <v>107</v>
+      </c>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
         <v>100</v>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
         <v>100</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4893,26 +4892,34 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>108</v>
-      </c>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
+        <v>107</v>
+      </c>
+      <c r="C105" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E105" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>25.2</v>
+      </c>
       <c r="G105" t="n">
-        <v>16.7</v>
+        <v>22.7</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I105" t="n">
-        <v>100</v>
+        <v>43.8</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>28.7</v>
       </c>
       <c r="K105" t="n">
-        <v>100</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="106">
@@ -4920,34 +4927,34 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C106" t="n">
-        <v>71.7</v>
+        <v>80</v>
       </c>
       <c r="D106" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="E106" t="n">
-        <v>46.5</v>
+        <v>51.1</v>
       </c>
       <c r="F106" t="n">
-        <v>25.2</v>
+        <v>28.9</v>
       </c>
       <c r="G106" t="n">
-        <v>22.7</v>
+        <v>35.1</v>
       </c>
       <c r="H106" t="n">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="I106" t="n">
-        <v>43.8</v>
+        <v>36.1</v>
       </c>
       <c r="J106" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="K106" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="107">
@@ -4955,34 +4962,34 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C107" t="n">
-        <v>80</v>
+        <v>71.4</v>
       </c>
       <c r="D107" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="E107" t="n">
-        <v>54.2</v>
+        <v>35.7</v>
       </c>
       <c r="F107" t="n">
-        <v>25.8</v>
+        <v>35.7</v>
       </c>
       <c r="G107" t="n">
-        <v>33.9</v>
+        <v>5.3</v>
       </c>
       <c r="H107" t="n">
-        <v>7.9</v>
+        <v>5.9</v>
       </c>
       <c r="I107" t="n">
-        <v>33.9</v>
+        <v>42.9</v>
       </c>
       <c r="J107" t="n">
-        <v>32.2</v>
+        <v>14.3</v>
       </c>
       <c r="K107" t="n">
-        <v>49.2</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="108">
@@ -4990,34 +4997,34 @@
         <v>122</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C108" t="n">
-        <v>80</v>
+        <v>59.1</v>
       </c>
       <c r="D108" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="E108" t="n">
-        <v>-20</v>
+        <v>40.6</v>
       </c>
       <c r="F108" t="n">
-        <v>100</v>
+        <v>18.5</v>
       </c>
       <c r="G108" t="n">
-        <v>54.5</v>
+        <v>31.2</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I108" t="n">
-        <v>100</v>
+        <v>34.6</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>34.6</v>
       </c>
       <c r="K108" t="n">
-        <v>50</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="109">
@@ -5025,34 +5032,34 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C109" t="n">
-        <v>71.4</v>
+        <v>79.8</v>
       </c>
       <c r="D109" t="n">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="E109" t="n">
-        <v>35.7</v>
+        <v>53.1</v>
       </c>
       <c r="F109" t="n">
-        <v>35.7</v>
+        <v>26.7</v>
       </c>
       <c r="G109" t="n">
-        <v>5.3</v>
+        <v>35.4</v>
       </c>
       <c r="H109" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="I109" t="n">
-        <v>42.9</v>
+        <v>39.3</v>
       </c>
       <c r="J109" t="n">
-        <v>14.3</v>
+        <v>28.6</v>
       </c>
       <c r="K109" t="n">
-        <v>33.3</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="110">
@@ -5060,34 +5067,34 @@
         <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C110" t="n">
-        <v>59.1</v>
+        <v>66.2</v>
       </c>
       <c r="D110" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="E110" t="n">
-        <v>40.6</v>
+        <v>49.6</v>
       </c>
       <c r="F110" t="n">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="G110" t="n">
-        <v>31.2</v>
+        <v>17.2</v>
       </c>
       <c r="H110" t="n">
-        <v>4.2</v>
+        <v>10.2</v>
       </c>
       <c r="I110" t="n">
-        <v>34.6</v>
+        <v>39.8</v>
       </c>
       <c r="J110" t="n">
-        <v>34.6</v>
+        <v>21.5</v>
       </c>
       <c r="K110" t="n">
-        <v>42.3</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="111">
@@ -5095,34 +5102,34 @@
         <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C111" t="n">
-        <v>79.8</v>
+        <v>57.8</v>
       </c>
       <c r="D111" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E111" t="n">
-        <v>53.1</v>
+        <v>35.6</v>
       </c>
       <c r="F111" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="G111" t="n">
-        <v>35.4</v>
+        <v>18.9</v>
       </c>
       <c r="H111" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="I111" t="n">
-        <v>39.3</v>
+        <v>41.6</v>
       </c>
       <c r="J111" t="n">
-        <v>28.6</v>
+        <v>23.4</v>
       </c>
       <c r="K111" t="n">
-        <v>39.3</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="112">
@@ -5130,34 +5137,34 @@
         <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" t="n">
-        <v>66.2</v>
+        <v>66</v>
       </c>
       <c r="D112" t="n">
-        <v>16.6</v>
+        <v>15.7</v>
       </c>
       <c r="E112" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="F112" t="n">
-        <v>16.6</v>
+        <v>15.7</v>
       </c>
       <c r="G112" t="n">
-        <v>17.2</v>
+        <v>25.1</v>
       </c>
       <c r="H112" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="I112" t="n">
-        <v>39.8</v>
+        <v>53.3</v>
       </c>
       <c r="J112" t="n">
-        <v>21.5</v>
+        <v>26.7</v>
       </c>
       <c r="K112" t="n">
-        <v>45.7</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="113">
@@ -5165,104 +5172,96 @@
         <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C113" t="n">
-        <v>57.8</v>
+        <v>66.2</v>
       </c>
       <c r="D113" t="n">
-        <v>22.2</v>
+        <v>36.1</v>
       </c>
       <c r="E113" t="n">
-        <v>35.6</v>
+        <v>30.1</v>
       </c>
       <c r="F113" t="n">
-        <v>22.2</v>
+        <v>36.1</v>
       </c>
       <c r="G113" t="n">
-        <v>18.9</v>
+        <v>27.9</v>
       </c>
       <c r="H113" t="n">
-        <v>11.2</v>
+        <v>7.9</v>
       </c>
       <c r="I113" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="J113" t="n">
-        <v>23.4</v>
+        <v>33.3</v>
       </c>
       <c r="K113" t="n">
-        <v>40.3</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" t="s">
         <v>128</v>
       </c>
-      <c r="B114" t="s">
-        <v>108</v>
-      </c>
-      <c r="C114" t="n">
-        <v>66</v>
-      </c>
-      <c r="D114" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="E114" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="F114" t="n">
-        <v>15.7</v>
-      </c>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
       <c r="G114" t="n">
-        <v>25.1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="J114" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="K114" t="n">
-        <v>51.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C115" t="n">
-        <v>66.2</v>
+        <v>80</v>
       </c>
       <c r="D115" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>30.1</v>
+        <v>80</v>
       </c>
       <c r="F115" t="n">
-        <v>36.1</v>
+        <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>27.9</v>
+        <v>25</v>
       </c>
       <c r="H115" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="K115" t="n">
-        <v>48.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5270,26 +5269,34 @@
         <v>131</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
-      </c>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
+        <v>128</v>
+      </c>
+      <c r="C116" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D116" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E116" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="F116" t="n">
+        <v>21.9</v>
+      </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>9.8</v>
       </c>
       <c r="I116" t="n">
-        <v>33.3</v>
+        <v>39.3</v>
       </c>
       <c r="J116" t="n">
-        <v>33.3</v>
+        <v>31.1</v>
       </c>
       <c r="K116" t="n">
-        <v>33.3</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="117">
@@ -5297,34 +5304,34 @@
         <v>132</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C117" t="n">
-        <v>80</v>
+        <v>68.2</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="E117" t="n">
-        <v>80</v>
+        <v>43.7</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="G117" t="n">
-        <v>25</v>
+        <v>29.5</v>
       </c>
       <c r="H117" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>43.6</v>
       </c>
       <c r="J117" t="n">
-        <v>100</v>
+        <v>25.5</v>
       </c>
       <c r="K117" t="n">
-        <v>0</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="118">
@@ -5332,34 +5339,34 @@
         <v>133</v>
       </c>
       <c r="B118" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C118" t="n">
-        <v>71.3</v>
+        <v>79.5</v>
       </c>
       <c r="D118" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="E118" t="n">
-        <v>49.4</v>
+        <v>47.6</v>
       </c>
       <c r="F118" t="n">
-        <v>21.9</v>
+        <v>31.9</v>
       </c>
       <c r="G118" t="n">
-        <v>14.4</v>
+        <v>25.8</v>
       </c>
       <c r="H118" t="n">
-        <v>9.8</v>
+        <v>6</v>
       </c>
       <c r="I118" t="n">
-        <v>39.3</v>
+        <v>42.7</v>
       </c>
       <c r="J118" t="n">
-        <v>31.1</v>
+        <v>25.6</v>
       </c>
       <c r="K118" t="n">
-        <v>50.8</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="119">
@@ -5367,34 +5374,34 @@
         <v>134</v>
       </c>
       <c r="B119" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C119" t="n">
-        <v>68.2</v>
+        <v>59.2</v>
       </c>
       <c r="D119" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="E119" t="n">
-        <v>43.7</v>
+        <v>35.7</v>
       </c>
       <c r="F119" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="G119" t="n">
-        <v>29.5</v>
+        <v>23.2</v>
       </c>
       <c r="H119" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="I119" t="n">
-        <v>43.6</v>
+        <v>62.3</v>
       </c>
       <c r="J119" t="n">
-        <v>25.5</v>
+        <v>15.1</v>
       </c>
       <c r="K119" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="120">
@@ -5402,34 +5409,34 @@
         <v>135</v>
       </c>
       <c r="B120" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C120" t="n">
-        <v>79.5</v>
+        <v>54.7</v>
       </c>
       <c r="D120" t="n">
-        <v>31.9</v>
+        <v>19.6</v>
       </c>
       <c r="E120" t="n">
-        <v>47.6</v>
+        <v>35.1</v>
       </c>
       <c r="F120" t="n">
-        <v>31.9</v>
+        <v>19.6</v>
       </c>
       <c r="G120" t="n">
-        <v>25.8</v>
+        <v>9.5</v>
       </c>
       <c r="H120" t="n">
-        <v>6</v>
+        <v>11.6</v>
       </c>
       <c r="I120" t="n">
-        <v>42.7</v>
+        <v>63.4</v>
       </c>
       <c r="J120" t="n">
-        <v>25.6</v>
+        <v>11.8</v>
       </c>
       <c r="K120" t="n">
-        <v>30.9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121">
@@ -5437,34 +5444,34 @@
         <v>136</v>
       </c>
       <c r="B121" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C121" t="n">
-        <v>59.2</v>
+        <v>80</v>
       </c>
       <c r="D121" t="n">
-        <v>23.5</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="n">
-        <v>35.7</v>
+        <v>68.9</v>
       </c>
       <c r="F121" t="n">
-        <v>23.5</v>
+        <v>11.1</v>
       </c>
       <c r="G121" t="n">
-        <v>23.2</v>
+        <v>39.5</v>
       </c>
       <c r="H121" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I121" t="n">
-        <v>62.3</v>
+        <v>63.6</v>
       </c>
       <c r="J121" t="n">
-        <v>15.1</v>
+        <v>9.1</v>
       </c>
       <c r="K121" t="n">
-        <v>47.2</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="122">
@@ -5472,34 +5479,34 @@
         <v>137</v>
       </c>
       <c r="B122" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C122" t="n">
-        <v>54.7</v>
+        <v>70.6</v>
       </c>
       <c r="D122" t="n">
-        <v>19.6</v>
+        <v>28.7</v>
       </c>
       <c r="E122" t="n">
-        <v>35.1</v>
+        <v>41.9</v>
       </c>
       <c r="F122" t="n">
-        <v>19.6</v>
+        <v>28.7</v>
       </c>
       <c r="G122" t="n">
-        <v>9.5</v>
+        <v>21.8</v>
       </c>
       <c r="H122" t="n">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
       <c r="I122" t="n">
-        <v>63.4</v>
+        <v>39.6</v>
       </c>
       <c r="J122" t="n">
-        <v>11.8</v>
+        <v>31.5</v>
       </c>
       <c r="K122" t="n">
-        <v>25</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="123">
@@ -5507,34 +5514,34 @@
         <v>138</v>
       </c>
       <c r="B123" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C123" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="E123" t="n">
-        <v>68.9</v>
+        <v>43.3</v>
       </c>
       <c r="F123" t="n">
-        <v>11.1</v>
+        <v>26.7</v>
       </c>
       <c r="G123" t="n">
-        <v>39.5</v>
+        <v>14.8</v>
       </c>
       <c r="H123" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I123" t="n">
+        <v>60</v>
+      </c>
+      <c r="J123" t="n">
+        <v>30</v>
+      </c>
+      <c r="K123" t="n">
         <v>10</v>
-      </c>
-      <c r="I123" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J123" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K123" t="n">
-        <v>45.5</v>
       </c>
     </row>
     <row r="124">
@@ -5542,34 +5549,34 @@
         <v>139</v>
       </c>
       <c r="B124" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C124" t="n">
-        <v>70.6</v>
+        <v>56.9</v>
       </c>
       <c r="D124" t="n">
-        <v>28.7</v>
+        <v>19.7</v>
       </c>
       <c r="E124" t="n">
-        <v>41.9</v>
+        <v>37.2</v>
       </c>
       <c r="F124" t="n">
-        <v>28.7</v>
+        <v>19.7</v>
       </c>
       <c r="G124" t="n">
-        <v>21.8</v>
+        <v>15.2</v>
       </c>
       <c r="H124" t="n">
-        <v>4.9</v>
+        <v>13.3</v>
       </c>
       <c r="I124" t="n">
-        <v>39.6</v>
+        <v>48.1</v>
       </c>
       <c r="J124" t="n">
-        <v>31.5</v>
+        <v>29.6</v>
       </c>
       <c r="K124" t="n">
-        <v>39.6</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="125">
@@ -5577,34 +5584,34 @@
         <v>140</v>
       </c>
       <c r="B125" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C125" t="n">
-        <v>70</v>
+        <v>72.6</v>
       </c>
       <c r="D125" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="E125" t="n">
-        <v>43.3</v>
+        <v>51.5</v>
       </c>
       <c r="F125" t="n">
-        <v>26.7</v>
+        <v>21.1</v>
       </c>
       <c r="G125" t="n">
-        <v>14.8</v>
+        <v>32.9</v>
       </c>
       <c r="H125" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="I125" t="n">
-        <v>60</v>
+        <v>48.6</v>
       </c>
       <c r="J125" t="n">
-        <v>30</v>
+        <v>18.9</v>
       </c>
       <c r="K125" t="n">
-        <v>10</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="126">
@@ -5612,34 +5619,34 @@
         <v>141</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C126" t="n">
-        <v>56.9</v>
+        <v>74.7</v>
       </c>
       <c r="D126" t="n">
-        <v>19.7</v>
+        <v>24.3</v>
       </c>
       <c r="E126" t="n">
-        <v>37.2</v>
+        <v>50.4</v>
       </c>
       <c r="F126" t="n">
-        <v>19.7</v>
+        <v>24.3</v>
       </c>
       <c r="G126" t="n">
-        <v>15.2</v>
+        <v>32</v>
       </c>
       <c r="H126" t="n">
-        <v>13.3</v>
+        <v>8.3</v>
       </c>
       <c r="I126" t="n">
-        <v>48.1</v>
+        <v>38.6</v>
       </c>
       <c r="J126" t="n">
-        <v>29.6</v>
+        <v>26.5</v>
       </c>
       <c r="K126" t="n">
-        <v>53.8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="127">
@@ -5647,34 +5654,34 @@
         <v>142</v>
       </c>
       <c r="B127" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C127" t="n">
-        <v>72.6</v>
+        <v>75.2</v>
       </c>
       <c r="D127" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="E127" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F127" t="n">
-        <v>21.1</v>
+        <v>23.1</v>
       </c>
       <c r="G127" t="n">
-        <v>32.9</v>
+        <v>24.8</v>
       </c>
       <c r="H127" t="n">
-        <v>12.9</v>
+        <v>8.2</v>
       </c>
       <c r="I127" t="n">
-        <v>48.6</v>
+        <v>41.1</v>
       </c>
       <c r="J127" t="n">
-        <v>18.9</v>
+        <v>33.7</v>
       </c>
       <c r="K127" t="n">
-        <v>41.3</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="128">
@@ -5682,34 +5689,34 @@
         <v>143</v>
       </c>
       <c r="B128" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C128" t="n">
-        <v>74.7</v>
+        <v>68.2</v>
       </c>
       <c r="D128" t="n">
-        <v>24.3</v>
+        <v>18.2</v>
       </c>
       <c r="E128" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F128" t="n">
-        <v>24.3</v>
+        <v>18.2</v>
       </c>
       <c r="G128" t="n">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="H128" t="n">
-        <v>8.3</v>
+        <v>11.9</v>
       </c>
       <c r="I128" t="n">
-        <v>38.6</v>
+        <v>48.3</v>
       </c>
       <c r="J128" t="n">
-        <v>26.5</v>
+        <v>17.2</v>
       </c>
       <c r="K128" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="129">
@@ -5717,104 +5724,104 @@
         <v>144</v>
       </c>
       <c r="B129" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C129" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
       <c r="D129" t="n">
         <v>23.1</v>
       </c>
       <c r="E129" t="n">
-        <v>52.1</v>
+        <v>48.9</v>
       </c>
       <c r="F129" t="n">
         <v>23.1</v>
       </c>
       <c r="G129" t="n">
-        <v>24.8</v>
+        <v>14.3</v>
       </c>
       <c r="H129" t="n">
-        <v>8.2</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>41.1</v>
+        <v>36.4</v>
       </c>
       <c r="J129" t="n">
-        <v>33.7</v>
+        <v>18.2</v>
       </c>
       <c r="K129" t="n">
-        <v>49.5</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
+        <v>146</v>
+      </c>
+      <c r="B130" t="s">
         <v>145</v>
       </c>
-      <c r="B130" t="s">
-        <v>130</v>
-      </c>
       <c r="C130" t="n">
-        <v>68.2</v>
+        <v>66.7</v>
       </c>
       <c r="D130" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="E130" t="n">
-        <v>50</v>
+        <v>6.7</v>
       </c>
       <c r="F130" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="G130" t="n">
-        <v>21.5</v>
+        <v>33.3</v>
       </c>
       <c r="H130" t="n">
-        <v>11.9</v>
+        <v>11.1</v>
       </c>
       <c r="I130" t="n">
-        <v>48.3</v>
+        <v>25</v>
       </c>
       <c r="J130" t="n">
-        <v>17.2</v>
+        <v>25</v>
       </c>
       <c r="K130" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B131" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C131" t="n">
-        <v>72</v>
+        <v>66.2</v>
       </c>
       <c r="D131" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
       <c r="E131" t="n">
-        <v>48.9</v>
+        <v>46.2</v>
       </c>
       <c r="F131" t="n">
-        <v>23.1</v>
+        <v>20</v>
       </c>
       <c r="G131" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I131" t="n">
-        <v>36.4</v>
+        <v>43.9</v>
       </c>
       <c r="J131" t="n">
-        <v>18.2</v>
+        <v>24.6</v>
       </c>
       <c r="K131" t="n">
-        <v>27.3</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="132">
@@ -5822,31 +5829,31 @@
         <v>148</v>
       </c>
       <c r="B132" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C132" t="n">
-        <v>66.7</v>
+        <v>35</v>
       </c>
       <c r="D132" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="E132" t="n">
-        <v>6.7</v>
+        <v>21.7</v>
       </c>
       <c r="F132" t="n">
-        <v>60</v>
+        <v>13.3</v>
       </c>
       <c r="G132" t="n">
         <v>33.3</v>
       </c>
       <c r="H132" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5857,34 +5864,34 @@
         <v>149</v>
       </c>
       <c r="B133" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C133" t="n">
-        <v>66.2</v>
+        <v>72.2</v>
       </c>
       <c r="D133" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E133" t="n">
-        <v>46.2</v>
+        <v>44.2</v>
       </c>
       <c r="F133" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G133" t="n">
-        <v>14.1</v>
+        <v>32.4</v>
       </c>
       <c r="H133" t="n">
-        <v>5.1</v>
+        <v>9.8</v>
       </c>
       <c r="I133" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="J133" t="n">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
       <c r="K133" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="134">
@@ -5892,31 +5899,25 @@
         <v>150</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C134" t="n">
-        <v>35</v>
-      </c>
-      <c r="D134" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E134" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F134" t="n">
-        <v>13.3</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
       <c r="G134" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
       </c>
       <c r="I134" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
@@ -5927,34 +5928,34 @@
         <v>151</v>
       </c>
       <c r="B135" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C135" t="n">
-        <v>72.2</v>
+        <v>74.5</v>
       </c>
       <c r="D135" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="E135" t="n">
-        <v>44.2</v>
+        <v>47.3</v>
       </c>
       <c r="F135" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="G135" t="n">
-        <v>32.4</v>
+        <v>30.8</v>
       </c>
       <c r="H135" t="n">
         <v>9.8</v>
       </c>
       <c r="I135" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="J135" t="n">
-        <v>23.7</v>
+        <v>26.3</v>
       </c>
       <c r="K135" t="n">
-        <v>42.1</v>
+        <v>39.3</v>
       </c>
     </row>
     <row r="136">
@@ -5962,28 +5963,34 @@
         <v>152</v>
       </c>
       <c r="B136" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C136" t="n">
-        <v>100</v>
-      </c>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
+        <v>48.1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>25</v>
+      </c>
+      <c r="E136" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="F136" t="n">
+        <v>25</v>
+      </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>44.4</v>
       </c>
       <c r="J136" t="n">
-        <v>100</v>
+        <v>22.2</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="137">
@@ -5991,34 +5998,34 @@
         <v>153</v>
       </c>
       <c r="B137" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C137" t="n">
-        <v>74.5</v>
+        <v>66</v>
       </c>
       <c r="D137" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="E137" t="n">
-        <v>47.3</v>
+        <v>41.7</v>
       </c>
       <c r="F137" t="n">
-        <v>27.2</v>
+        <v>24.3</v>
       </c>
       <c r="G137" t="n">
-        <v>30.8</v>
+        <v>21.9</v>
       </c>
       <c r="H137" t="n">
-        <v>9.8</v>
+        <v>7.7</v>
       </c>
       <c r="I137" t="n">
-        <v>47.4</v>
+        <v>54.3</v>
       </c>
       <c r="J137" t="n">
-        <v>26.3</v>
+        <v>15.7</v>
       </c>
       <c r="K137" t="n">
-        <v>39.3</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="138">
@@ -6026,34 +6033,34 @@
         <v>154</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C138" t="n">
-        <v>48.1</v>
+        <v>66.7</v>
       </c>
       <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>75</v>
+      </c>
+      <c r="J138" t="n">
         <v>25</v>
       </c>
-      <c r="E138" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="F138" t="n">
-        <v>25</v>
-      </c>
-      <c r="G138" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="H138" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="I138" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J138" t="n">
-        <v>22.2</v>
-      </c>
       <c r="K138" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -6061,34 +6068,34 @@
         <v>155</v>
       </c>
       <c r="B139" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C139" t="n">
-        <v>66</v>
+        <v>72.2</v>
       </c>
       <c r="D139" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="E139" t="n">
-        <v>41.7</v>
+        <v>52.8</v>
       </c>
       <c r="F139" t="n">
-        <v>24.3</v>
+        <v>19.4</v>
       </c>
       <c r="G139" t="n">
-        <v>21.9</v>
+        <v>27.4</v>
       </c>
       <c r="H139" t="n">
-        <v>7.7</v>
+        <v>5.1</v>
       </c>
       <c r="I139" t="n">
-        <v>54.3</v>
+        <v>69.2</v>
       </c>
       <c r="J139" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>31.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="140">
@@ -6096,25 +6103,25 @@
         <v>156</v>
       </c>
       <c r="B140" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C140" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="E140" t="n">
-        <v>66.7</v>
+        <v>35.7</v>
       </c>
       <c r="F140" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G140" t="n">
-        <v>18.2</v>
+        <v>28.6</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I140" t="n">
         <v>75</v>
@@ -6123,7 +6130,7 @@
         <v>25</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="141">
@@ -6131,34 +6138,34 @@
         <v>157</v>
       </c>
       <c r="B141" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C141" t="n">
-        <v>72.2</v>
+        <v>68.5</v>
       </c>
       <c r="D141" t="n">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="E141" t="n">
-        <v>52.8</v>
+        <v>39.5</v>
       </c>
       <c r="F141" t="n">
-        <v>19.4</v>
+        <v>29</v>
       </c>
       <c r="G141" t="n">
-        <v>27.4</v>
+        <v>31.8</v>
       </c>
       <c r="H141" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I141" t="n">
-        <v>69.2</v>
+        <v>35.9</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="K141" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="142">
@@ -6166,139 +6173,139 @@
         <v>158</v>
       </c>
       <c r="B142" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D142" t="n">
-        <v>14.3</v>
+        <v>24</v>
       </c>
       <c r="E142" t="n">
-        <v>35.7</v>
+        <v>41.8</v>
       </c>
       <c r="F142" t="n">
-        <v>14.3</v>
+        <v>24</v>
       </c>
       <c r="G142" t="n">
-        <v>28.6</v>
+        <v>21.9</v>
       </c>
       <c r="H142" t="n">
-        <v>12.5</v>
+        <v>2.3</v>
       </c>
       <c r="I142" t="n">
-        <v>75</v>
+        <v>59.7</v>
       </c>
       <c r="J142" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="K142" t="n">
-        <v>50</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="B143" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C143" t="n">
-        <v>68.5</v>
+        <v>56.1</v>
       </c>
       <c r="D143" t="n">
-        <v>29</v>
+        <v>19.2</v>
       </c>
       <c r="E143" t="n">
-        <v>39.5</v>
+        <v>36.9</v>
       </c>
       <c r="F143" t="n">
-        <v>29</v>
+        <v>19.2</v>
       </c>
       <c r="G143" t="n">
-        <v>31.8</v>
+        <v>22.5</v>
       </c>
       <c r="H143" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>35.9</v>
+        <v>40.5</v>
       </c>
       <c r="J143" t="n">
-        <v>28.1</v>
+        <v>27</v>
       </c>
       <c r="K143" t="n">
-        <v>43.8</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B144" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C144" t="n">
-        <v>65.8</v>
+        <v>79.6</v>
       </c>
       <c r="D144" t="n">
-        <v>24</v>
+        <v>36.8</v>
       </c>
       <c r="E144" t="n">
-        <v>41.8</v>
+        <v>42.8</v>
       </c>
       <c r="F144" t="n">
-        <v>24</v>
+        <v>36.8</v>
       </c>
       <c r="G144" t="n">
-        <v>21.9</v>
+        <v>34.2</v>
       </c>
       <c r="H144" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="I144" t="n">
-        <v>59.7</v>
+        <v>44</v>
       </c>
       <c r="J144" t="n">
-        <v>23.9</v>
+        <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>30.3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
       <c r="B145" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C145" t="n">
-        <v>56.1</v>
+        <v>57.8</v>
       </c>
       <c r="D145" t="n">
-        <v>19.2</v>
+        <v>14.1</v>
       </c>
       <c r="E145" t="n">
-        <v>36.9</v>
+        <v>43.7</v>
       </c>
       <c r="F145" t="n">
-        <v>19.2</v>
+        <v>14.1</v>
       </c>
       <c r="G145" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>10.2</v>
       </c>
       <c r="I145" t="n">
-        <v>40.5</v>
+        <v>52.8</v>
       </c>
       <c r="J145" t="n">
-        <v>27</v>
+        <v>9.7</v>
       </c>
       <c r="K145" t="n">
-        <v>40.5</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="146">
@@ -6306,34 +6313,34 @@
         <v>161</v>
       </c>
       <c r="B146" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>79.6</v>
+        <v>63.2</v>
       </c>
       <c r="D146" t="n">
-        <v>36.8</v>
+        <v>45</v>
       </c>
       <c r="E146" t="n">
-        <v>42.8</v>
+        <v>18.2</v>
       </c>
       <c r="F146" t="n">
-        <v>36.8</v>
+        <v>45</v>
       </c>
       <c r="G146" t="n">
-        <v>34.2</v>
+        <v>26.9</v>
       </c>
       <c r="H146" t="n">
-        <v>2.9</v>
+        <v>7.7</v>
       </c>
       <c r="I146" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K146" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147">
@@ -6341,34 +6348,34 @@
         <v>162</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C147" t="n">
-        <v>57.8</v>
+        <v>74.2</v>
       </c>
       <c r="D147" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="E147" t="n">
-        <v>43.7</v>
+        <v>62.1</v>
       </c>
       <c r="F147" t="n">
-        <v>14.1</v>
+        <v>12.1</v>
       </c>
       <c r="G147" t="n">
-        <v>12.5</v>
+        <v>23.4</v>
       </c>
       <c r="H147" t="n">
-        <v>10.2</v>
+        <v>14.8</v>
       </c>
       <c r="I147" t="n">
-        <v>52.8</v>
+        <v>32.9</v>
       </c>
       <c r="J147" t="n">
-        <v>9.7</v>
+        <v>37</v>
       </c>
       <c r="K147" t="n">
-        <v>35.7</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="148">
@@ -6376,34 +6383,34 @@
         <v>163</v>
       </c>
       <c r="B148" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C148" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D148" t="n">
-        <v>45</v>
+        <v>26.1</v>
       </c>
       <c r="E148" t="n">
-        <v>18.2</v>
+        <v>48.1</v>
       </c>
       <c r="F148" t="n">
-        <v>45</v>
+        <v>26.1</v>
       </c>
       <c r="G148" t="n">
-        <v>26.9</v>
+        <v>9.2</v>
       </c>
       <c r="H148" t="n">
-        <v>7.7</v>
+        <v>2.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="J148" t="n">
-        <v>25</v>
+        <v>20.8</v>
       </c>
       <c r="K148" t="n">
-        <v>25</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="149">
@@ -6411,104 +6418,104 @@
         <v>164</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C149" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D149" t="n">
-        <v>12.1</v>
+        <v>20.5</v>
       </c>
       <c r="E149" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="F149" t="n">
-        <v>12.1</v>
+        <v>20.5</v>
       </c>
       <c r="G149" t="n">
-        <v>23.4</v>
+        <v>37.7</v>
       </c>
       <c r="H149" t="n">
-        <v>14.8</v>
+        <v>9.2</v>
       </c>
       <c r="I149" t="n">
-        <v>32.9</v>
+        <v>51.9</v>
       </c>
       <c r="J149" t="n">
-        <v>37</v>
+        <v>21.2</v>
       </c>
       <c r="K149" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
+        <v>166</v>
+      </c>
+      <c r="B150" t="s">
         <v>165</v>
       </c>
-      <c r="B150" t="s">
-        <v>147</v>
-      </c>
       <c r="C150" t="n">
-        <v>74.2</v>
+        <v>68.6</v>
       </c>
       <c r="D150" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E150" t="n">
         <v>48.1</v>
       </c>
       <c r="F150" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G150" t="n">
-        <v>9.2</v>
+        <v>14.9</v>
       </c>
       <c r="H150" t="n">
-        <v>2.2</v>
+        <v>6.6</v>
       </c>
       <c r="I150" t="n">
-        <v>48.1</v>
+        <v>57.3</v>
       </c>
       <c r="J150" t="n">
-        <v>20.8</v>
+        <v>18.7</v>
       </c>
       <c r="K150" t="n">
-        <v>32.5</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C151" t="n">
-        <v>70.5</v>
+        <v>64.6</v>
       </c>
       <c r="D151" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E151" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="F151" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="G151" t="n">
         <v>37.7</v>
       </c>
       <c r="H151" t="n">
-        <v>9.2</v>
+        <v>12.5</v>
       </c>
       <c r="I151" t="n">
-        <v>51.9</v>
+        <v>29.6</v>
       </c>
       <c r="J151" t="n">
-        <v>21.2</v>
+        <v>48.1</v>
       </c>
       <c r="K151" t="n">
-        <v>39.1</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="152">
@@ -6516,34 +6523,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C152" t="n">
-        <v>68.6</v>
+        <v>60</v>
       </c>
       <c r="D152" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="E152" t="n">
-        <v>48.1</v>
+        <v>38.9</v>
       </c>
       <c r="F152" t="n">
-        <v>20.5</v>
+        <v>21.1</v>
       </c>
       <c r="G152" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="H152" t="n">
         <v>14.9</v>
       </c>
-      <c r="H152" t="n">
-        <v>6.6</v>
-      </c>
       <c r="I152" t="n">
-        <v>57.3</v>
+        <v>34.8</v>
       </c>
       <c r="J152" t="n">
-        <v>18.7</v>
+        <v>30.4</v>
       </c>
       <c r="K152" t="n">
-        <v>45.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="153">
@@ -6551,34 +6558,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C153" t="n">
-        <v>64.6</v>
+        <v>66.3</v>
       </c>
       <c r="D153" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E153" t="n">
-        <v>47.9</v>
+        <v>51.9</v>
       </c>
       <c r="F153" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="G153" t="n">
-        <v>37.7</v>
+        <v>9</v>
       </c>
       <c r="H153" t="n">
-        <v>12.5</v>
+        <v>18.2</v>
       </c>
       <c r="I153" t="n">
-        <v>29.6</v>
+        <v>62.2</v>
       </c>
       <c r="J153" t="n">
-        <v>48.1</v>
+        <v>17.3</v>
       </c>
       <c r="K153" t="n">
-        <v>38.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="154">
@@ -6586,34 +6593,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C154" t="n">
-        <v>60</v>
+        <v>80.4</v>
       </c>
       <c r="D154" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="E154" t="n">
-        <v>38.9</v>
+        <v>63.9</v>
       </c>
       <c r="F154" t="n">
-        <v>21.1</v>
+        <v>16.5</v>
       </c>
       <c r="G154" t="n">
-        <v>32.4</v>
+        <v>23.3</v>
       </c>
       <c r="H154" t="n">
-        <v>14.9</v>
+        <v>9.4</v>
       </c>
       <c r="I154" t="n">
-        <v>34.8</v>
+        <v>36.2</v>
       </c>
       <c r="J154" t="n">
-        <v>30.4</v>
+        <v>34</v>
       </c>
       <c r="K154" t="n">
-        <v>33.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="155">
@@ -6621,34 +6628,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C155" t="n">
-        <v>66.3</v>
+        <v>55.6</v>
       </c>
       <c r="D155" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="E155" t="n">
-        <v>51.9</v>
+        <v>38</v>
       </c>
       <c r="F155" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="G155" t="n">
-        <v>9</v>
+        <v>25.7</v>
       </c>
       <c r="H155" t="n">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="I155" t="n">
-        <v>62.2</v>
+        <v>47.4</v>
       </c>
       <c r="J155" t="n">
-        <v>17.3</v>
+        <v>22.8</v>
       </c>
       <c r="K155" t="n">
-        <v>36.2</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="156">
@@ -6656,34 +6663,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C156" t="n">
-        <v>80.4</v>
+        <v>75</v>
       </c>
       <c r="D156" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>63.9</v>
+        <v>75</v>
       </c>
       <c r="F156" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>23.3</v>
+        <v>66.7</v>
       </c>
       <c r="H156" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>36.2</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6691,34 +6698,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C157" t="n">
-        <v>55.6</v>
+        <v>56.2</v>
       </c>
       <c r="D157" t="n">
         <v>17.6</v>
       </c>
       <c r="E157" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="F157" t="n">
         <v>17.6</v>
       </c>
       <c r="G157" t="n">
-        <v>25.7</v>
+        <v>14.6</v>
       </c>
       <c r="H157" t="n">
-        <v>12.6</v>
+        <v>16.5</v>
       </c>
       <c r="I157" t="n">
-        <v>47.4</v>
+        <v>37</v>
       </c>
       <c r="J157" t="n">
-        <v>22.8</v>
+        <v>28.8</v>
       </c>
       <c r="K157" t="n">
-        <v>26.4</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="158">
@@ -6726,34 +6733,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C158" t="n">
-        <v>75</v>
+        <v>61.4</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="E158" t="n">
-        <v>75</v>
+        <v>40.6</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>20.8</v>
       </c>
       <c r="G158" t="n">
-        <v>66.7</v>
+        <v>9.8</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>60.4</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="159">
@@ -6761,34 +6768,34 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C159" t="n">
-        <v>56.2</v>
+        <v>71.5</v>
       </c>
       <c r="D159" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="E159" t="n">
-        <v>38.6</v>
+        <v>54.8</v>
       </c>
       <c r="F159" t="n">
-        <v>17.6</v>
+        <v>16.7</v>
       </c>
       <c r="G159" t="n">
-        <v>14.6</v>
+        <v>24.7</v>
       </c>
       <c r="H159" t="n">
-        <v>16.5</v>
+        <v>11.8</v>
       </c>
       <c r="I159" t="n">
-        <v>37</v>
+        <v>34.8</v>
       </c>
       <c r="J159" t="n">
-        <v>28.8</v>
+        <v>31.5</v>
       </c>
       <c r="K159" t="n">
-        <v>49.3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="160">
@@ -6796,34 +6803,34 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C160" t="n">
-        <v>61.4</v>
+        <v>77.2</v>
       </c>
       <c r="D160" t="n">
-        <v>20.8</v>
+        <v>29.9</v>
       </c>
       <c r="E160" t="n">
-        <v>40.6</v>
+        <v>47.3</v>
       </c>
       <c r="F160" t="n">
-        <v>20.8</v>
+        <v>29.9</v>
       </c>
       <c r="G160" t="n">
-        <v>9.8</v>
+        <v>41.7</v>
       </c>
       <c r="H160" t="n">
-        <v>8.5</v>
+        <v>6.9</v>
       </c>
       <c r="I160" t="n">
-        <v>60.4</v>
+        <v>44.4</v>
       </c>
       <c r="J160" t="n">
-        <v>18</v>
+        <v>22.2</v>
       </c>
       <c r="K160" t="n">
-        <v>29.2</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="161">
@@ -6831,34 +6838,34 @@
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C161" t="n">
-        <v>71.5</v>
+        <v>75.5</v>
       </c>
       <c r="D161" t="n">
-        <v>16.7</v>
+        <v>20.4</v>
       </c>
       <c r="E161" t="n">
-        <v>54.8</v>
+        <v>55.1</v>
       </c>
       <c r="F161" t="n">
-        <v>16.7</v>
+        <v>20.4</v>
       </c>
       <c r="G161" t="n">
-        <v>24.7</v>
+        <v>19.7</v>
       </c>
       <c r="H161" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="I161" t="n">
-        <v>34.8</v>
+        <v>27.9</v>
       </c>
       <c r="J161" t="n">
-        <v>31.5</v>
+        <v>33.7</v>
       </c>
       <c r="K161" t="n">
-        <v>56</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="162">
@@ -6866,160 +6873,90 @@
         <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C162" t="n">
-        <v>77.2</v>
+        <v>37.5</v>
       </c>
       <c r="D162" t="n">
-        <v>29.9</v>
+        <v>33.3</v>
       </c>
       <c r="E162" t="n">
-        <v>47.3</v>
+        <v>4.2</v>
       </c>
       <c r="F162" t="n">
-        <v>29.9</v>
+        <v>33.3</v>
       </c>
       <c r="G162" t="n">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="I162" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="J162" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="K162" t="n">
-        <v>66.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I162"/>
+      <c r="J162"/>
+      <c r="K162"/>
     </row>
     <row r="163">
       <c r="A163" t="s">
         <v>179</v>
       </c>
       <c r="B163" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C163" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E163" t="n">
-        <v>55.1</v>
+        <v>-33.3</v>
       </c>
       <c r="F163" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G163" t="n">
-        <v>19.7</v>
+        <v>100</v>
       </c>
       <c r="H163" t="n">
-        <v>11</v>
-      </c>
-      <c r="I163" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J163" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K163" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I163"/>
+      <c r="J163"/>
+      <c r="K163"/>
     </row>
     <row r="164">
-      <c r="A164" t="s">
+      <c r="A164"/>
+      <c r="B164" t="s">
         <v>180</v>
       </c>
-      <c r="B164" t="s">
-        <v>167</v>
-      </c>
       <c r="C164" t="n">
-        <v>37.5</v>
+        <v>68</v>
       </c>
       <c r="D164" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="E164" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="F164" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164"/>
-      <c r="J164"/>
-      <c r="K164"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>181</v>
-      </c>
-      <c r="B165" t="s">
-        <v>167</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0</v>
-      </c>
-      <c r="D165" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E165" t="n">
-        <v>-33.3</v>
-      </c>
-      <c r="F165" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="G165" t="n">
-        <v>100</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165"/>
-      <c r="J165"/>
-      <c r="K165"/>
-    </row>
-    <row r="166">
-      <c r="A166"/>
-      <c r="B166" t="s">
-        <v>182</v>
-      </c>
-      <c r="C166" t="n">
-        <v>68.1</v>
-      </c>
-      <c r="D166" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="E166" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="F166" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="G166" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="H166" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I166" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="J166" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="K166" t="n">
-        <v>39.4</v>
+        <v>9.5</v>
+      </c>
+      <c r="I164" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="J164" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="K164" t="n">
+        <v>39.3</v>
       </c>
     </row>
   </sheetData>
@@ -7051,22 +6988,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7075,18 +7012,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7121,7 +7058,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7156,7 +7093,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7226,7 +7163,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7261,7 +7198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7296,7 +7233,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
@@ -7331,7 +7268,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -7366,7 +7303,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -7436,7 +7373,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
@@ -7471,7 +7408,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
@@ -7506,7 +7443,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
@@ -7541,7 +7478,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
@@ -7576,7 +7513,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
@@ -7644,7 +7581,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
@@ -7679,7 +7616,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
@@ -7714,7 +7651,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
@@ -7784,7 +7721,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
@@ -7819,7 +7756,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
@@ -7854,7 +7791,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
@@ -7889,7 +7826,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
@@ -7924,7 +7861,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
@@ -7959,7 +7896,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
@@ -7994,7 +7931,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -8029,7 +7966,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
@@ -8064,7 +8001,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
@@ -8099,7 +8036,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
@@ -8134,7 +8071,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
@@ -8169,7 +8106,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -8204,10 +8141,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C34" t="n">
         <v>78.6</v>
@@ -8239,10 +8176,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" t="n">
         <v>52.5</v>
@@ -8274,10 +8211,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C36" t="n">
         <v>45.8</v>
@@ -8309,10 +8246,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" t="n">
         <v>52.9</v>
@@ -8344,10 +8281,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C38" t="n">
         <v>47.8</v>
@@ -8379,10 +8316,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" t="n">
         <v>48.8</v>
@@ -8414,10 +8351,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" t="n">
         <v>59</v>
@@ -8449,10 +8386,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41" t="n">
         <v>54.8</v>
@@ -8484,10 +8421,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C42" t="n">
         <v>100</v>
@@ -8517,10 +8454,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>66.3</v>
@@ -8552,10 +8489,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C44" t="n">
         <v>57</v>
@@ -8587,10 +8524,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C45" t="n">
         <v>60.4</v>
@@ -8622,10 +8559,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C46" t="n">
         <v>55.4</v>
@@ -8657,10 +8594,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C47" t="n">
         <v>81.2</v>
@@ -8692,10 +8629,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" t="n">
         <v>58</v>
@@ -8727,10 +8664,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C49" t="n">
         <v>44.4</v>
@@ -8760,10 +8697,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
         <v>51.8</v>
@@ -8795,10 +8732,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C51" t="n">
         <v>60</v>
@@ -8830,10 +8767,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C52" t="n">
         <v>70.9</v>
@@ -8865,10 +8802,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C53" t="n">
         <v>60.6</v>
@@ -8900,10 +8837,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
         <v>66.7</v>
@@ -8933,10 +8870,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C55" t="n">
         <v>77.8</v>
@@ -8968,10 +8905,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C56" t="n">
         <v>65.6</v>
@@ -9003,10 +8940,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" t="n">
         <v>57.3</v>
@@ -9038,10 +8975,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C58" t="n">
         <v>67.6</v>
@@ -9073,10 +9010,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" t="n">
         <v>61.1</v>
@@ -9108,10 +9045,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" t="n">
         <v>62</v>
@@ -9143,10 +9080,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C61" t="n">
         <v>56.5</v>
@@ -9178,10 +9115,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C62" t="n">
         <v>65.7</v>
@@ -9213,10 +9150,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C63" t="n">
         <v>62.3</v>
@@ -9248,10 +9185,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C64" t="n">
         <v>30</v>
@@ -9283,10 +9220,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" t="n">
         <v>44.4</v>
@@ -9318,10 +9255,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" t="n">
         <v>62.5</v>
@@ -9353,10 +9290,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C67" t="n">
         <v>72.4</v>
@@ -9388,10 +9325,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C68" t="n">
         <v>66.7</v>
@@ -9423,10 +9360,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C69" t="n">
         <v>50</v>
@@ -9458,10 +9395,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C70" t="n">
         <v>55.6</v>
@@ -9493,10 +9430,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C71" t="n">
         <v>54.8</v>
@@ -9528,10 +9465,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C72" t="n">
         <v>61.1</v>
@@ -9563,10 +9500,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C73" t="n">
         <v>63.8</v>
@@ -9598,10 +9535,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C74" t="n">
         <v>51.6</v>
@@ -9633,10 +9570,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C75" t="n">
         <v>58.8</v>
@@ -9668,10 +9605,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C76" t="n">
         <v>69.4</v>
@@ -9703,10 +9640,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" t="n">
         <v>60.3</v>
@@ -9738,10 +9675,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C78" t="n">
         <v>61.5</v>
@@ -9773,10 +9710,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C79" t="n">
         <v>42</v>
@@ -9808,10 +9745,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" t="n">
         <v>64.6</v>
@@ -9843,10 +9780,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" t="n">
         <v>50</v>
@@ -9878,10 +9815,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C82" t="n">
         <v>28.6</v>
@@ -9911,10 +9848,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C83" t="n">
         <v>63.6</v>
@@ -9946,10 +9883,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" t="n">
         <v>48.6</v>
@@ -9981,10 +9918,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" t="n">
         <v>57.6</v>
@@ -10016,1780 +9953,1745 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C86" t="n">
-        <v>71.4</v>
+        <v>61.6</v>
       </c>
       <c r="D86" t="n">
-        <v>70.6</v>
+        <v>66.2</v>
       </c>
       <c r="E86" t="n">
-        <v>22.2</v>
+        <v>26.6</v>
       </c>
       <c r="F86" t="n">
-        <v>28.6</v>
+        <v>37.4</v>
       </c>
       <c r="G86" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="H86" t="n">
-        <v>45.5</v>
+        <v>44.6</v>
       </c>
       <c r="I86" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J86" t="n">
-        <v>10.7</v>
+        <v>21.4</v>
       </c>
       <c r="K86" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" t="n">
-        <v>61</v>
+        <v>45.8</v>
       </c>
       <c r="D87" t="n">
-        <v>65.9</v>
+        <v>55.1</v>
       </c>
       <c r="E87" t="n">
-        <v>27</v>
+        <v>10.4</v>
       </c>
       <c r="F87" t="n">
-        <v>38</v>
+        <v>26.3</v>
       </c>
       <c r="G87" t="n">
-        <v>5.6</v>
+        <v>15.3</v>
       </c>
       <c r="H87" t="n">
-        <v>44.5</v>
+        <v>47.1</v>
       </c>
       <c r="I87" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="J87" t="n">
-        <v>22.2</v>
+        <v>33.9</v>
       </c>
       <c r="K87" t="n">
-        <v>10.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
       <c r="D88" t="n">
-        <v>55.1</v>
+        <v>65.4</v>
       </c>
       <c r="E88" t="n">
-        <v>10.4</v>
+        <v>27.7</v>
       </c>
       <c r="F88" t="n">
-        <v>26.3</v>
+        <v>39.3</v>
       </c>
       <c r="G88" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="I88" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J88" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="K88" t="n">
-        <v>1.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" t="n">
-        <v>67.3</v>
+        <v>59.3</v>
       </c>
       <c r="D89" t="n">
-        <v>65.4</v>
+        <v>61.4</v>
       </c>
       <c r="E89" t="n">
-        <v>27.7</v>
+        <v>20</v>
       </c>
       <c r="F89" t="n">
-        <v>39.3</v>
+        <v>35</v>
       </c>
       <c r="G89" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H89" t="n">
-        <v>46.7</v>
+        <v>56.4</v>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="K89" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>59.3</v>
+        <v>52.6</v>
       </c>
       <c r="D90" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="E90" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="F90" t="n">
-        <v>35</v>
+        <v>38.5</v>
       </c>
       <c r="G90" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="H90" t="n">
-        <v>56.4</v>
+        <v>30</v>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J90" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
       <c r="K90" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91" t="n">
-        <v>52.6</v>
+        <v>57.9</v>
       </c>
       <c r="D91" t="n">
-        <v>55.6</v>
+        <v>61.6</v>
       </c>
       <c r="E91" t="n">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="F91" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="G91" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="H91" t="n">
-        <v>30</v>
+        <v>51.2</v>
       </c>
       <c r="I91" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J91" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="K91" t="n">
-        <v>3.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C92" t="n">
-        <v>57.9</v>
+        <v>74.2</v>
       </c>
       <c r="D92" t="n">
-        <v>61.6</v>
+        <v>69.7</v>
       </c>
       <c r="E92" t="n">
-        <v>21.3</v>
+        <v>39.1</v>
       </c>
       <c r="F92" t="n">
-        <v>39.4</v>
+        <v>33.3</v>
       </c>
       <c r="G92" t="n">
-        <v>7.6</v>
+        <v>9.7</v>
       </c>
       <c r="H92" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="I92" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>24.8</v>
+        <v>22.9</v>
       </c>
       <c r="K92" t="n">
-        <v>14.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B93" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C93" t="n">
-        <v>74.2</v>
+        <v>64.4</v>
       </c>
       <c r="D93" t="n">
-        <v>69.7</v>
+        <v>57.5</v>
       </c>
       <c r="E93" t="n">
-        <v>39.1</v>
+        <v>17.9</v>
       </c>
       <c r="F93" t="n">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="G93" t="n">
-        <v>9.7</v>
+        <v>15.3</v>
       </c>
       <c r="H93" t="n">
-        <v>52.2</v>
+        <v>40.5</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J93" t="n">
-        <v>22.9</v>
+        <v>27.2</v>
       </c>
       <c r="K93" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B94" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C94" t="n">
-        <v>64.4</v>
+        <v>57.5</v>
       </c>
       <c r="D94" t="n">
-        <v>57.5</v>
+        <v>63.9</v>
       </c>
       <c r="E94" t="n">
-        <v>17.9</v>
+        <v>26.6</v>
       </c>
       <c r="F94" t="n">
-        <v>41.9</v>
+        <v>36.8</v>
       </c>
       <c r="G94" t="n">
-        <v>15.3</v>
+        <v>7.4</v>
       </c>
       <c r="H94" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="I94" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J94" t="n">
-        <v>27.2</v>
+        <v>22.5</v>
       </c>
       <c r="K94" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B95" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C95" t="n">
-        <v>57.5</v>
+        <v>80</v>
       </c>
       <c r="D95" t="n">
-        <v>63.9</v>
+        <v>68.6</v>
       </c>
       <c r="E95" t="n">
-        <v>26.6</v>
+        <v>21.4</v>
       </c>
       <c r="F95" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="G95" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="K95" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B96" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C96" t="n">
-        <v>80</v>
+        <v>62.1</v>
       </c>
       <c r="D96" t="n">
-        <v>68.6</v>
+        <v>64.9</v>
       </c>
       <c r="E96" t="n">
-        <v>21.4</v>
+        <v>29.3</v>
       </c>
       <c r="F96" t="n">
-        <v>25</v>
+        <v>52.2</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H96" t="n">
-        <v>25</v>
+        <v>63.5</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J96" t="n">
-        <v>15</v>
+        <v>33.1</v>
       </c>
       <c r="K96" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B97" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C97" t="n">
-        <v>62.1</v>
+        <v>62.7</v>
       </c>
       <c r="D97" t="n">
-        <v>64.9</v>
+        <v>65.6</v>
       </c>
       <c r="E97" t="n">
-        <v>29.3</v>
+        <v>32.5</v>
       </c>
       <c r="F97" t="n">
-        <v>52.2</v>
+        <v>58.6</v>
       </c>
       <c r="G97" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="H97" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J97" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="K97" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B98" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C98" t="n">
-        <v>62.7</v>
+        <v>74.3</v>
       </c>
       <c r="D98" t="n">
-        <v>65.6</v>
+        <v>71.8</v>
       </c>
       <c r="E98" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.6</v>
+        <v>42.9</v>
       </c>
       <c r="G98" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="H98" t="n">
-        <v>55.6</v>
+        <v>73.1</v>
       </c>
       <c r="I98" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J98" t="n">
-        <v>33</v>
+        <v>24.6</v>
       </c>
       <c r="K98" t="n">
-        <v>20.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B99" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C99" t="n">
-        <v>74.3</v>
+        <v>60.6</v>
       </c>
       <c r="D99" t="n">
-        <v>71.8</v>
+        <v>64.6</v>
       </c>
       <c r="E99" t="n">
-        <v>28.1</v>
+        <v>21.7</v>
       </c>
       <c r="F99" t="n">
-        <v>42.9</v>
+        <v>26.5</v>
       </c>
       <c r="G99" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H99" t="n">
-        <v>73.1</v>
+        <v>67.9</v>
       </c>
       <c r="I99" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J99" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="K99" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B100" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D100" t="n">
-        <v>64.6</v>
+        <v>67.5</v>
       </c>
       <c r="E100" t="n">
-        <v>21.7</v>
+        <v>31</v>
       </c>
       <c r="F100" t="n">
-        <v>26.5</v>
+        <v>54.5</v>
       </c>
       <c r="G100" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="H100" t="n">
-        <v>67.9</v>
+        <v>42.3</v>
       </c>
       <c r="I100" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J100" t="n">
-        <v>19.3</v>
+        <v>37.3</v>
       </c>
       <c r="K100" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B101" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C101" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D101" t="n">
-        <v>67.5</v>
+        <v>65.6</v>
       </c>
       <c r="E101" t="n">
-        <v>31</v>
+        <v>23.1</v>
       </c>
       <c r="F101" t="n">
-        <v>54.5</v>
+        <v>37.2</v>
       </c>
       <c r="G101" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
       <c r="I101" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>37.3</v>
+        <v>21.5</v>
       </c>
       <c r="K101" t="n">
-        <v>19.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B102" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C102" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="D102" t="n">
-        <v>65.6</v>
+        <v>68.8</v>
       </c>
       <c r="E102" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="F102" t="n">
-        <v>37.2</v>
+        <v>46.5</v>
       </c>
       <c r="G102" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="H102" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J102" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="K102" t="n">
-        <v>6.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B103" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C103" t="n">
-        <v>66.2</v>
+        <v>64.4</v>
       </c>
       <c r="D103" t="n">
-        <v>68.8</v>
+        <v>61.4</v>
       </c>
       <c r="E103" t="n">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="F103" t="n">
-        <v>46.5</v>
+        <v>58</v>
       </c>
       <c r="G103" t="n">
-        <v>1.9</v>
+        <v>16.4</v>
       </c>
       <c r="H103" t="n">
-        <v>42.3</v>
+        <v>32.3</v>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J103" t="n">
-        <v>21.9</v>
+        <v>36.4</v>
       </c>
       <c r="K103" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B104" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="C104" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D104" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E104" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F104" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H104" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J104" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C105" t="n">
-        <v>33.3</v>
+        <v>58.8</v>
       </c>
       <c r="D105" t="n">
-        <v>56.2</v>
+        <v>59.6</v>
       </c>
       <c r="E105" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G105" t="n">
-        <v>33.3</v>
+        <v>13.7</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="I105" t="n">
-        <v>33.3</v>
+        <v>2</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="K105" t="n">
-        <v>-33.3</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C106" t="n">
-        <v>58.8</v>
+        <v>51.6</v>
       </c>
       <c r="D106" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="E106" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F106" t="n">
-        <v>14.3</v>
+        <v>40.9</v>
       </c>
       <c r="G106" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H106" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J106" t="n">
-        <v>14.5</v>
+        <v>24.4</v>
       </c>
       <c r="K106" t="n">
-        <v>-7.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>146</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C107" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D107" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E107" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F107" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G107" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="H107" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I107" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J107" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K107" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B108" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C108" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D108" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E108" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F108" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F108"/>
       <c r="G108" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="H108" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C109" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D109" t="n">
-        <v>45.5</v>
+        <v>62.4</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109"/>
+        <v>23.5</v>
+      </c>
+      <c r="F109" t="n">
+        <v>30.5</v>
+      </c>
       <c r="G109" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H109" t="n">
-        <v>0</v>
+        <v>49.4</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="K109" t="n">
-        <v>-25</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C110" t="n">
-        <v>65.8</v>
+        <v>51</v>
       </c>
       <c r="D110" t="n">
-        <v>62.4</v>
+        <v>58.9</v>
       </c>
       <c r="E110" t="n">
-        <v>23.5</v>
+        <v>13.2</v>
       </c>
       <c r="F110" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="G110" t="n">
-        <v>12.9</v>
+        <v>6.4</v>
       </c>
       <c r="H110" t="n">
-        <v>49.4</v>
+        <v>41.7</v>
       </c>
       <c r="I110" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J110" t="n">
-        <v>25.9</v>
+        <v>19.2</v>
       </c>
       <c r="K110" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="B111" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C111" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="D111" t="n">
-        <v>58.9</v>
+        <v>59.9</v>
       </c>
       <c r="E111" t="n">
-        <v>13.2</v>
+        <v>30.4</v>
       </c>
       <c r="F111" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="G111" t="n">
-        <v>6.4</v>
+        <v>13.4</v>
       </c>
       <c r="H111" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="I111" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="J111" t="n">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="K111" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C112" t="n">
-        <v>51.5</v>
+        <v>63.3</v>
       </c>
       <c r="D112" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="E112" t="n">
-        <v>30.4</v>
+        <v>20.5</v>
       </c>
       <c r="F112" t="n">
-        <v>42.9</v>
+        <v>34.6</v>
       </c>
       <c r="G112" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="H112" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="I112" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J112" t="n">
-        <v>28</v>
+        <v>22.8</v>
       </c>
       <c r="K112" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C113" t="n">
-        <v>63.3</v>
+        <v>52.6</v>
       </c>
       <c r="D113" t="n">
-        <v>60.1</v>
+        <v>56.2</v>
       </c>
       <c r="E113" t="n">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="F113" t="n">
-        <v>34.6</v>
+        <v>10</v>
       </c>
       <c r="G113" t="n">
         <v>16.7</v>
       </c>
       <c r="H113" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="I113" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J113" t="n">
-        <v>22.8</v>
+        <v>15.2</v>
       </c>
       <c r="K113" t="n">
-        <v>2.1</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C114" t="n">
-        <v>52.6</v>
+        <v>65.9</v>
       </c>
       <c r="D114" t="n">
-        <v>56.2</v>
+        <v>64.2</v>
       </c>
       <c r="E114" t="n">
-        <v>30</v>
+        <v>20.5</v>
       </c>
       <c r="F114" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G114" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="H114" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="I114" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="K114" t="n">
-        <v>-11.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C115" t="n">
-        <v>65.9</v>
+        <v>60</v>
       </c>
       <c r="D115" t="n">
-        <v>64.2</v>
+        <v>61.5</v>
       </c>
       <c r="E115" t="n">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="F115" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G115" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H115" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="I115" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>28.1</v>
+        <v>35.6</v>
       </c>
       <c r="K115" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B116" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C116" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D116" t="n">
-        <v>61.5</v>
+        <v>56.3</v>
       </c>
       <c r="E116" t="n">
-        <v>18.9</v>
+        <v>23.1</v>
       </c>
       <c r="F116" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="G116" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H116" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J116" t="n">
-        <v>35.6</v>
+        <v>26.5</v>
       </c>
       <c r="K116" t="n">
-        <v>15.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C117" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D117" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E117" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F117" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G117" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H117" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I117" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J117" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K117" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C118" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="D118" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E118" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="F118" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G118" t="n">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="H118" t="n">
-        <v>22.2</v>
+        <v>60</v>
       </c>
       <c r="I118" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="K118" t="n">
-        <v>-11.1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B119" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C119" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D119" t="n">
-        <v>48.8</v>
+        <v>61.8</v>
       </c>
       <c r="E119" t="n">
-        <v>13.6</v>
+        <v>19.7</v>
       </c>
       <c r="F119" t="n">
-        <v>50</v>
+        <v>29.1</v>
       </c>
       <c r="G119" t="n">
-        <v>30</v>
+        <v>7.7</v>
       </c>
       <c r="H119" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J119" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="K119" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C120" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="D120" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="E120" t="n">
-        <v>19.7</v>
+        <v>24.1</v>
       </c>
       <c r="F120" t="n">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="G120" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="H120" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I120" t="n">
         <v>7.7</v>
       </c>
-      <c r="H120" t="n">
-        <v>57</v>
-      </c>
-      <c r="I120" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J120" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="K120" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C121" t="n">
-        <v>58</v>
+        <v>70.1</v>
       </c>
       <c r="D121" t="n">
-        <v>58.3</v>
+        <v>66.4</v>
       </c>
       <c r="E121" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="F121" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="G121" t="n">
-        <v>8.7</v>
+        <v>5.4</v>
       </c>
       <c r="H121" t="n">
-        <v>43.1</v>
+        <v>52.7</v>
       </c>
       <c r="I121" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="K121" t="n">
-        <v>3.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B122" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C122" t="n">
-        <v>70.1</v>
+        <v>61.6</v>
       </c>
       <c r="D122" t="n">
-        <v>66.4</v>
+        <v>65.8</v>
       </c>
       <c r="E122" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F122" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
       <c r="G122" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="H122" t="n">
-        <v>52.7</v>
+        <v>47.1</v>
       </c>
       <c r="I122" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="K122" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B123" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C123" t="n">
-        <v>61.6</v>
+        <v>60.7</v>
       </c>
       <c r="D123" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="E123" t="n">
-        <v>20.2</v>
+        <v>11.2</v>
       </c>
       <c r="F123" t="n">
-        <v>41.8</v>
+        <v>32.4</v>
       </c>
       <c r="G123" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="H123" t="n">
-        <v>47.1</v>
+        <v>29.6</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J123" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="K123" t="n">
-        <v>13.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B124" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C124" t="n">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="D124" t="n">
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E124" t="n">
-        <v>11.2</v>
+        <v>27.7</v>
       </c>
       <c r="F124" t="n">
-        <v>32.4</v>
+        <v>65.9</v>
       </c>
       <c r="G124" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="H124" t="n">
-        <v>29.6</v>
+        <v>42.3</v>
       </c>
       <c r="I124" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J124" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="K124" t="n">
-        <v>5.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="B125" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C125" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="D125" t="n">
-        <v>62.1</v>
+        <v>58.7</v>
       </c>
       <c r="E125" t="n">
-        <v>27.7</v>
+        <v>12.8</v>
       </c>
       <c r="F125" t="n">
-        <v>65.9</v>
+        <v>34.1</v>
       </c>
       <c r="G125" t="n">
         <v>11.1</v>
       </c>
       <c r="H125" t="n">
-        <v>42.3</v>
+        <v>35.5</v>
       </c>
       <c r="I125" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J125" t="n">
-        <v>37</v>
+        <v>23.9</v>
       </c>
       <c r="K125" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="B126" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C126" t="n">
-        <v>59.3</v>
+        <v>73.6</v>
       </c>
       <c r="D126" t="n">
-        <v>58.7</v>
+        <v>64.6</v>
       </c>
       <c r="E126" t="n">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="F126" t="n">
-        <v>34.1</v>
+        <v>56.9</v>
       </c>
       <c r="G126" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="H126" t="n">
-        <v>35.5</v>
+        <v>44.1</v>
       </c>
       <c r="I126" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J126" t="n">
-        <v>23.9</v>
+        <v>49.6</v>
       </c>
       <c r="K126" t="n">
-        <v>5.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B127" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C127" t="n">
-        <v>73.6</v>
+        <v>78.6</v>
       </c>
       <c r="D127" t="n">
-        <v>64.6</v>
-      </c>
-      <c r="E127" t="n">
-        <v>31</v>
-      </c>
+        <v>72.9</v>
+      </c>
+      <c r="E127"/>
       <c r="F127" t="n">
-        <v>56.9</v>
+        <v>45.5</v>
       </c>
       <c r="G127" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>44.1</v>
+        <v>46.5</v>
       </c>
       <c r="I127" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J127" t="n">
-        <v>49.6</v>
+        <v>26.7</v>
       </c>
       <c r="K127" t="n">
-        <v>34.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B128" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C128" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D128" t="n">
-        <v>72.9</v>
-      </c>
-      <c r="E128"/>
+        <v>45.1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
       <c r="F128" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H128" t="n">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J128" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="K128" t="n">
-        <v>18.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B129" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C129" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D129" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E129" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F129" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G129" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H129" t="n">
         <v>50</v>
       </c>
-      <c r="D129" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>25</v>
-      </c>
-      <c r="G129" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H129" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I129" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J129" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K129" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B130" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C130" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D130" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E130" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F130" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G130" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H130" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I130" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J130" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K130" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B131" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C131" t="n">
-        <v>65.8</v>
+        <v>50.9</v>
       </c>
       <c r="D131" t="n">
-        <v>67.5</v>
+        <v>60.7</v>
       </c>
       <c r="E131" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F131" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G131" t="n">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="H131" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="I131" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J131" t="n">
-        <v>26.8</v>
+        <v>21.7</v>
       </c>
       <c r="K131" t="n">
-        <v>13.2</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B132" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C132" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="D132" t="n">
-        <v>60.7</v>
+        <v>56.7</v>
       </c>
       <c r="E132" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F132" t="n">
-        <v>38.6</v>
+        <v>50</v>
       </c>
       <c r="G132" t="n">
-        <v>9.7</v>
+        <v>22.2</v>
       </c>
       <c r="H132" t="n">
-        <v>54.4</v>
+        <v>20</v>
       </c>
       <c r="I132" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K132" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B133" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C133" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D133" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E133" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F133" t="n">
         <v>50</v>
       </c>
       <c r="G133" t="n">
-        <v>22.2</v>
+        <v>4.1</v>
       </c>
       <c r="H133" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J133" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K133" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B134" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C134" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
       <c r="D134" t="n">
-        <v>70.3</v>
+        <v>63</v>
       </c>
       <c r="E134" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F134" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G134" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H134" t="n">
         <v>50</v>
       </c>
-      <c r="G134" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H134" t="n">
-        <v>41.9</v>
-      </c>
       <c r="I134" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J134" t="n">
-        <v>26.3</v>
+        <v>21</v>
       </c>
       <c r="K134" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="s">
-        <v>304</v>
-      </c>
+      <c r="A135"/>
       <c r="B135" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="C135" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="D135" t="n">
-        <v>63</v>
+        <v>61.3</v>
       </c>
       <c r="E135" t="n">
-        <v>27</v>
+        <v>20.7</v>
       </c>
       <c r="F135" t="n">
-        <v>42.2</v>
+        <v>37.3</v>
       </c>
       <c r="G135" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H135" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I135" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J135" t="n">
-        <v>21</v>
+        <v>24.9</v>
       </c>
       <c r="K135" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136"/>
-      <c r="B136" t="s">
-        <v>182</v>
-      </c>
-      <c r="C136" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="D136" t="n">
-        <v>61.4</v>
-      </c>
-      <c r="E136" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F136" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="G136" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H136" t="n">
-        <v>46</v>
-      </c>
-      <c r="I136" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J136" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K136" t="n">
         <v>8</v>
       </c>
     </row>

--- a/cbl/data/summary2026.xlsx
+++ b/cbl/data/summary2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t xml:space="preserve">Batter</t>
   </si>
@@ -465,9 +465,6 @@
     <t xml:space="preserve">Crixtian Taveras</t>
   </si>
   <si>
-    <t xml:space="preserve">Denis Dei Banning</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dennis Dei Baning</t>
   </si>
   <si>
@@ -585,9 +582,6 @@
     <t xml:space="preserve">Brady Encarnacion</t>
   </si>
   <si>
-    <t xml:space="preserve">Braeden Pakkala</t>
-  </si>
-  <si>
     <t xml:space="preserve">Brett Reid</t>
   </si>
   <si>
@@ -837,7 +831,7 @@
     <t xml:space="preserve">Zachary Laird</t>
   </si>
   <si>
-    <t xml:space="preserve">Alex Gerard</t>
+    <t xml:space="preserve">Alex Gerrard</t>
   </si>
   <si>
     <t xml:space="preserve">Alex Lanigan</t>
@@ -973,8 +967,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K164" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K164"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:K163" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K163"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Batter"/>
     <tableColumn id="2" name="Team"/>
@@ -993,8 +987,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K135" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:K135"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:K134" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:K134"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Pitcher"/>
     <tableColumn id="2" name="Team"/>
@@ -5902,25 +5896,31 @@
         <v>145</v>
       </c>
       <c r="C134" t="n">
-        <v>100</v>
-      </c>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
+        <v>74.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="E134" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="F134" t="n">
+        <v>27.2</v>
+      </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>30.6</v>
       </c>
       <c r="H134" t="n">
-        <v>0</v>
+        <v>9.7</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>46.6</v>
       </c>
       <c r="J134" t="n">
-        <v>100</v>
+        <v>27.6</v>
       </c>
       <c r="K134" t="n">
-        <v>0</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="135">
@@ -5931,31 +5931,31 @@
         <v>145</v>
       </c>
       <c r="C135" t="n">
-        <v>74.5</v>
+        <v>48.1</v>
       </c>
       <c r="D135" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="E135" t="n">
-        <v>47.3</v>
+        <v>23.1</v>
       </c>
       <c r="F135" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="G135" t="n">
-        <v>30.8</v>
+        <v>15.4</v>
       </c>
       <c r="H135" t="n">
-        <v>9.8</v>
+        <v>18.8</v>
       </c>
       <c r="I135" t="n">
-        <v>47.4</v>
+        <v>44.4</v>
       </c>
       <c r="J135" t="n">
-        <v>26.3</v>
+        <v>22.2</v>
       </c>
       <c r="K135" t="n">
-        <v>39.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="136">
@@ -5966,31 +5966,31 @@
         <v>145</v>
       </c>
       <c r="C136" t="n">
-        <v>48.1</v>
+        <v>66</v>
       </c>
       <c r="D136" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="E136" t="n">
-        <v>23.1</v>
+        <v>41.7</v>
       </c>
       <c r="F136" t="n">
-        <v>25</v>
+        <v>24.3</v>
       </c>
       <c r="G136" t="n">
-        <v>15.4</v>
+        <v>21.9</v>
       </c>
       <c r="H136" t="n">
-        <v>18.8</v>
+        <v>7.7</v>
       </c>
       <c r="I136" t="n">
-        <v>44.4</v>
+        <v>54.3</v>
       </c>
       <c r="J136" t="n">
-        <v>22.2</v>
+        <v>15.7</v>
       </c>
       <c r="K136" t="n">
-        <v>11.1</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="137">
@@ -6001,31 +6001,31 @@
         <v>145</v>
       </c>
       <c r="C137" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="D137" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>41.7</v>
+        <v>66.7</v>
       </c>
       <c r="F137" t="n">
-        <v>24.3</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>21.9</v>
+        <v>18.2</v>
       </c>
       <c r="H137" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>54.3</v>
+        <v>75</v>
       </c>
       <c r="J137" t="n">
-        <v>15.7</v>
+        <v>25</v>
       </c>
       <c r="K137" t="n">
-        <v>31.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6036,31 +6036,31 @@
         <v>145</v>
       </c>
       <c r="C138" t="n">
-        <v>66.7</v>
+        <v>72.2</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="E138" t="n">
-        <v>66.7</v>
+        <v>52.8</v>
       </c>
       <c r="F138" t="n">
-        <v>0</v>
+        <v>19.4</v>
       </c>
       <c r="G138" t="n">
-        <v>18.2</v>
+        <v>27.4</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I138" t="n">
-        <v>75</v>
+        <v>69.2</v>
       </c>
       <c r="J138" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="139">
@@ -6071,31 +6071,31 @@
         <v>145</v>
       </c>
       <c r="C139" t="n">
-        <v>72.2</v>
+        <v>50</v>
       </c>
       <c r="D139" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="E139" t="n">
-        <v>52.8</v>
+        <v>35.7</v>
       </c>
       <c r="F139" t="n">
-        <v>19.4</v>
+        <v>14.3</v>
       </c>
       <c r="G139" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="H139" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="I139" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K139" t="n">
-        <v>42.3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="140">
@@ -6106,31 +6106,31 @@
         <v>145</v>
       </c>
       <c r="C140" t="n">
-        <v>50</v>
+        <v>68.5</v>
       </c>
       <c r="D140" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="E140" t="n">
-        <v>35.7</v>
+        <v>39.5</v>
       </c>
       <c r="F140" t="n">
-        <v>14.3</v>
+        <v>29</v>
       </c>
       <c r="G140" t="n">
-        <v>28.6</v>
+        <v>31.8</v>
       </c>
       <c r="H140" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="I140" t="n">
-        <v>75</v>
+        <v>35.9</v>
       </c>
       <c r="J140" t="n">
-        <v>25</v>
+        <v>28.1</v>
       </c>
       <c r="K140" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="141">
@@ -6141,101 +6141,101 @@
         <v>145</v>
       </c>
       <c r="C141" t="n">
-        <v>68.5</v>
+        <v>65.8</v>
       </c>
       <c r="D141" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E141" t="n">
-        <v>39.5</v>
+        <v>41.8</v>
       </c>
       <c r="F141" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G141" t="n">
-        <v>31.8</v>
+        <v>21.9</v>
       </c>
       <c r="H141" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="I141" t="n">
-        <v>35.9</v>
+        <v>59.7</v>
       </c>
       <c r="J141" t="n">
-        <v>28.1</v>
+        <v>23.9</v>
       </c>
       <c r="K141" t="n">
-        <v>43.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="B142" t="s">
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>65.8</v>
+        <v>56.1</v>
       </c>
       <c r="D142" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="E142" t="n">
-        <v>41.8</v>
+        <v>36.9</v>
       </c>
       <c r="F142" t="n">
-        <v>24</v>
+        <v>19.2</v>
       </c>
       <c r="G142" t="n">
-        <v>21.9</v>
+        <v>22.5</v>
       </c>
       <c r="H142" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>59.7</v>
+        <v>40.5</v>
       </c>
       <c r="J142" t="n">
-        <v>23.9</v>
+        <v>27</v>
       </c>
       <c r="K142" t="n">
-        <v>30.3</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="B143" t="s">
         <v>145</v>
       </c>
       <c r="C143" t="n">
-        <v>56.1</v>
+        <v>79.6</v>
       </c>
       <c r="D143" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="E143" t="n">
-        <v>36.9</v>
+        <v>42.8</v>
       </c>
       <c r="F143" t="n">
-        <v>19.2</v>
+        <v>36.8</v>
       </c>
       <c r="G143" t="n">
-        <v>22.5</v>
+        <v>34.2</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I143" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
       <c r="J143" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>40.5</v>
+        <v>44</v>
       </c>
     </row>
     <row r="144">
@@ -6246,31 +6246,31 @@
         <v>145</v>
       </c>
       <c r="C144" t="n">
-        <v>79.6</v>
+        <v>57.8</v>
       </c>
       <c r="D144" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="E144" t="n">
-        <v>42.8</v>
+        <v>43.7</v>
       </c>
       <c r="F144" t="n">
-        <v>36.8</v>
+        <v>14.1</v>
       </c>
       <c r="G144" t="n">
-        <v>34.2</v>
+        <v>12.5</v>
       </c>
       <c r="H144" t="n">
-        <v>2.9</v>
+        <v>10.2</v>
       </c>
       <c r="I144" t="n">
-        <v>44</v>
+        <v>52.8</v>
       </c>
       <c r="J144" t="n">
-        <v>20</v>
+        <v>9.7</v>
       </c>
       <c r="K144" t="n">
-        <v>44</v>
+        <v>35.7</v>
       </c>
     </row>
     <row r="145">
@@ -6281,31 +6281,31 @@
         <v>145</v>
       </c>
       <c r="C145" t="n">
-        <v>57.8</v>
+        <v>63.2</v>
       </c>
       <c r="D145" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="E145" t="n">
-        <v>43.7</v>
+        <v>18.2</v>
       </c>
       <c r="F145" t="n">
-        <v>14.1</v>
+        <v>45</v>
       </c>
       <c r="G145" t="n">
-        <v>12.5</v>
+        <v>26.9</v>
       </c>
       <c r="H145" t="n">
-        <v>10.2</v>
+        <v>7.7</v>
       </c>
       <c r="I145" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>9.7</v>
+        <v>25</v>
       </c>
       <c r="K145" t="n">
-        <v>35.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -6316,31 +6316,31 @@
         <v>145</v>
       </c>
       <c r="C146" t="n">
-        <v>63.2</v>
+        <v>74.2</v>
       </c>
       <c r="D146" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="E146" t="n">
-        <v>18.2</v>
+        <v>62.1</v>
       </c>
       <c r="F146" t="n">
-        <v>45</v>
+        <v>12.1</v>
       </c>
       <c r="G146" t="n">
-        <v>26.9</v>
+        <v>23.4</v>
       </c>
       <c r="H146" t="n">
-        <v>7.7</v>
+        <v>14.8</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>32.9</v>
       </c>
       <c r="J146" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K146" t="n">
-        <v>25</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="147">
@@ -6354,28 +6354,28 @@
         <v>74.2</v>
       </c>
       <c r="D147" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="E147" t="n">
-        <v>62.1</v>
+        <v>48.1</v>
       </c>
       <c r="F147" t="n">
-        <v>12.1</v>
+        <v>26.1</v>
       </c>
       <c r="G147" t="n">
-        <v>23.4</v>
+        <v>9.2</v>
       </c>
       <c r="H147" t="n">
-        <v>14.8</v>
+        <v>2.2</v>
       </c>
       <c r="I147" t="n">
-        <v>32.9</v>
+        <v>48.1</v>
       </c>
       <c r="J147" t="n">
-        <v>37</v>
+        <v>20.8</v>
       </c>
       <c r="K147" t="n">
-        <v>38.4</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="148">
@@ -6383,69 +6383,69 @@
         <v>163</v>
       </c>
       <c r="B148" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C148" t="n">
-        <v>74.2</v>
+        <v>70.5</v>
       </c>
       <c r="D148" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="E148" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="F148" t="n">
-        <v>26.1</v>
+        <v>20.5</v>
       </c>
       <c r="G148" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H148" t="n">
         <v>9.2</v>
       </c>
-      <c r="H148" t="n">
-        <v>2.2</v>
-      </c>
       <c r="I148" t="n">
-        <v>48.1</v>
+        <v>51.9</v>
       </c>
       <c r="J148" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="K148" t="n">
-        <v>32.5</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
+        <v>165</v>
+      </c>
+      <c r="B149" t="s">
         <v>164</v>
       </c>
-      <c r="B149" t="s">
-        <v>165</v>
-      </c>
       <c r="C149" t="n">
-        <v>70.5</v>
+        <v>68.6</v>
       </c>
       <c r="D149" t="n">
         <v>20.5</v>
       </c>
       <c r="E149" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="F149" t="n">
         <v>20.5</v>
       </c>
       <c r="G149" t="n">
-        <v>37.7</v>
+        <v>14.9</v>
       </c>
       <c r="H149" t="n">
-        <v>9.2</v>
+        <v>6.6</v>
       </c>
       <c r="I149" t="n">
-        <v>51.9</v>
+        <v>57.3</v>
       </c>
       <c r="J149" t="n">
-        <v>21.2</v>
+        <v>18.7</v>
       </c>
       <c r="K149" t="n">
-        <v>39.1</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="150">
@@ -6453,34 +6453,34 @@
         <v>166</v>
       </c>
       <c r="B150" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C150" t="n">
-        <v>68.6</v>
+        <v>64.6</v>
       </c>
       <c r="D150" t="n">
-        <v>20.5</v>
+        <v>16.7</v>
       </c>
       <c r="E150" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="F150" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G150" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="H150" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I150" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="J150" t="n">
         <v>48.1</v>
       </c>
-      <c r="F150" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="G150" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H150" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I150" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J150" t="n">
-        <v>18.7</v>
-      </c>
       <c r="K150" t="n">
-        <v>45.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="151">
@@ -6488,34 +6488,34 @@
         <v>167</v>
       </c>
       <c r="B151" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C151" t="n">
-        <v>64.6</v>
+        <v>60</v>
       </c>
       <c r="D151" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E151" t="n">
-        <v>47.9</v>
+        <v>38.9</v>
       </c>
       <c r="F151" t="n">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="G151" t="n">
-        <v>37.7</v>
+        <v>32.4</v>
       </c>
       <c r="H151" t="n">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="I151" t="n">
-        <v>29.6</v>
+        <v>34.8</v>
       </c>
       <c r="J151" t="n">
-        <v>48.1</v>
+        <v>30.4</v>
       </c>
       <c r="K151" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="152">
@@ -6523,34 +6523,34 @@
         <v>168</v>
       </c>
       <c r="B152" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C152" t="n">
-        <v>60</v>
+        <v>66.3</v>
       </c>
       <c r="D152" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E152" t="n">
-        <v>38.9</v>
+        <v>51.9</v>
       </c>
       <c r="F152" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="G152" t="n">
-        <v>32.4</v>
+        <v>9</v>
       </c>
       <c r="H152" t="n">
-        <v>14.9</v>
+        <v>18.2</v>
       </c>
       <c r="I152" t="n">
-        <v>34.8</v>
+        <v>62.2</v>
       </c>
       <c r="J152" t="n">
-        <v>30.4</v>
+        <v>17.3</v>
       </c>
       <c r="K152" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="153">
@@ -6558,34 +6558,34 @@
         <v>169</v>
       </c>
       <c r="B153" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C153" t="n">
-        <v>66.3</v>
+        <v>80.4</v>
       </c>
       <c r="D153" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="E153" t="n">
-        <v>51.9</v>
+        <v>63.9</v>
       </c>
       <c r="F153" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="G153" t="n">
-        <v>9</v>
+        <v>23.3</v>
       </c>
       <c r="H153" t="n">
-        <v>18.2</v>
+        <v>9.4</v>
       </c>
       <c r="I153" t="n">
-        <v>62.2</v>
+        <v>36.2</v>
       </c>
       <c r="J153" t="n">
-        <v>17.3</v>
+        <v>34</v>
       </c>
       <c r="K153" t="n">
-        <v>36.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="154">
@@ -6593,34 +6593,34 @@
         <v>170</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C154" t="n">
-        <v>80.4</v>
+        <v>55.6</v>
       </c>
       <c r="D154" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="E154" t="n">
-        <v>63.9</v>
+        <v>38</v>
       </c>
       <c r="F154" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="G154" t="n">
-        <v>23.3</v>
+        <v>25.7</v>
       </c>
       <c r="H154" t="n">
-        <v>9.4</v>
+        <v>12.6</v>
       </c>
       <c r="I154" t="n">
-        <v>36.2</v>
+        <v>47.4</v>
       </c>
       <c r="J154" t="n">
-        <v>34</v>
+        <v>22.8</v>
       </c>
       <c r="K154" t="n">
-        <v>44.9</v>
+        <v>26.4</v>
       </c>
     </row>
     <row r="155">
@@ -6628,34 +6628,34 @@
         <v>171</v>
       </c>
       <c r="B155" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C155" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="D155" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="F155" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>25.7</v>
+        <v>66.7</v>
       </c>
       <c r="H155" t="n">
-        <v>12.6</v>
+        <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -6663,34 +6663,34 @@
         <v>172</v>
       </c>
       <c r="B156" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C156" t="n">
-        <v>75</v>
+        <v>56.2</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="E156" t="n">
-        <v>75</v>
+        <v>38.6</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="G156" t="n">
-        <v>66.7</v>
+        <v>14.6</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>28.8</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="157">
@@ -6698,34 +6698,34 @@
         <v>173</v>
       </c>
       <c r="B157" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C157" t="n">
-        <v>56.2</v>
+        <v>61.4</v>
       </c>
       <c r="D157" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="E157" t="n">
-        <v>38.6</v>
+        <v>40.6</v>
       </c>
       <c r="F157" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="G157" t="n">
-        <v>14.6</v>
+        <v>9.8</v>
       </c>
       <c r="H157" t="n">
-        <v>16.5</v>
+        <v>8.5</v>
       </c>
       <c r="I157" t="n">
-        <v>37</v>
+        <v>60.4</v>
       </c>
       <c r="J157" t="n">
-        <v>28.8</v>
+        <v>18</v>
       </c>
       <c r="K157" t="n">
-        <v>49.3</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="158">
@@ -6733,34 +6733,34 @@
         <v>174</v>
       </c>
       <c r="B158" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C158" t="n">
-        <v>61.4</v>
+        <v>71.5</v>
       </c>
       <c r="D158" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E158" t="n">
-        <v>40.6</v>
+        <v>54.8</v>
       </c>
       <c r="F158" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="G158" t="n">
-        <v>9.8</v>
+        <v>24.7</v>
       </c>
       <c r="H158" t="n">
-        <v>8.5</v>
+        <v>11.8</v>
       </c>
       <c r="I158" t="n">
-        <v>60.4</v>
+        <v>34.8</v>
       </c>
       <c r="J158" t="n">
-        <v>18</v>
+        <v>31.5</v>
       </c>
       <c r="K158" t="n">
-        <v>29.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="159">
@@ -6768,34 +6768,34 @@
         <v>175</v>
       </c>
       <c r="B159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C159" t="n">
-        <v>71.5</v>
+        <v>77.2</v>
       </c>
       <c r="D159" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="E159" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="F159" t="n">
-        <v>16.7</v>
+        <v>29.9</v>
       </c>
       <c r="G159" t="n">
-        <v>24.7</v>
+        <v>41.7</v>
       </c>
       <c r="H159" t="n">
-        <v>11.8</v>
+        <v>6.9</v>
       </c>
       <c r="I159" t="n">
-        <v>34.8</v>
+        <v>44.4</v>
       </c>
       <c r="J159" t="n">
-        <v>31.5</v>
+        <v>22.2</v>
       </c>
       <c r="K159" t="n">
-        <v>56</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="160">
@@ -6803,34 +6803,34 @@
         <v>176</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C160" t="n">
-        <v>77.2</v>
+        <v>75.5</v>
       </c>
       <c r="D160" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="E160" t="n">
-        <v>47.3</v>
+        <v>55.1</v>
       </c>
       <c r="F160" t="n">
-        <v>29.9</v>
+        <v>20.4</v>
       </c>
       <c r="G160" t="n">
-        <v>41.7</v>
+        <v>19.7</v>
       </c>
       <c r="H160" t="n">
-        <v>6.9</v>
+        <v>11</v>
       </c>
       <c r="I160" t="n">
-        <v>44.4</v>
+        <v>27.9</v>
       </c>
       <c r="J160" t="n">
-        <v>22.2</v>
+        <v>33.7</v>
       </c>
       <c r="K160" t="n">
-        <v>66.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="161">
@@ -6838,57 +6838,51 @@
         <v>177</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C161" t="n">
-        <v>75.5</v>
+        <v>37.5</v>
       </c>
       <c r="D161" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="E161" t="n">
-        <v>55.1</v>
+        <v>4.2</v>
       </c>
       <c r="F161" t="n">
-        <v>20.4</v>
+        <v>33.3</v>
       </c>
       <c r="G161" t="n">
-        <v>19.7</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>11</v>
-      </c>
-      <c r="I161" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="J161" t="n">
-        <v>33.7</v>
-      </c>
-      <c r="K161" t="n">
-        <v>46.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161"/>
     </row>
     <row r="162">
       <c r="A162" t="s">
         <v>178</v>
       </c>
       <c r="B162" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C162" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
         <v>33.3</v>
       </c>
       <c r="E162" t="n">
-        <v>4.2</v>
+        <v>-33.3</v>
       </c>
       <c r="F162" t="n">
         <v>33.3</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -6898,65 +6892,36 @@
       <c r="K162"/>
     </row>
     <row r="163">
-      <c r="A163" t="s">
+      <c r="A163"/>
+      <c r="B163" t="s">
         <v>179</v>
       </c>
-      <c r="B163" t="s">
-        <v>165</v>
-      </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>67.8</v>
       </c>
       <c r="D163" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="E163" t="n">
-        <v>-33.3</v>
+        <v>46</v>
       </c>
       <c r="F163" t="n">
-        <v>33.3</v>
+        <v>22.2</v>
       </c>
       <c r="G163" t="n">
-        <v>100</v>
+        <v>26.9</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163"/>
-      <c r="J163"/>
-      <c r="K163"/>
-    </row>
-    <row r="164">
-      <c r="A164"/>
-      <c r="B164" t="s">
-        <v>180</v>
-      </c>
-      <c r="C164" t="n">
-        <v>68</v>
-      </c>
-      <c r="D164" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="E164" t="n">
-        <v>46</v>
-      </c>
-      <c r="F164" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="G164" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H164" t="n">
         <v>9.5</v>
       </c>
-      <c r="I164" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="J164" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="K164" t="n">
-        <v>39.3</v>
+      <c r="I163" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="J163" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="K163" t="n">
+        <v>39.6</v>
       </c>
     </row>
   </sheetData>
@@ -6988,22 +6953,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>183</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>7</v>
@@ -7012,18 +6977,18 @@
         <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -7058,7 +7023,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
@@ -7093,7 +7058,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B4" t="s">
         <v>12</v>
@@ -7134,559 +7099,559 @@
         <v>12</v>
       </c>
       <c r="C5" t="n">
-        <v>57.7</v>
+        <v>58.4</v>
       </c>
       <c r="D5" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="E5" t="n">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="F5" t="n">
-        <v>46.7</v>
+        <v>42.9</v>
       </c>
       <c r="G5" t="n">
-        <v>16.7</v>
+        <v>16.2</v>
       </c>
       <c r="H5" t="n">
-        <v>52.3</v>
+        <v>45.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>27.7</v>
+        <v>24.6</v>
       </c>
       <c r="K5" t="n">
-        <v>10.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>60.9</v>
+        <v>49.2</v>
       </c>
       <c r="D6" t="n">
-        <v>58.5</v>
+        <v>56.4</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>19.7</v>
       </c>
       <c r="F6" t="n">
-        <v>27.3</v>
+        <v>35.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="H6" t="n">
-        <v>26.7</v>
+        <v>41.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>11.8</v>
+        <v>26.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>49.2</v>
+        <v>71.4</v>
       </c>
       <c r="D7" t="n">
-        <v>56.4</v>
+        <v>55.6</v>
       </c>
       <c r="E7" t="n">
-        <v>19.7</v>
+        <v>16.7</v>
       </c>
       <c r="F7" t="n">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>16.7</v>
       </c>
       <c r="H7" t="n">
-        <v>41.7</v>
+        <v>33.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>26.5</v>
+        <v>36.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6</v>
+        <v>-16.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>71.4</v>
+        <v>70.5</v>
       </c>
       <c r="D8" t="n">
-        <v>55.6</v>
+        <v>69.6</v>
       </c>
       <c r="E8" t="n">
-        <v>16.7</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>35.1</v>
       </c>
       <c r="G8" t="n">
-        <v>16.7</v>
+        <v>8.1</v>
       </c>
       <c r="H8" t="n">
-        <v>33.3</v>
+        <v>37.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>36.4</v>
+        <v>28.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.7</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>70.5</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>69.6</v>
+        <v>64.9</v>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>35.1</v>
+        <v>32.3</v>
       </c>
       <c r="G9" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>28.1</v>
+        <v>21.9</v>
       </c>
       <c r="K9" t="n">
-        <v>14.5</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>193</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>64</v>
+        <v>63.3</v>
       </c>
       <c r="D10" t="n">
-        <v>64.9</v>
+        <v>64.3</v>
       </c>
       <c r="E10" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="F10" t="n">
-        <v>32.3</v>
+        <v>35.3</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>81.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>21.9</v>
+        <v>18.8</v>
       </c>
       <c r="K10" t="n">
-        <v>9.9</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>192</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>63.3</v>
+        <v>59.4</v>
       </c>
       <c r="D11" t="n">
-        <v>64.3</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>13.5</v>
+        <v>16.6</v>
       </c>
       <c r="F11" t="n">
-        <v>35.3</v>
+        <v>27.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>81.8</v>
+        <v>41.7</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>18.8</v>
+        <v>17.2</v>
       </c>
       <c r="K11" t="n">
-        <v>13.3</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B12" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>59.4</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
         <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6</v>
+        <v>19.6</v>
       </c>
       <c r="F12" t="n">
-        <v>27.8</v>
+        <v>47.3</v>
       </c>
       <c r="G12" t="n">
-        <v>4.1</v>
+        <v>8.6</v>
       </c>
       <c r="H12" t="n">
-        <v>41.7</v>
+        <v>53</v>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
-        <v>17.2</v>
+        <v>33.7</v>
       </c>
       <c r="K12" t="n">
-        <v>8.7</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="F13" t="n">
-        <v>47.3</v>
+        <v>42.2</v>
       </c>
       <c r="G13" t="n">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="H13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>33.7</v>
+        <v>34.4</v>
       </c>
       <c r="K13" t="n">
-        <v>17.1</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>58.3</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>52.3</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8</v>
+        <v>8.3</v>
       </c>
       <c r="F14" t="n">
-        <v>42.2</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>10.3</v>
+        <v>16.7</v>
       </c>
       <c r="H14" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>34.4</v>
+        <v>23.5</v>
       </c>
       <c r="K14" t="n">
-        <v>14.1</v>
+        <v>8.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>58.3</v>
+        <v>57.2</v>
       </c>
       <c r="D15" t="n">
-        <v>52.3</v>
+        <v>63.9</v>
       </c>
       <c r="E15" t="n">
-        <v>8.3</v>
+        <v>18.3</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>48.9</v>
       </c>
       <c r="G15" t="n">
-        <v>16.7</v>
+        <v>7.1</v>
       </c>
       <c r="H15" t="n">
-        <v>66.7</v>
+        <v>54.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
-        <v>23.5</v>
+        <v>28.6</v>
       </c>
       <c r="K15" t="n">
-        <v>8.3</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>57.2</v>
+        <v>33.3</v>
       </c>
       <c r="D16" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="E16" t="n">
-        <v>18.3</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="E16"/>
       <c r="F16" t="n">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>54.5</v>
+        <v>66.7</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>30</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>33.3</v>
+        <v>42.9</v>
       </c>
       <c r="D17" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="E17"/>
+        <v>52.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.5</v>
+      </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="H17" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-21.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>42.9</v>
+        <v>51.6</v>
       </c>
       <c r="D18" t="n">
-        <v>52.2</v>
+        <v>56.1</v>
       </c>
       <c r="E18" t="n">
-        <v>10.5</v>
+        <v>17.4</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="G18" t="n">
-        <v>21.4</v>
+        <v>23.6</v>
       </c>
       <c r="H18" t="n">
-        <v>55.6</v>
+        <v>46.9</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.4</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="n">
-        <v>51.6</v>
+        <v>52.9</v>
       </c>
       <c r="D19" t="n">
-        <v>56.1</v>
+        <v>39.1</v>
       </c>
       <c r="E19" t="n">
-        <v>17.4</v>
+        <v>10.4</v>
       </c>
       <c r="F19" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>23.6</v>
+        <v>35.3</v>
       </c>
       <c r="H19" t="n">
-        <v>46.9</v>
+        <v>55.6</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>22.4</v>
+        <v>8.3</v>
       </c>
       <c r="K19" t="n">
-        <v>-9</v>
+        <v>-35.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="D20" t="n">
-        <v>39.1</v>
+        <v>59.6</v>
       </c>
       <c r="E20" t="n">
-        <v>10.4</v>
+        <v>7.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>35.3</v>
+        <v>17.4</v>
       </c>
       <c r="H20" t="n">
-        <v>55.6</v>
+        <v>38.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>8.3</v>
+        <v>27.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-35.3</v>
+        <v>8.7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
@@ -7695,4004 +7660,3969 @@
         <v>50</v>
       </c>
       <c r="D21" t="n">
-        <v>59.6</v>
+        <v>56.2</v>
       </c>
       <c r="E21" t="n">
-        <v>7.9</v>
+        <v>14.7</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>17.4</v>
+        <v>12.1</v>
       </c>
       <c r="H21" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="I21" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>27.8</v>
+        <v>17.3</v>
       </c>
       <c r="K21" t="n">
-        <v>8.7</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
         <v>33</v>
       </c>
       <c r="C22" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D22" t="n">
-        <v>56.2</v>
+        <v>62.6</v>
       </c>
       <c r="E22" t="n">
-        <v>14.7</v>
+        <v>29.5</v>
       </c>
       <c r="F22" t="n">
-        <v>22</v>
+        <v>38.5</v>
       </c>
       <c r="G22" t="n">
-        <v>12.1</v>
+        <v>9.3</v>
       </c>
       <c r="H22" t="n">
-        <v>38.6</v>
+        <v>45.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>17.3</v>
+        <v>25.8</v>
       </c>
       <c r="K22" t="n">
-        <v>-3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s">
         <v>33</v>
       </c>
       <c r="C23" t="n">
-        <v>64</v>
+        <v>66.7</v>
       </c>
       <c r="D23" t="n">
-        <v>62.6</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
-        <v>29.5</v>
+        <v>25</v>
       </c>
       <c r="F23" t="n">
-        <v>38.5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>9.3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>45.7</v>
+        <v>75</v>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>25.8</v>
+        <v>14.3</v>
       </c>
       <c r="K23" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B24" t="s">
         <v>33</v>
       </c>
       <c r="C24" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>61.5</v>
       </c>
       <c r="E24" t="n">
-        <v>25</v>
+        <v>33.8</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="H24" t="n">
-        <v>75</v>
+        <v>52.6</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>14.3</v>
+        <v>20.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B25" t="s">
         <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>55.6</v>
+        <v>58</v>
       </c>
       <c r="D25" t="n">
-        <v>61.5</v>
+        <v>60.6</v>
       </c>
       <c r="E25" t="n">
-        <v>33.8</v>
+        <v>12.1</v>
       </c>
       <c r="F25" t="n">
-        <v>33.3</v>
+        <v>48.5</v>
       </c>
       <c r="G25" t="n">
-        <v>7.4</v>
+        <v>17.9</v>
       </c>
       <c r="H25" t="n">
-        <v>52.6</v>
+        <v>46.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>20.5</v>
+        <v>37.3</v>
       </c>
       <c r="K25" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
         <v>33</v>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>43.3</v>
       </c>
       <c r="D26" t="n">
-        <v>60.6</v>
+        <v>51.2</v>
       </c>
       <c r="E26" t="n">
-        <v>12.1</v>
+        <v>15.9</v>
       </c>
       <c r="F26" t="n">
-        <v>48.5</v>
+        <v>37.9</v>
       </c>
       <c r="G26" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="H26" t="n">
-        <v>46.2</v>
+        <v>42.4</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>37.3</v>
+        <v>29.2</v>
       </c>
       <c r="K26" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s">
         <v>33</v>
       </c>
       <c r="C27" t="n">
-        <v>43.3</v>
+        <v>66.7</v>
       </c>
       <c r="D27" t="n">
-        <v>51.2</v>
+        <v>68.1</v>
       </c>
       <c r="E27" t="n">
-        <v>15.9</v>
+        <v>37.8</v>
       </c>
       <c r="F27" t="n">
-        <v>37.9</v>
+        <v>54.5</v>
       </c>
       <c r="G27" t="n">
-        <v>18.6</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>42.4</v>
+        <v>45.5</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>29.2</v>
+        <v>40.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>66.7</v>
+        <v>55.4</v>
       </c>
       <c r="D28" t="n">
-        <v>68.1</v>
+        <v>65.5</v>
       </c>
       <c r="E28" t="n">
-        <v>37.8</v>
+        <v>26.7</v>
       </c>
       <c r="F28" t="n">
-        <v>54.5</v>
+        <v>45.5</v>
       </c>
       <c r="G28" t="n">
-        <v>6.7</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>45.5</v>
+        <v>58.1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>40.2</v>
+        <v>24.1</v>
       </c>
       <c r="K28" t="n">
-        <v>33.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>
       </c>
       <c r="C29" t="n">
-        <v>55.4</v>
+        <v>55.7</v>
       </c>
       <c r="D29" t="n">
-        <v>65.5</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>26.7</v>
+        <v>21.3</v>
       </c>
       <c r="F29" t="n">
-        <v>45.5</v>
+        <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>17.4</v>
       </c>
       <c r="H29" t="n">
-        <v>58.1</v>
+        <v>53.7</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>24.1</v>
+        <v>21.2</v>
       </c>
       <c r="K29" t="n">
-        <v>14.4</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B30" t="s">
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>55.7</v>
+        <v>59.1</v>
       </c>
       <c r="D30" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
       <c r="E30" t="n">
-        <v>21.3</v>
+        <v>18.5</v>
       </c>
       <c r="F30" t="n">
-        <v>35</v>
+        <v>17.1</v>
       </c>
       <c r="G30" t="n">
-        <v>17.4</v>
+        <v>13.8</v>
       </c>
       <c r="H30" t="n">
-        <v>53.7</v>
+        <v>44.6</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.1</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
         <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>59.1</v>
+        <v>56.7</v>
       </c>
       <c r="D31" t="n">
-        <v>57.8</v>
+        <v>60.8</v>
       </c>
       <c r="E31" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>17.1</v>
+        <v>41.7</v>
       </c>
       <c r="G31" t="n">
-        <v>13.8</v>
+        <v>3.3</v>
       </c>
       <c r="H31" t="n">
-        <v>44.6</v>
+        <v>41.2</v>
       </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="J31" t="n">
-        <v>22.8</v>
+        <v>27.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-5.8</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B32" t="s">
         <v>33</v>
       </c>
       <c r="C32" t="n">
-        <v>56.7</v>
+        <v>58.2</v>
       </c>
       <c r="D32" t="n">
-        <v>60.8</v>
+        <v>60.5</v>
       </c>
       <c r="E32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F32" t="n">
         <v>41.7</v>
       </c>
       <c r="G32" t="n">
-        <v>3.3</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="n">
-        <v>41.2</v>
+        <v>43.9</v>
       </c>
       <c r="I32" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J32" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="C33" t="n">
-        <v>58.2</v>
+        <v>78.6</v>
       </c>
       <c r="D33" t="n">
-        <v>60.5</v>
+        <v>79.1</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>30.8</v>
       </c>
       <c r="F33" t="n">
-        <v>41.7</v>
+        <v>16.7</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>43.9</v>
+        <v>30.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4.5</v>
+        <v>21.4</v>
       </c>
       <c r="J33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>16.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s">
         <v>49</v>
       </c>
       <c r="C34" t="n">
-        <v>78.6</v>
+        <v>52.5</v>
       </c>
       <c r="D34" t="n">
-        <v>79.1</v>
+        <v>59.1</v>
       </c>
       <c r="E34" t="n">
-        <v>30.8</v>
+        <v>15.9</v>
       </c>
       <c r="F34" t="n">
-        <v>16.7</v>
+        <v>29.4</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H34" t="n">
-        <v>30.8</v>
+        <v>46</v>
       </c>
       <c r="I34" t="n">
-        <v>21.4</v>
+        <v>8.5</v>
       </c>
       <c r="J34" t="n">
-        <v>10</v>
+        <v>18.8</v>
       </c>
       <c r="K34" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B35" t="s">
         <v>49</v>
       </c>
       <c r="C35" t="n">
-        <v>52.5</v>
+        <v>45.8</v>
       </c>
       <c r="D35" t="n">
-        <v>59.1</v>
+        <v>57</v>
       </c>
       <c r="E35" t="n">
-        <v>15.9</v>
+        <v>17.6</v>
       </c>
       <c r="F35" t="n">
-        <v>29.4</v>
+        <v>28.6</v>
       </c>
       <c r="G35" t="n">
-        <v>10.3</v>
+        <v>20.8</v>
       </c>
       <c r="H35" t="n">
-        <v>46</v>
+        <v>42.9</v>
       </c>
       <c r="I35" t="n">
-        <v>8.5</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
-        <v>18.8</v>
+        <v>24.4</v>
       </c>
       <c r="K35" t="n">
-        <v>2.5</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B36" t="s">
         <v>49</v>
       </c>
       <c r="C36" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="D36" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H36" t="n">
         <v>45.8</v>
       </c>
-      <c r="D36" t="n">
-        <v>57</v>
-      </c>
-      <c r="E36" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F36" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="H36" t="n">
-        <v>42.9</v>
-      </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="K36" t="n">
-        <v>-4.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>52</v>
       </c>
       <c r="B37" t="s">
         <v>49</v>
       </c>
       <c r="C37" t="n">
-        <v>52.9</v>
+        <v>47.8</v>
       </c>
       <c r="D37" t="n">
-        <v>57.7</v>
+        <v>53.7</v>
       </c>
       <c r="E37" t="n">
-        <v>11.1</v>
+        <v>12.1</v>
       </c>
       <c r="F37" t="n">
-        <v>35.3</v>
+        <v>28.6</v>
       </c>
       <c r="G37" t="n">
-        <v>11.6</v>
+        <v>15.2</v>
       </c>
       <c r="H37" t="n">
-        <v>45.8</v>
+        <v>53.3</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J37" t="n">
-        <v>23.1</v>
+        <v>19.4</v>
       </c>
       <c r="K37" t="n">
-        <v>5.8</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>52</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
         <v>49</v>
       </c>
       <c r="C38" t="n">
-        <v>47.8</v>
+        <v>48.8</v>
       </c>
       <c r="D38" t="n">
-        <v>53.7</v>
+        <v>55.8</v>
       </c>
       <c r="E38" t="n">
-        <v>12.1</v>
+        <v>15.2</v>
       </c>
       <c r="F38" t="n">
-        <v>28.6</v>
+        <v>37.3</v>
       </c>
       <c r="G38" t="n">
-        <v>15.2</v>
+        <v>11.7</v>
       </c>
       <c r="H38" t="n">
-        <v>53.3</v>
+        <v>54.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4.3</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
-        <v>19.4</v>
+        <v>24.9</v>
       </c>
       <c r="K38" t="n">
-        <v>-2.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B39" t="s">
         <v>49</v>
       </c>
       <c r="C39" t="n">
-        <v>48.8</v>
+        <v>59</v>
       </c>
       <c r="D39" t="n">
-        <v>55.8</v>
+        <v>63.6</v>
       </c>
       <c r="E39" t="n">
-        <v>15.2</v>
+        <v>16.7</v>
       </c>
       <c r="F39" t="n">
-        <v>37.3</v>
+        <v>21.9</v>
       </c>
       <c r="G39" t="n">
-        <v>11.7</v>
+        <v>9.1</v>
       </c>
       <c r="H39" t="n">
-        <v>54.7</v>
+        <v>34.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J39" t="n">
-        <v>24.9</v>
+        <v>20.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B40" t="s">
         <v>49</v>
       </c>
       <c r="C40" t="n">
-        <v>59</v>
+        <v>54.8</v>
       </c>
       <c r="D40" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="E40" t="n">
-        <v>16.7</v>
+        <v>23.7</v>
       </c>
       <c r="F40" t="n">
-        <v>21.9</v>
+        <v>50</v>
       </c>
       <c r="G40" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="H40" t="n">
-        <v>34.5</v>
+        <v>38.1</v>
       </c>
       <c r="I40" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J40" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
         <v>49</v>
       </c>
       <c r="C41" t="n">
-        <v>54.8</v>
+        <v>100</v>
       </c>
       <c r="D41" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
+        <v>100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41"/>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>50</v>
       </c>
-      <c r="G41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H41" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>20.8</v>
-      </c>
       <c r="K41" t="n">
-        <v>16.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>218</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
       </c>
       <c r="C42" t="n">
-        <v>100</v>
+        <v>66.3</v>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>52.9</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42"/>
+        <v>2.4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>62.3</v>
+      </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>19.1</v>
       </c>
       <c r="K42" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B43" t="s">
         <v>49</v>
       </c>
       <c r="C43" t="n">
-        <v>66.3</v>
+        <v>57</v>
       </c>
       <c r="D43" t="n">
-        <v>65</v>
+        <v>61.8</v>
       </c>
       <c r="E43" t="n">
-        <v>15.5</v>
+        <v>18.4</v>
       </c>
       <c r="F43" t="n">
-        <v>52.9</v>
+        <v>48.6</v>
       </c>
       <c r="G43" t="n">
-        <v>2.4</v>
+        <v>11.6</v>
       </c>
       <c r="H43" t="n">
-        <v>62.3</v>
+        <v>47.3</v>
       </c>
       <c r="I43" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J43" t="n">
-        <v>19.1</v>
+        <v>27.3</v>
       </c>
       <c r="K43" t="n">
-        <v>19</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B44" t="s">
         <v>49</v>
       </c>
       <c r="C44" t="n">
-        <v>57</v>
+        <v>60.4</v>
       </c>
       <c r="D44" t="n">
-        <v>61.8</v>
+        <v>66.4</v>
       </c>
       <c r="E44" t="n">
-        <v>18.4</v>
+        <v>20.3</v>
       </c>
       <c r="F44" t="n">
-        <v>48.6</v>
+        <v>45.3</v>
       </c>
       <c r="G44" t="n">
-        <v>11.6</v>
+        <v>4.9</v>
       </c>
       <c r="H44" t="n">
-        <v>47.3</v>
+        <v>35.2</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J44" t="n">
-        <v>27.3</v>
+        <v>25.9</v>
       </c>
       <c r="K44" t="n">
-        <v>8.2</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B45" t="s">
         <v>49</v>
       </c>
       <c r="C45" t="n">
-        <v>60.4</v>
+        <v>55.4</v>
       </c>
       <c r="D45" t="n">
-        <v>66.4</v>
+        <v>62.1</v>
       </c>
       <c r="E45" t="n">
-        <v>20.3</v>
+        <v>22.8</v>
       </c>
       <c r="F45" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="G45" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="H45" t="n">
-        <v>35.2</v>
+        <v>48.9</v>
       </c>
       <c r="I45" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="J45" t="n">
-        <v>25.9</v>
+        <v>31.8</v>
       </c>
       <c r="K45" t="n">
-        <v>21.6</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B46" t="s">
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>55.4</v>
+        <v>81.2</v>
       </c>
       <c r="D46" t="n">
-        <v>62.1</v>
+        <v>72.9</v>
       </c>
       <c r="E46" t="n">
-        <v>22.8</v>
+        <v>25</v>
       </c>
       <c r="F46" t="n">
-        <v>45.2</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H46" t="n">
-        <v>48.9</v>
+        <v>54.5</v>
       </c>
       <c r="I46" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>31.8</v>
+        <v>29.2</v>
       </c>
       <c r="K46" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>81.2</v>
+        <v>58</v>
       </c>
       <c r="D47" t="n">
-        <v>72.9</v>
+        <v>64</v>
       </c>
       <c r="E47" t="n">
-        <v>25</v>
+        <v>16.3</v>
       </c>
       <c r="F47" t="n">
-        <v>50</v>
+        <v>44.7</v>
       </c>
       <c r="G47" t="n">
         <v>6.2</v>
       </c>
       <c r="H47" t="n">
-        <v>54.5</v>
+        <v>52.8</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="J47" t="n">
-        <v>29.2</v>
+        <v>26.6</v>
       </c>
       <c r="K47" t="n">
-        <v>18.8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
         <v>49</v>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>44.4</v>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.3</v>
-      </c>
+        <v>45.5</v>
+      </c>
+      <c r="E48"/>
       <c r="F48" t="n">
-        <v>44.7</v>
+        <v>25</v>
       </c>
       <c r="G48" t="n">
-        <v>6.2</v>
+        <v>33.3</v>
       </c>
       <c r="H48" t="n">
-        <v>52.8</v>
+        <v>20</v>
       </c>
       <c r="I48" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>26.6</v>
+        <v>27.3</v>
       </c>
       <c r="K48" t="n">
-        <v>21</v>
+        <v>-22.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s">
         <v>49</v>
       </c>
       <c r="C49" t="n">
-        <v>44.4</v>
+        <v>51.8</v>
       </c>
       <c r="D49" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="E49"/>
+        <v>57</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15.4</v>
+      </c>
       <c r="F49" t="n">
-        <v>25</v>
+        <v>22.8</v>
       </c>
       <c r="G49" t="n">
-        <v>33.3</v>
+        <v>9.6</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>38.4</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>27.3</v>
+        <v>12.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-22.2</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C50" t="n">
-        <v>51.8</v>
+        <v>60</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="E50" t="n">
-        <v>15.4</v>
+        <v>16.9</v>
       </c>
       <c r="F50" t="n">
-        <v>22.8</v>
+        <v>38.1</v>
       </c>
       <c r="G50" t="n">
-        <v>9.6</v>
+        <v>14.6</v>
       </c>
       <c r="H50" t="n">
-        <v>38.4</v>
+        <v>31.2</v>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="J50" t="n">
-        <v>12.9</v>
+        <v>28.4</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
         <v>67</v>
       </c>
       <c r="C51" t="n">
-        <v>60</v>
+        <v>70.9</v>
       </c>
       <c r="D51" t="n">
-        <v>56.5</v>
+        <v>74</v>
       </c>
       <c r="E51" t="n">
-        <v>16.9</v>
+        <v>40.8</v>
       </c>
       <c r="F51" t="n">
-        <v>38.1</v>
+        <v>71.4</v>
       </c>
       <c r="G51" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>31.2</v>
+        <v>41.4</v>
       </c>
       <c r="I51" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J51" t="n">
-        <v>28.4</v>
+        <v>43.3</v>
       </c>
       <c r="K51" t="n">
-        <v>4.9</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B52" t="s">
         <v>67</v>
       </c>
       <c r="C52" t="n">
-        <v>70.9</v>
+        <v>60.6</v>
       </c>
       <c r="D52" t="n">
-        <v>74</v>
+        <v>61.2</v>
       </c>
       <c r="E52" t="n">
-        <v>40.8</v>
+        <v>21.5</v>
       </c>
       <c r="F52" t="n">
-        <v>71.4</v>
+        <v>47.8</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="H52" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="J52" t="n">
-        <v>43.3</v>
+        <v>35.1</v>
       </c>
       <c r="K52" t="n">
-        <v>38.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B53" t="s">
         <v>67</v>
       </c>
       <c r="C53" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D53" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>21.5</v>
-      </c>
+        <v>71.4</v>
+      </c>
+      <c r="E53"/>
       <c r="F53" t="n">
-        <v>47.8</v>
+        <v>33.3</v>
       </c>
       <c r="G53" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>35.1</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>20.6</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>231</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
         <v>67</v>
       </c>
       <c r="C54" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>72.9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="F54" t="n">
         <v>66.7</v>
       </c>
-      <c r="D54" t="n">
-        <v>71.4</v>
-      </c>
-      <c r="E54"/>
-      <c r="F54" t="n">
-        <v>33.3</v>
-      </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>33.3</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>71</v>
+        <v>230</v>
       </c>
       <c r="B55" t="s">
         <v>67</v>
       </c>
       <c r="C55" t="n">
-        <v>77.8</v>
+        <v>65.6</v>
       </c>
       <c r="D55" t="n">
-        <v>72.9</v>
+        <v>67</v>
       </c>
       <c r="E55" t="n">
-        <v>42.9</v>
+        <v>18.2</v>
       </c>
       <c r="F55" t="n">
-        <v>66.7</v>
+        <v>34.1</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="H55" t="n">
-        <v>55.6</v>
+        <v>40.4</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>47.1</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
       </c>
       <c r="C56" t="n">
-        <v>65.6</v>
+        <v>57.3</v>
       </c>
       <c r="D56" t="n">
-        <v>67</v>
+        <v>60.4</v>
       </c>
       <c r="E56" t="n">
-        <v>18.2</v>
+        <v>24</v>
       </c>
       <c r="F56" t="n">
-        <v>34.1</v>
+        <v>44</v>
       </c>
       <c r="G56" t="n">
-        <v>4.4</v>
+        <v>12.6</v>
       </c>
       <c r="H56" t="n">
-        <v>40.4</v>
+        <v>38.6</v>
       </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
-        <v>22</v>
+        <v>35.9</v>
       </c>
       <c r="K56" t="n">
-        <v>12.2</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>233</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
         <v>67</v>
       </c>
       <c r="C57" t="n">
+        <v>67.6</v>
+      </c>
+      <c r="D57" t="n">
         <v>57.3</v>
       </c>
-      <c r="D57" t="n">
-        <v>60.4</v>
-      </c>
       <c r="E57" t="n">
-        <v>24</v>
+        <v>11.6</v>
       </c>
       <c r="F57" t="n">
-        <v>44</v>
+        <v>57.1</v>
       </c>
       <c r="G57" t="n">
-        <v>12.6</v>
+        <v>22.9</v>
       </c>
       <c r="H57" t="n">
-        <v>38.6</v>
+        <v>33.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>35.9</v>
+        <v>39.7</v>
       </c>
       <c r="K57" t="n">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
         <v>67</v>
       </c>
       <c r="C58" t="n">
-        <v>67.6</v>
+        <v>61.1</v>
       </c>
       <c r="D58" t="n">
-        <v>57.3</v>
+        <v>62.7</v>
       </c>
       <c r="E58" t="n">
-        <v>11.6</v>
+        <v>23.4</v>
       </c>
       <c r="F58" t="n">
-        <v>57.1</v>
+        <v>35.4</v>
       </c>
       <c r="G58" t="n">
-        <v>22.9</v>
+        <v>8.3</v>
       </c>
       <c r="H58" t="n">
-        <v>33.3</v>
+        <v>34.6</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
-        <v>39.7</v>
+        <v>15.7</v>
       </c>
       <c r="K58" t="n">
-        <v>11.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B59" t="s">
         <v>67</v>
       </c>
       <c r="C59" t="n">
-        <v>61.1</v>
+        <v>62</v>
       </c>
       <c r="D59" t="n">
-        <v>62.7</v>
+        <v>65</v>
       </c>
       <c r="E59" t="n">
-        <v>23.4</v>
+        <v>20.7</v>
       </c>
       <c r="F59" t="n">
-        <v>35.4</v>
+        <v>48.8</v>
       </c>
       <c r="G59" t="n">
-        <v>8.3</v>
+        <v>6.3</v>
       </c>
       <c r="H59" t="n">
-        <v>34.6</v>
+        <v>62</v>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J59" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>4.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B60" t="s">
         <v>67</v>
       </c>
       <c r="C60" t="n">
-        <v>62</v>
+        <v>56.5</v>
       </c>
       <c r="D60" t="n">
-        <v>65</v>
+        <v>61.6</v>
       </c>
       <c r="E60" t="n">
-        <v>20.7</v>
+        <v>6.5</v>
       </c>
       <c r="F60" t="n">
-        <v>48.8</v>
+        <v>42.9</v>
       </c>
       <c r="G60" t="n">
-        <v>6.3</v>
+        <v>8.9</v>
       </c>
       <c r="H60" t="n">
-        <v>62</v>
+        <v>56.2</v>
       </c>
       <c r="I60" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="J60" t="n">
-        <v>33.3</v>
+        <v>23.8</v>
       </c>
       <c r="K60" t="n">
-        <v>19</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B61" t="s">
         <v>67</v>
       </c>
       <c r="C61" t="n">
-        <v>56.5</v>
+        <v>65.7</v>
       </c>
       <c r="D61" t="n">
-        <v>61.6</v>
+        <v>66.9</v>
       </c>
       <c r="E61" t="n">
-        <v>6.5</v>
+        <v>29.4</v>
       </c>
       <c r="F61" t="n">
-        <v>42.9</v>
+        <v>34.5</v>
       </c>
       <c r="G61" t="n">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="H61" t="n">
-        <v>56.2</v>
+        <v>55.8</v>
       </c>
       <c r="I61" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="J61" t="n">
-        <v>23.8</v>
+        <v>19.6</v>
       </c>
       <c r="K61" t="n">
-        <v>11.1</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
         <v>67</v>
       </c>
       <c r="C62" t="n">
-        <v>65.7</v>
+        <v>62.3</v>
       </c>
       <c r="D62" t="n">
-        <v>66.9</v>
+        <v>64.6</v>
       </c>
       <c r="E62" t="n">
-        <v>29.4</v>
+        <v>25</v>
       </c>
       <c r="F62" t="n">
-        <v>34.5</v>
+        <v>37.5</v>
       </c>
       <c r="G62" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H62" t="n">
-        <v>55.8</v>
+        <v>22.9</v>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="K62" t="n">
-        <v>9.6</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>238</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
         <v>67</v>
       </c>
       <c r="C63" t="n">
-        <v>62.3</v>
+        <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>64.6</v>
+        <v>60.6</v>
       </c>
       <c r="E63" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
         <v>25</v>
       </c>
-      <c r="F63" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H63" t="n">
-        <v>22.9</v>
-      </c>
       <c r="I63" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J63" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>86</v>
+        <v>237</v>
       </c>
       <c r="B64" t="s">
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>30</v>
+        <v>44.4</v>
       </c>
       <c r="D64" t="n">
-        <v>60.6</v>
+        <v>48.6</v>
       </c>
       <c r="E64" t="n">
-        <v>46.7</v>
+        <v>15.7</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>23.8</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="H64" t="n">
-        <v>25</v>
+        <v>54.2</v>
       </c>
       <c r="I64" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>31.1</v>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="B65" t="s">
         <v>67</v>
       </c>
       <c r="C65" t="n">
-        <v>44.4</v>
+        <v>62.5</v>
       </c>
       <c r="D65" t="n">
-        <v>48.6</v>
+        <v>64</v>
       </c>
       <c r="E65" t="n">
-        <v>15.7</v>
+        <v>33.3</v>
       </c>
       <c r="F65" t="n">
-        <v>23.8</v>
+        <v>66.7</v>
       </c>
       <c r="G65" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>54.2</v>
+        <v>16.7</v>
       </c>
       <c r="I65" t="n">
-        <v>8.9</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>31.1</v>
+        <v>16.7</v>
       </c>
       <c r="K65" t="n">
-        <v>-15.6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>88</v>
+        <v>238</v>
       </c>
       <c r="B66" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C66" t="n">
-        <v>62.5</v>
+        <v>72.4</v>
       </c>
       <c r="D66" t="n">
-        <v>64</v>
+        <v>71.8</v>
       </c>
       <c r="E66" t="n">
-        <v>33.3</v>
+        <v>16.4</v>
       </c>
       <c r="F66" t="n">
-        <v>66.7</v>
+        <v>37.8</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="H66" t="n">
-        <v>16.7</v>
+        <v>45.8</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>1.1</v>
       </c>
       <c r="J66" t="n">
-        <v>16.7</v>
+        <v>22.8</v>
       </c>
       <c r="K66" t="n">
-        <v>25</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B67" t="s">
         <v>92</v>
       </c>
       <c r="C67" t="n">
-        <v>72.4</v>
+        <v>66.7</v>
       </c>
       <c r="D67" t="n">
-        <v>71.8</v>
+        <v>66</v>
       </c>
       <c r="E67" t="n">
-        <v>16.4</v>
+        <v>13.5</v>
       </c>
       <c r="F67" t="n">
-        <v>37.8</v>
+        <v>22.2</v>
       </c>
       <c r="G67" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="H67" t="n">
-        <v>45.8</v>
+        <v>37.9</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="J67" t="n">
-        <v>22.8</v>
+        <v>9.3</v>
       </c>
       <c r="K67" t="n">
-        <v>17.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B68" t="s">
         <v>92</v>
       </c>
       <c r="C68" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="D68" t="n">
-        <v>66</v>
+        <v>68.3</v>
       </c>
       <c r="E68" t="n">
-        <v>13.5</v>
+        <v>26.5</v>
       </c>
       <c r="F68" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="G68" t="n">
-        <v>2.8</v>
+        <v>9.1</v>
       </c>
       <c r="H68" t="n">
-        <v>37.9</v>
+        <v>38.9</v>
       </c>
       <c r="I68" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>9.3</v>
+        <v>8.9</v>
       </c>
       <c r="K68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B69" t="s">
         <v>92</v>
       </c>
       <c r="C69" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="D69" t="n">
-        <v>68.3</v>
+        <v>60.5</v>
       </c>
       <c r="E69" t="n">
-        <v>26.5</v>
+        <v>20</v>
       </c>
       <c r="F69" t="n">
-        <v>16.7</v>
+        <v>38.9</v>
       </c>
       <c r="G69" t="n">
-        <v>9.1</v>
+        <v>11.4</v>
       </c>
       <c r="H69" t="n">
-        <v>38.9</v>
+        <v>46.7</v>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J69" t="n">
-        <v>8.9</v>
+        <v>18.5</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>92</v>
       </c>
       <c r="C70" t="n">
-        <v>55.6</v>
+        <v>54.8</v>
       </c>
       <c r="D70" t="n">
-        <v>60.5</v>
+        <v>62.4</v>
       </c>
       <c r="E70" t="n">
         <v>20</v>
       </c>
       <c r="F70" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="G70" t="n">
-        <v>11.4</v>
+        <v>14.3</v>
       </c>
       <c r="H70" t="n">
-        <v>46.7</v>
+        <v>54.2</v>
       </c>
       <c r="I70" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>18.5</v>
+        <v>25.5</v>
       </c>
       <c r="K70" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>92</v>
       </c>
       <c r="C71" t="n">
-        <v>54.8</v>
+        <v>61.1</v>
       </c>
       <c r="D71" t="n">
-        <v>62.4</v>
+        <v>63</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>17.6</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G71" t="n">
-        <v>14.3</v>
+        <v>7.2</v>
       </c>
       <c r="H71" t="n">
-        <v>54.2</v>
+        <v>56.5</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
-        <v>25.5</v>
+        <v>36.2</v>
       </c>
       <c r="K71" t="n">
-        <v>4.7</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
         <v>92</v>
       </c>
       <c r="C72" t="n">
-        <v>61.1</v>
+        <v>63.8</v>
       </c>
       <c r="D72" t="n">
-        <v>63</v>
+        <v>61.7</v>
       </c>
       <c r="E72" t="n">
-        <v>17.6</v>
+        <v>26.4</v>
       </c>
       <c r="F72" t="n">
-        <v>55</v>
+        <v>57.6</v>
       </c>
       <c r="G72" t="n">
-        <v>7.2</v>
+        <v>8.2</v>
       </c>
       <c r="H72" t="n">
-        <v>56.5</v>
+        <v>53.3</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
-        <v>36.2</v>
+        <v>38.4</v>
       </c>
       <c r="K72" t="n">
-        <v>22.5</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s">
         <v>92</v>
       </c>
       <c r="C73" t="n">
-        <v>63.8</v>
+        <v>51.6</v>
       </c>
       <c r="D73" t="n">
-        <v>61.7</v>
+        <v>62.4</v>
       </c>
       <c r="E73" t="n">
-        <v>26.4</v>
+        <v>34.5</v>
       </c>
       <c r="F73" t="n">
-        <v>57.6</v>
+        <v>18.8</v>
       </c>
       <c r="G73" t="n">
-        <v>8.2</v>
+        <v>12.9</v>
       </c>
       <c r="H73" t="n">
-        <v>53.3</v>
+        <v>50</v>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J73" t="n">
-        <v>38.4</v>
+        <v>21.7</v>
       </c>
       <c r="K73" t="n">
-        <v>27.9</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B74" t="s">
         <v>92</v>
       </c>
       <c r="C74" t="n">
-        <v>51.6</v>
+        <v>58.8</v>
       </c>
       <c r="D74" t="n">
-        <v>62.4</v>
+        <v>60.7</v>
       </c>
       <c r="E74" t="n">
-        <v>34.5</v>
+        <v>23.5</v>
       </c>
       <c r="F74" t="n">
-        <v>18.8</v>
+        <v>36.4</v>
       </c>
       <c r="G74" t="n">
-        <v>12.9</v>
+        <v>15.2</v>
       </c>
       <c r="H74" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>21.7</v>
+        <v>30.5</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
         <v>92</v>
       </c>
       <c r="C75" t="n">
-        <v>58.8</v>
+        <v>69.4</v>
       </c>
       <c r="D75" t="n">
-        <v>60.7</v>
+        <v>69.9</v>
       </c>
       <c r="E75" t="n">
-        <v>23.5</v>
+        <v>26.9</v>
       </c>
       <c r="F75" t="n">
-        <v>36.4</v>
+        <v>44.9</v>
       </c>
       <c r="G75" t="n">
-        <v>15.2</v>
+        <v>7.4</v>
       </c>
       <c r="H75" t="n">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J75" t="n">
-        <v>30.5</v>
+        <v>25.1</v>
       </c>
       <c r="K75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B76" t="s">
         <v>92</v>
       </c>
       <c r="C76" t="n">
-        <v>69.4</v>
+        <v>60.3</v>
       </c>
       <c r="D76" t="n">
-        <v>69.9</v>
+        <v>63.2</v>
       </c>
       <c r="E76" t="n">
-        <v>26.9</v>
+        <v>24.5</v>
       </c>
       <c r="F76" t="n">
-        <v>44.9</v>
+        <v>54.4</v>
       </c>
       <c r="G76" t="n">
-        <v>7.4</v>
+        <v>8.3</v>
       </c>
       <c r="H76" t="n">
-        <v>51.9</v>
+        <v>42.6</v>
       </c>
       <c r="I76" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J76" t="n">
-        <v>25.1</v>
+        <v>29.9</v>
       </c>
       <c r="K76" t="n">
-        <v>13</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B77" t="s">
         <v>92</v>
       </c>
       <c r="C77" t="n">
-        <v>60.3</v>
+        <v>61.5</v>
       </c>
       <c r="D77" t="n">
-        <v>63.2</v>
+        <v>62.9</v>
       </c>
       <c r="E77" t="n">
-        <v>24.5</v>
+        <v>21.1</v>
       </c>
       <c r="F77" t="n">
-        <v>54.4</v>
+        <v>47.6</v>
       </c>
       <c r="G77" t="n">
-        <v>8.3</v>
+        <v>10</v>
       </c>
       <c r="H77" t="n">
-        <v>42.6</v>
+        <v>61.3</v>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
-        <v>29.9</v>
+        <v>21.7</v>
       </c>
       <c r="K77" t="n">
-        <v>18.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C78" t="n">
-        <v>61.5</v>
+        <v>42</v>
       </c>
       <c r="D78" t="n">
-        <v>62.9</v>
+        <v>44.7</v>
       </c>
       <c r="E78" t="n">
-        <v>21.1</v>
+        <v>6.3</v>
       </c>
       <c r="F78" t="n">
-        <v>47.6</v>
+        <v>46.4</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>32.4</v>
       </c>
       <c r="H78" t="n">
-        <v>61.3</v>
+        <v>41.4</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J78" t="n">
-        <v>21.7</v>
+        <v>30.4</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B79" t="s">
         <v>107</v>
       </c>
       <c r="C79" t="n">
-        <v>42</v>
+        <v>64.6</v>
       </c>
       <c r="D79" t="n">
-        <v>44.7</v>
+        <v>63.3</v>
       </c>
       <c r="E79" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>49</v>
+      </c>
+      <c r="G79" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H79" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I79" t="n">
         <v>6.3</v>
       </c>
-      <c r="F79" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="G79" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="H79" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2.9</v>
-      </c>
       <c r="J79" t="n">
-        <v>30.4</v>
+        <v>29.7</v>
       </c>
       <c r="K79" t="n">
-        <v>-13.3</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="B80" t="s">
         <v>107</v>
       </c>
       <c r="C80" t="n">
-        <v>64.6</v>
+        <v>50</v>
       </c>
       <c r="D80" t="n">
-        <v>63.3</v>
+        <v>53.1</v>
       </c>
       <c r="E80" t="n">
-        <v>27.6</v>
+        <v>10.1</v>
       </c>
       <c r="F80" t="n">
-        <v>49</v>
+        <v>46.4</v>
       </c>
       <c r="G80" t="n">
-        <v>10.5</v>
+        <v>14.1</v>
       </c>
       <c r="H80" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="I80" t="n">
-        <v>6.3</v>
+        <v>4.7</v>
       </c>
       <c r="J80" t="n">
-        <v>29.7</v>
+        <v>22.1</v>
       </c>
       <c r="K80" t="n">
-        <v>14.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>28.6</v>
       </c>
       <c r="D81" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="E81" t="n">
-        <v>10.1</v>
-      </c>
+        <v>41.9</v>
+      </c>
+      <c r="E81"/>
       <c r="F81" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>14.1</v>
+        <v>42.9</v>
       </c>
       <c r="H81" t="n">
-        <v>38.5</v>
+        <v>25</v>
       </c>
       <c r="I81" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>22.1</v>
+        <v>14.3</v>
       </c>
       <c r="K81" t="n">
-        <v>6.2</v>
+        <v>-42.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B82" t="s">
         <v>107</v>
       </c>
       <c r="C82" t="n">
-        <v>28.6</v>
+        <v>63.6</v>
       </c>
       <c r="D82" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E82"/>
+        <v>64.4</v>
+      </c>
+      <c r="E82" t="n">
+        <v>25.5</v>
+      </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="G82" t="n">
-        <v>42.9</v>
+        <v>12.1</v>
       </c>
       <c r="H82" t="n">
-        <v>25</v>
+        <v>39.1</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>14.3</v>
+        <v>24.6</v>
       </c>
       <c r="K82" t="n">
-        <v>-42.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B83" t="s">
         <v>107</v>
       </c>
       <c r="C83" t="n">
-        <v>63.6</v>
+        <v>48.6</v>
       </c>
       <c r="D83" t="n">
-        <v>64.4</v>
+        <v>56.4</v>
       </c>
       <c r="E83" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="F83" t="n">
-        <v>31.2</v>
+        <v>41.5</v>
       </c>
       <c r="G83" t="n">
-        <v>12.1</v>
+        <v>14.9</v>
       </c>
       <c r="H83" t="n">
-        <v>39.1</v>
+        <v>32.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="J83" t="n">
-        <v>24.6</v>
+        <v>33.6</v>
       </c>
       <c r="K83" t="n">
-        <v>3.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>256</v>
+        <v>109</v>
       </c>
       <c r="B84" t="s">
         <v>107</v>
       </c>
       <c r="C84" t="n">
-        <v>48.6</v>
+        <v>57.6</v>
       </c>
       <c r="D84" t="n">
-        <v>56.4</v>
+        <v>58.9</v>
       </c>
       <c r="E84" t="n">
-        <v>22.6</v>
+        <v>16.9</v>
       </c>
       <c r="F84" t="n">
-        <v>41.5</v>
+        <v>23.5</v>
       </c>
       <c r="G84" t="n">
-        <v>14.9</v>
+        <v>6.2</v>
       </c>
       <c r="H84" t="n">
-        <v>32.6</v>
+        <v>43.1</v>
       </c>
       <c r="I84" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="J84" t="n">
-        <v>33.6</v>
+        <v>21.1</v>
       </c>
       <c r="K84" t="n">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B85" t="s">
         <v>107</v>
       </c>
       <c r="C85" t="n">
-        <v>57.6</v>
+        <v>61.6</v>
       </c>
       <c r="D85" t="n">
-        <v>58.9</v>
+        <v>66.2</v>
       </c>
       <c r="E85" t="n">
-        <v>16.9</v>
+        <v>26.6</v>
       </c>
       <c r="F85" t="n">
-        <v>23.5</v>
+        <v>37.4</v>
       </c>
       <c r="G85" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H85" t="n">
-        <v>43.1</v>
+        <v>44.6</v>
       </c>
       <c r="I85" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J85" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="K85" t="n">
-        <v>6.1</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>110</v>
+        <v>255</v>
       </c>
       <c r="B86" t="s">
         <v>107</v>
       </c>
       <c r="C86" t="n">
-        <v>61.6</v>
+        <v>45.8</v>
       </c>
       <c r="D86" t="n">
-        <v>66.2</v>
+        <v>55.1</v>
       </c>
       <c r="E86" t="n">
-        <v>26.6</v>
+        <v>10.4</v>
       </c>
       <c r="F86" t="n">
-        <v>37.4</v>
+        <v>26.3</v>
       </c>
       <c r="G86" t="n">
-        <v>5.7</v>
+        <v>15.3</v>
       </c>
       <c r="H86" t="n">
-        <v>44.6</v>
+        <v>47.1</v>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="J86" t="n">
-        <v>21.4</v>
+        <v>33.9</v>
       </c>
       <c r="K86" t="n">
-        <v>10.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B87" t="s">
         <v>107</v>
       </c>
       <c r="C87" t="n">
-        <v>45.8</v>
+        <v>67.3</v>
       </c>
       <c r="D87" t="n">
-        <v>55.1</v>
+        <v>65.4</v>
       </c>
       <c r="E87" t="n">
-        <v>10.4</v>
+        <v>27.7</v>
       </c>
       <c r="F87" t="n">
-        <v>26.3</v>
+        <v>39.3</v>
       </c>
       <c r="G87" t="n">
-        <v>15.3</v>
+        <v>9</v>
       </c>
       <c r="H87" t="n">
-        <v>47.1</v>
+        <v>46.7</v>
       </c>
       <c r="I87" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J87" t="n">
-        <v>33.9</v>
+        <v>29</v>
       </c>
       <c r="K87" t="n">
-        <v>1.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B88" t="s">
         <v>107</v>
       </c>
       <c r="C88" t="n">
-        <v>67.3</v>
+        <v>59.3</v>
       </c>
       <c r="D88" t="n">
-        <v>65.4</v>
+        <v>61.4</v>
       </c>
       <c r="E88" t="n">
-        <v>27.7</v>
+        <v>20</v>
       </c>
       <c r="F88" t="n">
-        <v>39.3</v>
+        <v>35</v>
       </c>
       <c r="G88" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H88" t="n">
-        <v>46.7</v>
+        <v>56.4</v>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J88" t="n">
-        <v>29</v>
+        <v>28.2</v>
       </c>
       <c r="K88" t="n">
-        <v>10.8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B89" t="s">
         <v>107</v>
       </c>
       <c r="C89" t="n">
-        <v>59.3</v>
+        <v>52.6</v>
       </c>
       <c r="D89" t="n">
-        <v>61.4</v>
+        <v>55.6</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>25.6</v>
       </c>
       <c r="F89" t="n">
-        <v>35</v>
+        <v>38.5</v>
       </c>
       <c r="G89" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="H89" t="n">
-        <v>56.4</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J89" t="n">
-        <v>28.2</v>
+        <v>24.9</v>
       </c>
       <c r="K89" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B90" t="s">
         <v>107</v>
       </c>
       <c r="C90" t="n">
-        <v>52.6</v>
+        <v>57.9</v>
       </c>
       <c r="D90" t="n">
-        <v>55.6</v>
+        <v>61.6</v>
       </c>
       <c r="E90" t="n">
-        <v>25.6</v>
+        <v>21.3</v>
       </c>
       <c r="F90" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="G90" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="H90" t="n">
-        <v>30</v>
+        <v>51.2</v>
       </c>
       <c r="I90" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J90" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="K90" t="n">
-        <v>3.9</v>
+        <v>14.2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B91" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C91" t="n">
-        <v>57.9</v>
+        <v>74.2</v>
       </c>
       <c r="D91" t="n">
-        <v>61.6</v>
+        <v>69.7</v>
       </c>
       <c r="E91" t="n">
-        <v>21.3</v>
+        <v>39.1</v>
       </c>
       <c r="F91" t="n">
-        <v>39.4</v>
+        <v>33.3</v>
       </c>
       <c r="G91" t="n">
-        <v>7.6</v>
+        <v>9.7</v>
       </c>
       <c r="H91" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="I91" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>24.8</v>
+        <v>22.9</v>
       </c>
       <c r="K91" t="n">
-        <v>14.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B92" t="s">
         <v>128</v>
       </c>
       <c r="C92" t="n">
-        <v>74.2</v>
+        <v>64.4</v>
       </c>
       <c r="D92" t="n">
-        <v>69.7</v>
+        <v>57.5</v>
       </c>
       <c r="E92" t="n">
-        <v>39.1</v>
+        <v>17.9</v>
       </c>
       <c r="F92" t="n">
-        <v>33.3</v>
+        <v>41.9</v>
       </c>
       <c r="G92" t="n">
-        <v>9.7</v>
+        <v>15.3</v>
       </c>
       <c r="H92" t="n">
-        <v>52.2</v>
+        <v>40.5</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J92" t="n">
-        <v>22.9</v>
+        <v>27.2</v>
       </c>
       <c r="K92" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B93" t="s">
         <v>128</v>
       </c>
       <c r="C93" t="n">
-        <v>64.4</v>
+        <v>57.5</v>
       </c>
       <c r="D93" t="n">
-        <v>57.5</v>
+        <v>63.9</v>
       </c>
       <c r="E93" t="n">
-        <v>17.9</v>
+        <v>26.6</v>
       </c>
       <c r="F93" t="n">
-        <v>41.9</v>
+        <v>36.8</v>
       </c>
       <c r="G93" t="n">
-        <v>15.3</v>
+        <v>7.4</v>
       </c>
       <c r="H93" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="I93" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="J93" t="n">
-        <v>27.2</v>
+        <v>22.5</v>
       </c>
       <c r="K93" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B94" t="s">
         <v>128</v>
       </c>
       <c r="C94" t="n">
-        <v>57.5</v>
+        <v>80</v>
       </c>
       <c r="D94" t="n">
-        <v>63.9</v>
+        <v>68.6</v>
       </c>
       <c r="E94" t="n">
-        <v>26.6</v>
+        <v>21.4</v>
       </c>
       <c r="F94" t="n">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="G94" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="I94" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>22.5</v>
+        <v>15</v>
       </c>
       <c r="K94" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B95" t="s">
         <v>128</v>
       </c>
       <c r="C95" t="n">
-        <v>80</v>
+        <v>62.1</v>
       </c>
       <c r="D95" t="n">
-        <v>68.6</v>
+        <v>64.9</v>
       </c>
       <c r="E95" t="n">
-        <v>21.4</v>
+        <v>29.3</v>
       </c>
       <c r="F95" t="n">
-        <v>25</v>
+        <v>52.2</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="H95" t="n">
-        <v>25</v>
+        <v>63.5</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
-        <v>15</v>
+        <v>33.1</v>
       </c>
       <c r="K95" t="n">
-        <v>11.1</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B96" t="s">
         <v>128</v>
       </c>
       <c r="C96" t="n">
-        <v>62.1</v>
+        <v>62.7</v>
       </c>
       <c r="D96" t="n">
-        <v>64.9</v>
+        <v>65.6</v>
       </c>
       <c r="E96" t="n">
-        <v>29.3</v>
+        <v>32.5</v>
       </c>
       <c r="F96" t="n">
-        <v>52.2</v>
+        <v>58.6</v>
       </c>
       <c r="G96" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="H96" t="n">
-        <v>63.5</v>
+        <v>55.6</v>
       </c>
       <c r="I96" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J96" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="K96" t="n">
-        <v>18.8</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B97" t="s">
         <v>128</v>
       </c>
       <c r="C97" t="n">
-        <v>62.7</v>
+        <v>74.3</v>
       </c>
       <c r="D97" t="n">
-        <v>65.6</v>
+        <v>71.8</v>
       </c>
       <c r="E97" t="n">
-        <v>32.5</v>
+        <v>28.1</v>
       </c>
       <c r="F97" t="n">
-        <v>58.6</v>
+        <v>42.9</v>
       </c>
       <c r="G97" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="H97" t="n">
-        <v>55.6</v>
+        <v>73.1</v>
       </c>
       <c r="I97" t="n">
-        <v>5.1</v>
+        <v>2.9</v>
       </c>
       <c r="J97" t="n">
-        <v>33</v>
+        <v>24.6</v>
       </c>
       <c r="K97" t="n">
-        <v>20.3</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B98" t="s">
         <v>128</v>
       </c>
       <c r="C98" t="n">
-        <v>74.3</v>
+        <v>60.6</v>
       </c>
       <c r="D98" t="n">
-        <v>71.8</v>
+        <v>64.6</v>
       </c>
       <c r="E98" t="n">
-        <v>28.1</v>
+        <v>21.7</v>
       </c>
       <c r="F98" t="n">
-        <v>42.9</v>
+        <v>26.5</v>
       </c>
       <c r="G98" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="H98" t="n">
-        <v>73.1</v>
+        <v>67.9</v>
       </c>
       <c r="I98" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J98" t="n">
-        <v>24.6</v>
+        <v>19.3</v>
       </c>
       <c r="K98" t="n">
-        <v>11.4</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B99" t="s">
         <v>128</v>
       </c>
       <c r="C99" t="n">
-        <v>60.6</v>
+        <v>66.7</v>
       </c>
       <c r="D99" t="n">
-        <v>64.6</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>21.7</v>
+        <v>31</v>
       </c>
       <c r="F99" t="n">
-        <v>26.5</v>
+        <v>54.5</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="H99" t="n">
-        <v>67.9</v>
+        <v>42.3</v>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="J99" t="n">
-        <v>19.3</v>
+        <v>37.3</v>
       </c>
       <c r="K99" t="n">
-        <v>7.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B100" t="s">
         <v>128</v>
       </c>
       <c r="C100" t="n">
-        <v>66.7</v>
+        <v>65.8</v>
       </c>
       <c r="D100" t="n">
-        <v>67.5</v>
+        <v>65.6</v>
       </c>
       <c r="E100" t="n">
-        <v>31</v>
+        <v>23.1</v>
       </c>
       <c r="F100" t="n">
-        <v>54.5</v>
+        <v>37.2</v>
       </c>
       <c r="G100" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H100" t="n">
-        <v>42.3</v>
+        <v>41.3</v>
       </c>
       <c r="I100" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
-        <v>37.3</v>
+        <v>21.5</v>
       </c>
       <c r="K100" t="n">
-        <v>19.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B101" t="s">
         <v>128</v>
       </c>
       <c r="C101" t="n">
-        <v>65.8</v>
+        <v>66.2</v>
       </c>
       <c r="D101" t="n">
-        <v>65.6</v>
+        <v>68.8</v>
       </c>
       <c r="E101" t="n">
-        <v>23.1</v>
+        <v>19.7</v>
       </c>
       <c r="F101" t="n">
-        <v>37.2</v>
+        <v>46.5</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>1.9</v>
       </c>
       <c r="H101" t="n">
-        <v>41.3</v>
+        <v>42.3</v>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J101" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="K101" t="n">
-        <v>6.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
         <v>128</v>
       </c>
       <c r="C102" t="n">
-        <v>66.2</v>
+        <v>64.4</v>
       </c>
       <c r="D102" t="n">
-        <v>68.8</v>
+        <v>61.4</v>
       </c>
       <c r="E102" t="n">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="F102" t="n">
-        <v>46.5</v>
+        <v>58</v>
       </c>
       <c r="G102" t="n">
-        <v>1.9</v>
+        <v>16.4</v>
       </c>
       <c r="H102" t="n">
-        <v>42.3</v>
+        <v>32.3</v>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J102" t="n">
-        <v>21.9</v>
+        <v>36.4</v>
       </c>
       <c r="K102" t="n">
-        <v>20.8</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C103" t="n">
-        <v>64.4</v>
+        <v>33.3</v>
       </c>
       <c r="D103" t="n">
-        <v>61.4</v>
+        <v>56.2</v>
       </c>
       <c r="E103" t="n">
-        <v>13.4</v>
+        <v>36.4</v>
       </c>
       <c r="F103" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>16.4</v>
+        <v>33.3</v>
       </c>
       <c r="H103" t="n">
-        <v>32.3</v>
+        <v>0</v>
       </c>
       <c r="I103" t="n">
-        <v>2.7</v>
+        <v>33.3</v>
       </c>
       <c r="J103" t="n">
-        <v>36.4</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>23.3</v>
+        <v>-33.3</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B104" t="s">
         <v>145</v>
       </c>
       <c r="C104" t="n">
-        <v>33.3</v>
+        <v>58.8</v>
       </c>
       <c r="D104" t="n">
-        <v>56.2</v>
+        <v>59.6</v>
       </c>
       <c r="E104" t="n">
-        <v>36.4</v>
+        <v>20</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="G104" t="n">
-        <v>33.3</v>
+        <v>13.7</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>44.7</v>
       </c>
       <c r="I104" t="n">
-        <v>33.3</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="K104" t="n">
-        <v>-33.3</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>275</v>
+        <v>144</v>
       </c>
       <c r="B105" t="s">
         <v>145</v>
       </c>
       <c r="C105" t="n">
-        <v>58.8</v>
+        <v>51.6</v>
       </c>
       <c r="D105" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="E105" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F105" t="n">
-        <v>14.3</v>
+        <v>40.9</v>
       </c>
       <c r="G105" t="n">
-        <v>13.7</v>
+        <v>12.9</v>
       </c>
       <c r="H105" t="n">
-        <v>44.7</v>
+        <v>44.4</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>8.1</v>
       </c>
       <c r="J105" t="n">
-        <v>14.5</v>
+        <v>24.4</v>
       </c>
       <c r="K105" t="n">
-        <v>-7.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>144</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
         <v>145</v>
       </c>
       <c r="C106" t="n">
-        <v>51.6</v>
+        <v>62</v>
       </c>
       <c r="D106" t="n">
-        <v>58.9</v>
+        <v>65.2</v>
       </c>
       <c r="E106" t="n">
-        <v>16</v>
+        <v>19.6</v>
       </c>
       <c r="F106" t="n">
-        <v>40.9</v>
+        <v>35.7</v>
       </c>
       <c r="G106" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="H106" t="n">
-        <v>44.4</v>
+        <v>37.7</v>
       </c>
       <c r="I106" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J106" t="n">
-        <v>24.4</v>
+        <v>18.1</v>
       </c>
       <c r="K106" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B107" t="s">
         <v>145</v>
       </c>
       <c r="C107" t="n">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D107" t="n">
-        <v>65.2</v>
+        <v>45.5</v>
       </c>
       <c r="E107" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="F107" t="n">
-        <v>35.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F107"/>
       <c r="G107" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="H107" t="n">
-        <v>37.7</v>
+        <v>0</v>
       </c>
       <c r="I107" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>18.1</v>
+        <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>5.6</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B108" t="s">
         <v>145</v>
       </c>
       <c r="C108" t="n">
-        <v>50</v>
+        <v>65.8</v>
       </c>
       <c r="D108" t="n">
-        <v>45.5</v>
+        <v>62.4</v>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108"/>
+        <v>23.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>30.5</v>
+      </c>
       <c r="G108" t="n">
-        <v>25</v>
+        <v>12.9</v>
       </c>
       <c r="H108" t="n">
-        <v>0</v>
+        <v>49.4</v>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="J108" t="n">
-        <v>0</v>
+        <v>25.9</v>
       </c>
       <c r="K108" t="n">
-        <v>-25</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B109" t="s">
         <v>145</v>
       </c>
       <c r="C109" t="n">
-        <v>65.8</v>
+        <v>51</v>
       </c>
       <c r="D109" t="n">
-        <v>62.4</v>
+        <v>58.9</v>
       </c>
       <c r="E109" t="n">
-        <v>23.5</v>
+        <v>13.2</v>
       </c>
       <c r="F109" t="n">
-        <v>30.5</v>
+        <v>25</v>
       </c>
       <c r="G109" t="n">
-        <v>12.9</v>
+        <v>6.4</v>
       </c>
       <c r="H109" t="n">
-        <v>49.4</v>
+        <v>41.7</v>
       </c>
       <c r="I109" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J109" t="n">
-        <v>25.9</v>
+        <v>19.2</v>
       </c>
       <c r="K109" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>279</v>
+        <v>155</v>
       </c>
       <c r="B110" t="s">
         <v>145</v>
       </c>
       <c r="C110" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="D110" t="n">
-        <v>58.9</v>
+        <v>59.9</v>
       </c>
       <c r="E110" t="n">
-        <v>13.2</v>
+        <v>30.4</v>
       </c>
       <c r="F110" t="n">
-        <v>25</v>
+        <v>42.9</v>
       </c>
       <c r="G110" t="n">
-        <v>6.4</v>
+        <v>13.4</v>
       </c>
       <c r="H110" t="n">
-        <v>41.7</v>
+        <v>47.2</v>
       </c>
       <c r="I110" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="J110" t="n">
-        <v>19.2</v>
+        <v>28</v>
       </c>
       <c r="K110" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>156</v>
+        <v>278</v>
       </c>
       <c r="B111" t="s">
         <v>145</v>
       </c>
       <c r="C111" t="n">
-        <v>51.5</v>
+        <v>63.3</v>
       </c>
       <c r="D111" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="E111" t="n">
-        <v>30.4</v>
+        <v>20.5</v>
       </c>
       <c r="F111" t="n">
-        <v>42.9</v>
+        <v>34.6</v>
       </c>
       <c r="G111" t="n">
-        <v>13.4</v>
+        <v>16.7</v>
       </c>
       <c r="H111" t="n">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="I111" t="n">
-        <v>7.5</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
-        <v>28</v>
+        <v>22.8</v>
       </c>
       <c r="K111" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B112" t="s">
         <v>145</v>
       </c>
       <c r="C112" t="n">
-        <v>63.3</v>
+        <v>52.6</v>
       </c>
       <c r="D112" t="n">
-        <v>60.1</v>
+        <v>56.2</v>
       </c>
       <c r="E112" t="n">
-        <v>20.5</v>
+        <v>30</v>
       </c>
       <c r="F112" t="n">
-        <v>34.6</v>
+        <v>10</v>
       </c>
       <c r="G112" t="n">
         <v>16.7</v>
       </c>
       <c r="H112" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="I112" t="n">
-        <v>2.1</v>
+        <v>5.6</v>
       </c>
       <c r="J112" t="n">
-        <v>22.8</v>
+        <v>15.2</v>
       </c>
       <c r="K112" t="n">
-        <v>2.1</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B113" t="s">
         <v>145</v>
       </c>
       <c r="C113" t="n">
-        <v>52.6</v>
+        <v>65.9</v>
       </c>
       <c r="D113" t="n">
-        <v>56.2</v>
+        <v>64.2</v>
       </c>
       <c r="E113" t="n">
-        <v>30</v>
+        <v>20.5</v>
       </c>
       <c r="F113" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="G113" t="n">
-        <v>16.7</v>
+        <v>10.3</v>
       </c>
       <c r="H113" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="I113" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
-        <v>15.2</v>
+        <v>28.1</v>
       </c>
       <c r="K113" t="n">
-        <v>-11.1</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B114" t="s">
         <v>145</v>
       </c>
       <c r="C114" t="n">
-        <v>65.9</v>
+        <v>60</v>
       </c>
       <c r="D114" t="n">
-        <v>64.2</v>
+        <v>61.5</v>
       </c>
       <c r="E114" t="n">
-        <v>20.5</v>
+        <v>18.9</v>
       </c>
       <c r="F114" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G114" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H114" t="n">
-        <v>41.4</v>
+        <v>42.6</v>
       </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>28.1</v>
+        <v>35.6</v>
       </c>
       <c r="K114" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B115" t="s">
         <v>145</v>
       </c>
       <c r="C115" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D115" t="n">
-        <v>61.5</v>
+        <v>56.3</v>
       </c>
       <c r="E115" t="n">
-        <v>18.9</v>
+        <v>23.1</v>
       </c>
       <c r="F115" t="n">
-        <v>51.1</v>
+        <v>38.5</v>
       </c>
       <c r="G115" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="H115" t="n">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J115" t="n">
-        <v>35.6</v>
+        <v>26.5</v>
       </c>
       <c r="K115" t="n">
-        <v>15.8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B116" t="s">
         <v>145</v>
       </c>
       <c r="C116" t="n">
-        <v>44</v>
+        <v>38.9</v>
       </c>
       <c r="D116" t="n">
-        <v>56.3</v>
+        <v>52</v>
       </c>
       <c r="E116" t="n">
-        <v>23.1</v>
+        <v>16.3</v>
       </c>
       <c r="F116" t="n">
-        <v>38.5</v>
+        <v>33.3</v>
       </c>
       <c r="G116" t="n">
-        <v>8</v>
+        <v>27.8</v>
       </c>
       <c r="H116" t="n">
-        <v>50</v>
+        <v>22.2</v>
       </c>
       <c r="I116" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="J116" t="n">
-        <v>26.5</v>
+        <v>31</v>
       </c>
       <c r="K116" t="n">
-        <v>12</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B117" t="s">
         <v>145</v>
       </c>
       <c r="C117" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="D117" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E117" t="n">
-        <v>16.3</v>
+        <v>13.6</v>
       </c>
       <c r="F117" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="G117" t="n">
-        <v>27.8</v>
+        <v>30</v>
       </c>
       <c r="H117" t="n">
-        <v>22.2</v>
+        <v>60</v>
       </c>
       <c r="I117" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>31</v>
+        <v>27.3</v>
       </c>
       <c r="K117" t="n">
-        <v>-11.1</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B118" t="s">
         <v>145</v>
       </c>
       <c r="C118" t="n">
-        <v>50</v>
+        <v>57.7</v>
       </c>
       <c r="D118" t="n">
-        <v>48.8</v>
+        <v>61.8</v>
       </c>
       <c r="E118" t="n">
-        <v>13.6</v>
+        <v>19.7</v>
       </c>
       <c r="F118" t="n">
-        <v>50</v>
+        <v>29.1</v>
       </c>
       <c r="G118" t="n">
-        <v>30</v>
+        <v>7.7</v>
       </c>
       <c r="H118" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
-        <v>27.3</v>
+        <v>21.6</v>
       </c>
       <c r="K118" t="n">
-        <v>-10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B119" t="s">
         <v>145</v>
       </c>
       <c r="C119" t="n">
-        <v>57.7</v>
+        <v>58</v>
       </c>
       <c r="D119" t="n">
-        <v>61.8</v>
+        <v>58.3</v>
       </c>
       <c r="E119" t="n">
-        <v>19.7</v>
+        <v>24.1</v>
       </c>
       <c r="F119" t="n">
-        <v>29.1</v>
+        <v>32.9</v>
       </c>
       <c r="G119" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I119" t="n">
         <v>7.7</v>
       </c>
-      <c r="H119" t="n">
-        <v>57</v>
-      </c>
-      <c r="I119" t="n">
-        <v>2.7</v>
-      </c>
       <c r="J119" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="K119" t="n">
-        <v>6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="C120" t="n">
-        <v>58</v>
+        <v>70.1</v>
       </c>
       <c r="D120" t="n">
-        <v>58.3</v>
+        <v>66.4</v>
       </c>
       <c r="E120" t="n">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="F120" t="n">
-        <v>32.9</v>
+        <v>42.9</v>
       </c>
       <c r="G120" t="n">
-        <v>8.7</v>
+        <v>5.4</v>
       </c>
       <c r="H120" t="n">
-        <v>43.1</v>
+        <v>52.7</v>
       </c>
       <c r="I120" t="n">
-        <v>7.7</v>
+        <v>2.7</v>
       </c>
       <c r="J120" t="n">
-        <v>18.6</v>
+        <v>22.3</v>
       </c>
       <c r="K120" t="n">
-        <v>3.9</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B121" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C121" t="n">
-        <v>70.1</v>
+        <v>61.6</v>
       </c>
       <c r="D121" t="n">
-        <v>66.4</v>
+        <v>65.8</v>
       </c>
       <c r="E121" t="n">
-        <v>22.2</v>
+        <v>20.2</v>
       </c>
       <c r="F121" t="n">
-        <v>42.9</v>
+        <v>41.8</v>
       </c>
       <c r="G121" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="H121" t="n">
-        <v>52.7</v>
+        <v>47.1</v>
       </c>
       <c r="I121" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
-        <v>22.3</v>
+        <v>20.1</v>
       </c>
       <c r="K121" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C122" t="n">
-        <v>61.6</v>
+        <v>60.7</v>
       </c>
       <c r="D122" t="n">
-        <v>65.8</v>
+        <v>64.8</v>
       </c>
       <c r="E122" t="n">
-        <v>20.2</v>
+        <v>11.2</v>
       </c>
       <c r="F122" t="n">
-        <v>41.8</v>
+        <v>32.4</v>
       </c>
       <c r="G122" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="H122" t="n">
-        <v>47.1</v>
+        <v>29.6</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
-        <v>20.1</v>
+        <v>19.6</v>
       </c>
       <c r="K122" t="n">
-        <v>13.2</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B123" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C123" t="n">
-        <v>60.7</v>
+        <v>58.2</v>
       </c>
       <c r="D123" t="n">
-        <v>64.8</v>
+        <v>62.1</v>
       </c>
       <c r="E123" t="n">
-        <v>11.2</v>
+        <v>27.7</v>
       </c>
       <c r="F123" t="n">
-        <v>32.4</v>
+        <v>65.9</v>
       </c>
       <c r="G123" t="n">
-        <v>6.8</v>
+        <v>11.1</v>
       </c>
       <c r="H123" t="n">
-        <v>29.6</v>
+        <v>42.3</v>
       </c>
       <c r="I123" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J123" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="K123" t="n">
-        <v>5.7</v>
+        <v>33.3</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>292</v>
+        <v>217</v>
       </c>
       <c r="B124" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C124" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="D124" t="n">
-        <v>62.1</v>
+        <v>58.7</v>
       </c>
       <c r="E124" t="n">
-        <v>27.7</v>
+        <v>12.8</v>
       </c>
       <c r="F124" t="n">
-        <v>65.9</v>
+        <v>34.1</v>
       </c>
       <c r="G124" t="n">
         <v>11.1</v>
       </c>
       <c r="H124" t="n">
-        <v>42.3</v>
+        <v>35.5</v>
       </c>
       <c r="I124" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J124" t="n">
-        <v>37</v>
+        <v>23.9</v>
       </c>
       <c r="K124" t="n">
-        <v>33.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="B125" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C125" t="n">
-        <v>59.3</v>
+        <v>73.6</v>
       </c>
       <c r="D125" t="n">
-        <v>58.7</v>
+        <v>64.6</v>
       </c>
       <c r="E125" t="n">
-        <v>12.8</v>
+        <v>31</v>
       </c>
       <c r="F125" t="n">
-        <v>34.1</v>
+        <v>56.9</v>
       </c>
       <c r="G125" t="n">
-        <v>11.1</v>
+        <v>7.1</v>
       </c>
       <c r="H125" t="n">
-        <v>35.5</v>
+        <v>44.1</v>
       </c>
       <c r="I125" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J125" t="n">
-        <v>23.9</v>
+        <v>49.6</v>
       </c>
       <c r="K125" t="n">
-        <v>5.6</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B126" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C126" t="n">
-        <v>73.6</v>
+        <v>78.6</v>
       </c>
       <c r="D126" t="n">
-        <v>64.6</v>
-      </c>
-      <c r="E126" t="n">
-        <v>31</v>
-      </c>
+        <v>72.9</v>
+      </c>
+      <c r="E126"/>
       <c r="F126" t="n">
-        <v>56.9</v>
+        <v>45.5</v>
       </c>
       <c r="G126" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>44.1</v>
+        <v>46.5</v>
       </c>
       <c r="I126" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
-        <v>49.6</v>
+        <v>26.7</v>
       </c>
       <c r="K126" t="n">
-        <v>34.3</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B127" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C127" t="n">
-        <v>78.6</v>
+        <v>50</v>
       </c>
       <c r="D127" t="n">
-        <v>72.9</v>
-      </c>
-      <c r="E127"/>
+        <v>45.1</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
       <c r="F127" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>30.8</v>
       </c>
       <c r="H127" t="n">
-        <v>46.5</v>
+        <v>37.5</v>
       </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>7.7</v>
       </c>
       <c r="J127" t="n">
-        <v>26.7</v>
+        <v>31.2</v>
       </c>
       <c r="K127" t="n">
-        <v>18.5</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C128" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="D128" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="E128" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F128" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G128" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H128" t="n">
         <v>50</v>
       </c>
-      <c r="D128" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>25</v>
-      </c>
-      <c r="G128" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="H128" t="n">
-        <v>37.5</v>
-      </c>
       <c r="I128" t="n">
-        <v>7.7</v>
+        <v>3.2</v>
       </c>
       <c r="J128" t="n">
-        <v>31.2</v>
+        <v>29.4</v>
       </c>
       <c r="K128" t="n">
-        <v>-23.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B129" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C129" t="n">
-        <v>61.3</v>
+        <v>65.8</v>
       </c>
       <c r="D129" t="n">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="E129" t="n">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="F129" t="n">
-        <v>31.8</v>
+        <v>38.1</v>
       </c>
       <c r="G129" t="n">
-        <v>16.1</v>
+        <v>7.9</v>
       </c>
       <c r="H129" t="n">
-        <v>50</v>
+        <v>53.8</v>
       </c>
       <c r="I129" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J129" t="n">
-        <v>29.4</v>
+        <v>26.8</v>
       </c>
       <c r="K129" t="n">
-        <v>6.5</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B130" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C130" t="n">
-        <v>65.8</v>
+        <v>50.9</v>
       </c>
       <c r="D130" t="n">
-        <v>67.5</v>
+        <v>60.7</v>
       </c>
       <c r="E130" t="n">
-        <v>36.4</v>
+        <v>24.6</v>
       </c>
       <c r="F130" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G130" t="n">
-        <v>7.9</v>
+        <v>9.7</v>
       </c>
       <c r="H130" t="n">
-        <v>53.8</v>
+        <v>54.4</v>
       </c>
       <c r="I130" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J130" t="n">
-        <v>26.8</v>
+        <v>21.7</v>
       </c>
       <c r="K130" t="n">
-        <v>13.2</v>
+        <v>9.8</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B131" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C131" t="n">
-        <v>50.9</v>
+        <v>66.7</v>
       </c>
       <c r="D131" t="n">
-        <v>60.7</v>
+        <v>56.7</v>
       </c>
       <c r="E131" t="n">
-        <v>24.6</v>
+        <v>14.3</v>
       </c>
       <c r="F131" t="n">
-        <v>38.6</v>
+        <v>50</v>
       </c>
       <c r="G131" t="n">
-        <v>9.7</v>
+        <v>22.2</v>
       </c>
       <c r="H131" t="n">
-        <v>54.4</v>
+        <v>20</v>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="K131" t="n">
-        <v>9.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B132" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C132" t="n">
-        <v>66.7</v>
+        <v>69.5</v>
       </c>
       <c r="D132" t="n">
-        <v>56.7</v>
+        <v>70.3</v>
       </c>
       <c r="E132" t="n">
-        <v>14.3</v>
+        <v>25</v>
       </c>
       <c r="F132" t="n">
         <v>50</v>
       </c>
       <c r="G132" t="n">
-        <v>22.2</v>
+        <v>4.1</v>
       </c>
       <c r="H132" t="n">
-        <v>20</v>
+        <v>41.9</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J132" t="n">
-        <v>25</v>
+        <v>26.3</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C133" t="n">
-        <v>69.5</v>
+        <v>59</v>
       </c>
       <c r="D133" t="n">
-        <v>70.3</v>
+        <v>63</v>
       </c>
       <c r="E133" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F133" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G133" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H133" t="n">
         <v>50</v>
       </c>
-      <c r="G133" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H133" t="n">
-        <v>41.9</v>
-      </c>
       <c r="I133" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J133" t="n">
-        <v>26.3</v>
+        <v>21</v>
       </c>
       <c r="K133" t="n">
-        <v>18.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="s">
-        <v>301</v>
-      </c>
+      <c r="A134"/>
       <c r="B134" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="C134" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="D134" t="n">
-        <v>63</v>
+        <v>61.4</v>
       </c>
       <c r="E134" t="n">
-        <v>27</v>
+        <v>20.8</v>
       </c>
       <c r="F134" t="n">
-        <v>42.2</v>
+        <v>37.3</v>
       </c>
       <c r="G134" t="n">
-        <v>6.9</v>
+        <v>11.2</v>
       </c>
       <c r="H134" t="n">
-        <v>50</v>
+        <v>46.1</v>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="J134" t="n">
-        <v>21</v>
+        <v>24.9</v>
       </c>
       <c r="K134" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135"/>
-      <c r="B135" t="s">
-        <v>180</v>
-      </c>
-      <c r="C135" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="D135" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="E135" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F135" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="G135" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H135" t="n">
-        <v>46</v>
-      </c>
-      <c r="I135" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J135" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="K135" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
